--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -11,57 +11,58 @@
     <sheet name="contentAttributes" sheetId="7" r:id="rId7"/>
     <sheet name="contentArchetypes" sheetId="8" r:id="rId8"/>
     <sheet name="contentBooks" sheetId="9" r:id="rId9"/>
-    <sheet name="eras" sheetId="10" r:id="rId10"/>
-    <sheet name="eraSmallTalk" sheetId="11" r:id="rId11"/>
-    <sheet name="countries" sheetId="12" r:id="rId12"/>
-    <sheet name="countryBaselines" sheetId="13" r:id="rId13"/>
-    <sheet name="countryHair" sheetId="14" r:id="rId14"/>
-    <sheet name="countryFonts" sheetId="15" r:id="rId15"/>
-    <sheet name="countrySeeds" sheetId="16" r:id="rId16"/>
-    <sheet name="countryOverrides" sheetId="17" r:id="rId17"/>
-    <sheet name="countryArt" sheetId="18" r:id="rId18"/>
-    <sheet name="places" sheetId="19" r:id="rId19"/>
-    <sheet name="placeFacts" sheetId="20" r:id="rId20"/>
-    <sheet name="placeSmallTalk" sheetId="21" r:id="rId21"/>
-    <sheet name="wardrobeSets" sheetId="22" r:id="rId22"/>
-    <sheet name="wardrobe" sheetId="23" r:id="rId23"/>
-    <sheet name="placeHair" sheetId="24" r:id="rId24"/>
-    <sheet name="rules" sheetId="25" r:id="rId25"/>
-    <sheet name="days" sheetId="26" r:id="rId26"/>
-    <sheet name="dayEras" sheetId="27" r:id="rId27"/>
-    <sheet name="dayForced" sheetId="28" r:id="rId28"/>
-    <sheet name="interview" sheetId="29" r:id="rId29"/>
-    <sheet name="interviewRequests" sheetId="30" r:id="rId30"/>
-    <sheet name="questions" sheetId="31" r:id="rId31"/>
-    <sheet name="questionConditions" sheetId="32" r:id="rId32"/>
-    <sheet name="questionOverrides" sheetId="33" r:id="rId33"/>
-    <sheet name="dialogs" sheetId="34" r:id="rId34"/>
-    <sheet name="dialogConditions" sheetId="35" r:id="rId35"/>
-    <sheet name="dialogNodes" sheetId="36" r:id="rId36"/>
-    <sheet name="dialogLines" sheetId="37" r:id="rId37"/>
-    <sheet name="dialogChoices" sheetId="38" r:id="rId38"/>
-    <sheet name="choiceLines" sheetId="39" r:id="rId39"/>
-    <sheet name="premades" sheetId="40" r:id="rId40"/>
-    <sheet name="premadeImpacts" sheetId="41" r:id="rId41"/>
-    <sheet name="history" sheetId="42" r:id="rId42"/>
-    <sheet name="historyRules" sheetId="43" r:id="rId43"/>
-    <sheet name="historyConditions" sheetId="44" r:id="rId44"/>
-    <sheet name="historyEdits" sheetId="45" r:id="rId45"/>
-    <sheet name="ui" sheetId="46" r:id="rId46"/>
-    <sheet name="uiPalette" sheetId="47" r:id="rId47"/>
-    <sheet name="uiNeutral" sheetId="48" r:id="rId48"/>
-    <sheet name="neutralFonts" sheetId="49" r:id="rId49"/>
-    <sheet name="neutralSeeds" sheetId="50" r:id="rId50"/>
-    <sheet name="neutralOverrides" sheetId="51" r:id="rId51"/>
-    <sheet name="neutralArt" sheetId="52" r:id="rId52"/>
-    <sheet name="uiStrings" sheetId="53" r:id="rId53"/>
-    <sheet name="uiLanguages" sheetId="54" r:id="rId54"/>
-    <sheet name="uiLanguageEntries" sheetId="55" r:id="rId55"/>
-    <sheet name="translation" sheetId="56" r:id="rId56"/>
-    <sheet name="scripts" sheetId="57" r:id="rId57"/>
-    <sheet name="scriptFonts" sheetId="58" r:id="rId58"/>
-    <sheet name="packs" sheetId="59" r:id="rId59"/>
-    <sheet name="tongues" sheetId="60" r:id="rId60"/>
+    <sheet name="agency" sheetId="10" r:id="rId10"/>
+    <sheet name="eras" sheetId="11" r:id="rId11"/>
+    <sheet name="eraSmallTalk" sheetId="12" r:id="rId12"/>
+    <sheet name="countries" sheetId="13" r:id="rId13"/>
+    <sheet name="countryBaselines" sheetId="14" r:id="rId14"/>
+    <sheet name="countryHair" sheetId="15" r:id="rId15"/>
+    <sheet name="countryFonts" sheetId="16" r:id="rId16"/>
+    <sheet name="countrySeeds" sheetId="17" r:id="rId17"/>
+    <sheet name="countryOverrides" sheetId="18" r:id="rId18"/>
+    <sheet name="countryArt" sheetId="19" r:id="rId19"/>
+    <sheet name="places" sheetId="20" r:id="rId20"/>
+    <sheet name="placeFacts" sheetId="21" r:id="rId21"/>
+    <sheet name="placeSmallTalk" sheetId="22" r:id="rId22"/>
+    <sheet name="wardrobeSets" sheetId="23" r:id="rId23"/>
+    <sheet name="wardrobe" sheetId="24" r:id="rId24"/>
+    <sheet name="placeHair" sheetId="25" r:id="rId25"/>
+    <sheet name="rules" sheetId="26" r:id="rId26"/>
+    <sheet name="days" sheetId="27" r:id="rId27"/>
+    <sheet name="dayEras" sheetId="28" r:id="rId28"/>
+    <sheet name="dayForced" sheetId="29" r:id="rId29"/>
+    <sheet name="interview" sheetId="30" r:id="rId30"/>
+    <sheet name="interviewRequests" sheetId="31" r:id="rId31"/>
+    <sheet name="questions" sheetId="32" r:id="rId32"/>
+    <sheet name="questionConditions" sheetId="33" r:id="rId33"/>
+    <sheet name="questionOverrides" sheetId="34" r:id="rId34"/>
+    <sheet name="dialogs" sheetId="35" r:id="rId35"/>
+    <sheet name="dialogConditions" sheetId="36" r:id="rId36"/>
+    <sheet name="dialogNodes" sheetId="37" r:id="rId37"/>
+    <sheet name="dialogLines" sheetId="38" r:id="rId38"/>
+    <sheet name="dialogChoices" sheetId="39" r:id="rId39"/>
+    <sheet name="choiceLines" sheetId="40" r:id="rId40"/>
+    <sheet name="premades" sheetId="41" r:id="rId41"/>
+    <sheet name="premadeImpacts" sheetId="42" r:id="rId42"/>
+    <sheet name="history" sheetId="43" r:id="rId43"/>
+    <sheet name="historyRules" sheetId="44" r:id="rId44"/>
+    <sheet name="historyConditions" sheetId="45" r:id="rId45"/>
+    <sheet name="historyEdits" sheetId="46" r:id="rId46"/>
+    <sheet name="ui" sheetId="47" r:id="rId47"/>
+    <sheet name="uiPalette" sheetId="48" r:id="rId48"/>
+    <sheet name="uiNeutral" sheetId="49" r:id="rId49"/>
+    <sheet name="neutralFonts" sheetId="50" r:id="rId50"/>
+    <sheet name="neutralSeeds" sheetId="51" r:id="rId51"/>
+    <sheet name="neutralOverrides" sheetId="52" r:id="rId52"/>
+    <sheet name="neutralArt" sheetId="53" r:id="rId53"/>
+    <sheet name="uiStrings" sheetId="54" r:id="rId54"/>
+    <sheet name="uiLanguages" sheetId="55" r:id="rId55"/>
+    <sheet name="uiLanguageEntries" sheetId="56" r:id="rId56"/>
+    <sheet name="translation" sheetId="57" r:id="rId57"/>
+    <sheet name="scripts" sheetId="58" r:id="rId58"/>
+    <sheet name="scriptFonts" sheetId="59" r:id="rId59"/>
+    <sheet name="packs" sheetId="60" r:id="rId60"/>
+    <sheet name="tongues" sheetId="61" r:id="rId61"/>
   </sheets>
 </workbook>
 </file>
@@ -777,29 +778,29 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">eras</t>
+          <t xml:space="preserve">agency</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">Single</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.eras, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">one row: the object $.agency</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">eras</t>
+          <t xml:space="preserve">agency</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -809,24 +810,24 @@
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the agency's printed name</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">eras</t>
+          <t xml:space="preserve">agency</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">programme</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -843,22 +844,27 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">eras</t>
+          <t xml:space="preserve">agency</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">order</t>
+          <t xml:space="preserve">firstDate</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the desk calendar's date on day 1</t>
         </is>
       </c>
     </row>
@@ -868,193 +874,183 @@
           <t xml:space="preserve">eras</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">future</t>
-        </is>
-      </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="F37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the office's own time (at most one era)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.eras, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">eraSmallTalk</t>
+          <t xml:space="preserve">eras</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Values</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.eras[].smallTalk, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">small talk any traveller of the era may say</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">eraSmallTalk</t>
+          <t xml:space="preserve">eras</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'eras' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">eraSmallTalk</t>
+          <t xml:space="preserve">eras</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">order</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countries</t>
+          <t xml:space="preserve">eras</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.countries, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the office's own time (at most one era)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countries</t>
-        </is>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">eraSmallTalk</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Values</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.eras[].smallTalk, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">small talk any traveller of the era may say</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countries</t>
+          <t xml:space="preserve">eraSmallTalk</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'eras' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countries</t>
+          <t xml:space="preserve">eraSmallTalk</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">looks.skin</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">skin tone weights 1..5</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -1064,19 +1060,14 @@
           <t xml:space="preserve">countries</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">culture.displayName</t>
-        </is>
-      </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.countries, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1079,7 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">culture.language</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -1098,7 +1089,12 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1106,17 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">culture.runtimeFont</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -1132,17 +1128,27 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">culture.headingAdd</t>
+          <t xml:space="preserve">looks.skin</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number list</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skin tone weights 1..5</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1160,7 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">culture.buttonAdd</t>
+          <t xml:space="preserve">culture.displayName</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1176,17 +1182,17 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">culture.stripItalic</t>
+          <t xml:space="preserve">culture.language</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -1198,117 +1204,112 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">culture.wallpaper</t>
+          <t xml:space="preserve">culture.runtimeFont</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryBaselines</t>
+          <t xml:space="preserve">countries</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">culture.headingAdd</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.countries[].baselines, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryBaselines</t>
+          <t xml:space="preserve">countries</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">country</t>
+          <t xml:space="preserve">culture.buttonAdd</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryBaselines</t>
+          <t xml:space="preserve">countries</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">culture.stripItalic</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryBaselines</t>
+          <t xml:space="preserve">countries</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">score</t>
+          <t xml:space="preserve">culture.wallpaper</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryHair</t>
+          <t xml:space="preserve">countryBaselines</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -1318,14 +1319,14 @@
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.countries[].looks.hair, in order; the first column names the parent row</t>
+          <t xml:space="preserve">one row per item of the list $.countries[].baselines, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryHair</t>
+          <t xml:space="preserve">countryBaselines</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
@@ -1352,12 +1353,12 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryHair</t>
+          <t xml:space="preserve">countryBaselines</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">colour</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -1368,23 +1369,28 @@
       <c r="D58" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryHair</t>
+          <t xml:space="preserve">countryBaselines</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight</t>
+          <t xml:space="preserve">score</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
@@ -1396,7 +1402,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryFonts</t>
+          <t xml:space="preserve">countryHair</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -1406,19 +1412,14 @@
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.countries[].culture.fonts, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">one row per item of the list $.countries[].looks.hair, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryFonts</t>
+          <t xml:space="preserve">countryHair</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
@@ -1445,12 +1446,12 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryFonts</t>
+          <t xml:space="preserve">countryHair</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">file</t>
+          <t xml:space="preserve">colour</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -1467,17 +1468,17 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryFonts</t>
+          <t xml:space="preserve">countryHair</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">face</t>
+          <t xml:space="preserve">weight</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
@@ -1492,19 +1493,19 @@
           <t xml:space="preserve">countryFonts</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">family</t>
-        </is>
-      </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.countries[].culture.fonts, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
         </is>
       </c>
     </row>
@@ -1516,73 +1517,78 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">style</t>
+          <t xml:space="preserve">country</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countrySeeds</t>
+          <t xml:space="preserve">countryFonts</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">file</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.countries[].culture.seeds, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countrySeeds</t>
+          <t xml:space="preserve">countryFonts</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">country</t>
+          <t xml:space="preserve">face</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countrySeeds</t>
+          <t xml:space="preserve">countryFonts</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -1599,12 +1605,12 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countrySeeds</t>
+          <t xml:space="preserve">countryFonts</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hex</t>
+          <t xml:space="preserve">style</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -1621,7 +1627,7 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryOverrides</t>
+          <t xml:space="preserve">countrySeeds</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -1631,14 +1637,14 @@
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.countries[].culture.overrides, in order; the first column names the parent row</t>
+          <t xml:space="preserve">one row per item of the list $.countries[].culture.seeds, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryOverrides</t>
+          <t xml:space="preserve">countrySeeds</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
@@ -1665,12 +1671,12 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryOverrides</t>
+          <t xml:space="preserve">countrySeeds</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">role</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -1687,12 +1693,12 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryOverrides</t>
+          <t xml:space="preserve">countrySeeds</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fill</t>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -1712,75 +1718,75 @@
           <t xml:space="preserve">countryOverrides</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ink</t>
-        </is>
-      </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.countries[].culture.overrides, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryArt</t>
+          <t xml:space="preserve">countryOverrides</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">country</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.countries[].culture.art, in order; the first column names the parent row</t>
+          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryArt</t>
+          <t xml:space="preserve">countryOverrides</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">country</t>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E76" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryArt</t>
+          <t xml:space="preserve">countryOverrides</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">fill</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -1797,12 +1803,12 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryArt</t>
+          <t xml:space="preserve">countryOverrides</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hex</t>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -1819,7 +1825,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">places</t>
+          <t xml:space="preserve">countryArt</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -1829,19 +1835,14 @@
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.places, in order; a row's name is {country}_{era}, unique</t>
-        </is>
-      </c>
-      <c r="F79" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a place is a country in an era; child sheets name it {country}_{era}</t>
+          <t xml:space="preserve">one row per item of the list $.countries[].culture.art, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">places</t>
+          <t xml:space="preserve">countryArt</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
@@ -1851,7 +1852,7 @@
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
@@ -1861,19 +1862,19 @@
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name; names a row of 'countries'</t>
+          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">places</t>
+          <t xml:space="preserve">countryArt</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
@@ -1883,24 +1884,19 @@
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name; names a row of 'eras'</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">places</t>
+          <t xml:space="preserve">countryArt</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -1920,24 +1916,19 @@
           <t xml:space="preserve">places</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">moment</t>
-        </is>
-      </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E83" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.places, in order; a row's name is {country}_{era}, unique</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">research context only (not generated)</t>
+          <t xml:space="preserve">a place is a country in an era; child sheets name it {country}_{era}</t>
         </is>
       </c>
     </row>
@@ -1949,17 +1940,22 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">year</t>
+          <t xml:space="preserve">country</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E84" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name; names a row of 'countries'</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1967,7 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongue</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -1981,12 +1977,12 @@
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'tongues'</t>
+          <t xml:space="preserve">part of the row's name; names a row of 'eras'</t>
         </is>
       </c>
     </row>
@@ -1998,22 +1994,17 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">maleNames</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E86" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -2025,22 +2016,22 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">femaleNames</t>
+          <t xml:space="preserve">moment</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E87" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">research context only (not generated)</t>
         </is>
       </c>
     </row>
@@ -2052,139 +2043,154 @@
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">looks.skin</t>
+          <t xml:space="preserve">year</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number list</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F88" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">overrides the country's skin weights</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeFacts</t>
+          <t xml:space="preserve">places</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongue</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.places[].facts, in order; the first column names the parent row</t>
+          <t xml:space="preserve">names a row of 'tongues'</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeFacts</t>
+          <t xml:space="preserve">places</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">maleNames</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">no items</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'places' this row belongs to</t>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeFacts</t>
+          <t xml:space="preserve">places</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">femaleNames</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E91" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeFacts</t>
+          <t xml:space="preserve">places</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">looks.skin</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number list</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E92" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F92" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">overrides the country's skin weights</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeSmallTalk</t>
+          <t xml:space="preserve">placeFacts</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Values</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.places[].smallTalk, in order; the first column names the parent row; left out of the JSON when it has no rows</t>
+          <t xml:space="preserve">one row per item of the list $.places[].facts, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeSmallTalk</t>
+          <t xml:space="preserve">placeFacts</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
@@ -2211,12 +2217,12 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeSmallTalk</t>
+          <t xml:space="preserve">placeFacts</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -2226,68 +2232,63 @@
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardrobeSets</t>
+          <t xml:space="preserve">placeFacts</t>
+        </is>
+      </c>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keyed</t>
-        </is>
-      </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per member of $.places[].wardrobe, named in 'gender'; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardrobeSets</t>
-        </is>
-      </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">placeSmallTalk</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D97" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Values</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'places' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.places[].smallTalk, in order; the first column names the parent row; left out of the JSON when it has no rows</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardrobeSets</t>
+          <t xml:space="preserve">placeSmallTalk</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gender</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
@@ -2297,19 +2298,19 @@
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the member's name, unique per parent row; one of: m, f</t>
+          <t xml:space="preserve">names the row of 'places' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardrobeSets</t>
+          <t xml:space="preserve">placeSmallTalk</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">signature</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
@@ -2319,19 +2320,14 @@
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the slot whose item is the dress signature</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardrobe</t>
+          <t xml:space="preserve">wardrobeSets</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -2341,19 +2337,14 @@
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per member of $.places[].wardrobe.&lt;gender&gt;, named in 'slot'; the first columns name the parent row</t>
-        </is>
-      </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one worn item per row</t>
+          <t xml:space="preserve">one row per member of $.places[].wardrobe, named in 'gender'; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardrobe</t>
+          <t xml:space="preserve">wardrobeSets</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
@@ -2380,7 +2371,7 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardrobe</t>
+          <t xml:space="preserve">wardrobeSets</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
@@ -2390,7 +2381,7 @@
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
@@ -2400,19 +2391,19 @@
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'wardrobeSets' this row belongs to</t>
+          <t xml:space="preserve">the member's name, unique per parent row; one of: m, f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardrobe</t>
+          <t xml:space="preserve">wardrobeSets</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">slot</t>
+          <t xml:space="preserve">signature</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
@@ -2422,12 +2413,12 @@
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the member's name, unique per parent row; one of: outfit, hair, facialHair, headwear, accessory</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F103" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the slot whose item is the dress signature</t>
         </is>
       </c>
     </row>
@@ -2437,19 +2428,19 @@
           <t xml:space="preserve">wardrobe</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">label</t>
-        </is>
-      </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Keyed</t>
+        </is>
+      </c>
+      <c r="E104" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per member of $.places[].wardrobe.&lt;gender&gt;, named in 'slot'; the first columns name the parent row</t>
+        </is>
+      </c>
+      <c r="F104" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one worn item per row</t>
         </is>
       </c>
     </row>
@@ -2461,17 +2452,22 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wig</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E105" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'places' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -2483,17 +2479,22 @@
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">back</t>
+          <t xml:space="preserve">gender</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E106" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'wardrobeSets' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -2505,17 +2506,22 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">leakable</t>
+          <t xml:space="preserve">slot</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E107" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the member's name, unique per parent row; one of: outfit, hair, facialHair, headwear, accessory</t>
         </is>
       </c>
     </row>
@@ -2527,27 +2533,17 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">covers</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">slots this item hides</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -2559,122 +2555,127 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">artNation</t>
+          <t xml:space="preserve">wig</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">files the art under another nation (blank: the place's own)</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeHair</t>
+          <t xml:space="preserve">wardrobe</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">back</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.places[].looks.hair, in order; the first column names the parent row; left out of the JSON when it has no rows</t>
-        </is>
-      </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">overrides the country's hair weights</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeHair</t>
+          <t xml:space="preserve">wardrobe</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">leakable</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'places' this row belongs to</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeHair</t>
+          <t xml:space="preserve">wardrobe</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">colour</t>
+          <t xml:space="preserve">covers</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E112" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F112" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slots this item hides</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeHair</t>
+          <t xml:space="preserve">wardrobe</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight</t>
+          <t xml:space="preserve">artNation</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="F113" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">files the art under another nation (blank: the place's own)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rules</t>
+          <t xml:space="preserve">placeHair</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -2684,29 +2685,29 @@
       </c>
       <c r="E114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.rules, in order; a row's name is asset, unique</t>
+          <t xml:space="preserve">one row per item of the list $.places[].looks.hair, in order; the first column names the parent row; left out of the JSON when it has no rows</t>
         </is>
       </c>
       <c r="F114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">travel rules a day can switch on</t>
+          <t xml:space="preserve">overrides the country's hair weights</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rules</t>
+          <t xml:space="preserve">placeHair</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">asset</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
@@ -2716,24 +2717,19 @@
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the rule asset's name</t>
+          <t xml:space="preserve">names the row of 'places' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rules</t>
+          <t xml:space="preserve">placeHair</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">colour</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -2750,27 +2746,22 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rules</t>
+          <t xml:space="preserve">placeHair</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">country</t>
+          <t xml:space="preserve">weight</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -2780,24 +2771,19 @@
           <t xml:space="preserve">rules</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">era</t>
-        </is>
-      </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'eras'</t>
+          <t xml:space="preserve">one row per item of the list $.rules, in order; a row's name is asset, unique</t>
+        </is>
+      </c>
+      <c r="F118" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">travel rules a day can switch on</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2795,7 @@
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">asset</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -2819,36 +2805,51 @@
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E119" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
+        </is>
+      </c>
+      <c r="F119" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the rule asset's name</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">days</t>
+          <t xml:space="preserve">rules</t>
+        </is>
+      </c>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.days, in order; a row's name is day, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">days</t>
+          <t xml:space="preserve">rules</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">asset</t>
+          <t xml:space="preserve">country</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
@@ -2858,56 +2859,61 @@
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E121" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">days</t>
+          <t xml:space="preserve">rules</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">day</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">names a row of 'eras'</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">days</t>
+          <t xml:space="preserve">rules</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">queue</t>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -2917,19 +2923,14 @@
           <t xml:space="preserve">days</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tells</t>
-        </is>
-      </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E124" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.days, in order; a row's name is day, unique</t>
         </is>
       </c>
     </row>
@@ -2941,22 +2942,17 @@
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">channels</t>
+          <t xml:space="preserve">asset</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -2968,22 +2964,22 @@
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countries</t>
+          <t xml:space="preserve">day</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">each item names a row of 'countries'; separate items with |</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -2995,22 +2991,17 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rules</t>
+          <t xml:space="preserve">queue</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E127" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">each item names a row of 'rules'; separate items with |</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -3022,27 +3013,17 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">tells</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">each item names a row of 'premades'; separate items with |</t>
-        </is>
-      </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">premades that may roll this day</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -3054,105 +3035,125 @@
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeChance</t>
+          <t xml:space="preserve">channels</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E129" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayEras</t>
+          <t xml:space="preserve">days</t>
+        </is>
+      </c>
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">countries</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text list</t>
+        </is>
+      </c>
+      <c r="D130" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no items</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.days[].eras, in order; the first column names the parent row</t>
+          <t xml:space="preserve">each item names a row of 'countries'; separate items with |</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayEras</t>
+          <t xml:space="preserve">days</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">day</t>
+          <t xml:space="preserve">rules</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">no items</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
+          <t xml:space="preserve">each item names a row of 'rules'; separate items with |</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayEras</t>
+          <t xml:space="preserve">days</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">no items</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'eras'</t>
+          <t xml:space="preserve">each item names a row of 'premades'; separate items with |</t>
+        </is>
+      </c>
+      <c r="F132" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">premades that may roll this day</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayEras</t>
+          <t xml:space="preserve">days</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight</t>
+          <t xml:space="preserve">premadeChance</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
@@ -3164,7 +3165,7 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayForced</t>
+          <t xml:space="preserve">dayEras</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
@@ -3174,14 +3175,14 @@
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.days[].forced, in order; the first column names the parent row</t>
+          <t xml:space="preserve">one row per item of the list $.days[].eras, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayForced</t>
+          <t xml:space="preserve">dayEras</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
@@ -3208,49 +3209,49 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayForced</t>
+          <t xml:space="preserve">dayEras</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">slot</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E136" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'eras'</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayForced</t>
+          <t xml:space="preserve">dayEras</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premade</t>
+          <t xml:space="preserve">weight</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E137" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'premades'</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -3260,75 +3261,75 @@
           <t xml:space="preserve">dayForced</t>
         </is>
       </c>
-      <c r="B138" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blueprint</t>
-        </is>
-      </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D138" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E138" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.days[].forced, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interview</t>
+          <t xml:space="preserve">dayForced</t>
+        </is>
+      </c>
+      <c r="B139" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">day</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D139" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row: the object $.interview</t>
-        </is>
-      </c>
-      <c r="F139" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the interview's wording</t>
+          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interview</t>
+          <t xml:space="preserve">dayForced</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">deskName</t>
+          <t xml:space="preserve">slot</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interview</t>
+          <t xml:space="preserve">dayForced</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">opener</t>
+          <t xml:space="preserve">premade</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
@@ -3339,18 +3340,23 @@
       <c r="D141" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E141" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'premades'</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interview</t>
+          <t xml:space="preserve">dayForced</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">openerLegendary</t>
+          <t xml:space="preserve">blueprint</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
@@ -3370,19 +3376,19 @@
           <t xml:space="preserve">interview</t>
         </is>
       </c>
-      <c r="B143" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">claim</t>
-        </is>
-      </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D143" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E143" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.interview</t>
+        </is>
+      </c>
+      <c r="F143" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the interview's wording</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3400,7 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificMale</t>
+          <t xml:space="preserve">deskName</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
@@ -3416,7 +3422,7 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificFemale</t>
+          <t xml:space="preserve">opener</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
@@ -3438,7 +3444,7 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificUnknown</t>
+          <t xml:space="preserve">openerLegendary</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
@@ -3460,7 +3466,7 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">requestLabel</t>
+          <t xml:space="preserve">claim</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
@@ -3482,7 +3488,7 @@
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">requestPrompt</t>
+          <t xml:space="preserve">honorificMale</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
@@ -3504,7 +3510,7 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">requestReply</t>
+          <t xml:space="preserve">honorificFemale</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
@@ -3526,7 +3532,7 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">askLabel</t>
+          <t xml:space="preserve">honorificUnknown</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
@@ -3548,7 +3554,7 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">backLabel</t>
+          <t xml:space="preserve">requestLabel</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
@@ -3570,7 +3576,7 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">smallTalkLabel</t>
+          <t xml:space="preserve">requestPrompt</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
@@ -3592,7 +3598,7 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">smallTalkPrompt</t>
+          <t xml:space="preserve">requestReply</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -3614,17 +3620,17 @@
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">menuCapacity</t>
+          <t xml:space="preserve">askLabel</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -3636,17 +3642,17 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">maxLineChars</t>
+          <t xml:space="preserve">backLabel</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3664,7 @@
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lookLabel</t>
+          <t xml:space="preserve">smallTalkLabel</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
@@ -3675,83 +3681,78 @@
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interviewRequests</t>
+          <t xml:space="preserve">interview</t>
+        </is>
+      </c>
+      <c r="B157" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smallTalkPrompt</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E157" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.interview.requests, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F157" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spoken requests: the wheel entry, the desk's prompt and the traveller's reply</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D157" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interviewRequests</t>
+          <t xml:space="preserve">interview</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">menuCapacity</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E158" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interviewRequests</t>
+          <t xml:space="preserve">interview</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">maxLineChars</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interviewRequests</t>
+          <t xml:space="preserve">interview</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">lookLabel</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
@@ -3771,48 +3772,58 @@
           <t xml:space="preserve">interviewRequests</t>
         </is>
       </c>
-      <c r="B161" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reply</t>
-        </is>
-      </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D161" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E161" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.interview.requests, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F161" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spoken requests: the wheel entry, the desk's prompt and the traveller's reply</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
+          <t xml:space="preserve">interviewRequests</t>
+        </is>
+      </c>
+      <c r="B162" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D162" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.questions, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
+          <t xml:space="preserve">interviewRequests</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -3822,24 +3833,19 @@
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E163" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
+          <t xml:space="preserve">interviewRequests</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -3856,12 +3862,12 @@
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
+          <t xml:space="preserve">interviewRequests</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">reply</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -3881,19 +3887,14 @@
           <t xml:space="preserve">questions</t>
         </is>
       </c>
-      <c r="B166" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prompt</t>
-        </is>
-      </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D166" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E166" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.questions, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3906,7 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -3915,7 +3916,12 @@
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E167" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -3927,17 +3933,17 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3955,7 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">announce</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -3966,83 +3972,78 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questions</t>
+        </is>
+      </c>
+      <c r="B170" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E170" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.questions[].conditions, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F170" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all must pass</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D170" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questions</t>
         </is>
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">question</t>
+          <t xml:space="preserve">answer</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D171" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E171" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questions</t>
         </is>
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D172" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questions</t>
         </is>
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">announce</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -4062,19 +4063,19 @@
           <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
-      <c r="B174" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">threshold</t>
-        </is>
-      </c>
       <c r="C174" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
-        </is>
-      </c>
-      <c r="D174" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E174" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.questions[].conditions, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F174" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all must pass</t>
         </is>
       </c>
     </row>
@@ -4086,22 +4087,22 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">question</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4114,7 @@
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -4123,12 +4124,7 @@
       </c>
       <c r="D176" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E176" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4136,7 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -4150,73 +4146,68 @@
       </c>
       <c r="D177" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E177" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
+          <t xml:space="preserve">questionConditions</t>
+        </is>
+      </c>
+      <c r="B178" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E178" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.questions[].overrides, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F178" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the wording in one era</t>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D178" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
+          <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">question</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
+          <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -4226,24 +4217,24 @@
       </c>
       <c r="D180" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E180" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'eras'</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
+          <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -4253,7 +4244,12 @@
       </c>
       <c r="D181" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E181" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
@@ -4263,53 +4259,58 @@
           <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
-      <c r="B182" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">answer</t>
-        </is>
-      </c>
       <c r="C182" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D182" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E182" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.questions[].overrides, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F182" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the wording in one era</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
+          <t xml:space="preserve">questionOverrides</t>
+        </is>
+      </c>
+      <c r="B183" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D183" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E183" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F183" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">narrative dialogs: nodes, their lines and the player's choices</t>
+          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
+          <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
@@ -4319,24 +4320,24 @@
       </c>
       <c r="D184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">names a row of 'eras'</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
+          <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -4347,40 +4348,35 @@
       <c r="D185" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F185" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the wheel entry</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
+          <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">repeatable</t>
+          <t xml:space="preserve">answer</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
+          <t xml:space="preserve">dialogs</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -4390,29 +4386,29 @@
       </c>
       <c r="E187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].conditions, in order; the first column names the parent row</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs, in order; a row's name is id, unique</t>
         </is>
       </c>
       <c r="F187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">all must pass</t>
+          <t xml:space="preserve">narrative dialogs: nodes, their lines and the player's choices</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
+          <t xml:space="preserve">dialogs</t>
         </is>
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D188" s="1" t="inlineStr">
@@ -4422,19 +4418,19 @@
       </c>
       <c r="E188" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
+          <t xml:space="preserve">dialogs</t>
         </is>
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -4444,29 +4440,34 @@
       </c>
       <c r="D189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F189" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the wheel entry</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
+          <t xml:space="preserve">dialogs</t>
         </is>
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">repeatable</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -4476,19 +4477,19 @@
           <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
-      <c r="B191" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">threshold</t>
-        </is>
-      </c>
       <c r="C191" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
-        </is>
-      </c>
-      <c r="D191" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E191" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].conditions, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F191" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all must pass</t>
         </is>
       </c>
     </row>
@@ -4500,22 +4501,22 @@
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D192" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E192" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4528,7 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
@@ -4537,12 +4538,7 @@
       </c>
       <c r="D193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E193" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4550,7 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -4564,68 +4560,68 @@
       </c>
       <c r="D194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E194" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogNodes</t>
+          <t xml:space="preserve">dialogConditions</t>
+        </is>
+      </c>
+      <c r="B195" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E195" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes, in order; a row's name is id, unique per parent row; the first column names the parent row</t>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D195" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogNodes</t>
+          <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogNodes</t>
+          <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
@@ -4635,68 +4631,68 @@
       </c>
       <c r="D197" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E197" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
+          <t xml:space="preserve">dialogConditions</t>
+        </is>
+      </c>
+      <c r="B198" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D198" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].lines, in order; the first columns name the parent row</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
-        </is>
-      </c>
-      <c r="B199" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D199" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes, in order; a row's name is id, unique per parent row; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
+          <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
@@ -4711,14 +4707,14 @@
       </c>
       <c r="E200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
+          <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
       <c r="B201" s="1" t="inlineStr">
@@ -4733,7 +4729,12 @@
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E201" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -4743,19 +4744,14 @@
           <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
-      <c r="B202" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">speaker</t>
-        </is>
-      </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D202" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E202" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].lines, in order; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -4767,17 +4763,22 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">expression</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E203" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -4789,100 +4790,100 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D204" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E204" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">dialogLines</t>
+        </is>
+      </c>
+      <c r="B205" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E205" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices, in order; a row's name is id, unique per parent row; the first columns name the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D205" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">speaker</t>
         </is>
       </c>
       <c r="C206" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D206" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E206" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">expression</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D207" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E207" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
@@ -4892,12 +4893,7 @@
       </c>
       <c r="D208" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E208" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -4907,19 +4903,14 @@
           <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
-      <c r="B209" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">label</t>
-        </is>
-      </c>
       <c r="C209" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D209" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E209" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices, in order; a row's name is id, unique per parent row; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -4931,22 +4922,22 @@
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">next</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D210" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F210" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the node it leads to (blank: the dialog ends)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E210" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -4958,115 +4949,120 @@
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">effect</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C211" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D211" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E211" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">dialogChoices</t>
+        </is>
+      </c>
+      <c r="B212" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D212" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices[].lines, in order; the first columns name the parent row</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D213" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E213" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">next</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D214" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E214" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F214" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the node it leads to (blank: the dialog ends)</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choice</t>
+          <t xml:space="preserve">effect</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D215" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E215" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogChoices' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5076,19 +5072,14 @@
           <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
-      <c r="B216" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D216" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E216" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices[].lines, in order; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -5100,17 +5091,22 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">speaker</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E217" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -5122,17 +5118,22 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">expression</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E218" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -5144,51 +5145,56 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">choice</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E219" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogChoices' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">choiceLines</t>
+        </is>
+      </c>
+      <c r="B220" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E220" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.premades, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F220" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">premade characters: real people and written stories</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D220" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">speaker</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr">
@@ -5198,24 +5204,19 @@
       </c>
       <c r="D221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E221" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">expression</t>
         </is>
       </c>
       <c r="C222" s="1" t="inlineStr">
@@ -5225,19 +5226,19 @@
       </c>
       <c r="D222" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gender</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C223" s="1" t="inlineStr">
@@ -5257,24 +5258,19 @@
           <t xml:space="preserve">premades</t>
         </is>
       </c>
-      <c r="B224" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">place</t>
-        </is>
-      </c>
       <c r="C224" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D224" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E224" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">one row per item of the list $.premades, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F224" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">premade characters: real people and written stories</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5282,7 @@
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">truePlace</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C225" s="1" t="inlineStr">
@@ -5296,17 +5292,12 @@
       </c>
       <c r="D225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
-        </is>
-      </c>
-      <c r="F225" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">where they really come from (blank: honest)</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5309,7 @@
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">birthDate</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C226" s="1" t="inlineStr">
@@ -5340,7 +5331,7 @@
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">archetype</t>
+          <t xml:space="preserve">gender</t>
         </is>
       </c>
       <c r="C227" s="1" t="inlineStr">
@@ -5362,7 +5353,7 @@
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">intro</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C228" s="1" t="inlineStr">
@@ -5373,6 +5364,11 @@
       <c r="D228" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E228" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5380,7 @@
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">recordNote</t>
+          <t xml:space="preserve">truePlace</t>
         </is>
       </c>
       <c r="C229" s="1" t="inlineStr">
@@ -5395,6 +5391,16 @@
       <c r="D229" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E229" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
+        </is>
+      </c>
+      <c r="F229" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">where they really come from (blank: honest)</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5412,7 @@
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">birthDate</t>
         </is>
       </c>
       <c r="C230" s="1" t="inlineStr">
@@ -5417,11 +5423,6 @@
       <c r="D230" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E230" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'dialogs'</t>
         </is>
       </c>
     </row>
@@ -5433,73 +5434,73 @@
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">repeatable</t>
+          <t xml:space="preserve">archetype</t>
         </is>
       </c>
       <c r="C231" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D231" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">premades</t>
+        </is>
+      </c>
+      <c r="B232" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">intro</t>
         </is>
       </c>
       <c r="C232" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E232" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.premades[].impacts, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D232" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premade</t>
+          <t xml:space="preserve">recordNote</t>
         </is>
       </c>
       <c r="C233" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D233" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E233" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'premades' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C234" s="1" t="inlineStr">
@@ -5514,29 +5515,29 @@
       </c>
       <c r="E234" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">names a row of 'dialogs'</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">onCorrect</t>
+          <t xml:space="preserve">repeatable</t>
         </is>
       </c>
       <c r="C235" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D235" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -5546,19 +5547,14 @@
           <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
-      <c r="B236" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">onWrong</t>
-        </is>
-      </c>
       <c r="C236" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
-        </is>
-      </c>
-      <c r="D236" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E236" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.premades[].impacts, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -5570,134 +5566,144 @@
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">skipNationScore</t>
+          <t xml:space="preserve">premade</t>
         </is>
       </c>
       <c r="C237" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D237" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E237" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'premades' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">premadeImpacts</t>
+        </is>
+      </c>
+      <c r="B238" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D238" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row: the object $.history</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.leaderGained</t>
+          <t xml:space="preserve">onCorrect</t>
         </is>
       </c>
       <c r="C239" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D239" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
       <c r="B240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.leaderLost</t>
+          <t xml:space="preserve">onWrong</t>
         </is>
       </c>
       <c r="C240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.carry</t>
+          <t xml:space="preserve">skipNationScore</t>
         </is>
       </c>
       <c r="C241" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D241" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyRules</t>
+          <t xml:space="preserve">history</t>
         </is>
       </c>
       <c r="C242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">Single</t>
         </is>
       </c>
       <c r="E242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F242" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">history rules: when their conditions pass at night they rewrite a place's fact</t>
+          <t xml:space="preserve">one row: the object $.history</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyRules</t>
+          <t xml:space="preserve">history</t>
         </is>
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">lines.leaderGained</t>
         </is>
       </c>
       <c r="C243" s="1" t="inlineStr">
@@ -5707,24 +5713,19 @@
       </c>
       <c r="D243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E243" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyRules</t>
+          <t xml:space="preserve">history</t>
         </is>
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">lines.leaderLost</t>
         </is>
       </c>
       <c r="C244" s="1" t="inlineStr">
@@ -5741,12 +5742,12 @@
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyRules</t>
+          <t xml:space="preserve">history</t>
         </is>
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">news</t>
+          <t xml:space="preserve">lines.carry</t>
         </is>
       </c>
       <c r="C245" s="1" t="inlineStr">
@@ -5763,7 +5764,7 @@
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
+          <t xml:space="preserve">historyRules</t>
         </is>
       </c>
       <c r="C246" s="1" t="inlineStr">
@@ -5773,24 +5774,29 @@
       </c>
       <c r="E246" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules[].conditions, in order; the first column names the parent row</t>
+          <t xml:space="preserve">one row per item of the list $.history.rules, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F246" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">history rules: when their conditions pass at night they rewrite a place's fact</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
+          <t xml:space="preserve">historyRules</t>
         </is>
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rule</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D247" s="1" t="inlineStr">
@@ -5800,19 +5806,19 @@
       </c>
       <c r="E247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
+          <t xml:space="preserve">historyRules</t>
         </is>
       </c>
       <c r="B248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C248" s="1" t="inlineStr">
@@ -5822,19 +5828,19 @@
       </c>
       <c r="D248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
+          <t xml:space="preserve">historyRules</t>
         </is>
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">news</t>
         </is>
       </c>
       <c r="C249" s="1" t="inlineStr">
@@ -5844,7 +5850,7 @@
       </c>
       <c r="D249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5854,24 +5860,14 @@
           <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
-      <c r="B250" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nation</t>
-        </is>
-      </c>
       <c r="C250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D250" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">one row per item of the list $.history.rules[].conditions, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -5883,22 +5879,22 @@
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">rule</t>
         </is>
       </c>
       <c r="C251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5906,7 @@
       </c>
       <c r="B252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C252" s="1" t="inlineStr">
@@ -5920,12 +5916,7 @@
       </c>
       <c r="D252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E252" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -5937,73 +5928,83 @@
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (left out of the JSON)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
+          <t xml:space="preserve">historyConditions</t>
+        </is>
+      </c>
+      <c r="B254" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C254" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D254" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E254" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules[].edits, in order; the first column names the parent row</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
+          <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rule</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
+          <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C256" s="1" t="inlineStr">
@@ -6013,34 +6014,34 @@
       </c>
       <c r="D256" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E256" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
+          <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
       <c r="B257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0 (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -6050,48 +6051,53 @@
           <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
-      <c r="B258" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">value</t>
-        </is>
-      </c>
       <c r="C258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D258" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E258" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.history.rules[].edits, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">historyEdits</t>
+        </is>
+      </c>
+      <c r="B259" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rule</t>
         </is>
       </c>
       <c r="C259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D259" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row: the object $.ui</t>
+          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">readingLanguage</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C260" s="1" t="inlineStr">
@@ -6102,50 +6108,55 @@
       <c r="D260" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E260" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
       <c r="B261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">glossPercent</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">labelMinScale</t>
+          <t xml:space="preserve">value</t>
         </is>
       </c>
       <c r="C262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6155,19 +6166,14 @@
           <t xml:space="preserve">ui</t>
         </is>
       </c>
-      <c r="B263" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">contrast.text</t>
-        </is>
-      </c>
       <c r="C263" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
-        </is>
-      </c>
-      <c r="D263" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E263" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.ui</t>
         </is>
       </c>
     </row>
@@ -6179,17 +6185,17 @@
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.largeText</t>
+          <t xml:space="preserve">readingLanguage</t>
         </is>
       </c>
       <c r="C264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6207,12 @@
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.glyph</t>
+          <t xml:space="preserve">glossPercent</t>
         </is>
       </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D265" s="1" t="inlineStr">
@@ -6223,7 +6229,7 @@
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.hint</t>
+          <t xml:space="preserve">labelMinScale</t>
         </is>
       </c>
       <c r="C266" s="1" t="inlineStr">
@@ -6245,7 +6251,7 @@
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.outline</t>
+          <t xml:space="preserve">contrast.text</t>
         </is>
       </c>
       <c r="C267" s="1" t="inlineStr">
@@ -6267,7 +6273,7 @@
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.minTextFillAlpha</t>
+          <t xml:space="preserve">contrast.largeText</t>
         </is>
       </c>
       <c r="C268" s="1" t="inlineStr">
@@ -6289,100 +6295,105 @@
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">latinFallbackFont</t>
+          <t xml:space="preserve">contrast.glyph</t>
         </is>
       </c>
       <c r="C269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="B270" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">contrast.hint</t>
         </is>
       </c>
       <c r="C270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E270" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.paletteMap, in order</t>
+          <t xml:space="preserve">decimal</t>
+        </is>
+      </c>
+      <c r="D270" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">role</t>
+          <t xml:space="preserve">contrast.outline</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D271" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fill</t>
+          <t xml:space="preserve">contrast.minTextFillAlpha</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">alpha</t>
+          <t xml:space="preserve">latinFallbackFont</t>
         </is>
       </c>
       <c r="C273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6392,19 +6403,14 @@
           <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
-      <c r="B274" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ink</t>
-        </is>
-      </c>
       <c r="C274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D274" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E274" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.paletteMap, in order</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6422,7 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">textClass</t>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr">
@@ -6433,51 +6439,56 @@
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">uiPalette</t>
+        </is>
+      </c>
+      <c r="B276" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fill</t>
         </is>
       </c>
       <c r="C276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E276" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.ui.neutral</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D276" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">alpha</t>
         </is>
       </c>
       <c r="C277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C278" s="1" t="inlineStr">
@@ -6494,12 +6505,12 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">textClass</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
@@ -6519,19 +6530,14 @@
           <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
-      <c r="B280" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">runtimeFont</t>
-        </is>
-      </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
-        </is>
-      </c>
-      <c r="D280" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E280" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.ui.neutral</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6549,7 @@
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">headingAdd</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C281" s="1" t="inlineStr">
@@ -6565,7 +6571,7 @@
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">buttonAdd</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
@@ -6587,17 +6593,17 @@
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">stripItalic</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6609,51 +6615,51 @@
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wallpaper</t>
+          <t xml:space="preserve">runtimeFont</t>
         </is>
       </c>
       <c r="C284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiNeutral</t>
+        </is>
+      </c>
+      <c r="B285" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">headingAdd</t>
         </is>
       </c>
       <c r="C285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E285" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.fonts, in order</t>
-        </is>
-      </c>
-      <c r="F285" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D285" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">file</t>
+          <t xml:space="preserve">buttonAdd</t>
         </is>
       </c>
       <c r="C286" s="1" t="inlineStr">
@@ -6670,34 +6676,34 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">face</t>
+          <t xml:space="preserve">stripItalic</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">family</t>
+          <t xml:space="preserve">wallpaper</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr">
@@ -6717,70 +6723,75 @@
           <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
-      <c r="B289" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">style</t>
-        </is>
-      </c>
       <c r="C289" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D289" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E289" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.fonts, in order</t>
+        </is>
+      </c>
+      <c r="F289" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
+          <t xml:space="preserve">neutralFonts</t>
+        </is>
+      </c>
+      <c r="B290" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">file</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E290" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.seeds, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D290" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
+          <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">face</t>
         </is>
       </c>
       <c r="C291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
+          <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hex</t>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
@@ -6797,51 +6808,51 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">neutralFonts</t>
+        </is>
+      </c>
+      <c r="B293" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">style</t>
         </is>
       </c>
       <c r="C293" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E293" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.overrides, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D293" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
-        </is>
-      </c>
-      <c r="B294" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">role</t>
+          <t xml:space="preserve">neutralSeeds</t>
         </is>
       </c>
       <c r="C294" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D294" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E294" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.seeds, in order</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">neutralSeeds</t>
         </is>
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fill</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
@@ -6858,12 +6869,12 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">neutralSeeds</t>
         </is>
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ink</t>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C296" s="1" t="inlineStr">
@@ -6880,7 +6891,7 @@
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
+          <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
       <c r="C297" s="1" t="inlineStr">
@@ -6890,19 +6901,19 @@
       </c>
       <c r="E297" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.art, in order</t>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.overrides, in order</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
+          <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C298" s="1" t="inlineStr">
@@ -6919,12 +6930,12 @@
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
+          <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hex</t>
+          <t xml:space="preserve">fill</t>
         </is>
       </c>
       <c r="C299" s="1" t="inlineStr">
@@ -6941,56 +6952,51 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">neutralOverrides</t>
+        </is>
+      </c>
+      <c r="B300" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C300" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E300" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.strings, in order; a row's name is key, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D300" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
-        </is>
-      </c>
-      <c r="B301" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
       <c r="C301" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D301" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E301" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.art, in order</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
       <c r="B302" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C302" s="1" t="inlineStr">
@@ -7007,12 +7013,12 @@
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gloss</t>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C303" s="1" t="inlineStr">
@@ -7032,48 +7038,53 @@
           <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
-      <c r="B304" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tier</t>
-        </is>
-      </c>
       <c r="C304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D304" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E304" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.strings, in order; a row's name is key, unique</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
+          <t xml:space="preserve">uiStrings</t>
+        </is>
+      </c>
+      <c r="B305" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C305" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D305" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E305" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.ui.languages, in order; a row's name is language, unique</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
+          <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C306" s="1" t="inlineStr">
@@ -7083,90 +7094,80 @@
       </c>
       <c r="D306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E306" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
+          <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rtl</t>
+          <t xml:space="preserve">gloss</t>
         </is>
       </c>
       <c r="C307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
+          <t xml:space="preserve">uiStrings</t>
+        </is>
+      </c>
+      <c r="B308" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tier</t>
         </is>
       </c>
       <c r="C308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E308" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.languages[].entries, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D308" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
-        </is>
-      </c>
-      <c r="B309" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">uiLanguages</t>
         </is>
       </c>
       <c r="C309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D309" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'uiLanguages' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.ui.languages, in order; a row's name is language, unique</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
+          <t xml:space="preserve">uiLanguages</t>
         </is>
       </c>
       <c r="B310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C310" s="1" t="inlineStr">
@@ -7176,85 +7177,90 @@
       </c>
       <c r="D310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'uiStrings'</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
+          <t xml:space="preserve">uiLanguages</t>
         </is>
       </c>
       <c r="B311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">rtl</t>
         </is>
       </c>
       <c r="C311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
       <c r="C312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row: the object $.translation</t>
+          <t xml:space="preserve">one row per item of the list $.ui.languages[].entries, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E313" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'uiLanguages' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
       <c r="B314" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">announce</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C314" s="1" t="inlineStr">
@@ -7265,28 +7271,33 @@
       <c r="D314" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E314" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'uiStrings'</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.startDelay</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7296,19 +7307,14 @@
           <t xml:space="preserve">translation</t>
         </is>
       </c>
-      <c r="B316" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">flip.letterInterval</t>
-        </is>
-      </c>
       <c r="C316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
-        </is>
-      </c>
-      <c r="D316" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E316" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.translation</t>
         </is>
       </c>
     </row>
@@ -7320,12 +7326,12 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.letterSeconds</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D317" s="1" t="inlineStr">
@@ -7342,17 +7348,17 @@
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.scrambleSteps</t>
+          <t xml:space="preserve">announce</t>
         </is>
       </c>
       <c r="C318" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D318" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7370,7 @@
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.rowStagger</t>
+          <t xml:space="preserve">flip.startDelay</t>
         </is>
       </c>
       <c r="C319" s="1" t="inlineStr">
@@ -7386,144 +7392,159 @@
       </c>
       <c r="B320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fallbackGlyphs</t>
+          <t xml:space="preserve">flip.letterInterval</t>
         </is>
       </c>
       <c r="C320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
+          <t xml:space="preserve">translation</t>
+        </is>
+      </c>
+      <c r="B321" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flip.letterSeconds</t>
         </is>
       </c>
       <c r="C321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E321" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.scripts, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">decimal</t>
+        </is>
+      </c>
+      <c r="D321" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">flip.scrambleSteps</t>
         </is>
       </c>
       <c r="C322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E322" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rightToLeft</t>
+          <t xml:space="preserve">keyWords.slots</t>
         </is>
       </c>
       <c r="C323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E323" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F323" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slots whose value stays English in untranslated speech</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">translation</t>
+        </is>
+      </c>
+      <c r="B324" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">keyWords.words</t>
         </is>
       </c>
       <c r="C324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text list</t>
+        </is>
+      </c>
+      <c r="D324" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no items</t>
         </is>
       </c>
       <c r="E324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.translation.scripts[].fonts, in order; the first column names the parent row</t>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
       <c r="F324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">words that stay English in untranslated speech</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">script</t>
+          <t xml:space="preserve">keyWords.digits</t>
         </is>
       </c>
       <c r="C325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E325" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'scripts' this row belongs to</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B326" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">file</t>
+          <t xml:space="preserve">fallbackGlyphs</t>
         </is>
       </c>
       <c r="C326" s="1" t="inlineStr">
@@ -7540,34 +7561,29 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
-        </is>
-      </c>
-      <c r="B327" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">face</t>
+          <t xml:space="preserve">scripts</t>
         </is>
       </c>
       <c r="C327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D327" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E327" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.translation.scripts, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">scripts</t>
         </is>
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">family</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C328" s="1" t="inlineStr">
@@ -7577,36 +7593,41 @@
       </c>
       <c r="D328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E328" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">scripts</t>
         </is>
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">style</t>
+          <t xml:space="preserve">rightToLeft</t>
         </is>
       </c>
       <c r="C329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
       <c r="C330" s="1" t="inlineStr">
@@ -7616,24 +7637,29 @@
       </c>
       <c r="E330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.translation.packs, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">one row per item of the list $.translation.scripts[].fonts, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F330" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
       <c r="B331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">script</t>
         </is>
       </c>
       <c r="C331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D331" s="1" t="inlineStr">
@@ -7643,19 +7669,19 @@
       </c>
       <c r="E331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">names the row of 'scripts' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
       <c r="B332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">file</t>
         </is>
       </c>
       <c r="C332" s="1" t="inlineStr">
@@ -7672,12 +7698,12 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
       <c r="B333" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">writtenCost</t>
+          <t xml:space="preserve">face</t>
         </is>
       </c>
       <c r="C333" s="1" t="inlineStr">
@@ -7694,78 +7720,73 @@
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">spokenCost</t>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">scriptFonts</t>
+        </is>
+      </c>
+      <c r="B335" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">style</t>
         </is>
       </c>
       <c r="C335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E335" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D335" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
-        </is>
-      </c>
-      <c r="B336" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">packs</t>
         </is>
       </c>
       <c r="C336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D336" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.translation.packs, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">packs</t>
         </is>
       </c>
       <c r="B337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C337" s="1" t="inlineStr">
@@ -7775,19 +7796,24 @@
       </c>
       <c r="D337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E337" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">packs</t>
         </is>
       </c>
       <c r="B338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">script</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C338" s="1" t="inlineStr">
@@ -7798,38 +7824,28 @@
       <c r="D338" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E338" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'scripts'</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">packs</t>
         </is>
       </c>
       <c r="B339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pack</t>
+          <t xml:space="preserve">spokenCost</t>
         </is>
       </c>
       <c r="C339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E339" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'packs'</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -7839,17 +7855,137 @@
           <t xml:space="preserve">tongues</t>
         </is>
       </c>
-      <c r="B340" s="1" t="inlineStr">
+      <c r="C340" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E340" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B341" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C341" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D341" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E341" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B342" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">displayName</t>
+        </is>
+      </c>
+      <c r="C342" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D342" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B343" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">script</t>
+        </is>
+      </c>
+      <c r="C343" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D343" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E343" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'scripts'</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B344" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pack</t>
+        </is>
+      </c>
+      <c r="C344" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D344" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E344" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'packs'</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B345" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">glyphs</t>
         </is>
       </c>
-      <c r="C340" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D340" s="1" t="inlineStr">
+      <c r="C345" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D345" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
         </is>
@@ -7860,6 +7996,53 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">programme</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firstDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TEMPORAL CUSTOMS</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debt Relief Departures</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14 Mar 2150</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7925,7 +8108,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7997,7 +8180,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8145,7 +8328,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8265,7 +8448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8355,7 +8538,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8577,7 +8760,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9355,7 +9538,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9391,7 +9574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9421,7 +9604,39 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">travellerAgeMin</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">travellerAgeMax</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>18</v>
+      </c>
+      <c r="B2">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9567,39 +9782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">travellerAgeMin</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">travellerAgeMax</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>18</v>
-      </c>
-      <c r="B2">
-        <v>70</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9799,7 +9982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9835,7 +10018,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9933,7 +10116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -10382,7 +10565,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -10412,7 +10595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -10508,7 +10691,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -10642,7 +10825,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -10717,7 +10900,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -10783,7 +10966,41 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="18" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greyFromAge</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wholeFigureLabel</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>60</v>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Period dress</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -10980,41 +11197,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="18" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">greyFromAge</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wholeFigureLabel</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>60</v>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Period dress</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11094,7 +11277,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11208,7 +11391,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11262,7 +11445,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11320,7 +11503,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11374,7 +11557,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11463,7 +11646,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11523,7 +11706,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11652,7 +11835,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11798,7 +11981,51 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="8" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">minAge</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">faces</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>18</v>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a|b</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">c</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11852,51 +12079,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="8" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">minAge</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">faces</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>18</v>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a|b</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>35</v>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">c</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12069,7 +12252,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12111,7 +12294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12158,7 +12341,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12222,7 +12405,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12310,7 +12493,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12390,7 +12573,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12498,7 +12681,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12585,7 +12768,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12666,42 +12849,6 @@
       <c r="H2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Assets/Art/Generated/xp_bliss.png</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="8" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="8" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">file</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">face</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">family</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">style</t>
         </is>
       </c>
     </row>
@@ -12809,6 +12956,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="8" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="8" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">file</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">face</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">family</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">style</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
     <col min="1" max="1" width="11" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" customWidth="1"/>
   </cols>
@@ -12853,7 +13036,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12912,7 +13095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12960,7 +13143,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13040,7 +13223,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13084,7 +13267,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14270,7 +14453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14280,8 +14463,10 @@
     <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="28" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21" style="1" customWidth="1"/>
+    <col min="8" max="8" width="44" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="28" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14317,10 +14502,20 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.rowStagger</t>
+          <t xml:space="preserve">keyWords.slots</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">keyWords.words</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">keyWords.digits</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">fallbackGlyphs</t>
         </is>
@@ -14332,7 +14527,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Budget cuts close the interpreter pool. From today, foreign papers and speech reach the desk untranslated; translators are sold at Home. The scanner still compares untranslated text with the books.</t>
+          <t xml:space="preserve">Budget cuts close the interpreter pool. From today, foreign speech reaches the desk untranslated but for its key words; translators are sold at Home. Papers are still filled in English.</t>
         </is>
       </c>
       <c r="C2">
@@ -14347,10 +14542,20 @@
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="G2">
-        <v>0.15</v>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">place|name|document</t>
+        </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">home|please|papers|yes|no|Temporal Customs</t>
+        </is>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">olmnupqrystvwxazbcdfeghjik</t>
         </is>
@@ -14360,7 +14565,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14404,7 +14609,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14440,78 +14645,6 @@
         <is>
           <t xml:space="preserve">style</t>
         </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="15" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">displayName</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">writtenCost</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spokenCost</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">near_east</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Near East</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>100</v>
-      </c>
-      <c r="D2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mediterranean</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mediterranean</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>100</v>
-      </c>
-      <c r="D3">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -14569,6 +14702,66 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="15" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">displayName</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spokenCost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">near_east</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Near East</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mediterranean</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mediterranean</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="1" customWidth="1"/>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -32,37 +32,38 @@
     <sheet name="dayEras" sheetId="28" r:id="rId28"/>
     <sheet name="dayForced" sheetId="29" r:id="rId29"/>
     <sheet name="interview" sheetId="30" r:id="rId30"/>
-    <sheet name="interviewRequests" sheetId="31" r:id="rId31"/>
-    <sheet name="questions" sheetId="32" r:id="rId32"/>
-    <sheet name="questionConditions" sheetId="33" r:id="rId33"/>
-    <sheet name="questionOverrides" sheetId="34" r:id="rId34"/>
-    <sheet name="dialogs" sheetId="35" r:id="rId35"/>
-    <sheet name="dialogConditions" sheetId="36" r:id="rId36"/>
-    <sheet name="dialogNodes" sheetId="37" r:id="rId37"/>
-    <sheet name="dialogLines" sheetId="38" r:id="rId38"/>
-    <sheet name="dialogChoices" sheetId="39" r:id="rId39"/>
-    <sheet name="choiceLines" sheetId="40" r:id="rId40"/>
-    <sheet name="premades" sheetId="41" r:id="rId41"/>
-    <sheet name="premadeImpacts" sheetId="42" r:id="rId42"/>
-    <sheet name="history" sheetId="43" r:id="rId43"/>
-    <sheet name="historyRules" sheetId="44" r:id="rId44"/>
-    <sheet name="historyConditions" sheetId="45" r:id="rId45"/>
-    <sheet name="historyEdits" sheetId="46" r:id="rId46"/>
-    <sheet name="ui" sheetId="47" r:id="rId47"/>
-    <sheet name="uiPalette" sheetId="48" r:id="rId48"/>
-    <sheet name="uiNeutral" sheetId="49" r:id="rId49"/>
-    <sheet name="neutralFonts" sheetId="50" r:id="rId50"/>
-    <sheet name="neutralSeeds" sheetId="51" r:id="rId51"/>
-    <sheet name="neutralOverrides" sheetId="52" r:id="rId52"/>
-    <sheet name="neutralArt" sheetId="53" r:id="rId53"/>
-    <sheet name="uiStrings" sheetId="54" r:id="rId54"/>
-    <sheet name="uiLanguages" sheetId="55" r:id="rId55"/>
-    <sheet name="uiLanguageEntries" sheetId="56" r:id="rId56"/>
-    <sheet name="translation" sheetId="57" r:id="rId57"/>
-    <sheet name="scripts" sheetId="58" r:id="rId58"/>
-    <sheet name="scriptFonts" sheetId="59" r:id="rId59"/>
-    <sheet name="packs" sheetId="60" r:id="rId60"/>
-    <sheet name="tongues" sheetId="61" r:id="rId61"/>
+    <sheet name="claims" sheetId="31" r:id="rId31"/>
+    <sheet name="interviewRequests" sheetId="32" r:id="rId32"/>
+    <sheet name="questions" sheetId="33" r:id="rId33"/>
+    <sheet name="questionConditions" sheetId="34" r:id="rId34"/>
+    <sheet name="questionOverrides" sheetId="35" r:id="rId35"/>
+    <sheet name="dialogs" sheetId="36" r:id="rId36"/>
+    <sheet name="dialogConditions" sheetId="37" r:id="rId37"/>
+    <sheet name="dialogNodes" sheetId="38" r:id="rId38"/>
+    <sheet name="dialogLines" sheetId="39" r:id="rId39"/>
+    <sheet name="dialogChoices" sheetId="40" r:id="rId40"/>
+    <sheet name="choiceLines" sheetId="41" r:id="rId41"/>
+    <sheet name="premades" sheetId="42" r:id="rId42"/>
+    <sheet name="premadeImpacts" sheetId="43" r:id="rId43"/>
+    <sheet name="history" sheetId="44" r:id="rId44"/>
+    <sheet name="historyRules" sheetId="45" r:id="rId45"/>
+    <sheet name="historyConditions" sheetId="46" r:id="rId46"/>
+    <sheet name="historyEdits" sheetId="47" r:id="rId47"/>
+    <sheet name="ui" sheetId="48" r:id="rId48"/>
+    <sheet name="uiPalette" sheetId="49" r:id="rId49"/>
+    <sheet name="uiNeutral" sheetId="50" r:id="rId50"/>
+    <sheet name="neutralFonts" sheetId="51" r:id="rId51"/>
+    <sheet name="neutralSeeds" sheetId="52" r:id="rId52"/>
+    <sheet name="neutralOverrides" sheetId="53" r:id="rId53"/>
+    <sheet name="neutralArt" sheetId="54" r:id="rId54"/>
+    <sheet name="uiStrings" sheetId="55" r:id="rId55"/>
+    <sheet name="uiLanguages" sheetId="56" r:id="rId56"/>
+    <sheet name="uiLanguageEntries" sheetId="57" r:id="rId57"/>
+    <sheet name="translation" sheetId="58" r:id="rId58"/>
+    <sheet name="scripts" sheetId="59" r:id="rId59"/>
+    <sheet name="scriptFonts" sheetId="60" r:id="rId60"/>
+    <sheet name="packs" sheetId="61" r:id="rId61"/>
+    <sheet name="tongues" sheetId="62" r:id="rId62"/>
   </sheets>
 </workbook>
 </file>
@@ -871,66 +872,81 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">eras</t>
+          <t xml:space="preserve">agency</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">displaced.foundWithinDays</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.eras, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a displaced person was found 1 to this many days before today</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">eras</t>
+          <t xml:space="preserve">agency</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">displaced.validDaysMin</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the fewest days after today a Displacement Certificate is valid</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">eras</t>
+          <t xml:space="preserve">agency</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">displaced.validDaysMax</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the most days after today a Displacement Certificate is valid</t>
         </is>
       </c>
     </row>
@@ -940,19 +956,14 @@
           <t xml:space="preserve">eras</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">order</t>
-        </is>
-      </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.eras, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -964,127 +975,132 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the office's own time (at most one era)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">eraSmallTalk</t>
+          <t xml:space="preserve">eras</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Values</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.eras[].smallTalk, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">small talk any traveller of the era may say</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">eraSmallTalk</t>
+          <t xml:space="preserve">eras</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">order</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'eras' this row belongs to</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">eraSmallTalk</t>
+          <t xml:space="preserve">eras</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">future</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the office's own time (at most one era)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countries</t>
+          <t xml:space="preserve">eraSmallTalk</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">Values</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.countries, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">one row per item of the list $.eras[].smallTalk, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">small talk any traveller of the era may say</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countries</t>
+          <t xml:space="preserve">eraSmallTalk</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
@@ -1094,19 +1110,19 @@
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">names the row of 'eras' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countries</t>
+          <t xml:space="preserve">eraSmallTalk</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1116,7 +1132,7 @@
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -1126,29 +1142,14 @@
           <t xml:space="preserve">countries</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">looks.skin</t>
-        </is>
-      </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number list</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">no items</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">skin tone weights 1..5</t>
+          <t xml:space="preserve">one row per item of the list $.countries, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1161,7 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">culture.displayName</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1170,7 +1171,12 @@
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1188,7 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">culture.language</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -1204,17 +1210,27 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">culture.runtimeFont</t>
+          <t xml:space="preserve">looks.skin</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">number list</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skin tone weights 1..5</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1242,7 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">culture.headingAdd</t>
+          <t xml:space="preserve">culture.displayName</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -1248,7 +1264,7 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">culture.buttonAdd</t>
+          <t xml:space="preserve">culture.language</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -1270,7 +1286,7 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">culture.stripItalic</t>
+          <t xml:space="preserve">culture.runtimeFont</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -1292,7 +1308,7 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">culture.wallpaper</t>
+          <t xml:space="preserve">culture.headingAdd</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -1309,56 +1325,56 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryBaselines</t>
+          <t xml:space="preserve">countries</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">culture.buttonAdd</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.countries[].baselines, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryBaselines</t>
+          <t xml:space="preserve">countries</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">country</t>
+          <t xml:space="preserve">culture.stripItalic</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryBaselines</t>
+          <t xml:space="preserve">countries</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">culture.wallpaper</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -1369,11 +1385,6 @@
       <c r="D58" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
@@ -1383,85 +1394,90 @@
           <t xml:space="preserve">countryBaselines</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">score</t>
-        </is>
-      </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.countries[].baselines, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryHair</t>
+          <t xml:space="preserve">countryBaselines</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">country</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.countries[].looks.hair, in order; the first column names the parent row</t>
+          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryHair</t>
+          <t xml:space="preserve">countryBaselines</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">country</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryHair</t>
+          <t xml:space="preserve">countryBaselines</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">colour</t>
+          <t xml:space="preserve">score</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -1471,90 +1487,85 @@
           <t xml:space="preserve">countryHair</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">weight</t>
-        </is>
-      </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
-        </is>
-      </c>
-      <c r="D63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.countries[].looks.hair, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryFonts</t>
+          <t xml:space="preserve">countryHair</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">country</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.countries[].culture.fonts, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryFonts</t>
+          <t xml:space="preserve">countryHair</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">country</t>
+          <t xml:space="preserve">colour</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryFonts</t>
+          <t xml:space="preserve">countryHair</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">file</t>
+          <t xml:space="preserve">weight</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -1564,19 +1575,19 @@
           <t xml:space="preserve">countryFonts</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">face</t>
-        </is>
-      </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.countries[].culture.fonts, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1599,22 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">family</t>
+          <t xml:space="preserve">country</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1626,7 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">style</t>
+          <t xml:space="preserve">file</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -1627,56 +1643,56 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countrySeeds</t>
+          <t xml:space="preserve">countryFonts</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">face</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.countries[].culture.seeds, in order; the first column names the parent row</t>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countrySeeds</t>
+          <t xml:space="preserve">countryFonts</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">country</t>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countrySeeds</t>
+          <t xml:space="preserve">countryFonts</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">style</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -1696,75 +1712,75 @@
           <t xml:space="preserve">countrySeeds</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hex</t>
-        </is>
-      </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.countries[].culture.seeds, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryOverrides</t>
+          <t xml:space="preserve">countrySeeds</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">country</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.countries[].culture.overrides, in order; the first column names the parent row</t>
+          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryOverrides</t>
+          <t xml:space="preserve">countrySeeds</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">country</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryOverrides</t>
+          <t xml:space="preserve">countrySeeds</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">role</t>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -1784,19 +1800,14 @@
           <t xml:space="preserve">countryOverrides</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fill</t>
-        </is>
-      </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.countries[].culture.overrides, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -1808,73 +1819,78 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ink</t>
+          <t xml:space="preserve">country</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E78" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryArt</t>
+          <t xml:space="preserve">countryOverrides</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.countries[].culture.art, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryArt</t>
+          <t xml:space="preserve">countryOverrides</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">country</t>
+          <t xml:space="preserve">fill</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countryArt</t>
+          <t xml:space="preserve">countryOverrides</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
@@ -1894,53 +1910,53 @@
           <t xml:space="preserve">countryArt</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hex</t>
-        </is>
-      </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E82" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.countries[].culture.art, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">places</t>
+          <t xml:space="preserve">countryArt</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">country</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.places, in order; a row's name is {country}_{era}, unique</t>
-        </is>
-      </c>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a place is a country in an era; child sheets name it {country}_{era}</t>
+          <t xml:space="preserve">names the row of 'countries' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">places</t>
+          <t xml:space="preserve">countryArt</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">country</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -1950,24 +1966,19 @@
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name; names a row of 'countries'</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">places</t>
+          <t xml:space="preserve">countryArt</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -1977,12 +1988,7 @@
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name; names a row of 'eras'</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -1992,19 +1998,19 @@
           <t xml:space="preserve">places</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">displayName</t>
-        </is>
-      </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D86" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.places, in order; a row's name is {country}_{era}, unique</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a place is a country in an era; child sheets name it {country}_{era}</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2022,7 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">moment</t>
+          <t xml:space="preserve">country</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -2026,12 +2032,12 @@
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F87" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">research context only (not generated)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name; names a row of 'countries'</t>
         </is>
       </c>
     </row>
@@ -2043,17 +2049,22 @@
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">year</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name; names a row of 'eras'</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2076,7 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongue</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -2076,11 +2087,6 @@
       <c r="D89" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'tongues'</t>
         </is>
       </c>
     </row>
@@ -2092,22 +2098,22 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">maleNames</t>
+          <t xml:space="preserve">moment</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E90" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">research context only (not generated)</t>
         </is>
       </c>
     </row>
@@ -2119,22 +2125,17 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">femaleNames</t>
+          <t xml:space="preserve">year</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -2146,93 +2147,108 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">looks.skin</t>
+          <t xml:space="preserve">tongue</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">overrides the country's skin weights</t>
+          <t xml:space="preserve">names a row of 'tongues'</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeFacts</t>
+          <t xml:space="preserve">places</t>
+        </is>
+      </c>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maleNames</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text list</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no items</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.places[].facts, in order; the first column names the parent row</t>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeFacts</t>
+          <t xml:space="preserve">places</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">femaleNames</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">no items</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'places' this row belongs to</t>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeFacts</t>
+          <t xml:space="preserve">places</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">looks.skin</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number list</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E95" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F95" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">overrides the country's skin weights</t>
         </is>
       </c>
     </row>
@@ -2242,75 +2258,75 @@
           <t xml:space="preserve">placeFacts</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">value</t>
-        </is>
-      </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E96" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.places[].facts, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeSmallTalk</t>
+          <t xml:space="preserve">placeFacts</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Values</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.places[].smallTalk, in order; the first column names the parent row; left out of the JSON when it has no rows</t>
+          <t xml:space="preserve">names the row of 'places' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeSmallTalk</t>
+          <t xml:space="preserve">placeFacts</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E98" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'places' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeSmallTalk</t>
+          <t xml:space="preserve">placeFacts</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">value</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
@@ -2320,31 +2336,31 @@
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardrobeSets</t>
+          <t xml:space="preserve">placeSmallTalk</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keyed</t>
+          <t xml:space="preserve">Values</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per member of $.places[].wardrobe, named in 'gender'; the first column names the parent row</t>
+          <t xml:space="preserve">one row per item of the list $.places[].smallTalk, in order; the first column names the parent row; left out of the JSON when it has no rows</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardrobeSets</t>
+          <t xml:space="preserve">placeSmallTalk</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
@@ -2371,12 +2387,12 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardrobeSets</t>
+          <t xml:space="preserve">placeSmallTalk</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gender</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -2387,11 +2403,6 @@
       <c r="D102" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the member's name, unique per parent row; one of: m, f</t>
         </is>
       </c>
     </row>
@@ -2401,63 +2412,58 @@
           <t xml:space="preserve">wardrobeSets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">signature</t>
-        </is>
-      </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the slot whose item is the dress signature</t>
+          <t xml:space="preserve">Keyed</t>
+        </is>
+      </c>
+      <c r="E103" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per member of $.places[].wardrobe, named in 'gender'; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardrobe</t>
+          <t xml:space="preserve">wardrobeSets</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keyed</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per member of $.places[].wardrobe.&lt;gender&gt;, named in 'slot'; the first columns name the parent row</t>
-        </is>
-      </c>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one worn item per row</t>
+          <t xml:space="preserve">names the row of 'places' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardrobe</t>
+          <t xml:space="preserve">wardrobeSets</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">gender</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
@@ -2467,34 +2473,34 @@
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'places' this row belongs to</t>
+          <t xml:space="preserve">the member's name, unique per parent row; one of: m, f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wardrobe</t>
+          <t xml:space="preserve">wardrobeSets</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gender</t>
+          <t xml:space="preserve">signature</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'wardrobeSets' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F106" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the slot whose item is the dress signature</t>
         </is>
       </c>
     </row>
@@ -2504,24 +2510,19 @@
           <t xml:space="preserve">wardrobe</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">slot</t>
-        </is>
-      </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Keyed</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the member's name, unique per parent row; one of: outfit, hair, facialHair, headwear, accessory</t>
+          <t xml:space="preserve">one row per member of $.places[].wardrobe.&lt;gender&gt;, named in 'slot'; the first columns name the parent row</t>
+        </is>
+      </c>
+      <c r="F107" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one worn item per row</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2534,22 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E108" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'places' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -2555,17 +2561,22 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wig</t>
+          <t xml:space="preserve">gender</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E109" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'wardrobeSets' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -2577,17 +2588,22 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">back</t>
+          <t xml:space="preserve">slot</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E110" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the member's name, unique per parent row; one of: outfit, hair, facialHair, headwear, accessory</t>
         </is>
       </c>
     </row>
@@ -2599,17 +2615,17 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">leakable</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -2621,27 +2637,17 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">covers</t>
+          <t xml:space="preserve">wig</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">slots this item hides</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -2653,83 +2659,83 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">artNation</t>
+          <t xml:space="preserve">back</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">files the art under another nation (blank: the place's own)</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeHair</t>
+          <t xml:space="preserve">wardrobe</t>
+        </is>
+      </c>
+      <c r="B114" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leakable</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.places[].looks.hair, in order; the first column names the parent row; left out of the JSON when it has no rows</t>
-        </is>
-      </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">overrides the country's hair weights</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D114" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeHair</t>
+          <t xml:space="preserve">wardrobe</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">covers</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'places' this row belongs to</t>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F115" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slots this item hides</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">placeHair</t>
+          <t xml:space="preserve">wardrobe</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">colour</t>
+          <t xml:space="preserve">artNation</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -2739,7 +2745,12 @@
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="F116" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">files the art under another nation (blank: the place's own)</t>
         </is>
       </c>
     </row>
@@ -2749,53 +2760,58 @@
           <t xml:space="preserve">placeHair</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">weight</t>
-        </is>
-      </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E117" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.places[].looks.hair, in order; the first column names the parent row; left out of the JSON when it has no rows</t>
+        </is>
+      </c>
+      <c r="F117" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">overrides the country's hair weights</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rules</t>
+          <t xml:space="preserve">placeHair</t>
+        </is>
+      </c>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.rules, in order; a row's name is asset, unique</t>
-        </is>
-      </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">travel rules a day can switch on</t>
+          <t xml:space="preserve">names the row of 'places' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rules</t>
+          <t xml:space="preserve">placeHair</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">asset</t>
+          <t xml:space="preserve">colour</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -2805,39 +2821,29 @@
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E119" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
-        </is>
-      </c>
-      <c r="F119" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the rule asset's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rules</t>
+          <t xml:space="preserve">placeHair</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">weight</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -2847,24 +2853,19 @@
           <t xml:space="preserve">rules</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">country</t>
-        </is>
-      </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">one row per item of the list $.rules, in order; a row's name is asset, unique</t>
+        </is>
+      </c>
+      <c r="F121" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">travel rules a day can switch on</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2877,7 @@
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">asset</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
@@ -2886,12 +2887,17 @@
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'eras'</t>
+          <t xml:space="preserve">part of the row's name</t>
+        </is>
+      </c>
+      <c r="F122" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the rule asset's name</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2909,7 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">description</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -2920,29 +2926,39 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">days</t>
+          <t xml:space="preserve">rules</t>
+        </is>
+      </c>
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">country</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D124" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.days, in order; a row's name is day, unique</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">days</t>
+          <t xml:space="preserve">rules</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">asset</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
@@ -2952,34 +2968,34 @@
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E125" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'eras'</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">days</t>
+          <t xml:space="preserve">rules</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">day</t>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -2989,19 +3005,14 @@
           <t xml:space="preserve">days</t>
         </is>
       </c>
-      <c r="B127" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">queue</t>
-        </is>
-      </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D127" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E127" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.days, in order; a row's name is day, unique</t>
         </is>
       </c>
     </row>
@@ -3013,17 +3024,17 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tells</t>
+          <t xml:space="preserve">asset</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -3035,22 +3046,22 @@
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">channels</t>
+          <t xml:space="preserve">day</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">separate items with |</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -3062,22 +3073,17 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countries</t>
+          <t xml:space="preserve">queue</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">each item names a row of 'countries'; separate items with |</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -3089,22 +3095,17 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rules</t>
+          <t xml:space="preserve">tells</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">each item names a row of 'rules'; separate items with |</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3117,7 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">channels</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
@@ -3131,12 +3132,7 @@
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">each item names a row of 'premades'; separate items with |</t>
-        </is>
-      </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">premades that may roll this day</t>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
     </row>
@@ -3148,88 +3144,103 @@
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeChance</t>
+          <t xml:space="preserve">countries</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E133" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">each item names a row of 'countries'; separate items with |</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayEras</t>
+          <t xml:space="preserve">days</t>
+        </is>
+      </c>
+      <c r="B134" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rules</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text list</t>
+        </is>
+      </c>
+      <c r="D134" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no items</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.days[].eras, in order; the first column names the parent row</t>
+          <t xml:space="preserve">each item names a row of 'rules'; separate items with |</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayEras</t>
+          <t xml:space="preserve">days</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">day</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">no items</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
+          <t xml:space="preserve">each item names a row of 'premades'; separate items with |</t>
+        </is>
+      </c>
+      <c r="F135" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">premades that may roll this day</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayEras</t>
+          <t xml:space="preserve">days</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">premadeChance</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E136" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'eras'</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -3239,80 +3250,85 @@
           <t xml:space="preserve">dayEras</t>
         </is>
       </c>
-      <c r="B137" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">weight</t>
-        </is>
-      </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
-        </is>
-      </c>
-      <c r="D137" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E137" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.days[].eras, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayForced</t>
+          <t xml:space="preserve">dayEras</t>
+        </is>
+      </c>
+      <c r="B138" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">day</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D138" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.days[].forced, in order; the first column names the parent row</t>
+          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayForced</t>
+          <t xml:space="preserve">dayEras</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">day</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
+          <t xml:space="preserve">names a row of 'eras'</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayForced</t>
+          <t xml:space="preserve">dayEras</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">slot</t>
+          <t xml:space="preserve">weight</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
@@ -3327,24 +3343,14 @@
           <t xml:space="preserve">dayForced</t>
         </is>
       </c>
-      <c r="B141" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">premade</t>
-        </is>
-      </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D141" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'premades'</t>
+          <t xml:space="preserve">one row per item of the list $.days[].forced, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -3356,51 +3362,56 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">blueprint</t>
+          <t xml:space="preserve">day</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E142" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interview</t>
+          <t xml:space="preserve">dayForced</t>
+        </is>
+      </c>
+      <c r="B143" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slot</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E143" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.interview</t>
-        </is>
-      </c>
-      <c r="F143" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the interview's wording</t>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D143" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interview</t>
+          <t xml:space="preserve">dayForced</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">deskName</t>
+          <t xml:space="preserve">premade</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
@@ -3411,18 +3422,23 @@
       <c r="D144" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E144" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'premades'</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interview</t>
+          <t xml:space="preserve">dayForced</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">opener</t>
+          <t xml:space="preserve">blueprint</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
@@ -3442,19 +3458,19 @@
           <t xml:space="preserve">interview</t>
         </is>
       </c>
-      <c r="B146" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">openerLegendary</t>
-        </is>
-      </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D146" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E146" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.interview</t>
+        </is>
+      </c>
+      <c r="F146" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the interview's wording</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3482,7 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">claim</t>
+          <t xml:space="preserve">deskName</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
@@ -3488,7 +3504,7 @@
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificMale</t>
+          <t xml:space="preserve">opener</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
@@ -3510,7 +3526,7 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificFemale</t>
+          <t xml:space="preserve">openerLegendary</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
@@ -3532,7 +3548,7 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificUnknown</t>
+          <t xml:space="preserve">honorificMale</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
@@ -3554,7 +3570,7 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">requestLabel</t>
+          <t xml:space="preserve">honorificFemale</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
@@ -3576,7 +3592,7 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">requestPrompt</t>
+          <t xml:space="preserve">honorificUnknown</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
@@ -3598,7 +3614,7 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">requestReply</t>
+          <t xml:space="preserve">requestLabel</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -3620,7 +3636,7 @@
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">askLabel</t>
+          <t xml:space="preserve">papersLabel</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
@@ -3631,6 +3647,11 @@
       <c r="D154" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F154" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the hub entry that opens the papers menu</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3663,7 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">backLabel</t>
+          <t xml:space="preserve">requestPrompt</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
@@ -3664,7 +3685,7 @@
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">smallTalkLabel</t>
+          <t xml:space="preserve">requestReply</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
@@ -3686,7 +3707,7 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">smallTalkPrompt</t>
+          <t xml:space="preserve">askLabel</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
@@ -3708,17 +3729,17 @@
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">menuCapacity</t>
+          <t xml:space="preserve">backLabel</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -3730,17 +3751,17 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">maxLineChars</t>
+          <t xml:space="preserve">smallTalkLabel</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3773,7 @@
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lookLabel</t>
+          <t xml:space="preserve">smallTalkPrompt</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
@@ -3769,61 +3790,56 @@
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interviewRequests</t>
+          <t xml:space="preserve">interview</t>
+        </is>
+      </c>
+      <c r="B161" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">menuCapacity</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E161" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.interview.requests, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F161" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spoken requests: the wheel entry, the desk's prompt and the traveller's reply</t>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D161" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interviewRequests</t>
+          <t xml:space="preserve">interview</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">maxLineChars</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E162" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interviewRequests</t>
+          <t xml:space="preserve">interview</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">lookLabel</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -3840,34 +3856,34 @@
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interviewRequests</t>
-        </is>
-      </c>
-      <c r="B164" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">claims</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D164" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E164" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.interview.claims, in order</t>
+        </is>
+      </c>
+      <c r="F164" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the claim per traveller kind ({place}): one row per kind a blueprint makes</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interviewRequests</t>
+          <t xml:space="preserve">claims</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">reply</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -3877,63 +3893,68 @@
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E165" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
+          <t xml:space="preserve">claims</t>
+        </is>
+      </c>
+      <c r="B166" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E166" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.questions, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D166" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
-        </is>
-      </c>
-      <c r="B167" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">interviewRequests</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D167" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.interview.requests, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F167" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spoken requests: the wheel entry, the desk's prompt and the traveller's reply</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
+          <t xml:space="preserve">interviewRequests</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -3943,14 +3964,19 @@
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E168" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
+          <t xml:space="preserve">interviewRequests</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
@@ -3972,7 +3998,7 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
+          <t xml:space="preserve">interviewRequests</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
@@ -3994,12 +4020,12 @@
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
+          <t xml:space="preserve">interviewRequests</t>
         </is>
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">reply</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -4019,19 +4045,14 @@
           <t xml:space="preserve">questions</t>
         </is>
       </c>
-      <c r="B172" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fromDay</t>
-        </is>
-      </c>
       <c r="C172" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D172" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E172" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.questions, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4064,7 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">announce</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -4053,68 +4074,68 @@
       </c>
       <c r="D173" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E173" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questions</t>
+        </is>
+      </c>
+      <c r="B174" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E174" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.questions[].conditions, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F174" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all must pass</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D174" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questions</t>
         </is>
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">question</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E175" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questions</t>
         </is>
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -4124,19 +4145,19 @@
       </c>
       <c r="D176" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questions</t>
         </is>
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">answer</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -4153,17 +4174,17 @@
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questions</t>
         </is>
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D178" s="1" t="inlineStr">
@@ -4175,12 +4196,12 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questions</t>
         </is>
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">announce</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -4190,12 +4211,7 @@
       </c>
       <c r="D179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E179" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -4205,24 +4221,19 @@
           <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
-      <c r="B180" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attribute</t>
-        </is>
-      </c>
       <c r="C180" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D180" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E180" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">one row per item of the list $.questions[].conditions, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F180" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all must pass</t>
         </is>
       </c>
     </row>
@@ -4234,110 +4245,100 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">question</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D181" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E181" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
+          <t xml:space="preserve">questionConditions</t>
+        </is>
+      </c>
+      <c r="B182" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E182" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.questions[].overrides, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F182" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the wording in one era</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D182" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
+          <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">question</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D183" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E183" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
+          <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E184" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'eras'</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
+          <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -4347,19 +4348,24 @@
       </c>
       <c r="D185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E185" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
+          <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
@@ -4369,188 +4375,193 @@
       </c>
       <c r="D186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E186" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
+          <t xml:space="preserve">questionConditions</t>
+        </is>
+      </c>
+      <c r="B187" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D187" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F187" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">narrative dialogs: nodes, their lines and the player's choices</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
-        </is>
-      </c>
-      <c r="B188" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D188" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E188" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.questions[].overrides, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F188" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the wording in one era</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
+          <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">question</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F189" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the wheel entry</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E189" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
+          <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">repeatable</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E190" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'eras'</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
+          <t xml:space="preserve">questionOverrides</t>
+        </is>
+      </c>
+      <c r="B191" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E191" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].conditions, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F191" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all must pass</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D191" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
+          <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">answer</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D192" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E192" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
-        </is>
-      </c>
-      <c r="B193" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">dialogs</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D193" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E193" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F193" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrative dialogs: nodes, their lines and the player's choices</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
+          <t xml:space="preserve">dialogs</t>
         </is>
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -4560,56 +4571,61 @@
       </c>
       <c r="D194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E194" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
+          <t xml:space="preserve">dialogs</t>
         </is>
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F195" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the wheel entry</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
+          <t xml:space="preserve">dialogs</t>
         </is>
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">repeatable</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E196" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -4619,24 +4635,19 @@
           <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
-      <c r="B197" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attribute</t>
-        </is>
-      </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D197" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E197" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].conditions, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F197" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all must pass</t>
         </is>
       </c>
     </row>
@@ -4648,220 +4659,225 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogNodes</t>
+          <t xml:space="preserve">dialogConditions</t>
+        </is>
+      </c>
+      <c r="B199" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E199" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes, in order; a row's name is id, unique per parent row; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D199" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogNodes</t>
+          <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E200" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogNodes</t>
+          <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E201" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
+          <t xml:space="preserve">dialogConditions</t>
+        </is>
+      </c>
+      <c r="B202" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D202" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].lines, in order; the first columns name the parent row</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
+          <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
+          <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D204" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E204" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
-        </is>
-      </c>
-      <c r="B205" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D205" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E205" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes, in order; a row's name is id, unique per parent row; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
+          <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">speaker</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C206" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D206" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E206" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
+          <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">expression</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr">
@@ -4871,7 +4887,12 @@
       </c>
       <c r="D207" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E207" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -4881,48 +4902,53 @@
           <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
-      <c r="B208" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
       <c r="C208" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D208" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E208" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].lines, in order; the first columns name the parent row</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">dialogLines</t>
+        </is>
+      </c>
+      <c r="B209" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D209" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E209" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices, in order; a row's name is id, unique per parent row; the first columns name the parent row</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
@@ -4937,46 +4963,41 @@
       </c>
       <c r="E210" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C211" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D211" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E211" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">speaker</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
@@ -4986,24 +5007,19 @@
       </c>
       <c r="D212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E212" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">expression</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
@@ -5013,19 +5029,19 @@
       </c>
       <c r="D213" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">next</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
@@ -5036,11 +5052,6 @@
       <c r="D214" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F214" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the node it leads to (blank: the dialog ends)</t>
         </is>
       </c>
     </row>
@@ -5050,48 +5061,53 @@
           <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
-      <c r="B215" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">effect</t>
-        </is>
-      </c>
       <c r="C215" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D215" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E215" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices, in order; a row's name is id, unique per parent row; the first columns name the parent row</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">dialogChoices</t>
+        </is>
+      </c>
+      <c r="B216" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D216" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices[].lines, in order; the first columns name the parent row</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
@@ -5106,24 +5122,24 @@
       </c>
       <c r="E217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D218" s="1" t="inlineStr">
@@ -5133,46 +5149,41 @@
       </c>
       <c r="E218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choice</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E219" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogChoices' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">next</t>
         </is>
       </c>
       <c r="C220" s="1" t="inlineStr">
@@ -5183,18 +5194,23 @@
       <c r="D220" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F220" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the node it leads to (blank: the dialog ends)</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">speaker</t>
+          <t xml:space="preserve">effect</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr">
@@ -5214,19 +5230,14 @@
           <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
-      <c r="B222" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">expression</t>
-        </is>
-      </c>
       <c r="C222" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D222" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E222" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices[].lines, in order; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -5238,56 +5249,66 @@
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C223" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D223" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E223" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">choiceLines</t>
+        </is>
+      </c>
+      <c r="B224" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C224" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D224" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E224" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.premades, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F224" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">premade characters: real people and written stories</t>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">choice</t>
         </is>
       </c>
       <c r="C225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D225" s="1" t="inlineStr">
@@ -5297,19 +5318,19 @@
       </c>
       <c r="E225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">names the row of 'dialogChoices' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C226" s="1" t="inlineStr">
@@ -5326,12 +5347,12 @@
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gender</t>
+          <t xml:space="preserve">speaker</t>
         </is>
       </c>
       <c r="C227" s="1" t="inlineStr">
@@ -5348,12 +5369,12 @@
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">expression</t>
         </is>
       </c>
       <c r="C228" s="1" t="inlineStr">
@@ -5363,24 +5384,19 @@
       </c>
       <c r="D228" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E228" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">truePlace</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C229" s="1" t="inlineStr">
@@ -5391,16 +5407,6 @@
       <c r="D229" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E229" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
-        </is>
-      </c>
-      <c r="F229" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">where they really come from (blank: honest)</t>
         </is>
       </c>
     </row>
@@ -5410,19 +5416,19 @@
           <t xml:space="preserve">premades</t>
         </is>
       </c>
-      <c r="B230" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">birthDate</t>
-        </is>
-      </c>
       <c r="C230" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D230" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E230" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.premades, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F230" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">premade characters: real people and written stories</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5440,7 @@
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">archetype</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C231" s="1" t="inlineStr">
@@ -5444,7 +5450,12 @@
       </c>
       <c r="D231" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E231" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5467,7 @@
       </c>
       <c r="B232" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">intro</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C232" s="1" t="inlineStr">
@@ -5478,7 +5489,7 @@
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">recordNote</t>
+          <t xml:space="preserve">gender</t>
         </is>
       </c>
       <c r="C233" s="1" t="inlineStr">
@@ -5500,7 +5511,7 @@
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C234" s="1" t="inlineStr">
@@ -5515,7 +5526,7 @@
       </c>
       <c r="E234" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'dialogs'</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -5527,73 +5538,83 @@
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">repeatable</t>
+          <t xml:space="preserve">truePlace</t>
         </is>
       </c>
       <c r="C235" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D235" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E235" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
+        </is>
+      </c>
+      <c r="F235" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">where they really come from (blank: honest)</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">premades</t>
+        </is>
+      </c>
+      <c r="B236" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">birthDate</t>
         </is>
       </c>
       <c r="C236" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E236" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.premades[].impacts, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D236" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premade</t>
+          <t xml:space="preserve">archetype</t>
         </is>
       </c>
       <c r="C237" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D237" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E237" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'premades' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">intro</t>
         </is>
       </c>
       <c r="C238" s="1" t="inlineStr">
@@ -5604,67 +5625,67 @@
       <c r="D238" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E238" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">onCorrect</t>
+          <t xml:space="preserve">recordNote</t>
         </is>
       </c>
       <c r="C239" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D239" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="B240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">onWrong</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E240" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'dialogs'</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">skipNationScore</t>
+          <t xml:space="preserve">repeatable</t>
         </is>
       </c>
       <c r="C241" s="1" t="inlineStr">
@@ -5674,58 +5695,63 @@
       </c>
       <c r="D241" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
       <c r="C242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row: the object $.history</t>
+          <t xml:space="preserve">one row per item of the list $.premades[].impacts, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.leaderGained</t>
+          <t xml:space="preserve">premade</t>
         </is>
       </c>
       <c r="C243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E243" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'premades' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.leaderLost</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C244" s="1" t="inlineStr">
@@ -5736,111 +5762,106 @@
       <c r="D244" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E244" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.carry</t>
+          <t xml:space="preserve">onCorrect</t>
         </is>
       </c>
       <c r="C245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyRules</t>
+          <t xml:space="preserve">premadeImpacts</t>
+        </is>
+      </c>
+      <c r="B246" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">onWrong</t>
         </is>
       </c>
       <c r="C246" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E246" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F246" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">history rules: when their conditions pass at night they rewrite a place's fact</t>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D246" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyRules</t>
+          <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">skipNationScore</t>
         </is>
       </c>
       <c r="C247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E247" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyRules</t>
-        </is>
-      </c>
-      <c r="B248" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">history</t>
         </is>
       </c>
       <c r="C248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D248" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E248" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.history</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyRules</t>
+          <t xml:space="preserve">history</t>
         </is>
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">news</t>
+          <t xml:space="preserve">lines.leaderGained</t>
         </is>
       </c>
       <c r="C249" s="1" t="inlineStr">
@@ -5857,78 +5878,78 @@
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
+          <t xml:space="preserve">history</t>
+        </is>
+      </c>
+      <c r="B250" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lines.leaderLost</t>
         </is>
       </c>
       <c r="C250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E250" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules[].conditions, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D250" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
+          <t xml:space="preserve">history</t>
         </is>
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rule</t>
+          <t xml:space="preserve">lines.carry</t>
         </is>
       </c>
       <c r="C251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E251" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
-        </is>
-      </c>
-      <c r="B252" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">historyRules</t>
         </is>
       </c>
       <c r="C252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D252" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E252" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.history.rules, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F252" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">history rules: when their conditions pass at night they rewrite a place's fact</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
+          <t xml:space="preserve">historyRules</t>
         </is>
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C253" s="1" t="inlineStr">
@@ -5938,19 +5959,24 @@
       </c>
       <c r="D253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E253" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
+          <t xml:space="preserve">historyRules</t>
         </is>
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C254" s="1" t="inlineStr">
@@ -5960,24 +5986,19 @@
       </c>
       <c r="D254" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E254" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
+          <t xml:space="preserve">historyRules</t>
         </is>
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">news</t>
         </is>
       </c>
       <c r="C255" s="1" t="inlineStr">
@@ -5987,12 +6008,7 @@
       </c>
       <c r="D255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E255" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6002,24 +6018,14 @@
           <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
-      <c r="B256" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attribute</t>
-        </is>
-      </c>
       <c r="C256" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D256" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E256" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">one row per item of the list $.history.rules[].conditions, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -6031,73 +6037,78 @@
       </c>
       <c r="B257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">rule</t>
         </is>
       </c>
       <c r="C257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E257" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
+          <t xml:space="preserve">historyConditions</t>
+        </is>
+      </c>
+      <c r="B258" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E258" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules[].edits, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D258" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
+          <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rule</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E259" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
+          <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C260" s="1" t="inlineStr">
@@ -6107,24 +6118,24 @@
       </c>
       <c r="D260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
+          <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
       <c r="B261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C261" s="1" t="inlineStr">
@@ -6134,19 +6145,24 @@
       </c>
       <c r="D261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E261" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
+          <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C262" s="1" t="inlineStr">
@@ -6156,134 +6172,149 @@
       </c>
       <c r="D262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E262" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">historyConditions</t>
+        </is>
+      </c>
+      <c r="B263" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C263" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E263" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.ui</t>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D263" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
-        </is>
-      </c>
-      <c r="B264" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">readingLanguage</t>
+          <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
       <c r="C264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D264" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E264" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.history.rules[].edits, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">glossPercent</t>
+          <t xml:space="preserve">rule</t>
         </is>
       </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E265" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">labelMinScale</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E266" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.text</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.largeText</t>
+          <t xml:space="preserve">value</t>
         </is>
       </c>
       <c r="C268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6293,19 +6324,14 @@
           <t xml:space="preserve">ui</t>
         </is>
       </c>
-      <c r="B269" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">contrast.glyph</t>
-        </is>
-      </c>
       <c r="C269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
-        </is>
-      </c>
-      <c r="D269" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E269" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.ui</t>
         </is>
       </c>
     </row>
@@ -6317,17 +6343,17 @@
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.hint</t>
+          <t xml:space="preserve">readingLanguage</t>
         </is>
       </c>
       <c r="C270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6339,12 +6365,12 @@
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.outline</t>
+          <t xml:space="preserve">glossPercent</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D271" s="1" t="inlineStr">
@@ -6361,7 +6387,7 @@
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.minTextFillAlpha</t>
+          <t xml:space="preserve">labelMinScale</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
@@ -6383,95 +6409,100 @@
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">latinFallbackFont</t>
+          <t xml:space="preserve">contrast.text</t>
         </is>
       </c>
       <c r="C273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="B274" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">contrast.largeText</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E274" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.paletteMap, in order</t>
+          <t xml:space="preserve">decimal</t>
+        </is>
+      </c>
+      <c r="D274" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">role</t>
+          <t xml:space="preserve">contrast.glyph</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fill</t>
+          <t xml:space="preserve">contrast.hint</t>
         </is>
       </c>
       <c r="C276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">alpha</t>
+          <t xml:space="preserve">contrast.outline</t>
         </is>
       </c>
       <c r="C277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D277" s="1" t="inlineStr">
@@ -6483,34 +6514,34 @@
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ink</t>
+          <t xml:space="preserve">contrast.minTextFillAlpha</t>
         </is>
       </c>
       <c r="C278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">textClass</t>
+          <t xml:space="preserve">latinFallbackFont</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
@@ -6527,29 +6558,29 @@
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row: the object $.ui.neutral</t>
+          <t xml:space="preserve">one row per item of the list $.ui.paletteMap, in order</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C281" s="1" t="inlineStr">
@@ -6566,12 +6597,12 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">fill</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
@@ -6588,56 +6619,56 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">alpha</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">runtimeFont</t>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">headingAdd</t>
+          <t xml:space="preserve">textClass</t>
         </is>
       </c>
       <c r="C285" s="1" t="inlineStr">
@@ -6657,19 +6688,14 @@
           <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
-      <c r="B286" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">buttonAdd</t>
-        </is>
-      </c>
       <c r="C286" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D286" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E286" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.ui.neutral</t>
         </is>
       </c>
     </row>
@@ -6681,17 +6707,17 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">stripItalic</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6729,7 @@
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wallpaper</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr">
@@ -6720,78 +6746,78 @@
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiNeutral</t>
+        </is>
+      </c>
+      <c r="B289" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C289" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E289" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.fonts, in order</t>
-        </is>
-      </c>
-      <c r="F289" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D289" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">file</t>
+          <t xml:space="preserve">runtimeFont</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">face</t>
+          <t xml:space="preserve">headingAdd</t>
         </is>
       </c>
       <c r="C291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">family</t>
+          <t xml:space="preserve">buttonAdd</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
@@ -6808,73 +6834,78 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">style</t>
+          <t xml:space="preserve">stripItalic</t>
         </is>
       </c>
       <c r="C293" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D293" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
+          <t xml:space="preserve">uiNeutral</t>
+        </is>
+      </c>
+      <c r="B294" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wallpaper</t>
         </is>
       </c>
       <c r="C294" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E294" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.seeds, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D294" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
-        </is>
-      </c>
-      <c r="B295" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D295" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E295" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.fonts, in order</t>
+        </is>
+      </c>
+      <c r="F295" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
+          <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hex</t>
+          <t xml:space="preserve">file</t>
         </is>
       </c>
       <c r="C296" s="1" t="inlineStr">
@@ -6891,29 +6922,34 @@
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">neutralFonts</t>
+        </is>
+      </c>
+      <c r="B297" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">face</t>
         </is>
       </c>
       <c r="C297" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E297" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.overrides, in order</t>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D297" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">role</t>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C298" s="1" t="inlineStr">
@@ -6930,12 +6966,12 @@
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fill</t>
+          <t xml:space="preserve">style</t>
         </is>
       </c>
       <c r="C299" s="1" t="inlineStr">
@@ -6952,51 +6988,51 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
-        </is>
-      </c>
-      <c r="B300" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ink</t>
+          <t xml:space="preserve">neutralSeeds</t>
         </is>
       </c>
       <c r="C300" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D300" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E300" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.seeds, in order</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
+          <t xml:space="preserve">neutralSeeds</t>
+        </is>
+      </c>
+      <c r="B301" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C301" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E301" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.art, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D301" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
+          <t xml:space="preserve">neutralSeeds</t>
         </is>
       </c>
       <c r="B302" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C302" s="1" t="inlineStr">
@@ -7013,51 +7049,51 @@
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
-        </is>
-      </c>
-      <c r="B303" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hex</t>
+          <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
       <c r="C303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D303" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E303" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.overrides, in order</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">neutralOverrides</t>
+        </is>
+      </c>
+      <c r="B304" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E304" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.strings, in order; a row's name is key, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D304" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
       <c r="B305" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">fill</t>
         </is>
       </c>
       <c r="C305" s="1" t="inlineStr">
@@ -7067,24 +7103,19 @@
       </c>
       <c r="D305" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E305" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C306" s="1" t="inlineStr">
@@ -7101,34 +7132,29 @@
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
-        </is>
-      </c>
-      <c r="B307" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gloss</t>
+          <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
       <c r="C307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D307" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E307" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.art, in order</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tier</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C308" s="1" t="inlineStr">
@@ -7145,122 +7171,122 @@
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
+          <t xml:space="preserve">neutralArt</t>
+        </is>
+      </c>
+      <c r="B309" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E309" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.languages, in order; a row's name is language, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D309" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
-        </is>
-      </c>
-      <c r="B310" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
       <c r="C310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D310" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.ui.strings, in order; a row's name is key, unique</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
+          <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
       <c r="B311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rtl</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E311" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
+          <t xml:space="preserve">uiStrings</t>
+        </is>
+      </c>
+      <c r="B312" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E312" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.languages[].entries, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D312" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
+          <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">gloss</t>
         </is>
       </c>
       <c r="C313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E313" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'uiLanguages' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
+          <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
       <c r="B314" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">tier</t>
         </is>
       </c>
       <c r="C314" s="1" t="inlineStr">
@@ -7271,160 +7297,165 @@
       <c r="D314" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E314" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'uiStrings'</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
-        </is>
-      </c>
-      <c r="B315" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">uiLanguages</t>
         </is>
       </c>
       <c r="C315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D315" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E315" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.languages, in order; a row's name is language, unique</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiLanguages</t>
+        </is>
+      </c>
+      <c r="B316" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D316" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row: the object $.translation</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiLanguages</t>
         </is>
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">rtl</t>
         </is>
       </c>
       <c r="C317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
-        </is>
-      </c>
-      <c r="B318" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">announce</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
       <c r="C318" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D318" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E318" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.languages[].entries, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.startDelay</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E319" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'uiLanguages' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
       <c r="B320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.letterInterval</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E320" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'uiStrings'</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.letterSeconds</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7434,19 +7465,14 @@
           <t xml:space="preserve">translation</t>
         </is>
       </c>
-      <c r="B322" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">flip.scrambleSteps</t>
-        </is>
-      </c>
       <c r="C322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D322" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E322" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.translation</t>
         </is>
       </c>
     </row>
@@ -7458,27 +7484,17 @@
       </c>
       <c r="B323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.slots</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E323" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F323" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">slots whose value stays English in untranslated speech</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -7490,27 +7506,17 @@
       </c>
       <c r="B324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.words</t>
+          <t xml:space="preserve">announce</t>
         </is>
       </c>
       <c r="C324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E324" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F324" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">words that stay English in untranslated speech</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7522,17 +7528,17 @@
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.digits</t>
+          <t xml:space="preserve">flip.startDelay</t>
         </is>
       </c>
       <c r="C325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -7544,144 +7550,159 @@
       </c>
       <c r="B326" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fallbackGlyphs</t>
+          <t xml:space="preserve">flip.letterInterval</t>
         </is>
       </c>
       <c r="C326" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D326" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
+          <t xml:space="preserve">translation</t>
+        </is>
+      </c>
+      <c r="B327" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flip.letterSeconds</t>
         </is>
       </c>
       <c r="C327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E327" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.scripts, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">decimal</t>
+        </is>
+      </c>
+      <c r="D327" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">flip.scrambleSteps</t>
         </is>
       </c>
       <c r="C328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E328" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rightToLeft</t>
+          <t xml:space="preserve">keyWords.slots</t>
         </is>
       </c>
       <c r="C329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E329" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F329" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slots whose value stays English in untranslated speech</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">translation</t>
+        </is>
+      </c>
+      <c r="B330" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">keyWords.words</t>
         </is>
       </c>
       <c r="C330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text list</t>
+        </is>
+      </c>
+      <c r="D330" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no items</t>
         </is>
       </c>
       <c r="E330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.translation.scripts[].fonts, in order; the first column names the parent row</t>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
       <c r="F330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">words that stay English in untranslated speech</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">script</t>
+          <t xml:space="preserve">keyWords.digits</t>
         </is>
       </c>
       <c r="C331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E331" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'scripts' this row belongs to</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">file</t>
+          <t xml:space="preserve">fallbackGlyphs</t>
         </is>
       </c>
       <c r="C332" s="1" t="inlineStr">
@@ -7698,34 +7719,29 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
-        </is>
-      </c>
-      <c r="B333" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">face</t>
+          <t xml:space="preserve">scripts</t>
         </is>
       </c>
       <c r="C333" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D333" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E333" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.translation.scripts, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">scripts</t>
         </is>
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">family</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C334" s="1" t="inlineStr">
@@ -7735,36 +7751,41 @@
       </c>
       <c r="D334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E334" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">scripts</t>
         </is>
       </c>
       <c r="B335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">style</t>
+          <t xml:space="preserve">rightToLeft</t>
         </is>
       </c>
       <c r="C335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
       <c r="C336" s="1" t="inlineStr">
@@ -7774,24 +7795,29 @@
       </c>
       <c r="E336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.translation.packs, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">one row per item of the list $.translation.scripts[].fonts, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F336" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
       <c r="B337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">script</t>
         </is>
       </c>
       <c r="C337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D337" s="1" t="inlineStr">
@@ -7801,19 +7827,19 @@
       </c>
       <c r="E337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">names the row of 'scripts' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
       <c r="B338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">file</t>
         </is>
       </c>
       <c r="C338" s="1" t="inlineStr">
@@ -7830,12 +7856,12 @@
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
       <c r="B339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">spokenCost</t>
+          <t xml:space="preserve">face</t>
         </is>
       </c>
       <c r="C339" s="1" t="inlineStr">
@@ -7852,29 +7878,34 @@
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">scriptFonts</t>
+        </is>
+      </c>
+      <c r="B340" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E340" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D340" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
       <c r="B341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">style</t>
         </is>
       </c>
       <c r="C341" s="1" t="inlineStr">
@@ -7884,46 +7915,36 @@
       </c>
       <c r="D341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E341" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
-        </is>
-      </c>
-      <c r="B342" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">packs</t>
         </is>
       </c>
       <c r="C342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D342" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E342" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.translation.packs, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">packs</t>
         </is>
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">script</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C343" s="1" t="inlineStr">
@@ -7933,24 +7954,24 @@
       </c>
       <c r="D343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'scripts'</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">packs</t>
         </is>
       </c>
       <c r="B344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pack</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C344" s="1" t="inlineStr">
@@ -7961,31 +7982,168 @@
       <c r="D344" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E344" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'packs'</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">packs</t>
+        </is>
+      </c>
+      <c r="B345" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spokenCost</t>
+        </is>
+      </c>
+      <c r="C345" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D345" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">tongues</t>
         </is>
       </c>
-      <c r="B345" s="1" t="inlineStr">
+      <c r="C346" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E346" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B347" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C347" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D347" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E347" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B348" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">displayName</t>
+        </is>
+      </c>
+      <c r="C348" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D348" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B349" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">script</t>
+        </is>
+      </c>
+      <c r="C349" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D349" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E349" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'scripts'</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B350" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pack</t>
+        </is>
+      </c>
+      <c r="C350" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D350" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E350" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'packs'</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B351" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">glyphs</t>
         </is>
       </c>
-      <c r="C345" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D345" s="1" t="inlineStr">
+      <c r="C351" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D351" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
         </is>
@@ -8002,6 +8160,9 @@
     <col min="1" max="1" width="18" style="1" customWidth="1"/>
     <col min="2" max="2" width="24" style="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8020,6 +8181,21 @@
           <t xml:space="preserve">firstDate</t>
         </is>
       </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">displaced.foundWithinDays</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">displaced.validDaysMin</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">displaced.validDaysMax</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -8036,6 +8212,15 @@
         <is>
           <t xml:space="preserve">14 Mar 2150</t>
         </is>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -11007,11 +11192,11 @@
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" customWidth="1"/>
     <col min="3" max="3" width="27" style="1" customWidth="1"/>
-    <col min="4" max="4" width="36" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" customWidth="1"/>
+    <col min="7" max="7" width="20" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18" style="1" customWidth="1"/>
     <col min="9" max="9" width="26" style="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="1" customWidth="1"/>
     <col min="11" max="11" width="18" style="1" customWidth="1"/>
@@ -11041,27 +11226,27 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">claim</t>
+          <t xml:space="preserve">honorificMale</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificMale</t>
+          <t xml:space="preserve">honorificFemale</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificFemale</t>
+          <t xml:space="preserve">honorificUnknown</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificUnknown</t>
+          <t xml:space="preserve">requestLabel</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">requestLabel</t>
+          <t xml:space="preserve">papersLabel</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -11128,27 +11313,27 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">I request passage home to {place}.</t>
+          <t xml:space="preserve">sir</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">sir</t>
+          <t xml:space="preserve">madam</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">madam</t>
+          <t xml:space="preserve">traveller</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">traveller</t>
+          <t xml:space="preserve">Request {document}</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Request {document}</t>
+          <t xml:space="preserve">Request papers &gt;</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
@@ -11198,6 +11383,42 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11" style="1" customWidth="1"/>
+    <col min="2" max="2" width="34" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kind</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Please. Send me home to {place}.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11277,7 +11498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11391,7 +11612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11445,7 +11666,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11503,7 +11724,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11557,7 +11778,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11646,7 +11867,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11706,7 +11927,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11828,152 +12049,6 @@
       <c r="F4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Calculators? I saw nothing. Nothing at all.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="21" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8" style="1" customWidth="1"/>
-    <col min="6" max="6" width="27" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dialog</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">node</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">label</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">next</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">effect</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dlg_rumour</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">more</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tell me more.</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dlg_rumour</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ignore</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not my business.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dlg_rumour</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">detail</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">noted</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Noted. Thank you.</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Effect_Dialog_RumourHeard</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dlg_rumour_followup</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bye</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Of course. Next!</t>
         </is>
       </c>
     </row>
@@ -12029,6 +12104,152 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="21" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8" style="1" customWidth="1"/>
+    <col min="6" max="6" width="27" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dialog</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">node</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">label</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">next</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dlg_rumour</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">start</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">more</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tell me more.</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dlg_rumour</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">start</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ignore</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not my business.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dlg_rumour</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detail</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">noted</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Noted. Thank you.</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Effect_Dialog_RumourHeard</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dlg_rumour_followup</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">start</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bye</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Of course. Next!</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
     <col min="1" max="1" width="8" style="1" customWidth="1"/>
     <col min="2" max="2" width="8" style="1" customWidth="1"/>
     <col min="3" max="3" width="8" style="1" customWidth="1"/>
@@ -12079,7 +12300,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12252,7 +12473,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12294,7 +12515,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12341,7 +12562,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12405,7 +12626,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12493,7 +12714,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12573,7 +12794,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12681,7 +12902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12761,94 +12982,6 @@
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Text</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="12" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="35" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">displayName</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">language</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">runtimeFont</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">headingAdd</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">buttonAdd</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stripItalic</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wallpaper</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">neutral</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Temporal Customs standard issue</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">en</t>
-        </is>
-      </c>
-      <c r="D2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/Art/Generated/xp_bliss.png</t>
         </is>
       </c>
     </row>
@@ -12956,6 +13089,94 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="12" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="35" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">displayName</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">language</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">runtimeFont</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">headingAdd</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buttonAdd</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stripItalic</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wallpaper</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">neutral</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temporal Customs standard issue</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">en</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/Art/Generated/xp_bliss.png</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
     <col min="1" max="1" width="8" style="1" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="8" style="1" customWidth="1"/>
@@ -12988,7 +13209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13036,7 +13257,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13095,7 +13316,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13143,7 +13364,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13223,7 +13444,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13267,7 +13488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14453,7 +14674,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14565,7 +14786,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14609,7 +14830,54 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="55" style="1" customWidth="1"/>
+    <col min="2" max="2" width="57" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">library</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blueprint</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dayPlanFolder</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/Data/Content Library/ContentLibrary_Main.asset</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/Data/Investigation/CaseBlueprint_Displaced.asset</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assets/Data/Investigation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14651,54 +14919,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="55" style="1" customWidth="1"/>
-    <col min="2" max="2" width="60" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">library</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blueprint</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dayPlanFolder</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/Data/Content Library/ContentLibrary_Main.asset</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/Data/Investigation/CaseBlueprint_Investigation.asset</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Assets/Data/Investigation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -14758,7 +14979,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -16361,12 +16361,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">records.title</t>
+          <t xml:space="preserve">records.search</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">سجلات المواطنين</t>
+          <t xml:space="preserve">بحث</t>
         </is>
       </c>
     </row>
@@ -16378,12 +16378,12 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">records.search</t>
+          <t xml:space="preserve">compare.match</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">بحث</t>
+          <t xml:space="preserve">تطابق</t>
         </is>
       </c>
     </row>
@@ -16395,12 +16395,12 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">compare.match</t>
+          <t xml:space="preserve">compare.mismatch</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">تطابق</t>
+          <t xml:space="preserve">عدم تطابق</t>
         </is>
       </c>
     </row>
@@ -16412,12 +16412,12 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">compare.mismatch</t>
+          <t xml:space="preserve">citation.title</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">عدم تطابق</t>
+          <t xml:space="preserve">إشعار انحراف زمني</t>
         </is>
       </c>
     </row>
@@ -16429,12 +16429,12 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">citation.title</t>
+          <t xml:space="preserve">citation.acknowledge</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">إشعار انحراف زمني</t>
+          <t xml:space="preserve">تم الاطلاع</t>
         </is>
       </c>
     </row>
@@ -16446,12 +16446,12 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">citation.acknowledge</t>
+          <t xml:space="preserve">window.settings</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">تم الاطلاع</t>
+          <t xml:space="preserve">الإعدادات</t>
         </is>
       </c>
     </row>
@@ -16463,12 +16463,12 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">window.directives</t>
+          <t xml:space="preserve">icon.internet</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">التوجيهات</t>
+          <t xml:space="preserve">الإنترنت</t>
         </is>
       </c>
     </row>
@@ -16480,12 +16480,12 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">window.scanner</t>
+          <t xml:space="preserve">icon.notes</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">تقرير الانحرافات</t>
+          <t xml:space="preserve">ملاحظات</t>
         </is>
       </c>
     </row>
@@ -16497,12 +16497,12 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">window.settings</t>
+          <t xml:space="preserve">icon.investigation</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">الإعدادات</t>
+          <t xml:space="preserve">التحقيق</t>
         </is>
       </c>
     </row>
@@ -16514,12 +16514,12 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.directives</t>
+          <t xml:space="preserve">icon.mail</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">التوجيهات</t>
+          <t xml:space="preserve">البريد</t>
         </is>
       </c>
     </row>
@@ -16531,12 +16531,12 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.scanner</t>
+          <t xml:space="preserve">icon.account</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">تقرير الانحرافات</t>
+          <t xml:space="preserve">حساب المواطن</t>
         </is>
       </c>
     </row>
@@ -16548,12 +16548,12 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.records</t>
+          <t xml:space="preserve">icon.settings</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">السجلات</t>
+          <t xml:space="preserve">الإعدادات</t>
         </is>
       </c>
     </row>
@@ -16565,12 +16565,12 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.internet</t>
+          <t xml:space="preserve">tray.day</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">الإنترنت</t>
+          <t xml:space="preserve">اليوم {0}</t>
         </is>
       </c>
     </row>
@@ -16582,12 +16582,12 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.lexicon</t>
+          <t xml:space="preserve">tray.stability</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">المعجم</t>
+          <t xml:space="preserve">الاستقرار: {0:0}%</t>
         </is>
       </c>
     </row>
@@ -16599,12 +16599,12 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.dialect</t>
+          <t xml:space="preserve">taskbar.desk</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">اللهجات</t>
+          <t xml:space="preserve">العودة إلى المكتب</t>
         </is>
       </c>
     </row>
@@ -16616,12 +16616,12 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.material</t>
+          <t xml:space="preserve">briefing.title</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">المواد</t>
+          <t xml:space="preserve">اليوم {0} — الإحاطة الصباحية</t>
         </is>
       </c>
     </row>
@@ -16633,12 +16633,12 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.notes</t>
+          <t xml:space="preserve">results.title</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ملاحظات</t>
+          <t xml:space="preserve">اليوم {0} — تقرير المناوبة</t>
         </is>
       </c>
     </row>
@@ -16650,114 +16650,114 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.clueLog</t>
+          <t xml:space="preserve">briefing.newsHeader</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">سجل الأدلة</t>
+          <t xml:space="preserve">— أخبار الخط الزمني —</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ar</t>
+          <t xml:space="preserve">el</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tray.day</t>
+          <t xml:space="preserve">accept</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">اليوم {0}</t>
+          <t xml:space="preserve">ΕΓΚΡΙΣΗ</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ar</t>
+          <t xml:space="preserve">el</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tray.stability</t>
+          <t xml:space="preserve">deny</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">الاستقرار: {0:0}%</t>
+          <t xml:space="preserve">ΑΠΟΡΡΙΨΗ</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ar</t>
+          <t xml:space="preserve">el</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">taskbar.desk</t>
+          <t xml:space="preserve">taskbar.start</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">العودة إلى المكتب</t>
+          <t xml:space="preserve">έναρξη</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ar</t>
+          <t xml:space="preserve">el</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">briefing.title</t>
+          <t xml:space="preserve">startmenu.settings</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">اليوم {0} — الإحاطة الصباحية</t>
+          <t xml:space="preserve">Ρυθμίσεις</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ar</t>
+          <t xml:space="preserve">el</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">results.title</t>
+          <t xml:space="preserve">startmenu.screenOff</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">اليوم {0} — تقرير المناوبة</t>
+          <t xml:space="preserve">Σβήσιμο οθόνης</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ar</t>
+          <t xml:space="preserve">el</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">briefing.newsHeader</t>
+          <t xml:space="preserve">startmenu.quit</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">— أخبار الخط الزمني —</t>
+          <t xml:space="preserve">Έξοδος από το παιχνίδι</t>
         </is>
       </c>
     </row>
@@ -16769,12 +16769,12 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">accept</t>
+          <t xml:space="preserve">briefing.masthead</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΕΓΚΡΙΣΗ</t>
+          <t xml:space="preserve">Η ΧΡΟΝΙΚΗ ΕΦΗΜΕΡΙΔΑ</t>
         </is>
       </c>
     </row>
@@ -16786,12 +16786,12 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">deny</t>
+          <t xml:space="preserve">briefing.start</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΑΠΟΡΡΙΨΗ</t>
+          <t xml:space="preserve">ΕΝΑΡΞΗ ΒΑΡΔΙΑΣ</t>
         </is>
       </c>
     </row>
@@ -16803,12 +16803,12 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">taskbar.start</t>
+          <t xml:space="preserve">results.masthead</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">έναρξη</t>
+          <t xml:space="preserve">ΗΜΕΡΟΛΟΓΙΟ ΒΑΡΔΙΑΣ — ΑΠΟΓΕΥΜΑΤΙΝΗ ΕΚΔΟΣΗ</t>
         </is>
       </c>
     </row>
@@ -16820,12 +16820,12 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">startmenu.settings</t>
+          <t xml:space="preserve">results.goHome</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ρυθμίσεις</t>
+          <t xml:space="preserve">ΣΠΙΤΙ</t>
         </is>
       </c>
     </row>
@@ -16837,12 +16837,12 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">startmenu.screenOff</t>
+          <t xml:space="preserve">records.search</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Σβήσιμο οθόνης</t>
+          <t xml:space="preserve">ΑΝΑΖΗΤΗΣΗ</t>
         </is>
       </c>
     </row>
@@ -16854,12 +16854,12 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">startmenu.quit</t>
+          <t xml:space="preserve">compare.match</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Έξοδος από το παιχνίδι</t>
+          <t xml:space="preserve">ΤΑΙΡΙΑΖΕΙ</t>
         </is>
       </c>
     </row>
@@ -16871,12 +16871,12 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">briefing.masthead</t>
+          <t xml:space="preserve">compare.mismatch</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Η ΧΡΟΝΙΚΗ ΕΦΗΜΕΡΙΔΑ</t>
+          <t xml:space="preserve">ΔΕΝ ΤΑΙΡΙΑΖΕΙ</t>
         </is>
       </c>
     </row>
@@ -16888,12 +16888,12 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">briefing.start</t>
+          <t xml:space="preserve">citation.title</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΕΝΑΡΞΗ ΒΑΡΔΙΑΣ</t>
+          <t xml:space="preserve">ΕΙΔΟΠΟΙΗΣΗ ΧΡΟΝΙΚΗΣ ΑΠΟΚΛΙΣΗΣ</t>
         </is>
       </c>
     </row>
@@ -16905,12 +16905,12 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">results.masthead</t>
+          <t xml:space="preserve">citation.acknowledge</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΗΜΕΡΟΛΟΓΙΟ ΒΑΡΔΙΑΣ — ΑΠΟΓΕΥΜΑΤΙΝΗ ΕΚΔΟΣΗ</t>
+          <t xml:space="preserve">Ελήφθη</t>
         </is>
       </c>
     </row>
@@ -16922,12 +16922,12 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">results.goHome</t>
+          <t xml:space="preserve">window.settings</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΣΠΙΤΙ</t>
+          <t xml:space="preserve">Ρυθμίσεις</t>
         </is>
       </c>
     </row>
@@ -16939,12 +16939,12 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">records.title</t>
+          <t xml:space="preserve">icon.internet</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Μητρώο Πολιτών</t>
+          <t xml:space="preserve">Διαδίκτυο</t>
         </is>
       </c>
     </row>
@@ -16956,12 +16956,12 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">records.search</t>
+          <t xml:space="preserve">icon.notes</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΑΝΑΖΗΤΗΣΗ</t>
+          <t xml:space="preserve">Σημειώσεις</t>
         </is>
       </c>
     </row>
@@ -16973,12 +16973,12 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">compare.match</t>
+          <t xml:space="preserve">icon.investigation</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΤΑΙΡΙΑΖΕΙ</t>
+          <t xml:space="preserve">Έρευνα</t>
         </is>
       </c>
     </row>
@@ -16990,12 +16990,12 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">compare.mismatch</t>
+          <t xml:space="preserve">icon.mail</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΔΕΝ ΤΑΙΡΙΑΖΕΙ</t>
+          <t xml:space="preserve">Αλληλογραφία</t>
         </is>
       </c>
     </row>
@@ -17007,12 +17007,12 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">citation.title</t>
+          <t xml:space="preserve">icon.account</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΕΙΔΟΠΟΙΗΣΗ ΧΡΟΝΙΚΗΣ ΑΠΟΚΛΙΣΗΣ</t>
+          <t xml:space="preserve">Λογαριασμός πολίτη</t>
         </is>
       </c>
     </row>
@@ -17024,12 +17024,12 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">citation.acknowledge</t>
+          <t xml:space="preserve">icon.settings</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ελήφθη</t>
+          <t xml:space="preserve">Ρυθμίσεις</t>
         </is>
       </c>
     </row>
@@ -17041,12 +17041,12 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">window.directives</t>
+          <t xml:space="preserve">tray.day</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Οδηγίες</t>
+          <t xml:space="preserve">Ημέρα {0}</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">window.scanner</t>
+          <t xml:space="preserve">tray.stability</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Αναφορά αποκλίσεων</t>
+          <t xml:space="preserve">Σταθερότητα: {0:0}%</t>
         </is>
       </c>
     </row>
@@ -17075,12 +17075,12 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">window.settings</t>
+          <t xml:space="preserve">taskbar.desk</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ρυθμίσεις</t>
+          <t xml:space="preserve">&lt; Γραφείο</t>
         </is>
       </c>
     </row>
@@ -17092,12 +17092,12 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.directives</t>
+          <t xml:space="preserve">briefing.title</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Οδηγίες</t>
+          <t xml:space="preserve">Ημέρα {0} — Πρωινή ενημέρωση</t>
         </is>
       </c>
     </row>
@@ -17109,12 +17109,12 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.scanner</t>
+          <t xml:space="preserve">results.title</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Αναφορά αποκλίσεων</t>
+          <t xml:space="preserve">Ημέρα {0} — Αναφορά βάρδιας</t>
         </is>
       </c>
     </row>
@@ -17126,214 +17126,10 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.records</t>
+          <t xml:space="preserve">briefing.newsHeader</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Μητρώο</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.internet</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Διαδίκτυο</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.lexicon</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Λεξικό</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.dialect</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Διάλεκτος</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.material</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Υλικά</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.notes</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Σημειώσεις</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.clueLog</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ενδείξεις</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tray.day</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ημέρα {0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tray.stability</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Σταθερότητα: {0:0}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taskbar.desk</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt; Γραφείο</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">briefing.title</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ημέρα {0} — Πρωινή ενημέρωση</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">results.title</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ημέρα {0} — Αναφορά βάρδιας</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">briefing.newsHeader</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">— ΕΙΔΗΣΕΙΣ ΧΡΟΝΟΓΡΑΜΜΗΣ —</t>
         </is>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -54,28 +54,30 @@
     <sheet name="historyEdits" sheetId="50" r:id="rId50"/>
     <sheet name="newsDebt" sheetId="51" r:id="rId51"/>
     <sheet name="pc" sheetId="52" r:id="rId52"/>
-    <sheet name="pcSites" sheetId="53" r:id="rId53"/>
-    <sheet name="pcPages" sheetId="54" r:id="rId54"/>
-    <sheet name="pcPageBlocks" sheetId="55" r:id="rId55"/>
-    <sheet name="pcPeople" sheetId="56" r:id="rId56"/>
-    <sheet name="pcRelations" sheetId="57" r:id="rId57"/>
-    <sheet name="pcMail" sheetId="58" r:id="rId58"/>
-    <sheet name="pcMailBody" sheetId="59" r:id="rId59"/>
-    <sheet name="ui" sheetId="60" r:id="rId60"/>
-    <sheet name="uiPalette" sheetId="61" r:id="rId61"/>
-    <sheet name="uiNeutral" sheetId="62" r:id="rId62"/>
-    <sheet name="neutralFonts" sheetId="63" r:id="rId63"/>
-    <sheet name="neutralSeeds" sheetId="64" r:id="rId64"/>
-    <sheet name="neutralOverrides" sheetId="65" r:id="rId65"/>
-    <sheet name="neutralArt" sheetId="66" r:id="rId66"/>
-    <sheet name="uiStrings" sheetId="67" r:id="rId67"/>
-    <sheet name="uiLanguages" sheetId="68" r:id="rId68"/>
-    <sheet name="uiLanguageEntries" sheetId="69" r:id="rId69"/>
-    <sheet name="translation" sheetId="70" r:id="rId70"/>
-    <sheet name="scripts" sheetId="71" r:id="rId71"/>
-    <sheet name="scriptFonts" sheetId="72" r:id="rId72"/>
-    <sheet name="packs" sheetId="73" r:id="rId73"/>
-    <sheet name="tongues" sheetId="74" r:id="rId74"/>
+    <sheet name="pcStepSets" sheetId="53" r:id="rId53"/>
+    <sheet name="pcSteps" sheetId="54" r:id="rId54"/>
+    <sheet name="pcSites" sheetId="55" r:id="rId55"/>
+    <sheet name="pcPages" sheetId="56" r:id="rId56"/>
+    <sheet name="pcPageBlocks" sheetId="57" r:id="rId57"/>
+    <sheet name="pcPeople" sheetId="58" r:id="rId58"/>
+    <sheet name="pcRelations" sheetId="59" r:id="rId59"/>
+    <sheet name="pcMail" sheetId="60" r:id="rId60"/>
+    <sheet name="pcMailBody" sheetId="61" r:id="rId61"/>
+    <sheet name="ui" sheetId="62" r:id="rId62"/>
+    <sheet name="uiPalette" sheetId="63" r:id="rId63"/>
+    <sheet name="uiNeutral" sheetId="64" r:id="rId64"/>
+    <sheet name="neutralFonts" sheetId="65" r:id="rId65"/>
+    <sheet name="neutralSeeds" sheetId="66" r:id="rId66"/>
+    <sheet name="neutralOverrides" sheetId="67" r:id="rId67"/>
+    <sheet name="neutralArt" sheetId="68" r:id="rId68"/>
+    <sheet name="uiStrings" sheetId="69" r:id="rId69"/>
+    <sheet name="uiLanguages" sheetId="70" r:id="rId70"/>
+    <sheet name="uiLanguageEntries" sheetId="71" r:id="rId71"/>
+    <sheet name="translation" sheetId="72" r:id="rId72"/>
+    <sheet name="scripts" sheetId="73" r:id="rId73"/>
+    <sheet name="scriptFonts" sheetId="74" r:id="rId74"/>
+    <sheet name="packs" sheetId="75" r:id="rId75"/>
+    <sheet name="tongues" sheetId="76" r:id="rId76"/>
   </sheets>
 </workbook>
 </file>
@@ -7257,7 +7259,7 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSites</t>
+          <t xml:space="preserve">pcStepSets</t>
         </is>
       </c>
       <c r="C306" s="1" t="inlineStr">
@@ -7267,24 +7269,24 @@
       </c>
       <c r="E306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.sites, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">one row per item of the list $.pc.steps.sets, in order; a row's name is type, unique</t>
         </is>
       </c>
       <c r="F306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Internet's sites</t>
+          <t xml:space="preserve">the optional steps checklist, one set per traveller kind</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSites</t>
+          <t xml:space="preserve">pcStepSets</t>
         </is>
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C307" s="1" t="inlineStr">
@@ -7299,19 +7301,24 @@
       </c>
       <c r="E307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">part of the row's name; one of: default, RichTourist, PoorTourist, Labourer, Displaced</t>
+        </is>
+      </c>
+      <c r="F307" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a traveller kind, or default: the steps of a kind with no set of its own</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSites</t>
+          <t xml:space="preserve">pcStepSets</t>
         </is>
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">inherit</t>
         </is>
       </c>
       <c r="C308" s="1" t="inlineStr">
@@ -7321,105 +7328,105 @@
       </c>
       <c r="D308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: News, History, Ancestry, Static</t>
+          <t xml:space="preserve">names a row of 'pcStepSets'</t>
         </is>
       </c>
       <c r="F308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the page builder that serves it</t>
+          <t xml:space="preserve">the set whose steps it starts from; its own step of the same id replaces the parent's (blank: none)</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSites</t>
+          <t xml:space="preserve">pcStepSets</t>
         </is>
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">dataOnly</t>
         </is>
       </c>
       <c r="C309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="F309" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true while the kind is not in play yet: its forms and categories may name what a later phase adds</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSites</t>
-        </is>
-      </c>
-      <c r="B310" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">domain</t>
+          <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
       <c r="C310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D310" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E310" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.steps.sets[].steps, in order; the first column names the parent row</t>
         </is>
       </c>
       <c r="F310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">chronet://{domain}: lower-case letters, digits, dots and dashes</t>
+          <t xml:space="preserve">a set's steps, in order</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSites</t>
+          <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
       <c r="B311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">glyph</t>
+          <t xml:space="preserve">stepSet</t>
         </is>
       </c>
       <c r="C311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F311" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the start-page tile's art key</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E311" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'pcStepSets' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSites</t>
+          <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C312" s="1" t="inlineStr">
@@ -7429,68 +7436,88 @@
       </c>
       <c r="D312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="F312" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its label is the UI string steps.{id}</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSites</t>
+          <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">when</t>
         </is>
       </c>
       <c r="C313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E313" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: PapersReceived, PaperRead, Requested, RulesViewed, RecordViewed, Compared, Asked, LookedAt</t>
         </is>
       </c>
       <c r="F313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the first day it is listed</t>
+          <t xml:space="preserve">the check it waits for, never what the check found</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPages</t>
+          <t xml:space="preserve">pcSteps</t>
+        </is>
+      </c>
+      <c r="B314" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">categories</t>
         </is>
       </c>
       <c r="C314" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text list</t>
+        </is>
+      </c>
+      <c r="D314" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
         </is>
       </c>
       <c r="E314" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.pages, in order; a row's name is {site}/{path}, unique</t>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
       <c r="F314" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Static site's authored pages</t>
+          <t xml:space="preserve">the categories a Compared or Asked step counts (blank: derived from the case)</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPages</t>
+          <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">site</t>
+          <t xml:space="preserve">statement</t>
         </is>
       </c>
       <c r="C315" s="1" t="inlineStr">
@@ -7500,24 +7527,29 @@
       </c>
       <c r="D315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name; names a row of 'pcSites'</t>
+          <t xml:space="preserve">one of: Any, Field, Answer, Garment</t>
+        </is>
+      </c>
+      <c r="F315" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a Compared step's statement side (blank: any)</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPages</t>
+          <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">path</t>
+          <t xml:space="preserve">truth</t>
         </is>
       </c>
       <c r="C316" s="1" t="inlineStr">
@@ -7527,95 +7559,125 @@
       </c>
       <c r="D316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one of: Any, Reference, Record, Paper</t>
         </is>
       </c>
       <c r="F316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank: the site's front page</t>
+          <t xml:space="preserve">a Compared step's truth side (blank: any)</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPages</t>
+          <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">title</t>
+          <t xml:space="preserve">forms</t>
         </is>
       </c>
       <c r="C317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E317" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F317" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the form numbers a paper step counts (blank: every paper)</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPageBlocks</t>
+          <t xml:space="preserve">pcSteps</t>
+        </is>
+      </c>
+      <c r="B318" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jump.source</t>
         </is>
       </c>
       <c r="C318" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D318" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E318" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.pages[].blocks, in order; the first column names the parent row</t>
+          <t xml:space="preserve">one of: Documents, Records, Reference, Transcript, Report, Rules</t>
+        </is>
+      </c>
+      <c r="F318" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the tab a click on the step shows</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPageBlocks</t>
+          <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">page</t>
+          <t xml:space="preserve">jump.link</t>
         </is>
       </c>
       <c r="C319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'pcPages' this row belongs to</t>
+          <t xml:space="preserve">one of: PrimaryName, FirstUncheckedField, CostumeClaimed</t>
+        </is>
+      </c>
+      <c r="F319" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">where a click goes instead of a tab</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPageBlocks</t>
+          <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
       <c r="B320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">hint</t>
         </is>
       </c>
       <c r="C320" s="1" t="inlineStr">
@@ -7625,127 +7687,137 @@
       </c>
       <c r="D320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: Headline, Heading, Paragraph, Note, Link, Box</t>
+          <t xml:space="preserve">names a row of 'uiStrings'</t>
+        </is>
+      </c>
+      <c r="F320" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the UI string of the toast a click shows instead of a jump</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPageBlocks</t>
+          <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0 (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="F321" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its first day (blank: day 1)</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPageBlocks</t>
-        </is>
-      </c>
-      <c r="B322" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">address</t>
+          <t xml:space="preserve">pcSites</t>
         </is>
       </c>
       <c r="C322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D322" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E322" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.sites, in order; a row's name is id, unique</t>
         </is>
       </c>
       <c r="F322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Link's site name, domain or chronet:// address</t>
+          <t xml:space="preserve">the Internet's sites</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPageBlocks</t>
+          <t xml:space="preserve">pcSites</t>
         </is>
       </c>
       <c r="B323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F323" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a Box's lines</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPeople</t>
+          <t xml:space="preserve">pcSites</t>
+        </is>
+      </c>
+      <c r="B324" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D324" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.ancestry.people, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">one of: News, History, Ancestry, Static</t>
         </is>
       </c>
       <c r="F324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Lineage Archive's people of the past (no traveller's name)</t>
+          <t xml:space="preserve">the page builder that serves it</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPeople</t>
+          <t xml:space="preserve">pcSites</t>
         </is>
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C325" s="1" t="inlineStr">
@@ -7755,24 +7827,19 @@
       </c>
       <c r="D325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E325" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPeople</t>
+          <t xml:space="preserve">pcSites</t>
         </is>
       </c>
       <c r="B326" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">domain</t>
         </is>
       </c>
       <c r="C326" s="1" t="inlineStr">
@@ -7783,18 +7850,23 @@
       <c r="D326" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F326" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chronet://{domain}: lower-case letters, digits, dots and dashes</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPeople</t>
+          <t xml:space="preserve">pcSites</t>
         </is>
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">born</t>
+          <t xml:space="preserve">glyph</t>
         </is>
       </c>
       <c r="C327" s="1" t="inlineStr">
@@ -7805,18 +7877,23 @@
       <c r="D327" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F327" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the start-page tile's art key</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPeople</t>
+          <t xml:space="preserve">pcSites</t>
         </is>
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">died</t>
+          <t xml:space="preserve">blurb</t>
         </is>
       </c>
       <c r="C328" s="1" t="inlineStr">
@@ -7833,83 +7910,88 @@
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPeople</t>
+          <t xml:space="preserve">pcSites</t>
         </is>
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E329" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F329" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the first day it is listed</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPeople</t>
-        </is>
-      </c>
-      <c r="B330" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">note</t>
+          <t xml:space="preserve">pcPages</t>
         </is>
       </c>
       <c r="C330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D330" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E330" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.pages, in order; a row's name is {site}/{path}, unique</t>
+        </is>
+      </c>
+      <c r="F330" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a Static site's authored pages</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcRelations</t>
+          <t xml:space="preserve">pcPages</t>
+        </is>
+      </c>
+      <c r="B331" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">site</t>
         </is>
       </c>
       <c r="C331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D331" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.ancestry.relations, in order</t>
-        </is>
-      </c>
-      <c r="F331" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one direction per row</t>
+          <t xml:space="preserve">part of the row's name; names a row of 'pcSites'</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcRelations</t>
+          <t xml:space="preserve">pcPages</t>
         </is>
       </c>
       <c r="B332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">person</t>
+          <t xml:space="preserve">path</t>
         </is>
       </c>
       <c r="C332" s="1" t="inlineStr">
@@ -7919,24 +8001,29 @@
       </c>
       <c r="D332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E332" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
       <c r="F332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a person's or a premade's id: the card it shows on</t>
+          <t xml:space="preserve">blank: the site's front page</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcRelations</t>
+          <t xml:space="preserve">pcPages</t>
         </is>
       </c>
       <c r="B333" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">title</t>
         </is>
       </c>
       <c r="C333" s="1" t="inlineStr">
@@ -7953,61 +8040,56 @@
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcRelations</t>
-        </is>
-      </c>
-      <c r="B334" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">other</t>
+          <t xml:space="preserve">pcPageBlocks</t>
         </is>
       </c>
       <c r="C334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D334" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="F334" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the other card's id</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E334" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.pages[].blocks, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMail</t>
+          <t xml:space="preserve">pcPageBlocks</t>
+        </is>
+      </c>
+      <c r="B335" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">page</t>
         </is>
       </c>
       <c r="C335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D335" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.mail, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F335" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mail's authored messages</t>
+          <t xml:space="preserve">names the row of 'pcPages' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMail</t>
+          <t xml:space="preserve">pcPageBlocks</t>
         </is>
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C336" s="1" t="inlineStr">
@@ -8017,127 +8099,127 @@
       </c>
       <c r="D336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one of: Headline, Heading, Paragraph, Note, Link, Box</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMail</t>
+          <t xml:space="preserve">pcPageBlocks</t>
         </is>
       </c>
       <c r="B337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F337" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the day it arrives (its date)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMail</t>
+          <t xml:space="preserve">pcPageBlocks</t>
         </is>
       </c>
       <c r="B338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">untilDay</t>
+          <t xml:space="preserve">address</t>
         </is>
       </c>
       <c r="C338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="F338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the last day it is in the inbox; 0 keeps it for the run</t>
+          <t xml:space="preserve">a Link's site name, domain or chronet:// address</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMail</t>
+          <t xml:space="preserve">pcPageBlocks</t>
         </is>
       </c>
       <c r="B339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flag</t>
+          <t xml:space="preserve">lines</t>
         </is>
       </c>
       <c r="C339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E339" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
       <c r="F339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a story flag it waits for (blank: none)</t>
+          <t xml:space="preserve">a Box's lines</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMail</t>
-        </is>
-      </c>
-      <c r="B340" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">from</t>
+          <t xml:space="preserve">pcPeople</t>
         </is>
       </c>
       <c r="C340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D340" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E340" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.ancestry.people, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F340" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the Lineage Archive's people of the past (no traveller's name)</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMail</t>
+          <t xml:space="preserve">pcPeople</t>
         </is>
       </c>
       <c r="B341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">subject</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C341" s="1" t="inlineStr">
@@ -8147,68 +8229,68 @@
       </c>
       <c r="D341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E341" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMailBody</t>
+          <t xml:space="preserve">pcPeople</t>
+        </is>
+      </c>
+      <c r="B342" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Values</t>
-        </is>
-      </c>
-      <c r="E342" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.mail[].body, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F342" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its paragraphs</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D342" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMailBody</t>
+          <t xml:space="preserve">pcPeople</t>
         </is>
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">mail</t>
+          <t xml:space="preserve">born</t>
         </is>
       </c>
       <c r="C343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E343" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'pcMail' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMailBody</t>
+          <t xml:space="preserve">pcPeople</t>
         </is>
       </c>
       <c r="B344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">died</t>
         </is>
       </c>
       <c r="C344" s="1" t="inlineStr">
@@ -8218,36 +8300,46 @@
       </c>
       <c r="D344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">pcPeople</t>
+        </is>
+      </c>
+      <c r="B345" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C345" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D345" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E345" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row: the object $.ui</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">pcPeople</t>
         </is>
       </c>
       <c r="B346" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">readingLanguage</t>
+          <t xml:space="preserve">note</t>
         </is>
       </c>
       <c r="C346" s="1" t="inlineStr">
@@ -8264,188 +8356,213 @@
     <row r="347">
       <c r="A347" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
-        </is>
-      </c>
-      <c r="B347" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">glossPercent</t>
+          <t xml:space="preserve">pcRelations</t>
         </is>
       </c>
       <c r="C347" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D347" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E347" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.ancestry.relations, in order</t>
+        </is>
+      </c>
+      <c r="F347" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one direction per row</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">pcRelations</t>
         </is>
       </c>
       <c r="B348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">labelMinScale</t>
+          <t xml:space="preserve">person</t>
         </is>
       </c>
       <c r="C348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="F348" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a person's or a premade's id: the card it shows on</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">pcRelations</t>
         </is>
       </c>
       <c r="B349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.text</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">pcRelations</t>
         </is>
       </c>
       <c r="B350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.largeText</t>
+          <t xml:space="preserve">other</t>
         </is>
       </c>
       <c r="C350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="F350" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the other card's id</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
-        </is>
-      </c>
-      <c r="B351" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">contrast.glyph</t>
+          <t xml:space="preserve">pcMail</t>
         </is>
       </c>
       <c r="C351" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
-        </is>
-      </c>
-      <c r="D351" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E351" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.mail, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F351" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mail's authored messages</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">pcMail</t>
         </is>
       </c>
       <c r="B352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.hint</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E352" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">pcMail</t>
         </is>
       </c>
       <c r="B353" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.outline</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C353" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D353" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F353" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the day it arrives (its date)</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">pcMail</t>
         </is>
       </c>
       <c r="B354" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.minTextFillAlpha</t>
+          <t xml:space="preserve">untilDay</t>
         </is>
       </c>
       <c r="C354" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D354" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F354" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the last day it is in the inbox; 0 keeps it for the run</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">pcMail</t>
         </is>
       </c>
       <c r="B355" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">latinFallbackFont</t>
+          <t xml:space="preserve">flag</t>
         </is>
       </c>
       <c r="C355" s="1" t="inlineStr">
@@ -8456,35 +8573,45 @@
       <c r="D355" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F355" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a story flag it waits for (blank: none)</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">pcMail</t>
+        </is>
+      </c>
+      <c r="B356" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from</t>
         </is>
       </c>
       <c r="C356" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E356" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.paletteMap, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D356" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">pcMail</t>
         </is>
       </c>
       <c r="B357" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">role</t>
+          <t xml:space="preserve">subject</t>
         </is>
       </c>
       <c r="C357" s="1" t="inlineStr">
@@ -8501,56 +8628,61 @@
     <row r="358">
       <c r="A358" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
-        </is>
-      </c>
-      <c r="B358" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fill</t>
+          <t xml:space="preserve">pcMailBody</t>
         </is>
       </c>
       <c r="C358" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D358" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Values</t>
+        </is>
+      </c>
+      <c r="E358" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.mail[].body, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F358" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its paragraphs</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">pcMailBody</t>
         </is>
       </c>
       <c r="B359" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">alpha</t>
+          <t xml:space="preserve">mail</t>
         </is>
       </c>
       <c r="C359" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D359" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E359" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'pcMail' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">pcMailBody</t>
         </is>
       </c>
       <c r="B360" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ink</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C360" s="1" t="inlineStr">
@@ -8560,300 +8692,295 @@
       </c>
       <c r="D360" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
-        </is>
-      </c>
-      <c r="B361" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">textClass</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="C361" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D361" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E361" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.ui</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="B362" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">readingLanguage</t>
         </is>
       </c>
       <c r="C362" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E362" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.ui.neutral</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D362" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B363" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">glossPercent</t>
         </is>
       </c>
       <c r="C363" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D363" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">labelMinScale</t>
         </is>
       </c>
       <c r="C364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B365" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">contrast.text</t>
         </is>
       </c>
       <c r="C365" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D365" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B366" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">runtimeFont</t>
+          <t xml:space="preserve">contrast.largeText</t>
         </is>
       </c>
       <c r="C366" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D366" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">headingAdd</t>
+          <t xml:space="preserve">contrast.glyph</t>
         </is>
       </c>
       <c r="C367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">buttonAdd</t>
+          <t xml:space="preserve">contrast.hint</t>
         </is>
       </c>
       <c r="C368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B369" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">stripItalic</t>
+          <t xml:space="preserve">contrast.outline</t>
         </is>
       </c>
       <c r="C369" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D369" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wallpaper</t>
+          <t xml:space="preserve">contrast.minTextFillAlpha</t>
         </is>
       </c>
       <c r="C370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="B371" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">latinFallbackFont</t>
         </is>
       </c>
       <c r="C371" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E371" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.fonts, in order</t>
-        </is>
-      </c>
-      <c r="F371" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D371" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
-        </is>
-      </c>
-      <c r="B372" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">file</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="C372" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D372" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E372" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.paletteMap, in order</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="B373" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">face</t>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C373" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D373" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">family</t>
+          <t xml:space="preserve">fill</t>
         </is>
       </c>
       <c r="C374" s="1" t="inlineStr">
@@ -8870,51 +8997,56 @@
     <row r="375">
       <c r="A375" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="B375" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">style</t>
+          <t xml:space="preserve">alpha</t>
         </is>
       </c>
       <c r="C375" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D375" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
+          <t xml:space="preserve">uiPalette</t>
+        </is>
+      </c>
+      <c r="B376" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C376" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E376" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.seeds, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D376" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="B377" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">textClass</t>
         </is>
       </c>
       <c r="C377" s="1" t="inlineStr">
@@ -8931,51 +9063,51 @@
     <row r="378">
       <c r="A378" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
-        </is>
-      </c>
-      <c r="B378" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hex</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="C378" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D378" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E378" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.ui.neutral</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">uiNeutral</t>
+        </is>
+      </c>
+      <c r="B379" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C379" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E379" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.overrides, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D379" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="B380" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">role</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C380" s="1" t="inlineStr">
@@ -8992,12 +9124,12 @@
     <row r="381">
       <c r="A381" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="B381" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fill</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C381" s="1" t="inlineStr">
@@ -9014,51 +9146,56 @@
     <row r="382">
       <c r="A382" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="B382" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ink</t>
+          <t xml:space="preserve">runtimeFont</t>
         </is>
       </c>
       <c r="C382" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D382" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
+          <t xml:space="preserve">uiNeutral</t>
+        </is>
+      </c>
+      <c r="B383" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">headingAdd</t>
         </is>
       </c>
       <c r="C383" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E383" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.art, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D383" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="B384" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">buttonAdd</t>
         </is>
       </c>
       <c r="C384" s="1" t="inlineStr">
@@ -9075,78 +9212,78 @@
     <row r="385">
       <c r="A385" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hex</t>
+          <t xml:space="preserve">stripItalic</t>
         </is>
       </c>
       <c r="C385" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D385" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">uiNeutral</t>
+        </is>
+      </c>
+      <c r="B386" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wallpaper</t>
         </is>
       </c>
       <c r="C386" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E386" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.strings, in order; a row's name is key, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D386" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
-        </is>
-      </c>
-      <c r="B387" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
       <c r="C387" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D387" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E387" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.fonts, in order</t>
+        </is>
+      </c>
+      <c r="F387" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
       <c r="B388" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">file</t>
         </is>
       </c>
       <c r="C388" s="1" t="inlineStr">
@@ -9163,34 +9300,34 @@
     <row r="389">
       <c r="A389" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
       <c r="B389" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gloss</t>
+          <t xml:space="preserve">face</t>
         </is>
       </c>
       <c r="C389" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D389" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
       <c r="B390" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tier</t>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C390" s="1" t="inlineStr">
@@ -9207,122 +9344,112 @@
     <row r="391">
       <c r="A391" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
+          <t xml:space="preserve">neutralFonts</t>
+        </is>
+      </c>
+      <c r="B391" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">style</t>
         </is>
       </c>
       <c r="C391" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E391" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.languages, in order; a row's name is language, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D391" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
-        </is>
-      </c>
-      <c r="B392" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">neutralSeeds</t>
         </is>
       </c>
       <c r="C392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D392" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.seeds, in order</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
+          <t xml:space="preserve">neutralSeeds</t>
         </is>
       </c>
       <c r="B393" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rtl</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C393" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D393" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
+          <t xml:space="preserve">neutralSeeds</t>
+        </is>
+      </c>
+      <c r="B394" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C394" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E394" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.languages[].entries, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D394" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
-        </is>
-      </c>
-      <c r="B395" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
       <c r="C395" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D395" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E395" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'uiLanguages' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.overrides, in order</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
+          <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
       <c r="B396" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C396" s="1" t="inlineStr">
@@ -9333,23 +9460,18 @@
       <c r="D396" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E396" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'uiStrings'</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
+          <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
       <c r="B397" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">fill</t>
         </is>
       </c>
       <c r="C397" s="1" t="inlineStr">
@@ -9366,51 +9488,51 @@
     <row r="398">
       <c r="A398" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">neutralOverrides</t>
+        </is>
+      </c>
+      <c r="B398" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C398" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E398" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.translation</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D398" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
-        </is>
-      </c>
-      <c r="B399" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
       <c r="C399" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D399" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E399" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.art, in order</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
       <c r="B400" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">announce</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C400" s="1" t="inlineStr">
@@ -9427,186 +9549,161 @@
     <row r="401">
       <c r="A401" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
       <c r="B401" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.startDelay</t>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C401" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D401" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
-        </is>
-      </c>
-      <c r="B402" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">flip.letterInterval</t>
+          <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
       <c r="C402" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
-        </is>
-      </c>
-      <c r="D402" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E402" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.strings, in order; a row's name is key, unique</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
       <c r="B403" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.letterSeconds</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C403" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D403" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E403" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
       <c r="B404" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.scrambleSteps</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C404" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D404" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
       <c r="B405" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.slots</t>
+          <t xml:space="preserve">gloss</t>
         </is>
       </c>
       <c r="C405" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D405" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E405" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F405" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">slots whose value stays English in untranslated speech</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
       <c r="B406" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.words</t>
+          <t xml:space="preserve">tier</t>
         </is>
       </c>
       <c r="C406" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D406" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E406" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F406" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">words that stay English in untranslated speech</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
-        </is>
-      </c>
-      <c r="B407" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">keyWords.digits</t>
+          <t xml:space="preserve">uiLanguages</t>
         </is>
       </c>
       <c r="C407" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
-        </is>
-      </c>
-      <c r="D407" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E407" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.languages, in order; a row's name is language, unique</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiLanguages</t>
         </is>
       </c>
       <c r="B408" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fallbackGlyphs</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C408" s="1" t="inlineStr">
@@ -9616,156 +9713,156 @@
       </c>
       <c r="D408" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E408" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
+          <t xml:space="preserve">uiLanguages</t>
+        </is>
+      </c>
+      <c r="B409" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rtl</t>
         </is>
       </c>
       <c r="C409" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E409" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.scripts, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D409" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
-        </is>
-      </c>
-      <c r="B410" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
       <c r="C410" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D410" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E410" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.ui.languages[].entries, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
       <c r="B411" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rightToLeft</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C411" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D411" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E411" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'uiLanguages' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
+        </is>
+      </c>
+      <c r="B412" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C412" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D412" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E412" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.translation.scripts[].fonts, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F412" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">names a row of 'uiStrings'</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
       <c r="B413" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">script</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C413" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D413" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E413" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'scripts' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
-        </is>
-      </c>
-      <c r="B414" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">file</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="C414" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D414" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E414" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.translation</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B415" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">face</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C415" s="1" t="inlineStr">
@@ -9782,12 +9879,12 @@
     <row r="416">
       <c r="A416" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B416" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">family</t>
+          <t xml:space="preserve">announce</t>
         </is>
       </c>
       <c r="C416" s="1" t="inlineStr">
@@ -9804,166 +9901,186 @@
     <row r="417">
       <c r="A417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">style</t>
+          <t xml:space="preserve">flip.startDelay</t>
         </is>
       </c>
       <c r="C417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">translation</t>
+        </is>
+      </c>
+      <c r="B418" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flip.letterInterval</t>
         </is>
       </c>
       <c r="C418" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E418" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.packs, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">decimal</t>
+        </is>
+      </c>
+      <c r="D418" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B419" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">flip.letterSeconds</t>
         </is>
       </c>
       <c r="C419" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D419" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E419" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B420" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">flip.scrambleSteps</t>
         </is>
       </c>
       <c r="C420" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D420" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B421" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">spokenCost</t>
+          <t xml:space="preserve">keyWords.slots</t>
         </is>
       </c>
       <c r="C421" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D421" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E421" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F421" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slots whose value stays English in untranslated speech</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">translation</t>
+        </is>
+      </c>
+      <c r="B422" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">keyWords.words</t>
         </is>
       </c>
       <c r="C422" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text list</t>
+        </is>
+      </c>
+      <c r="D422" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no items</t>
         </is>
       </c>
       <c r="E422" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F422" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">words that stay English in untranslated speech</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B423" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">keyWords.digits</t>
         </is>
       </c>
       <c r="C423" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D423" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E423" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B424" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">fallbackGlyphs</t>
         </is>
       </c>
       <c r="C424" s="1" t="inlineStr">
@@ -9980,39 +10097,29 @@
     <row r="425">
       <c r="A425" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
-        </is>
-      </c>
-      <c r="B425" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">script</t>
+          <t xml:space="preserve">scripts</t>
         </is>
       </c>
       <c r="C425" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D425" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E425" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'scripts'</t>
+          <t xml:space="preserve">one row per item of the list $.translation.scripts, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">scripts</t>
         </is>
       </c>
       <c r="B426" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pack</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C426" s="1" t="inlineStr">
@@ -10022,32 +10129,399 @@
       </c>
       <c r="D426" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E426" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'packs'</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">scripts</t>
+        </is>
+      </c>
+      <c r="B427" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rightToLeft</t>
+        </is>
+      </c>
+      <c r="C427" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D427" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scriptFonts</t>
+        </is>
+      </c>
+      <c r="C428" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E428" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.translation.scripts[].fonts, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F428" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scriptFonts</t>
+        </is>
+      </c>
+      <c r="B429" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">script</t>
+        </is>
+      </c>
+      <c r="C429" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D429" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E429" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'scripts' this row belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scriptFonts</t>
+        </is>
+      </c>
+      <c r="B430" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">file</t>
+        </is>
+      </c>
+      <c r="C430" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D430" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scriptFonts</t>
+        </is>
+      </c>
+      <c r="B431" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">face</t>
+        </is>
+      </c>
+      <c r="C431" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D431" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scriptFonts</t>
+        </is>
+      </c>
+      <c r="B432" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">family</t>
+        </is>
+      </c>
+      <c r="C432" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D432" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scriptFonts</t>
+        </is>
+      </c>
+      <c r="B433" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">style</t>
+        </is>
+      </c>
+      <c r="C433" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D433" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">packs</t>
+        </is>
+      </c>
+      <c r="C434" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E434" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.translation.packs, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">packs</t>
+        </is>
+      </c>
+      <c r="B435" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C435" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D435" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E435" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">packs</t>
+        </is>
+      </c>
+      <c r="B436" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">displayName</t>
+        </is>
+      </c>
+      <c r="C436" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D436" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">packs</t>
+        </is>
+      </c>
+      <c r="B437" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spokenCost</t>
+        </is>
+      </c>
+      <c r="C437" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D437" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">tongues</t>
         </is>
       </c>
-      <c r="B427" s="1" t="inlineStr">
+      <c r="C438" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E438" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B439" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C439" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D439" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E439" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B440" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">displayName</t>
+        </is>
+      </c>
+      <c r="C440" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D440" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B441" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">script</t>
+        </is>
+      </c>
+      <c r="C441" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D441" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E441" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'scripts'</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B442" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pack</t>
+        </is>
+      </c>
+      <c r="C442" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D442" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E442" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'packs'</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B443" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">glyphs</t>
         </is>
       </c>
-      <c r="C427" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D427" s="1" t="inlineStr">
+      <c r="C443" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D443" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
         </is>
@@ -15279,6 +15753,637 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="11" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inherit</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dataOnly</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">default</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21" style="1" customWidth="1"/>
+    <col min="10" max="10" width="18" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stepSet</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">when</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">categories</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">statement</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">truth</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">forms</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jump.source</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jump.link</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hint</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fromDay</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">default</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rules</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RulesViewed</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">default</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">papers</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PapersReceived</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">default</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">read</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PaperRead</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">default</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">identity</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compared</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name|CitizenId|BirthDate</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Field</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Record</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PrimaryName</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">default</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">facts</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compared</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Field</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reference</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FirstUncheckedField</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">default</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">questions</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asked</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">steps.hint.wheel</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">default</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">answers</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compared</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answer</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">default</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dress</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compared</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Culture</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Garment</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reference</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CostumeClaimed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rules</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RulesViewed</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">papers</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PapersReceived</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">read</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PaperRead</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">identity</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compared</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name|CitizenId|BirthDate</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Field</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Record</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PrimaryName</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">facts</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compared</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Field</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reference</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FirstUncheckedField</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">questions</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asked</t>
+        </is>
+      </c>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">steps.hint.wheel</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">answers</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compared</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answer</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dress</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compared</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Culture</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Garment</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reference</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CostumeClaimed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">returnOrder</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Compared</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Destination|Incident</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Field</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paper</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dates</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PaperRead</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-630|TC-610</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Documents</t>
+        </is>
+      </c>
+      <c r="K19">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
     <col min="1" max="1" width="9" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" customWidth="1"/>
     <col min="3" max="3" width="20" style="1" customWidth="1"/>
@@ -15399,7 +16504,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -15429,7 +16534,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -15471,7 +16576,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -15573,7 +16678,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -15630,137 +16735,6 @@
       <c r="C3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">hatshepsut</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="8" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fromDay</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">untilDay</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">flag</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">from</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">subject</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welcome</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Customs Directorate</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Welcome to Desk 3</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="60" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mail</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welcome</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Welcome to Temporal Customs. Every traveller at your desk wants to depart for the past; your desk decides who goes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welcome</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Check each paper against the Citizen Records and the reference books, log every deviation before you deny, and follow the day's directives.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welcome</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Your pay is credited when each shift ends. Your Citizen Account holds your statement. Departures are voluntary.</t>
         </is>
       </c>
     </row>
@@ -15816,6 +16790,137 @@
 </file>
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="8" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fromDay</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">untilDay</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flag</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subject</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welcome</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customs Directorate</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Welcome to Desk 3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="60" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mail</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welcome</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Welcome to Temporal Customs. Every traveller at your desk wants to depart for the past; your desk decides who goes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welcome</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check each paper against the Citizen Records and the reference books, log every deviation before you deny, and follow the day's directives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welcome</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your pay is credited when each shift ends. Your Citizen Account holds your statement. Departures are voluntary.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -15923,7 +17028,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -16010,7 +17115,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -16098,7 +17203,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -16127,113 +17232,6 @@
       <c r="D1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">style</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="11" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hex</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wallpaper</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#3B73BD</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chrome</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#2157DB</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="11" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">role</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fill</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ink</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Panel</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#171C29FA</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#FFFFFF</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">StartMenu</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#1A1F2EF7</t>
         </is>
       </c>
     </row>
@@ -16264,24 +17262,24 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">skyTop</t>
+          <t xml:space="preserve">wallpaper</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">#336EC2</t>
+          <t xml:space="preserve">#3B73BD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">skyBottom</t>
+          <t xml:space="preserve">chrome</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">#C7E6FF</t>
+          <t xml:space="preserve">#2157DB</t>
         </is>
       </c>
     </row>
@@ -16290,6 +17288,113 @@
 </file>
 
 <file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">role</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fill</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ink</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panel</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#171C29FA</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#FFFFFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StartMenu</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#1A1F2EF7</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hex</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skyTop</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#336EC2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skyBottom</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#C7E6FF</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -16362,1032 +17467,6 @@
       <c r="D3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Flavour</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">language</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rtl</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22" style="1" customWidth="1"/>
-    <col min="3" max="3" width="42" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">language</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">key</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">accept</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">قبول</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deny</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">رفض</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taskbar.start</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ابدأ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">startmenu.settings</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الإعدادات</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">startmenu.screenOff</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">إطفاء الشاشة</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">startmenu.quit</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">إنهاء اللعبة</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">briefing.masthead</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">صحيفة الزمن</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">briefing.start</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ابدأ المناوبة</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">results.masthead</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">سجل المناوبة — الطبعة المسائية</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">results.goHome</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">إلى البيت</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">records.search</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بحث</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compare.match</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تطابق</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compare.mismatch</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">عدم تطابق</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">citation.title</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">إشعار انحراف زمني</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">citation.acknowledge</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تم الاطلاع</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">window.settings</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الإعدادات</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.internet</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الإنترنت</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.notes</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ملاحظات</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.investigation</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">التحقيق</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.mail</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">البريد</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.account</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">حساب المواطن</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.settings</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الإعدادات</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tray.day</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اليوم {0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tray.stability</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الاستقرار: {0:0}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taskbar.desk</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">العودة إلى المكتب</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">briefing.title</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اليوم {0} — الإحاطة الصباحية</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">results.title</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اليوم {0} — تقرير المناوبة</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ar</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">briefing.newsHeader</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">— أخبار الخط الزمني —</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">accept</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ΕΓΚΡΙΣΗ</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deny</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ΑΠΟΡΡΙΨΗ</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taskbar.start</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">έναρξη</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">startmenu.settings</t>
-        </is>
-      </c>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ρυθμίσεις</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">startmenu.screenOff</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Σβήσιμο οθόνης</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">startmenu.quit</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Έξοδος από το παιχνίδι</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">briefing.masthead</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Η ΧΡΟΝΙΚΗ ΕΦΗΜΕΡΙΔΑ</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">briefing.start</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ΕΝΑΡΞΗ ΒΑΡΔΙΑΣ</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">results.masthead</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ΗΜΕΡΟΛΟΓΙΟ ΒΑΡΔΙΑΣ — ΑΠΟΓΕΥΜΑΤΙΝΗ ΕΚΔΟΣΗ</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">results.goHome</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ΣΠΙΤΙ</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">records.search</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ΑΝΑΖΗΤΗΣΗ</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compare.match</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ΤΑΙΡΙΑΖΕΙ</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compare.mismatch</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ΔΕΝ ΤΑΙΡΙΑΖΕΙ</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">citation.title</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ΕΙΔΟΠΟΙΗΣΗ ΧΡΟΝΙΚΗΣ ΑΠΟΚΛΙΣΗΣ</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">citation.acknowledge</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ελήφθη</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">window.settings</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ρυθμίσεις</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.internet</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Διαδίκτυο</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.notes</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Σημειώσεις</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.investigation</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Έρευνα</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.mail</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Αλληλογραφία</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.account</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Λογαριασμός πολίτη</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">icon.settings</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ρυθμίσεις</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tray.day</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ημέρα {0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tray.stability</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Σταθερότητα: {0:0}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">taskbar.desk</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt; Γραφείο</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">briefing.title</t>
-        </is>
-      </c>
-      <c r="C55" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ημέρα {0} — Πρωινή ενημέρωση</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">results.title</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ημέρα {0} — Αναφορά βάρδιας</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">el</t>
-        </is>
-      </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">briefing.newsHeader</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">— ΕΙΔΗΣΕΙΣ ΧΡΟΝΟΓΡΑΜΜΗΣ —</t>
         </is>
       </c>
     </row>
@@ -17444,6 +17523,1032 @@
 </file>
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">language</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rtl</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22" style="1" customWidth="1"/>
+    <col min="3" max="3" width="42" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">language</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">key</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accept</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">قبول</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deny</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">رفض</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taskbar.start</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ابدأ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">startmenu.settings</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الإعدادات</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">startmenu.screenOff</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إطفاء الشاشة</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">startmenu.quit</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إنهاء اللعبة</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">briefing.masthead</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">صحيفة الزمن</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">briefing.start</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ابدأ المناوبة</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">results.masthead</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سجل المناوبة — الطبعة المسائية</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">results.goHome</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إلى البيت</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">records.search</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بحث</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compare.match</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تطابق</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compare.mismatch</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عدم تطابق</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation.title</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">إشعار انحراف زمني</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation.acknowledge</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تم الاطلاع</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">window.settings</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الإعدادات</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icon.internet</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الإنترنت</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icon.notes</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ملاحظات</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icon.investigation</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">التحقيق</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icon.mail</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">البريد</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icon.account</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حساب المواطن</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icon.settings</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الإعدادات</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tray.day</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اليوم {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tray.stability</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الاستقرار: {0:0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taskbar.desk</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">العودة إلى المكتب</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">briefing.title</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اليوم {0} — الإحاطة الصباحية</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">results.title</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اليوم {0} — تقرير المناوبة</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ar</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">briefing.newsHeader</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— أخبار الخط الزمني —</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accept</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΕΓΚΡΙΣΗ</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deny</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΑΠΟΡΡΙΨΗ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taskbar.start</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">έναρξη</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">startmenu.settings</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ρυθμίσεις</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">startmenu.screenOff</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Σβήσιμο οθόνης</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">startmenu.quit</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Έξοδος από το παιχνίδι</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">briefing.masthead</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Η ΧΡΟΝΙΚΗ ΕΦΗΜΕΡΙΔΑ</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">briefing.start</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΕΝΑΡΞΗ ΒΑΡΔΙΑΣ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">results.masthead</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΗΜΕΡΟΛΟΓΙΟ ΒΑΡΔΙΑΣ — ΑΠΟΓΕΥΜΑΤΙΝΗ ΕΚΔΟΣΗ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">results.goHome</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΣΠΙΤΙ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">records.search</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΑΝΑΖΗΤΗΣΗ</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compare.match</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΤΑΙΡΙΑΖΕΙ</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compare.mismatch</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΔΕΝ ΤΑΙΡΙΑΖΕΙ</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation.title</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ΕΙΔΟΠΟΙΗΣΗ ΧΡΟΝΙΚΗΣ ΑΠΟΚΛΙΣΗΣ</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation.acknowledge</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ελήφθη</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">window.settings</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ρυθμίσεις</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icon.internet</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Διαδίκτυο</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icon.notes</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Σημειώσεις</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icon.investigation</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Έρευνα</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icon.mail</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Αλληλογραφία</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icon.account</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Λογαριασμός πολίτη</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icon.settings</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ρυθμίσεις</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tray.day</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ημέρα {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tray.stability</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Σταθερότητα: {0:0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taskbar.desk</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt; Γραφείο</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">briefing.title</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ημέρα {0} — Πρωινή ενημέρωση</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">results.title</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ημέρα {0} — Αναφορά βάρδιας</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">briefing.newsHeader</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">— ΕΙΔΗΣΕΙΣ ΧΡΟΝΟΓΡΑΜΜΗΣ —</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -17555,7 +18660,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -17599,7 +18704,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -17641,7 +18746,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -17701,7 +18806,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -4476,7 +4476,7 @@
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countries</t>
+          <t xml:space="preserve">lies</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -4491,7 +4491,12 @@
       </c>
       <c r="E187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">each item names a row of 'countries'; separate items with |</t>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F187" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the lies enabled this day (FalseOrigin, PoorPosingAsRich, DoctoredIdentity); a traveller draws among those that fit their kind</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4508,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rules</t>
+          <t xml:space="preserve">countries</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -4518,7 +4523,7 @@
       </c>
       <c r="E188" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">each item names a row of 'rules'; separate items with |</t>
+          <t xml:space="preserve">each item names a row of 'countries'; separate items with |</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4535,7 @@
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">rules</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -4545,12 +4550,7 @@
       </c>
       <c r="E189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">each item names a row of 'premades'; separate items with |</t>
-        </is>
-      </c>
-      <c r="F189" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">premades that may roll this day</t>
+          <t xml:space="preserve">each item names a row of 'rules'; separate items with |</t>
         </is>
       </c>
     </row>
@@ -4562,17 +4562,27 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeChance</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E190" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">each item names a row of 'premades'; separate items with |</t>
+        </is>
+      </c>
+      <c r="F190" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">premades that may roll this day</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4594,7 @@
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">costumeErrorChance</t>
+          <t xml:space="preserve">premadeChance</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
@@ -4595,33 +4605,33 @@
       <c r="D191" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F191" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chance per 2150 citizen of a costume error (0 before the dress rule's first day)</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayKinds</t>
+          <t xml:space="preserve">days</t>
+        </is>
+      </c>
+      <c r="B192" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">costumeErrorChance</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E192" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.days[].kinds, in order; the first column names the parent row</t>
+          <t xml:space="preserve">decimal</t>
+        </is>
+      </c>
+      <c r="D192" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F192" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the day's traveller mix: each kind's weight</t>
+          <t xml:space="preserve">chance per 2150 citizen of a costume error (0 before the dress rule's first day)</t>
         </is>
       </c>
     </row>
@@ -4631,24 +4641,19 @@
           <t xml:space="preserve">dayKinds</t>
         </is>
       </c>
-      <c r="B193" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">day</t>
-        </is>
-      </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D193" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.days[].kinds, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F193" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the day's traveller mix: each kind's weight</t>
         </is>
       </c>
     </row>
@@ -4660,12 +4665,12 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">day</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr">
@@ -4675,7 +4680,7 @@
       </c>
       <c r="E194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
+          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -4687,34 +4692,44 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E195" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayEras</t>
+          <t xml:space="preserve">dayKinds</t>
+        </is>
+      </c>
+      <c r="B196" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weight</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E196" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.days[].eras, in order; the first column names the parent row</t>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D196" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -4724,24 +4739,14 @@
           <t xml:space="preserve">dayEras</t>
         </is>
       </c>
-      <c r="B197" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">day</t>
-        </is>
-      </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D197" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E197" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.days[].eras, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -4753,22 +4758,22 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">day</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'eras'</t>
+          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -4780,34 +4785,44 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E199" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'eras'</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayForced</t>
+          <t xml:space="preserve">dayEras</t>
+        </is>
+      </c>
+      <c r="B200" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weight</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E200" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.days[].forced, in order; the first column names the parent row</t>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D200" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -4817,24 +4832,14 @@
           <t xml:space="preserve">dayForced</t>
         </is>
       </c>
-      <c r="B201" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">day</t>
-        </is>
-      </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D201" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.days[].forced, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -4846,17 +4851,22 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">slot</t>
+          <t xml:space="preserve">day</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E202" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -4868,22 +4878,17 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premade</t>
+          <t xml:space="preserve">slot</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E203" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'premades'</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4900,7 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">blueprint</t>
+          <t xml:space="preserve">premade</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
@@ -4906,28 +4911,33 @@
       <c r="D204" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E204" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'premades'</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interview</t>
+          <t xml:space="preserve">dayForced</t>
+        </is>
+      </c>
+      <c r="B205" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blueprint</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E205" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.interview</t>
-        </is>
-      </c>
-      <c r="F205" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the interview's wording</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D205" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -4937,19 +4947,19 @@
           <t xml:space="preserve">interview</t>
         </is>
       </c>
-      <c r="B206" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deskName</t>
-        </is>
-      </c>
       <c r="C206" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D206" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E206" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.interview</t>
+        </is>
+      </c>
+      <c r="F206" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the interview's wording</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4971,7 @@
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">opener</t>
+          <t xml:space="preserve">deskName</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr">
@@ -4983,7 +4993,7 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">openerLegendary</t>
+          <t xml:space="preserve">opener</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
@@ -5005,7 +5015,7 @@
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificMale</t>
+          <t xml:space="preserve">openerLegendary</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr">
@@ -5027,7 +5037,7 @@
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificFemale</t>
+          <t xml:space="preserve">honorificMale</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
@@ -5049,7 +5059,7 @@
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificUnknown</t>
+          <t xml:space="preserve">honorificFemale</t>
         </is>
       </c>
       <c r="C211" s="1" t="inlineStr">
@@ -5071,7 +5081,7 @@
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">requestLabel</t>
+          <t xml:space="preserve">honorificUnknown</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
@@ -5093,7 +5103,7 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">papersLabel</t>
+          <t xml:space="preserve">requestLabel</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
@@ -5104,11 +5114,6 @@
       <c r="D213" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F213" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the hub entry that opens the papers menu</t>
         </is>
       </c>
     </row>
@@ -5120,7 +5125,7 @@
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">requestPrompt</t>
+          <t xml:space="preserve">papersLabel</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
@@ -5131,6 +5136,11 @@
       <c r="D214" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F214" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the hub entry that opens the papers menu</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5152,7 @@
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">requestReply</t>
+          <t xml:space="preserve">requestPrompt</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
@@ -5164,7 +5174,7 @@
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">askLabel</t>
+          <t xml:space="preserve">requestReply</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
@@ -5186,7 +5196,7 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">backLabel</t>
+          <t xml:space="preserve">askLabel</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
@@ -5208,7 +5218,7 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">smallTalkLabel</t>
+          <t xml:space="preserve">backLabel</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
@@ -5230,7 +5240,7 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">smallTalkPrompt</t>
+          <t xml:space="preserve">smallTalkLabel</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr">
@@ -5252,17 +5262,17 @@
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">menuCapacity</t>
+          <t xml:space="preserve">smallTalkPrompt</t>
         </is>
       </c>
       <c r="C220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5284,7 @@
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">maxLineChars</t>
+          <t xml:space="preserve">menuCapacity</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr">
@@ -5296,39 +5306,39 @@
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lookLabel</t>
+          <t xml:space="preserve">maxLineChars</t>
         </is>
       </c>
       <c r="C222" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D222" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">claims</t>
+          <t xml:space="preserve">interview</t>
+        </is>
+      </c>
+      <c r="B223" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lookLabel</t>
         </is>
       </c>
       <c r="C223" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E223" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.interview.claims, in order</t>
-        </is>
-      </c>
-      <c r="F223" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the claim per traveller kind ({place}): one row per kind a blueprint makes</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D223" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5338,24 +5348,19 @@
           <t xml:space="preserve">claims</t>
         </is>
       </c>
-      <c r="B224" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kind</t>
-        </is>
-      </c>
       <c r="C224" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D224" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E224" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
+          <t xml:space="preserve">one row per item of the list $.interview.claims, in order</t>
+        </is>
+      </c>
+      <c r="F224" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the claim per traveller kind ({place}): one row per kind a blueprint makes</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5372,7 @@
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C225" s="1" t="inlineStr">
@@ -5377,29 +5382,34 @@
       </c>
       <c r="D225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E225" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interviewRequests</t>
+          <t xml:space="preserve">claims</t>
+        </is>
+      </c>
+      <c r="B226" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C226" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E226" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.interview.requests, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F226" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spoken requests: the wheel entry, the desk's prompt and the traveller's reply</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D226" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5409,24 +5419,19 @@
           <t xml:space="preserve">interviewRequests</t>
         </is>
       </c>
-      <c r="B227" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C227" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D227" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E227" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.interview.requests, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F227" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spoken requests: the wheel entry, the desk's prompt and the traveller's reply</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5443,7 @@
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C228" s="1" t="inlineStr">
@@ -5448,7 +5453,12 @@
       </c>
       <c r="D228" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E228" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5470,7 @@
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C229" s="1" t="inlineStr">
@@ -5482,7 +5492,7 @@
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">reply</t>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C230" s="1" t="inlineStr">
@@ -5499,17 +5509,22 @@
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
+          <t xml:space="preserve">interviewRequests</t>
+        </is>
+      </c>
+      <c r="B231" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reply</t>
         </is>
       </c>
       <c r="C231" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E231" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.questions, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D231" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5519,24 +5534,14 @@
           <t xml:space="preserve">questions</t>
         </is>
       </c>
-      <c r="B232" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C232" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D232" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E232" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.questions, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5553,7 @@
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C233" s="1" t="inlineStr">
@@ -5558,7 +5563,12 @@
       </c>
       <c r="D233" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E233" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5580,7 @@
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C234" s="1" t="inlineStr">
@@ -5592,7 +5602,7 @@
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C235" s="1" t="inlineStr">
@@ -5614,7 +5624,7 @@
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C236" s="1" t="inlineStr">
@@ -5636,17 +5646,17 @@
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">answer</t>
         </is>
       </c>
       <c r="C237" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D237" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5658,39 +5668,39 @@
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">announce</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questions</t>
+        </is>
+      </c>
+      <c r="B239" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">announce</t>
         </is>
       </c>
       <c r="C239" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E239" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.questions[].conditions, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F239" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all must pass</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D239" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5700,24 +5710,19 @@
           <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
-      <c r="B240" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">question</t>
-        </is>
-      </c>
       <c r="C240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D240" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.questions[].conditions, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F240" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all must pass</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5734,22 @@
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">question</t>
         </is>
       </c>
       <c r="C241" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D241" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E241" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5761,7 @@
       </c>
       <c r="B242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C242" s="1" t="inlineStr">
@@ -5761,7 +5771,7 @@
       </c>
       <c r="D242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -5773,17 +5783,17 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5795,22 +5805,17 @@
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E244" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5827,7 @@
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C245" s="1" t="inlineStr">
@@ -5837,7 +5842,7 @@
       </c>
       <c r="E245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5854,7 @@
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C246" s="1" t="inlineStr">
@@ -5864,29 +5869,34 @@
       </c>
       <c r="E246" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
+          <t xml:space="preserve">questionConditions</t>
+        </is>
+      </c>
+      <c r="B247" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D247" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.questions[].overrides, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F247" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the wording in one era</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
@@ -5896,24 +5906,19 @@
           <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
-      <c r="B248" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">question</t>
-        </is>
-      </c>
       <c r="C248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D248" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.questions[].overrides, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F248" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the wording in one era</t>
         </is>
       </c>
     </row>
@@ -5925,22 +5930,22 @@
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">question</t>
         </is>
       </c>
       <c r="C249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'eras'</t>
+          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -5952,7 +5957,7 @@
       </c>
       <c r="B250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C250" s="1" t="inlineStr">
@@ -5963,6 +5968,11 @@
       <c r="D250" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E250" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'eras'</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5984,7 @@
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C251" s="1" t="inlineStr">
@@ -5991,22 +6001,22 @@
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
+          <t xml:space="preserve">questionOverrides</t>
+        </is>
+      </c>
+      <c r="B252" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">answer</t>
         </is>
       </c>
       <c r="C252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E252" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F252" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">narrative dialogs: nodes, their lines and the player's choices</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D252" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6016,24 +6026,19 @@
           <t xml:space="preserve">dialogs</t>
         </is>
       </c>
-      <c r="B253" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D253" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F253" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrative dialogs: nodes, their lines and the player's choices</t>
         </is>
       </c>
     </row>
@@ -6045,7 +6050,7 @@
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C254" s="1" t="inlineStr">
@@ -6055,12 +6060,12 @@
       </c>
       <c r="D254" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F254" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the wheel entry</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E254" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -6072,39 +6077,44 @@
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">repeatable</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F255" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the wheel entry</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
+          <t xml:space="preserve">dialogs</t>
+        </is>
+      </c>
+      <c r="B256" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repeatable</t>
         </is>
       </c>
       <c r="C256" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E256" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].conditions, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F256" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all must pass</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D256" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -6114,24 +6124,19 @@
           <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
-      <c r="B257" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dialog</t>
-        </is>
-      </c>
       <c r="C257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D257" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].conditions, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F257" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all must pass</t>
         </is>
       </c>
     </row>
@@ -6143,17 +6148,22 @@
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D258" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E258" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6165,7 +6175,7 @@
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C259" s="1" t="inlineStr">
@@ -6175,7 +6185,7 @@
       </c>
       <c r="D259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -6187,17 +6197,17 @@
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6209,22 +6219,17 @@
       </c>
       <c r="B261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E261" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6241,7 @@
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C262" s="1" t="inlineStr">
@@ -6251,7 +6256,7 @@
       </c>
       <c r="E262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6268,7 @@
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C263" s="1" t="inlineStr">
@@ -6278,24 +6283,34 @@
       </c>
       <c r="E263" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogNodes</t>
+          <t xml:space="preserve">dialogConditions</t>
+        </is>
+      </c>
+      <c r="B264" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D264" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes, in order; a row's name is id, unique per parent row; the first column names the parent row</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
@@ -6305,24 +6320,14 @@
           <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
-      <c r="B265" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dialog</t>
-        </is>
-      </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D265" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes, in order; a row's name is id, unique per parent row; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -6334,12 +6339,12 @@
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D266" s="1" t="inlineStr">
@@ -6349,24 +6354,34 @@
       </c>
       <c r="E266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
+          <t xml:space="preserve">dialogNodes</t>
+        </is>
+      </c>
+      <c r="B267" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D267" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].lines, in order; the first columns name the parent row</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -6376,24 +6391,14 @@
           <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
-      <c r="B268" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dialog</t>
-        </is>
-      </c>
       <c r="C268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D268" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].lines, in order; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -6405,7 +6410,7 @@
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C269" s="1" t="inlineStr">
@@ -6420,7 +6425,7 @@
       </c>
       <c r="E269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6432,17 +6437,22 @@
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E270" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6464,7 @@
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">speaker</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
@@ -6476,7 +6486,7 @@
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">expression</t>
+          <t xml:space="preserve">speaker</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
@@ -6486,7 +6496,7 @@
       </c>
       <c r="D272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6508,7 @@
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">expression</t>
         </is>
       </c>
       <c r="C273" s="1" t="inlineStr">
@@ -6508,24 +6518,29 @@
       </c>
       <c r="D273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">dialogLines</t>
+        </is>
+      </c>
+      <c r="B274" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E274" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices, in order; a row's name is id, unique per parent row; the first columns name the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D274" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6535,24 +6550,14 @@
           <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
-      <c r="B275" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dialog</t>
-        </is>
-      </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D275" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices, in order; a row's name is id, unique per parent row; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -6564,7 +6569,7 @@
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C276" s="1" t="inlineStr">
@@ -6579,7 +6584,7 @@
       </c>
       <c r="E276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6591,12 +6596,12 @@
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D277" s="1" t="inlineStr">
@@ -6606,7 +6611,7 @@
       </c>
       <c r="E277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6623,7 @@
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C278" s="1" t="inlineStr">
@@ -6628,7 +6633,12 @@
       </c>
       <c r="D278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E278" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -6640,7 +6650,7 @@
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">next</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
@@ -6651,11 +6661,6 @@
       <c r="D279" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F279" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the node it leads to (blank: the dialog ends)</t>
         </is>
       </c>
     </row>
@@ -6667,7 +6672,7 @@
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">effect</t>
+          <t xml:space="preserve">next</t>
         </is>
       </c>
       <c r="C280" s="1" t="inlineStr">
@@ -6678,23 +6683,33 @@
       <c r="D280" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F280" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the node it leads to (blank: the dialog ends)</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">dialogChoices</t>
+        </is>
+      </c>
+      <c r="B281" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">effect</t>
         </is>
       </c>
       <c r="C281" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E281" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices[].lines, in order; the first columns name the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D281" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6704,24 +6719,14 @@
           <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
-      <c r="B282" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dialog</t>
-        </is>
-      </c>
       <c r="C282" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D282" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E282" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices[].lines, in order; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -6733,7 +6738,7 @@
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
@@ -6748,7 +6753,7 @@
       </c>
       <c r="E283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6760,7 +6765,7 @@
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choice</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C284" s="1" t="inlineStr">
@@ -6775,7 +6780,7 @@
       </c>
       <c r="E284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogChoices' this row belongs to</t>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6787,17 +6792,22 @@
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">choice</t>
         </is>
       </c>
       <c r="C285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E285" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogChoices' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6819,7 @@
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">speaker</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C286" s="1" t="inlineStr">
@@ -6831,7 +6841,7 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">expression</t>
+          <t xml:space="preserve">speaker</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
@@ -6841,7 +6851,7 @@
       </c>
       <c r="D287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6863,7 @@
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">expression</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr">
@@ -6863,29 +6873,29 @@
       </c>
       <c r="D288" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">choiceLines</t>
+        </is>
+      </c>
+      <c r="B289" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C289" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E289" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.premades, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F289" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">premade characters: real people and written stories</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D289" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6895,24 +6905,19 @@
           <t xml:space="preserve">premades</t>
         </is>
       </c>
-      <c r="B290" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D290" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.premades, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F290" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">premade characters: real people and written stories</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6929,7 @@
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C291" s="1" t="inlineStr">
@@ -6934,7 +6939,12 @@
       </c>
       <c r="D291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E291" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6956,7 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gender</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
@@ -6968,7 +6978,7 @@
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">gender</t>
         </is>
       </c>
       <c r="C293" s="1" t="inlineStr">
@@ -6979,11 +6989,6 @@
       <c r="D293" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E293" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -6995,7 +7000,7 @@
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">truePlace</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C294" s="1" t="inlineStr">
@@ -7011,11 +7016,6 @@
       <c r="E294" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">names a row of 'places'</t>
-        </is>
-      </c>
-      <c r="F294" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">where they really come from (blank: honest)</t>
         </is>
       </c>
     </row>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">birthDate</t>
+          <t xml:space="preserve">truePlace</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
@@ -7038,6 +7038,16 @@
       <c r="D295" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E295" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
+        </is>
+      </c>
+      <c r="F295" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">where they really come from (blank: honest)</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7059,7 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">archetype</t>
+          <t xml:space="preserve">birthDate</t>
         </is>
       </c>
       <c r="C296" s="1" t="inlineStr">
@@ -7071,7 +7081,7 @@
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">intro</t>
+          <t xml:space="preserve">archetype</t>
         </is>
       </c>
       <c r="C297" s="1" t="inlineStr">
@@ -7093,7 +7103,7 @@
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">recordNote</t>
+          <t xml:space="preserve">intro</t>
         </is>
       </c>
       <c r="C298" s="1" t="inlineStr">
@@ -7115,7 +7125,7 @@
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">recordNote</t>
         </is>
       </c>
       <c r="C299" s="1" t="inlineStr">
@@ -7126,11 +7136,6 @@
       <c r="D299" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E299" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'dialogs'</t>
         </is>
       </c>
     </row>
@@ -7142,34 +7147,44 @@
       </c>
       <c r="B300" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">repeatable</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C300" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D300" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E300" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'dialogs'</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">premades</t>
+        </is>
+      </c>
+      <c r="B301" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repeatable</t>
         </is>
       </c>
       <c r="C301" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E301" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.premades[].impacts, in order; the first column names the parent row</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D301" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -7179,24 +7194,14 @@
           <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
-      <c r="B302" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">premade</t>
-        </is>
-      </c>
       <c r="C302" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D302" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E302" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'premades' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.premades[].impacts, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -7208,22 +7213,22 @@
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">premade</t>
         </is>
       </c>
       <c r="C303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">names the row of 'premades' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7235,17 +7240,22 @@
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">onCorrect</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E304" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7267,7 @@
       </c>
       <c r="B305" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">onWrong</t>
+          <t xml:space="preserve">onCorrect</t>
         </is>
       </c>
       <c r="C305" s="1" t="inlineStr">
@@ -7279,34 +7289,39 @@
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">skipNationScore</t>
+          <t xml:space="preserve">onWrong</t>
         </is>
       </c>
       <c r="C306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">premadeImpacts</t>
+        </is>
+      </c>
+      <c r="B307" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skipNationScore</t>
         </is>
       </c>
       <c r="C307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E307" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.history</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D307" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -7316,19 +7331,14 @@
           <t xml:space="preserve">history</t>
         </is>
       </c>
-      <c r="B308" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lines.leaderGained</t>
-        </is>
-      </c>
       <c r="C308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D308" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E308" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.history</t>
         </is>
       </c>
     </row>
@@ -7340,7 +7350,7 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.leaderLost</t>
+          <t xml:space="preserve">lines.leaderGained</t>
         </is>
       </c>
       <c r="C309" s="1" t="inlineStr">
@@ -7362,7 +7372,7 @@
       </c>
       <c r="B310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.carry</t>
+          <t xml:space="preserve">lines.leaderLost</t>
         </is>
       </c>
       <c r="C310" s="1" t="inlineStr">
@@ -7384,7 +7394,7 @@
       </c>
       <c r="B311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.dominant</t>
+          <t xml:space="preserve">lines.carry</t>
         </is>
       </c>
       <c r="C311" s="1" t="inlineStr">
@@ -7395,11 +7405,6 @@
       <c r="D311" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F311" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">an attribute becomes dominant in a place: {attribute} and {place}</t>
         </is>
       </c>
     </row>
@@ -7411,7 +7416,7 @@
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.panic</t>
+          <t xml:space="preserve">lines.dominant</t>
         </is>
       </c>
       <c r="C312" s="1" t="inlineStr">
@@ -7426,29 +7431,34 @@
       </c>
       <c r="F312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">an accepted costume error caused a panic: {place} and {value} (the wrong item)</t>
+          <t xml:space="preserve">an attribute becomes dominant in a place: {attribute} and {place}</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyRules</t>
+          <t xml:space="preserve">history</t>
+        </is>
+      </c>
+      <c r="B313" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lines.panic</t>
         </is>
       </c>
       <c r="C313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E313" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D313" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history rules: when their conditions pass at night they rewrite a place's fact</t>
+          <t xml:space="preserve">an accepted costume error caused a panic: {place} and {value} (the wrong item)</t>
         </is>
       </c>
     </row>
@@ -7458,24 +7468,19 @@
           <t xml:space="preserve">historyRules</t>
         </is>
       </c>
-      <c r="B314" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C314" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D314" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E314" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.history.rules, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F314" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">history rules: when their conditions pass at night they rewrite a place's fact</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7492,7 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C315" s="1" t="inlineStr">
@@ -7497,7 +7502,12 @@
       </c>
       <c r="D315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E315" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -7509,7 +7519,7 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">news</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C316" s="1" t="inlineStr">
@@ -7526,17 +7536,22 @@
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
+          <t xml:space="preserve">historyRules</t>
+        </is>
+      </c>
+      <c r="B317" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">news</t>
         </is>
       </c>
       <c r="C317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E317" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules[].conditions, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D317" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7546,24 +7561,14 @@
           <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
-      <c r="B318" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rule</t>
-        </is>
-      </c>
       <c r="C318" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D318" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E318" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.history.rules[].conditions, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -7575,17 +7580,22 @@
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">rule</t>
         </is>
       </c>
       <c r="C319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D319" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E319" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7607,7 @@
       </c>
       <c r="B320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C320" s="1" t="inlineStr">
@@ -7607,7 +7617,7 @@
       </c>
       <c r="D320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -7619,7 +7629,7 @@
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C321" s="1" t="inlineStr">
@@ -7630,11 +7640,6 @@
       <c r="D321" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E321" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
@@ -7646,7 +7651,7 @@
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C322" s="1" t="inlineStr">
@@ -7661,7 +7666,7 @@
       </c>
       <c r="E322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7678,7 @@
       </c>
       <c r="B323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C323" s="1" t="inlineStr">
@@ -7688,7 +7693,7 @@
       </c>
       <c r="E323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -7700,34 +7705,44 @@
       </c>
       <c r="B324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (left out of the JSON)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E324" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
+          <t xml:space="preserve">historyConditions</t>
+        </is>
+      </c>
+      <c r="B325" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E325" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules[].edits, in order; the first column names the parent row</t>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D325" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -7737,24 +7752,14 @@
           <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
-      <c r="B326" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rule</t>
-        </is>
-      </c>
       <c r="C326" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D326" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E326" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.history.rules[].edits, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -7766,22 +7771,22 @@
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">rule</t>
         </is>
       </c>
       <c r="C327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7798,7 @@
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C328" s="1" t="inlineStr">
@@ -7804,6 +7809,11 @@
       <c r="D328" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E328" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7825,7 @@
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C329" s="1" t="inlineStr">
@@ -7832,22 +7842,22 @@
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">newsDebt</t>
+          <t xml:space="preserve">historyEdits</t>
+        </is>
+      </c>
+      <c r="B330" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
         </is>
       </c>
       <c r="C330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Values</t>
-        </is>
-      </c>
-      <c r="E330" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.news.debt, in order</t>
-        </is>
-      </c>
-      <c r="F330" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the morning paper's debt lines: one a day, in a shuffled order per run</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D330" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7857,36 +7867,41 @@
           <t xml:space="preserve">newsDebt</t>
         </is>
       </c>
-      <c r="B331" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
       <c r="C331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D331" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Values</t>
+        </is>
+      </c>
+      <c r="E331" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.news.debt, in order</t>
+        </is>
+      </c>
+      <c r="F331" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the morning paper's debt lines: one a day, in a shuffled order per run</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pc</t>
+          <t xml:space="preserve">newsDebt</t>
+        </is>
+      </c>
+      <c r="B332" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E332" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.pc</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D332" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -7896,46 +7911,41 @@
           <t xml:space="preserve">pc</t>
         </is>
       </c>
-      <c r="B333" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ancestry.includePremades</t>
-        </is>
-      </c>
       <c r="C333" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
-        </is>
-      </c>
-      <c r="D333" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="F333" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the premades who are who they claim get cards</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E333" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.pc</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSites</t>
+          <t xml:space="preserve">pc</t>
+        </is>
+      </c>
+      <c r="B334" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ancestry.includePremades</t>
         </is>
       </c>
       <c r="C334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E334" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.sites, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D334" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="F334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Internet's sites</t>
+          <t xml:space="preserve">the premades who are who they claim get cards</t>
         </is>
       </c>
     </row>
@@ -7945,24 +7955,19 @@
           <t xml:space="preserve">pcSites</t>
         </is>
       </c>
-      <c r="B335" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D335" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.pc.sites, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F335" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the Internet's sites</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7979,7 @@
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C336" s="1" t="inlineStr">
@@ -7984,17 +7989,12 @@
       </c>
       <c r="D336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: News, History, Ancestry, Static</t>
-        </is>
-      </c>
-      <c r="F336" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the page builder that serves it</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="B337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C337" s="1" t="inlineStr">
@@ -8017,6 +8017,16 @@
       <c r="D337" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E337" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: News, History, Ancestry, Static</t>
+        </is>
+      </c>
+      <c r="F337" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the page builder that serves it</t>
         </is>
       </c>
     </row>
@@ -8028,7 +8038,7 @@
       </c>
       <c r="B338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">domain</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C338" s="1" t="inlineStr">
@@ -8039,11 +8049,6 @@
       <c r="D338" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F338" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chronet://{domain}: lower-case letters, digits, dots and dashes</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8060,7 @@
       </c>
       <c r="B339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">glyph</t>
+          <t xml:space="preserve">domain</t>
         </is>
       </c>
       <c r="C339" s="1" t="inlineStr">
@@ -8070,7 +8075,7 @@
       </c>
       <c r="F339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the start-page tile's art key</t>
+          <t xml:space="preserve">chronet://{domain}: lower-case letters, digits, dots and dashes</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8087,7 @@
       </c>
       <c r="B340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb</t>
+          <t xml:space="preserve">glyph</t>
         </is>
       </c>
       <c r="C340" s="1" t="inlineStr">
@@ -8093,6 +8098,11 @@
       <c r="D340" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F340" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the start-page tile's art key</t>
         </is>
       </c>
     </row>
@@ -8104,44 +8114,44 @@
       </c>
       <c r="B341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">blurb</t>
         </is>
       </c>
       <c r="C341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F341" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the first day it is listed</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPages</t>
+          <t xml:space="preserve">pcSites</t>
+        </is>
+      </c>
+      <c r="B342" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E342" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.pages, in order; a row's name is {site}/{path}, unique</t>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D342" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Static site's authored pages</t>
+          <t xml:space="preserve">the first day it is listed</t>
         </is>
       </c>
     </row>
@@ -8151,24 +8161,19 @@
           <t xml:space="preserve">pcPages</t>
         </is>
       </c>
-      <c r="B343" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">site</t>
-        </is>
-      </c>
       <c r="C343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D343" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name; names a row of 'pcSites'</t>
+          <t xml:space="preserve">one row per item of the list $.pc.pages, in order; a row's name is {site}/{path}, unique</t>
+        </is>
+      </c>
+      <c r="F343" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a Static site's authored pages</t>
         </is>
       </c>
     </row>
@@ -8180,7 +8185,7 @@
       </c>
       <c r="B344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">path</t>
+          <t xml:space="preserve">site</t>
         </is>
       </c>
       <c r="C344" s="1" t="inlineStr">
@@ -8190,17 +8195,12 @@
       </c>
       <c r="D344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
-        </is>
-      </c>
-      <c r="F344" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank: the site's front page</t>
+          <t xml:space="preserve">part of the row's name; names a row of 'pcSites'</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">title</t>
+          <t xml:space="preserve">path</t>
         </is>
       </c>
       <c r="C345" s="1" t="inlineStr">
@@ -8223,23 +8223,38 @@
       <c r="D345" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E345" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
+        </is>
+      </c>
+      <c r="F345" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank: the site's front page</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPageBlocks</t>
+          <t xml:space="preserve">pcPages</t>
+        </is>
+      </c>
+      <c r="B346" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">title</t>
         </is>
       </c>
       <c r="C346" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E346" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.pages[].blocks, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D346" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -8249,24 +8264,14 @@
           <t xml:space="preserve">pcPageBlocks</t>
         </is>
       </c>
-      <c r="B347" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page</t>
-        </is>
-      </c>
       <c r="C347" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D347" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E347" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'pcPages' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.pc.pages[].blocks, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -8278,22 +8283,22 @@
       </c>
       <c r="B348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">page</t>
         </is>
       </c>
       <c r="C348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: Headline, Heading, Paragraph, Note, Link, Box</t>
+          <t xml:space="preserve">names the row of 'pcPages' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8310,7 @@
       </c>
       <c r="B349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C349" s="1" t="inlineStr">
@@ -8316,6 +8321,11 @@
       <c r="D349" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E349" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: Headline, Heading, Paragraph, Note, Link, Box</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8337,7 @@
       </c>
       <c r="B350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">address</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C350" s="1" t="inlineStr">
@@ -8337,12 +8347,7 @@
       </c>
       <c r="D350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="F350" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a Link's site name, domain or chronet:// address</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -8354,49 +8359,54 @@
       </c>
       <c r="B351" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines</t>
+          <t xml:space="preserve">address</t>
         </is>
       </c>
       <c r="C351" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D351" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E351" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="F351" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Box's lines</t>
+          <t xml:space="preserve">a Link's site name, domain or chronet:// address</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPeople</t>
+          <t xml:space="preserve">pcPageBlocks</t>
+        </is>
+      </c>
+      <c r="B352" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lines</t>
         </is>
       </c>
       <c r="C352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text list</t>
+        </is>
+      </c>
+      <c r="D352" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
         </is>
       </c>
       <c r="E352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.ancestry.people, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
       <c r="F352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Lineage Archive's people of the past (no traveller's name)</t>
+          <t xml:space="preserve">a Box's lines</t>
         </is>
       </c>
     </row>
@@ -8406,24 +8416,19 @@
           <t xml:space="preserve">pcPeople</t>
         </is>
       </c>
-      <c r="B353" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C353" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D353" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E353" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.pc.ancestry.people, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F353" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the Lineage Archive's people of the past (no traveller's name)</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8440,7 @@
       </c>
       <c r="B354" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C354" s="1" t="inlineStr">
@@ -8445,7 +8450,12 @@
       </c>
       <c r="D354" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E354" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -8457,7 +8467,7 @@
       </c>
       <c r="B355" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">born</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C355" s="1" t="inlineStr">
@@ -8479,7 +8489,7 @@
       </c>
       <c r="B356" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">died</t>
+          <t xml:space="preserve">born</t>
         </is>
       </c>
       <c r="C356" s="1" t="inlineStr">
@@ -8501,7 +8511,7 @@
       </c>
       <c r="B357" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">died</t>
         </is>
       </c>
       <c r="C357" s="1" t="inlineStr">
@@ -8512,11 +8522,6 @@
       <c r="D357" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E357" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -8528,7 +8533,7 @@
       </c>
       <c r="B358" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">note</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C358" s="1" t="inlineStr">
@@ -8539,28 +8544,33 @@
       <c r="D358" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E358" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcRelations</t>
+          <t xml:space="preserve">pcPeople</t>
+        </is>
+      </c>
+      <c r="B359" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">note</t>
         </is>
       </c>
       <c r="C359" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E359" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.ancestry.relations, in order</t>
-        </is>
-      </c>
-      <c r="F359" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one direction per row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D359" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -8570,24 +8580,19 @@
           <t xml:space="preserve">pcRelations</t>
         </is>
       </c>
-      <c r="B360" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">person</t>
-        </is>
-      </c>
       <c r="C360" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D360" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E360" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.ancestry.relations, in order</t>
         </is>
       </c>
       <c r="F360" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a person's or a premade's id: the card it shows on</t>
+          <t xml:space="preserve">one direction per row</t>
         </is>
       </c>
     </row>
@@ -8599,7 +8604,7 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">person</t>
         </is>
       </c>
       <c r="C361" s="1" t="inlineStr">
@@ -8609,7 +8614,12 @@
       </c>
       <c r="D361" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="F361" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a person's or a premade's id: the card it shows on</t>
         </is>
       </c>
     </row>
@@ -8621,7 +8631,7 @@
       </c>
       <c r="B362" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">other</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C362" s="1" t="inlineStr">
@@ -8631,34 +8641,34 @@
       </c>
       <c r="D362" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="F362" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the other card's id</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMail</t>
+          <t xml:space="preserve">pcRelations</t>
+        </is>
+      </c>
+      <c r="B363" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other</t>
         </is>
       </c>
       <c r="C363" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E363" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.mail, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D363" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="F363" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mail's authored messages</t>
+          <t xml:space="preserve">the other card's id</t>
         </is>
       </c>
     </row>
@@ -8668,24 +8678,19 @@
           <t xml:space="preserve">pcMail</t>
         </is>
       </c>
-      <c r="B364" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D364" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.pc.mail, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F364" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mail's authored messages</t>
         </is>
       </c>
     </row>
@@ -8697,22 +8702,22 @@
       </c>
       <c r="B365" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C365" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D365" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F365" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the day it arrives (its date)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E365" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8729,7 @@
       </c>
       <c r="B366" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">untilDay</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C366" s="1" t="inlineStr">
@@ -8739,7 +8744,7 @@
       </c>
       <c r="F366" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the last day it is in the inbox; 0 keeps it for the run</t>
+          <t xml:space="preserve">the day it arrives (its date)</t>
         </is>
       </c>
     </row>
@@ -8751,22 +8756,22 @@
       </c>
       <c r="B367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flag</t>
+          <t xml:space="preserve">untilDay</t>
         </is>
       </c>
       <c r="C367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a story flag it waits for (blank: none)</t>
+          <t xml:space="preserve">the last day it is in the inbox; 0 keeps it for the run</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8783,7 @@
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">from</t>
+          <t xml:space="preserve">flag</t>
         </is>
       </c>
       <c r="C368" s="1" t="inlineStr">
@@ -8789,6 +8794,11 @@
       <c r="D368" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F368" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a story flag it waits for (blank: none)</t>
         </is>
       </c>
     </row>
@@ -8800,7 +8810,7 @@
       </c>
       <c r="B369" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">subject</t>
+          <t xml:space="preserve">from</t>
         </is>
       </c>
       <c r="C369" s="1" t="inlineStr">
@@ -8817,22 +8827,22 @@
     <row r="370">
       <c r="A370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMailBody</t>
+          <t xml:space="preserve">pcMail</t>
+        </is>
+      </c>
+      <c r="B370" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subject</t>
         </is>
       </c>
       <c r="C370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Values</t>
-        </is>
-      </c>
-      <c r="E370" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.mail[].body, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F370" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its paragraphs</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D370" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -8842,24 +8852,19 @@
           <t xml:space="preserve">pcMailBody</t>
         </is>
       </c>
-      <c r="B371" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mail</t>
-        </is>
-      </c>
       <c r="C371" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D371" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Values</t>
         </is>
       </c>
       <c r="E371" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'pcMail' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.pc.mail[].body, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F371" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its paragraphs</t>
         </is>
       </c>
     </row>
@@ -8871,34 +8876,44 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">mail</t>
         </is>
       </c>
       <c r="C372" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D372" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E372" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'pcMail' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">pcMailBody</t>
+        </is>
+      </c>
+      <c r="B373" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C373" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E373" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.ui</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D373" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -8908,19 +8923,14 @@
           <t xml:space="preserve">ui</t>
         </is>
       </c>
-      <c r="B374" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">readingLanguage</t>
-        </is>
-      </c>
       <c r="C374" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D374" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E374" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.ui</t>
         </is>
       </c>
     </row>
@@ -8932,17 +8942,17 @@
       </c>
       <c r="B375" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">glossPercent</t>
+          <t xml:space="preserve">readingLanguage</t>
         </is>
       </c>
       <c r="C375" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D375" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -8954,12 +8964,12 @@
       </c>
       <c r="B376" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">labelMinScale</t>
+          <t xml:space="preserve">glossPercent</t>
         </is>
       </c>
       <c r="C376" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D376" s="1" t="inlineStr">
@@ -8976,7 +8986,7 @@
       </c>
       <c r="B377" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.text</t>
+          <t xml:space="preserve">labelMinScale</t>
         </is>
       </c>
       <c r="C377" s="1" t="inlineStr">
@@ -8998,7 +9008,7 @@
       </c>
       <c r="B378" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.largeText</t>
+          <t xml:space="preserve">contrast.text</t>
         </is>
       </c>
       <c r="C378" s="1" t="inlineStr">
@@ -9020,7 +9030,7 @@
       </c>
       <c r="B379" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.glyph</t>
+          <t xml:space="preserve">contrast.largeText</t>
         </is>
       </c>
       <c r="C379" s="1" t="inlineStr">
@@ -9042,7 +9052,7 @@
       </c>
       <c r="B380" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.hint</t>
+          <t xml:space="preserve">contrast.glyph</t>
         </is>
       </c>
       <c r="C380" s="1" t="inlineStr">
@@ -9064,7 +9074,7 @@
       </c>
       <c r="B381" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.outline</t>
+          <t xml:space="preserve">contrast.hint</t>
         </is>
       </c>
       <c r="C381" s="1" t="inlineStr">
@@ -9086,7 +9096,7 @@
       </c>
       <c r="B382" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.minTextFillAlpha</t>
+          <t xml:space="preserve">contrast.outline</t>
         </is>
       </c>
       <c r="C382" s="1" t="inlineStr">
@@ -9108,34 +9118,39 @@
       </c>
       <c r="B383" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">latinFallbackFont</t>
+          <t xml:space="preserve">contrast.minTextFillAlpha</t>
         </is>
       </c>
       <c r="C383" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D383" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="B384" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">latinFallbackFont</t>
         </is>
       </c>
       <c r="C384" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E384" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.paletteMap, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D384" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9145,19 +9160,14 @@
           <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
-      <c r="B385" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">role</t>
-        </is>
-      </c>
       <c r="C385" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D385" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E385" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.paletteMap, in order</t>
         </is>
       </c>
     </row>
@@ -9169,7 +9179,7 @@
       </c>
       <c r="B386" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fill</t>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C386" s="1" t="inlineStr">
@@ -9191,17 +9201,17 @@
       </c>
       <c r="B387" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">alpha</t>
+          <t xml:space="preserve">fill</t>
         </is>
       </c>
       <c r="C387" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D387" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9213,17 +9223,17 @@
       </c>
       <c r="B388" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ink</t>
+          <t xml:space="preserve">alpha</t>
         </is>
       </c>
       <c r="C388" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D388" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -9235,7 +9245,7 @@
       </c>
       <c r="B389" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">textClass</t>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C389" s="1" t="inlineStr">
@@ -9252,17 +9262,22 @@
     <row r="390">
       <c r="A390" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">uiPalette</t>
+        </is>
+      </c>
+      <c r="B390" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">textClass</t>
         </is>
       </c>
       <c r="C390" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E390" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.ui.neutral</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D390" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9272,19 +9287,14 @@
           <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
-      <c r="B391" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C391" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D391" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E391" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.ui.neutral</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9306,7 @@
       </c>
       <c r="B392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C392" s="1" t="inlineStr">
@@ -9318,7 +9328,7 @@
       </c>
       <c r="B393" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C393" s="1" t="inlineStr">
@@ -9340,17 +9350,17 @@
       </c>
       <c r="B394" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">runtimeFont</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C394" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D394" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9362,17 +9372,17 @@
       </c>
       <c r="B395" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">headingAdd</t>
+          <t xml:space="preserve">runtimeFont</t>
         </is>
       </c>
       <c r="C395" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D395" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -9384,7 +9394,7 @@
       </c>
       <c r="B396" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">buttonAdd</t>
+          <t xml:space="preserve">headingAdd</t>
         </is>
       </c>
       <c r="C396" s="1" t="inlineStr">
@@ -9406,17 +9416,17 @@
       </c>
       <c r="B397" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">stripItalic</t>
+          <t xml:space="preserve">buttonAdd</t>
         </is>
       </c>
       <c r="C397" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D397" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9428,39 +9438,39 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wallpaper</t>
+          <t xml:space="preserve">stripItalic</t>
         </is>
       </c>
       <c r="C398" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D398" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiNeutral</t>
+        </is>
+      </c>
+      <c r="B399" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wallpaper</t>
         </is>
       </c>
       <c r="C399" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E399" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.fonts, in order</t>
-        </is>
-      </c>
-      <c r="F399" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D399" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9470,19 +9480,19 @@
           <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
-      <c r="B400" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">file</t>
-        </is>
-      </c>
       <c r="C400" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D400" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E400" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.fonts, in order</t>
+        </is>
+      </c>
+      <c r="F400" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
         </is>
       </c>
     </row>
@@ -9494,17 +9504,17 @@
       </c>
       <c r="B401" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">face</t>
+          <t xml:space="preserve">file</t>
         </is>
       </c>
       <c r="C401" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D401" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9516,17 +9526,17 @@
       </c>
       <c r="B402" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">family</t>
+          <t xml:space="preserve">face</t>
         </is>
       </c>
       <c r="C402" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D402" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -9538,7 +9548,7 @@
       </c>
       <c r="B403" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">style</t>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C403" s="1" t="inlineStr">
@@ -9555,17 +9565,22 @@
     <row r="404">
       <c r="A404" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
+          <t xml:space="preserve">neutralFonts</t>
+        </is>
+      </c>
+      <c r="B404" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">style</t>
         </is>
       </c>
       <c r="C404" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E404" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.seeds, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D404" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9575,19 +9590,14 @@
           <t xml:space="preserve">neutralSeeds</t>
         </is>
       </c>
-      <c r="B405" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
       <c r="C405" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D405" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E405" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.seeds, in order</t>
         </is>
       </c>
     </row>
@@ -9599,7 +9609,7 @@
       </c>
       <c r="B406" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hex</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C406" s="1" t="inlineStr">
@@ -9616,17 +9626,22 @@
     <row r="407">
       <c r="A407" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">neutralSeeds</t>
+        </is>
+      </c>
+      <c r="B407" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C407" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E407" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.overrides, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D407" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9636,19 +9651,14 @@
           <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
-      <c r="B408" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">role</t>
-        </is>
-      </c>
       <c r="C408" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D408" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E408" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.overrides, in order</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9670,7 @@
       </c>
       <c r="B409" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fill</t>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C409" s="1" t="inlineStr">
@@ -9682,7 +9692,7 @@
       </c>
       <c r="B410" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ink</t>
+          <t xml:space="preserve">fill</t>
         </is>
       </c>
       <c r="C410" s="1" t="inlineStr">
@@ -9699,17 +9709,22 @@
     <row r="411">
       <c r="A411" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
+          <t xml:space="preserve">neutralOverrides</t>
+        </is>
+      </c>
+      <c r="B411" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C411" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E411" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.art, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D411" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9719,19 +9734,14 @@
           <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
-      <c r="B412" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
       <c r="C412" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D412" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E412" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.art, in order</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9753,7 @@
       </c>
       <c r="B413" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hex</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C413" s="1" t="inlineStr">
@@ -9760,17 +9770,22 @@
     <row r="414">
       <c r="A414" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">neutralArt</t>
+        </is>
+      </c>
+      <c r="B414" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C414" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E414" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.strings, in order; a row's name is key, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D414" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9780,24 +9795,14 @@
           <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
-      <c r="B415" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">key</t>
-        </is>
-      </c>
       <c r="C415" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D415" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E415" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.ui.strings, in order; a row's name is key, unique</t>
         </is>
       </c>
     </row>
@@ -9809,7 +9814,7 @@
       </c>
       <c r="B416" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C416" s="1" t="inlineStr">
@@ -9819,7 +9824,12 @@
       </c>
       <c r="D416" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E416" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9841,7 @@
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gloss</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C417" s="1" t="inlineStr">
@@ -9853,7 +9863,7 @@
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tier</t>
+          <t xml:space="preserve">gloss</t>
         </is>
       </c>
       <c r="C418" s="1" t="inlineStr">
@@ -9870,17 +9880,22 @@
     <row r="419">
       <c r="A419" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
+          <t xml:space="preserve">uiStrings</t>
+        </is>
+      </c>
+      <c r="B419" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tier</t>
         </is>
       </c>
       <c r="C419" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E419" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.languages, in order; a row's name is language, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D419" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9890,24 +9905,14 @@
           <t xml:space="preserve">uiLanguages</t>
         </is>
       </c>
-      <c r="B420" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">language</t>
-        </is>
-      </c>
       <c r="C420" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D420" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E420" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.ui.languages, in order; a row's name is language, unique</t>
         </is>
       </c>
     </row>
@@ -9919,34 +9924,44 @@
       </c>
       <c r="B421" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rtl</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C421" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D421" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E421" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
+          <t xml:space="preserve">uiLanguages</t>
+        </is>
+      </c>
+      <c r="B422" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rtl</t>
         </is>
       </c>
       <c r="C422" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E422" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.languages[].entries, in order; the first column names the parent row</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D422" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -9956,24 +9971,14 @@
           <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
-      <c r="B423" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">language</t>
-        </is>
-      </c>
       <c r="C423" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D423" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E423" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'uiLanguages' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.ui.languages[].entries, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -9985,22 +9990,22 @@
       </c>
       <c r="B424" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C424" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D424" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E424" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'uiStrings'</t>
+          <t xml:space="preserve">names the row of 'uiLanguages' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10017,7 @@
       </c>
       <c r="B425" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C425" s="1" t="inlineStr">
@@ -10023,23 +10028,33 @@
       <c r="D425" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E425" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'uiStrings'</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
+        </is>
+      </c>
+      <c r="B426" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C426" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E426" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.translation</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D426" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10049,19 +10064,14 @@
           <t xml:space="preserve">translation</t>
         </is>
       </c>
-      <c r="B427" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fromDay</t>
-        </is>
-      </c>
       <c r="C427" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D427" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E427" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.translation</t>
         </is>
       </c>
     </row>
@@ -10073,17 +10083,17 @@
       </c>
       <c r="B428" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">announce</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C428" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D428" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -10095,17 +10105,17 @@
       </c>
       <c r="B429" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.startDelay</t>
+          <t xml:space="preserve">announce</t>
         </is>
       </c>
       <c r="C429" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D429" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10117,7 +10127,7 @@
       </c>
       <c r="B430" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.letterInterval</t>
+          <t xml:space="preserve">flip.startDelay</t>
         </is>
       </c>
       <c r="C430" s="1" t="inlineStr">
@@ -10139,7 +10149,7 @@
       </c>
       <c r="B431" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.letterSeconds</t>
+          <t xml:space="preserve">flip.letterInterval</t>
         </is>
       </c>
       <c r="C431" s="1" t="inlineStr">
@@ -10161,12 +10171,12 @@
       </c>
       <c r="B432" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.scrambleSteps</t>
+          <t xml:space="preserve">flip.letterSeconds</t>
         </is>
       </c>
       <c r="C432" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D432" s="1" t="inlineStr">
@@ -10183,27 +10193,17 @@
       </c>
       <c r="B433" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.slots</t>
+          <t xml:space="preserve">flip.scrambleSteps</t>
         </is>
       </c>
       <c r="C433" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D433" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E433" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F433" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">slots whose value stays English in untranslated speech</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="B434" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.words</t>
+          <t xml:space="preserve">keyWords.slots</t>
         </is>
       </c>
       <c r="C434" s="1" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="F434" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">words that stay English in untranslated speech</t>
+          <t xml:space="preserve">slots whose value stays English in untranslated speech</t>
         </is>
       </c>
     </row>
@@ -10247,17 +10247,27 @@
       </c>
       <c r="B435" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.digits</t>
+          <t xml:space="preserve">keyWords.words</t>
         </is>
       </c>
       <c r="C435" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D435" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E435" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F435" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">words that stay English in untranslated speech</t>
         </is>
       </c>
     </row>
@@ -10269,34 +10279,39 @@
       </c>
       <c r="B436" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fallbackGlyphs</t>
+          <t xml:space="preserve">keyWords.digits</t>
         </is>
       </c>
       <c r="C436" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D436" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
+          <t xml:space="preserve">translation</t>
+        </is>
+      </c>
+      <c r="B437" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fallbackGlyphs</t>
         </is>
       </c>
       <c r="C437" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E437" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.scripts, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D437" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10306,24 +10321,14 @@
           <t xml:space="preserve">scripts</t>
         </is>
       </c>
-      <c r="B438" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C438" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D438" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E438" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.translation.scripts, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -10335,39 +10340,44 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rightToLeft</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C439" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D439" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E439" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">scripts</t>
+        </is>
+      </c>
+      <c r="B440" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rightToLeft</t>
         </is>
       </c>
       <c r="C440" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E440" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.scripts[].fonts, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F440" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D440" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -10377,24 +10387,19 @@
           <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
-      <c r="B441" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">script</t>
-        </is>
-      </c>
       <c r="C441" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D441" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E441" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'scripts' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.translation.scripts[].fonts, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F441" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
         </is>
       </c>
     </row>
@@ -10406,17 +10411,22 @@
       </c>
       <c r="B442" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">file</t>
+          <t xml:space="preserve">script</t>
         </is>
       </c>
       <c r="C442" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D442" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E442" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'scripts' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -10428,17 +10438,17 @@
       </c>
       <c r="B443" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">face</t>
+          <t xml:space="preserve">file</t>
         </is>
       </c>
       <c r="C443" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D443" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10450,17 +10460,17 @@
       </c>
       <c r="B444" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">family</t>
+          <t xml:space="preserve">face</t>
         </is>
       </c>
       <c r="C444" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D444" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -10472,7 +10482,7 @@
       </c>
       <c r="B445" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">style</t>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C445" s="1" t="inlineStr">
@@ -10489,17 +10499,22 @@
     <row r="446">
       <c r="A446" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">scriptFonts</t>
+        </is>
+      </c>
+      <c r="B446" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">style</t>
         </is>
       </c>
       <c r="C446" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E446" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.packs, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D446" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10509,24 +10524,14 @@
           <t xml:space="preserve">packs</t>
         </is>
       </c>
-      <c r="B447" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C447" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D447" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E447" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.translation.packs, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -10538,7 +10543,7 @@
       </c>
       <c r="B448" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C448" s="1" t="inlineStr">
@@ -10548,7 +10553,12 @@
       </c>
       <c r="D448" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E448" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -10560,34 +10570,39 @@
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">spokenCost</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C449" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D449" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">packs</t>
+        </is>
+      </c>
+      <c r="B450" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spokenCost</t>
         </is>
       </c>
       <c r="C450" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E450" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D450" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -10597,24 +10612,14 @@
           <t xml:space="preserve">tongues</t>
         </is>
       </c>
-      <c r="B451" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C451" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D451" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E451" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10631,7 @@
       </c>
       <c r="B452" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C452" s="1" t="inlineStr">
@@ -10636,7 +10641,12 @@
       </c>
       <c r="D452" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E452" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -10648,7 +10658,7 @@
       </c>
       <c r="B453" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">script</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C453" s="1" t="inlineStr">
@@ -10659,11 +10669,6 @@
       <c r="D453" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E453" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'scripts'</t>
         </is>
       </c>
     </row>
@@ -10675,7 +10680,7 @@
       </c>
       <c r="B454" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pack</t>
+          <t xml:space="preserve">script</t>
         </is>
       </c>
       <c r="C454" s="1" t="inlineStr">
@@ -10690,7 +10695,7 @@
       </c>
       <c r="E454" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'packs'</t>
+          <t xml:space="preserve">names a row of 'scripts'</t>
         </is>
       </c>
     </row>
@@ -10702,15 +10707,42 @@
       </c>
       <c r="B455" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">pack</t>
+        </is>
+      </c>
+      <c r="C455" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D455" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E455" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'packs'</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B456" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">glyphs</t>
         </is>
       </c>
-      <c r="C455" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D455" s="1" t="inlineStr">
+      <c r="C456" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D456" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
         </is>
@@ -14205,11 +14237,12 @@
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="39" style="1" customWidth="1"/>
-    <col min="7" max="7" width="46" style="1" customWidth="1"/>
-    <col min="8" max="8" width="32" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="6" max="6" width="47" style="1" customWidth="1"/>
+    <col min="7" max="7" width="39" style="1" customWidth="1"/>
+    <col min="8" max="8" width="46" style="1" customWidth="1"/>
+    <col min="9" max="9" width="32" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14240,25 +14273,30 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">lies</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">countries</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">rules</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">premades</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">premadeChance</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">costumeErrorChance</t>
         </is>
@@ -14286,13 +14324,23 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">PoorPosingAsRich|DoctoredIdentity|FalseOrigin</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">egypt|iraq|greece|italy</t>
         </is>
       </c>
-      <c r="I2">
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rule_LeisureDepartures</t>
+        </is>
+      </c>
+      <c r="J2">
         <v>0.05</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.0</v>
       </c>
     </row>
@@ -14318,23 +14366,28 @@
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">FalseOrigin</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">egypt|iraq|greece|italy|china|britain</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Rule_NoAncientEgypt|Rule_DressForDestination</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">aspasia|banzhao|arib|khwarizmi</t>
         </is>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.05</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.1</v>
       </c>
     </row>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -4478,7 +4478,7 @@
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">countries</t>
+          <t xml:space="preserve">lies</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -4493,7 +4493,12 @@
       </c>
       <c r="E187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">each item names a row of 'countries'; separate items with |</t>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F187" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the lies enabled this day (FalseOrigin, PoorPosingAsRich, DoctoredIdentity); a traveller draws among those that fit their kind</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4510,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rules</t>
+          <t xml:space="preserve">countries</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -4520,7 +4525,7 @@
       </c>
       <c r="E188" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">each item names a row of 'rules'; separate items with |</t>
+          <t xml:space="preserve">each item names a row of 'countries'; separate items with |</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4537,7 @@
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">rules</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -4547,12 +4552,7 @@
       </c>
       <c r="E189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">each item names a row of 'premades'; separate items with |</t>
-        </is>
-      </c>
-      <c r="F189" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">premades that may roll this day</t>
+          <t xml:space="preserve">each item names a row of 'rules'; separate items with |</t>
         </is>
       </c>
     </row>
@@ -4564,17 +4564,27 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeChance</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E190" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">each item names a row of 'premades'; separate items with |</t>
+        </is>
+      </c>
+      <c r="F190" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">premades that may roll this day</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4596,7 @@
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">costumeErrorChance</t>
+          <t xml:space="preserve">premadeChance</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
@@ -4597,33 +4607,33 @@
       <c r="D191" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F191" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chance per 2150 citizen of a costume error (0 before the dress rule's first day)</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayKinds</t>
+          <t xml:space="preserve">days</t>
+        </is>
+      </c>
+      <c r="B192" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">costumeErrorChance</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E192" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.days[].kinds, in order; the first column names the parent row</t>
+          <t xml:space="preserve">decimal</t>
+        </is>
+      </c>
+      <c r="D192" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F192" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the day's traveller mix: each kind's weight</t>
+          <t xml:space="preserve">chance per 2150 citizen of a costume error (0 before the dress rule's first day)</t>
         </is>
       </c>
     </row>
@@ -4633,24 +4643,19 @@
           <t xml:space="preserve">dayKinds</t>
         </is>
       </c>
-      <c r="B193" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">day</t>
-        </is>
-      </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D193" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.days[].kinds, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F193" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the day's traveller mix: each kind's weight</t>
         </is>
       </c>
     </row>
@@ -4662,12 +4667,12 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">day</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr">
@@ -4677,7 +4682,7 @@
       </c>
       <c r="E194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
+          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -4689,34 +4694,44 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E195" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayEras</t>
+          <t xml:space="preserve">dayKinds</t>
+        </is>
+      </c>
+      <c r="B196" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weight</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E196" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.days[].eras, in order; the first column names the parent row</t>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D196" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -4726,24 +4741,14 @@
           <t xml:space="preserve">dayEras</t>
         </is>
       </c>
-      <c r="B197" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">day</t>
-        </is>
-      </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D197" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E197" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.days[].eras, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -4755,22 +4760,22 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">day</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'eras'</t>
+          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -4782,34 +4787,44 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E199" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'eras'</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayForced</t>
+          <t xml:space="preserve">dayEras</t>
+        </is>
+      </c>
+      <c r="B200" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weight</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E200" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.days[].forced, in order; the first column names the parent row</t>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D200" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -4819,24 +4834,14 @@
           <t xml:space="preserve">dayForced</t>
         </is>
       </c>
-      <c r="B201" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">day</t>
-        </is>
-      </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D201" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.days[].forced, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -4848,17 +4853,22 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">slot</t>
+          <t xml:space="preserve">day</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E202" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -4870,22 +4880,17 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premade</t>
+          <t xml:space="preserve">slot</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E203" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'premades'</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4902,7 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">blueprint</t>
+          <t xml:space="preserve">premade</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
@@ -4908,28 +4913,33 @@
       <c r="D204" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E204" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'premades'</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interview</t>
+          <t xml:space="preserve">dayForced</t>
+        </is>
+      </c>
+      <c r="B205" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blueprint</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E205" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.interview</t>
-        </is>
-      </c>
-      <c r="F205" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the interview's wording</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D205" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -4939,19 +4949,19 @@
           <t xml:space="preserve">interview</t>
         </is>
       </c>
-      <c r="B206" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deskName</t>
-        </is>
-      </c>
       <c r="C206" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D206" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E206" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.interview</t>
+        </is>
+      </c>
+      <c r="F206" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the interview's wording</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4973,7 @@
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">opener</t>
+          <t xml:space="preserve">deskName</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr">
@@ -4985,7 +4995,7 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">openerLegendary</t>
+          <t xml:space="preserve">opener</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
@@ -5007,7 +5017,7 @@
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificMale</t>
+          <t xml:space="preserve">openerLegendary</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr">
@@ -5029,7 +5039,7 @@
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificFemale</t>
+          <t xml:space="preserve">honorificMale</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
@@ -5051,7 +5061,7 @@
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificUnknown</t>
+          <t xml:space="preserve">honorificFemale</t>
         </is>
       </c>
       <c r="C211" s="1" t="inlineStr">
@@ -5073,7 +5083,7 @@
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">requestLabel</t>
+          <t xml:space="preserve">honorificUnknown</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
@@ -5095,7 +5105,7 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">papersLabel</t>
+          <t xml:space="preserve">requestLabel</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
@@ -5106,11 +5116,6 @@
       <c r="D213" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F213" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the hub entry that opens the papers menu</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5127,7 @@
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">requestPrompt</t>
+          <t xml:space="preserve">papersLabel</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
@@ -5133,6 +5138,11 @@
       <c r="D214" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F214" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the hub entry that opens the papers menu</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5154,7 @@
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">requestReply</t>
+          <t xml:space="preserve">requestPrompt</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
@@ -5166,7 +5176,7 @@
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">askLabel</t>
+          <t xml:space="preserve">requestReply</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
@@ -5188,7 +5198,7 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">backLabel</t>
+          <t xml:space="preserve">askLabel</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
@@ -5210,7 +5220,7 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">smallTalkLabel</t>
+          <t xml:space="preserve">backLabel</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
@@ -5232,7 +5242,7 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">smallTalkPrompt</t>
+          <t xml:space="preserve">smallTalkLabel</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr">
@@ -5254,17 +5264,17 @@
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">menuCapacity</t>
+          <t xml:space="preserve">smallTalkPrompt</t>
         </is>
       </c>
       <c r="C220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5286,7 @@
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">maxLineChars</t>
+          <t xml:space="preserve">menuCapacity</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr">
@@ -5298,39 +5308,39 @@
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lookLabel</t>
+          <t xml:space="preserve">maxLineChars</t>
         </is>
       </c>
       <c r="C222" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D222" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">claims</t>
+          <t xml:space="preserve">interview</t>
+        </is>
+      </c>
+      <c r="B223" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lookLabel</t>
         </is>
       </c>
       <c r="C223" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E223" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.interview.claims, in order</t>
-        </is>
-      </c>
-      <c r="F223" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the claim per traveller kind ({place}): one row per kind a blueprint makes</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D223" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5340,24 +5350,19 @@
           <t xml:space="preserve">claims</t>
         </is>
       </c>
-      <c r="B224" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kind</t>
-        </is>
-      </c>
       <c r="C224" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D224" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E224" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
+          <t xml:space="preserve">one row per item of the list $.interview.claims, in order</t>
+        </is>
+      </c>
+      <c r="F224" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the claim per traveller kind ({place}): one row per kind a blueprint makes</t>
         </is>
       </c>
     </row>
@@ -5369,7 +5374,7 @@
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C225" s="1" t="inlineStr">
@@ -5379,29 +5384,34 @@
       </c>
       <c r="D225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E225" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interviewRequests</t>
+          <t xml:space="preserve">claims</t>
+        </is>
+      </c>
+      <c r="B226" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C226" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E226" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.interview.requests, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F226" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spoken requests: the wheel entry, the desk's prompt and the traveller's reply</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D226" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5411,24 +5421,19 @@
           <t xml:space="preserve">interviewRequests</t>
         </is>
       </c>
-      <c r="B227" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C227" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D227" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E227" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.interview.requests, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F227" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spoken requests: the wheel entry, the desk's prompt and the traveller's reply</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5445,7 @@
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C228" s="1" t="inlineStr">
@@ -5450,7 +5455,12 @@
       </c>
       <c r="D228" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E228" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5472,7 @@
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C229" s="1" t="inlineStr">
@@ -5484,7 +5494,7 @@
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">reply</t>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C230" s="1" t="inlineStr">
@@ -5501,17 +5511,22 @@
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
+          <t xml:space="preserve">interviewRequests</t>
+        </is>
+      </c>
+      <c r="B231" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reply</t>
         </is>
       </c>
       <c r="C231" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E231" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.questions, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D231" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5521,24 +5536,14 @@
           <t xml:space="preserve">questions</t>
         </is>
       </c>
-      <c r="B232" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C232" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D232" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E232" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.questions, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5555,7 @@
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C233" s="1" t="inlineStr">
@@ -5560,7 +5565,12 @@
       </c>
       <c r="D233" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E233" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5582,7 @@
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C234" s="1" t="inlineStr">
@@ -5594,7 +5604,7 @@
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C235" s="1" t="inlineStr">
@@ -5616,7 +5626,7 @@
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C236" s="1" t="inlineStr">
@@ -5638,17 +5648,17 @@
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">answer</t>
         </is>
       </c>
       <c r="C237" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D237" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5660,39 +5670,39 @@
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">announce</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questions</t>
+        </is>
+      </c>
+      <c r="B239" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">announce</t>
         </is>
       </c>
       <c r="C239" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E239" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.questions[].conditions, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F239" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all must pass</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D239" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5702,24 +5712,19 @@
           <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
-      <c r="B240" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">question</t>
-        </is>
-      </c>
       <c r="C240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D240" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.questions[].conditions, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F240" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all must pass</t>
         </is>
       </c>
     </row>
@@ -5731,17 +5736,22 @@
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">question</t>
         </is>
       </c>
       <c r="C241" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D241" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E241" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5763,7 @@
       </c>
       <c r="B242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C242" s="1" t="inlineStr">
@@ -5763,7 +5773,7 @@
       </c>
       <c r="D242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -5775,17 +5785,17 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5797,22 +5807,17 @@
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E244" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5829,7 @@
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C245" s="1" t="inlineStr">
@@ -5839,7 +5844,7 @@
       </c>
       <c r="E245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5856,7 @@
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C246" s="1" t="inlineStr">
@@ -5866,29 +5871,34 @@
       </c>
       <c r="E246" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
+          <t xml:space="preserve">questionConditions</t>
+        </is>
+      </c>
+      <c r="B247" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D247" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.questions[].overrides, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F247" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the wording in one era</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
@@ -5898,24 +5908,19 @@
           <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
-      <c r="B248" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">question</t>
-        </is>
-      </c>
       <c r="C248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D248" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.questions[].overrides, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F248" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the wording in one era</t>
         </is>
       </c>
     </row>
@@ -5927,22 +5932,22 @@
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">question</t>
         </is>
       </c>
       <c r="C249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'eras'</t>
+          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5959,7 @@
       </c>
       <c r="B250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C250" s="1" t="inlineStr">
@@ -5965,6 +5970,11 @@
       <c r="D250" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E250" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'eras'</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5986,7 @@
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C251" s="1" t="inlineStr">
@@ -5993,22 +6003,22 @@
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
+          <t xml:space="preserve">questionOverrides</t>
+        </is>
+      </c>
+      <c r="B252" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">answer</t>
         </is>
       </c>
       <c r="C252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E252" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F252" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">narrative dialogs: nodes, their lines and the player's choices</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D252" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6018,24 +6028,19 @@
           <t xml:space="preserve">dialogs</t>
         </is>
       </c>
-      <c r="B253" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D253" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F253" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrative dialogs: nodes, their lines and the player's choices</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6052,7 @@
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C254" s="1" t="inlineStr">
@@ -6057,12 +6062,12 @@
       </c>
       <c r="D254" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F254" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the wheel entry</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E254" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -6074,39 +6079,44 @@
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">repeatable</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F255" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the wheel entry</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
+          <t xml:space="preserve">dialogs</t>
+        </is>
+      </c>
+      <c r="B256" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repeatable</t>
         </is>
       </c>
       <c r="C256" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E256" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].conditions, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F256" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all must pass</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D256" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -6116,24 +6126,19 @@
           <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
-      <c r="B257" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dialog</t>
-        </is>
-      </c>
       <c r="C257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D257" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].conditions, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F257" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all must pass</t>
         </is>
       </c>
     </row>
@@ -6145,17 +6150,22 @@
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D258" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E258" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6177,7 @@
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C259" s="1" t="inlineStr">
@@ -6177,7 +6187,7 @@
       </c>
       <c r="D259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -6189,17 +6199,17 @@
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6211,22 +6221,17 @@
       </c>
       <c r="B261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E261" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6243,7 @@
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C262" s="1" t="inlineStr">
@@ -6253,7 +6258,7 @@
       </c>
       <c r="E262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -6265,7 +6270,7 @@
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C263" s="1" t="inlineStr">
@@ -6280,24 +6285,34 @@
       </c>
       <c r="E263" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogNodes</t>
+          <t xml:space="preserve">dialogConditions</t>
+        </is>
+      </c>
+      <c r="B264" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D264" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes, in order; a row's name is id, unique per parent row; the first column names the parent row</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
@@ -6307,24 +6322,14 @@
           <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
-      <c r="B265" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dialog</t>
-        </is>
-      </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D265" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes, in order; a row's name is id, unique per parent row; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -6336,12 +6341,12 @@
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D266" s="1" t="inlineStr">
@@ -6351,24 +6356,34 @@
       </c>
       <c r="E266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
+          <t xml:space="preserve">dialogNodes</t>
+        </is>
+      </c>
+      <c r="B267" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D267" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].lines, in order; the first columns name the parent row</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -6378,24 +6393,14 @@
           <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
-      <c r="B268" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dialog</t>
-        </is>
-      </c>
       <c r="C268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D268" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].lines, in order; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6412,7 @@
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C269" s="1" t="inlineStr">
@@ -6422,7 +6427,7 @@
       </c>
       <c r="E269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6434,17 +6439,22 @@
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E270" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6466,7 @@
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">speaker</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
@@ -6478,7 +6488,7 @@
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">expression</t>
+          <t xml:space="preserve">speaker</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
@@ -6488,7 +6498,7 @@
       </c>
       <c r="D272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6510,7 @@
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">expression</t>
         </is>
       </c>
       <c r="C273" s="1" t="inlineStr">
@@ -6510,24 +6520,29 @@
       </c>
       <c r="D273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">dialogLines</t>
+        </is>
+      </c>
+      <c r="B274" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E274" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices, in order; a row's name is id, unique per parent row; the first columns name the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D274" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6537,24 +6552,14 @@
           <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
-      <c r="B275" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dialog</t>
-        </is>
-      </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D275" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices, in order; a row's name is id, unique per parent row; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6571,7 @@
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C276" s="1" t="inlineStr">
@@ -6581,7 +6586,7 @@
       </c>
       <c r="E276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6593,12 +6598,12 @@
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D277" s="1" t="inlineStr">
@@ -6608,7 +6613,7 @@
       </c>
       <c r="E277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6625,7 @@
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C278" s="1" t="inlineStr">
@@ -6630,7 +6635,12 @@
       </c>
       <c r="D278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E278" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6652,7 @@
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">next</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
@@ -6653,11 +6663,6 @@
       <c r="D279" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F279" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the node it leads to (blank: the dialog ends)</t>
         </is>
       </c>
     </row>
@@ -6669,7 +6674,7 @@
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">effect</t>
+          <t xml:space="preserve">next</t>
         </is>
       </c>
       <c r="C280" s="1" t="inlineStr">
@@ -6680,23 +6685,33 @@
       <c r="D280" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F280" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the node it leads to (blank: the dialog ends)</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">dialogChoices</t>
+        </is>
+      </c>
+      <c r="B281" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">effect</t>
         </is>
       </c>
       <c r="C281" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E281" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices[].lines, in order; the first columns name the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D281" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6706,24 +6721,14 @@
           <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
-      <c r="B282" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dialog</t>
-        </is>
-      </c>
       <c r="C282" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D282" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E282" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices[].lines, in order; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6740,7 @@
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
@@ -6750,7 +6755,7 @@
       </c>
       <c r="E283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6767,7 @@
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choice</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C284" s="1" t="inlineStr">
@@ -6777,7 +6782,7 @@
       </c>
       <c r="E284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogChoices' this row belongs to</t>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6789,17 +6794,22 @@
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">choice</t>
         </is>
       </c>
       <c r="C285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E285" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogChoices' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6821,7 @@
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">speaker</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C286" s="1" t="inlineStr">
@@ -6833,7 +6843,7 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">expression</t>
+          <t xml:space="preserve">speaker</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
@@ -6843,7 +6853,7 @@
       </c>
       <c r="D287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6855,7 +6865,7 @@
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">expression</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr">
@@ -6865,29 +6875,29 @@
       </c>
       <c r="D288" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">choiceLines</t>
+        </is>
+      </c>
+      <c r="B289" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C289" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E289" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.premades, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F289" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">premade characters: real people and written stories</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D289" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6897,24 +6907,19 @@
           <t xml:space="preserve">premades</t>
         </is>
       </c>
-      <c r="B290" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D290" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.premades, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F290" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">premade characters: real people and written stories</t>
         </is>
       </c>
     </row>
@@ -6926,7 +6931,7 @@
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C291" s="1" t="inlineStr">
@@ -6936,7 +6941,12 @@
       </c>
       <c r="D291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E291" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6958,7 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gender</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
@@ -6970,7 +6980,7 @@
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">gender</t>
         </is>
       </c>
       <c r="C293" s="1" t="inlineStr">
@@ -6981,11 +6991,6 @@
       <c r="D293" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E293" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -6997,7 +7002,7 @@
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">truePlace</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C294" s="1" t="inlineStr">
@@ -7013,11 +7018,6 @@
       <c r="E294" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">names a row of 'places'</t>
-        </is>
-      </c>
-      <c r="F294" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">where they really come from (blank: honest)</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">birthDate</t>
+          <t xml:space="preserve">truePlace</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
@@ -7040,6 +7040,16 @@
       <c r="D295" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E295" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
+        </is>
+      </c>
+      <c r="F295" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">where they really come from (blank: honest)</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7061,7 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">archetype</t>
+          <t xml:space="preserve">birthDate</t>
         </is>
       </c>
       <c r="C296" s="1" t="inlineStr">
@@ -7073,7 +7083,7 @@
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">intro</t>
+          <t xml:space="preserve">archetype</t>
         </is>
       </c>
       <c r="C297" s="1" t="inlineStr">
@@ -7095,7 +7105,7 @@
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">recordNote</t>
+          <t xml:space="preserve">intro</t>
         </is>
       </c>
       <c r="C298" s="1" t="inlineStr">
@@ -7117,7 +7127,7 @@
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">recordNote</t>
         </is>
       </c>
       <c r="C299" s="1" t="inlineStr">
@@ -7128,11 +7138,6 @@
       <c r="D299" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E299" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'dialogs'</t>
         </is>
       </c>
     </row>
@@ -7144,34 +7149,44 @@
       </c>
       <c r="B300" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">repeatable</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C300" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D300" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E300" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'dialogs'</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">premades</t>
+        </is>
+      </c>
+      <c r="B301" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repeatable</t>
         </is>
       </c>
       <c r="C301" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E301" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.premades[].impacts, in order; the first column names the parent row</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D301" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -7181,24 +7196,14 @@
           <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
-      <c r="B302" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">premade</t>
-        </is>
-      </c>
       <c r="C302" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D302" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E302" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'premades' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.premades[].impacts, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -7210,22 +7215,22 @@
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">premade</t>
         </is>
       </c>
       <c r="C303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">names the row of 'premades' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7237,17 +7242,22 @@
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">onCorrect</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E304" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7269,7 @@
       </c>
       <c r="B305" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">onWrong</t>
+          <t xml:space="preserve">onCorrect</t>
         </is>
       </c>
       <c r="C305" s="1" t="inlineStr">
@@ -7281,34 +7291,39 @@
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">skipNationScore</t>
+          <t xml:space="preserve">onWrong</t>
         </is>
       </c>
       <c r="C306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">premadeImpacts</t>
+        </is>
+      </c>
+      <c r="B307" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skipNationScore</t>
         </is>
       </c>
       <c r="C307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E307" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.history</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D307" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -7318,19 +7333,14 @@
           <t xml:space="preserve">history</t>
         </is>
       </c>
-      <c r="B308" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lines.leaderGained</t>
-        </is>
-      </c>
       <c r="C308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D308" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E308" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.history</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7352,7 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.leaderLost</t>
+          <t xml:space="preserve">lines.leaderGained</t>
         </is>
       </c>
       <c r="C309" s="1" t="inlineStr">
@@ -7364,7 +7374,7 @@
       </c>
       <c r="B310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.carry</t>
+          <t xml:space="preserve">lines.leaderLost</t>
         </is>
       </c>
       <c r="C310" s="1" t="inlineStr">
@@ -7386,7 +7396,7 @@
       </c>
       <c r="B311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.dominant</t>
+          <t xml:space="preserve">lines.carry</t>
         </is>
       </c>
       <c r="C311" s="1" t="inlineStr">
@@ -7397,11 +7407,6 @@
       <c r="D311" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F311" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">an attribute becomes dominant in a place: {attribute} and {place}</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7418,7 @@
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.panic</t>
+          <t xml:space="preserve">lines.dominant</t>
         </is>
       </c>
       <c r="C312" s="1" t="inlineStr">
@@ -7428,29 +7433,34 @@
       </c>
       <c r="F312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">an accepted costume error caused a panic: {place} and {value} (the wrong item)</t>
+          <t xml:space="preserve">an attribute becomes dominant in a place: {attribute} and {place}</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyRules</t>
+          <t xml:space="preserve">history</t>
+        </is>
+      </c>
+      <c r="B313" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lines.panic</t>
         </is>
       </c>
       <c r="C313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E313" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D313" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history rules: when their conditions pass at night they rewrite a place's fact</t>
+          <t xml:space="preserve">an accepted costume error caused a panic: {place} and {value} (the wrong item)</t>
         </is>
       </c>
     </row>
@@ -7460,24 +7470,19 @@
           <t xml:space="preserve">historyRules</t>
         </is>
       </c>
-      <c r="B314" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C314" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D314" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E314" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.history.rules, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F314" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">history rules: when their conditions pass at night they rewrite a place's fact</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7494,7 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C315" s="1" t="inlineStr">
@@ -7499,7 +7504,12 @@
       </c>
       <c r="D315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E315" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7521,7 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">news</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C316" s="1" t="inlineStr">
@@ -7528,17 +7538,22 @@
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
+          <t xml:space="preserve">historyRules</t>
+        </is>
+      </c>
+      <c r="B317" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">news</t>
         </is>
       </c>
       <c r="C317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E317" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules[].conditions, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D317" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7548,24 +7563,14 @@
           <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
-      <c r="B318" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rule</t>
-        </is>
-      </c>
       <c r="C318" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D318" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E318" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.history.rules[].conditions, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -7577,17 +7582,22 @@
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">rule</t>
         </is>
       </c>
       <c r="C319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D319" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E319" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7609,7 @@
       </c>
       <c r="B320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C320" s="1" t="inlineStr">
@@ -7609,7 +7619,7 @@
       </c>
       <c r="D320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7631,7 @@
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C321" s="1" t="inlineStr">
@@ -7632,11 +7642,6 @@
       <c r="D321" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E321" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
@@ -7648,7 +7653,7 @@
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C322" s="1" t="inlineStr">
@@ -7663,7 +7668,7 @@
       </c>
       <c r="E322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7680,7 @@
       </c>
       <c r="B323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C323" s="1" t="inlineStr">
@@ -7690,7 +7695,7 @@
       </c>
       <c r="E323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -7702,34 +7707,44 @@
       </c>
       <c r="B324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (left out of the JSON)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E324" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
+          <t xml:space="preserve">historyConditions</t>
+        </is>
+      </c>
+      <c r="B325" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E325" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules[].edits, in order; the first column names the parent row</t>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D325" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -7739,24 +7754,14 @@
           <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
-      <c r="B326" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rule</t>
-        </is>
-      </c>
       <c r="C326" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D326" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E326" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.history.rules[].edits, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -7768,22 +7773,22 @@
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">rule</t>
         </is>
       </c>
       <c r="C327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7795,7 +7800,7 @@
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C328" s="1" t="inlineStr">
@@ -7806,6 +7811,11 @@
       <c r="D328" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E328" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -7817,7 +7827,7 @@
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C329" s="1" t="inlineStr">
@@ -7834,22 +7844,22 @@
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">newsDebt</t>
+          <t xml:space="preserve">historyEdits</t>
+        </is>
+      </c>
+      <c r="B330" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
         </is>
       </c>
       <c r="C330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Values</t>
-        </is>
-      </c>
-      <c r="E330" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.news.debt, in order</t>
-        </is>
-      </c>
-      <c r="F330" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the morning paper's debt lines: one a day, in a shuffled order per run</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D330" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7859,36 +7869,41 @@
           <t xml:space="preserve">newsDebt</t>
         </is>
       </c>
-      <c r="B331" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
       <c r="C331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D331" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Values</t>
+        </is>
+      </c>
+      <c r="E331" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.news.debt, in order</t>
+        </is>
+      </c>
+      <c r="F331" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the morning paper's debt lines: one a day, in a shuffled order per run</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pc</t>
+          <t xml:space="preserve">newsDebt</t>
+        </is>
+      </c>
+      <c r="B332" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E332" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.pc</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D332" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -7898,46 +7913,41 @@
           <t xml:space="preserve">pc</t>
         </is>
       </c>
-      <c r="B333" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ancestry.includePremades</t>
-        </is>
-      </c>
       <c r="C333" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
-        </is>
-      </c>
-      <c r="D333" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="F333" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the premades who are who they claim get cards</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E333" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.pc</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcStepSets</t>
+          <t xml:space="preserve">pc</t>
+        </is>
+      </c>
+      <c r="B334" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ancestry.includePremades</t>
         </is>
       </c>
       <c r="C334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E334" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.steps.sets, in order; a row's name is type, unique</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D334" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="F334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the optional steps checklist, one set per traveller kind</t>
+          <t xml:space="preserve">the premades who are who they claim get cards</t>
         </is>
       </c>
     </row>
@@ -7947,29 +7957,19 @@
           <t xml:space="preserve">pcStepSets</t>
         </is>
       </c>
-      <c r="B335" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">type</t>
-        </is>
-      </c>
       <c r="C335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D335" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name; one of: default, RichTourist, PoorTourist, Labourer, Displaced</t>
+          <t xml:space="preserve">one row per item of the list $.pc.steps.sets, in order; a row's name is type, unique</t>
         </is>
       </c>
       <c r="F335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a traveller kind, or default: the steps of a kind with no set of its own</t>
+          <t xml:space="preserve">the optional steps checklist, one set per traveller kind</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">inherit</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C336" s="1" t="inlineStr">
@@ -7991,17 +7991,17 @@
       </c>
       <c r="D336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'pcStepSets'</t>
+          <t xml:space="preserve">part of the row's name; one of: default, RichTourist, PoorTourist, Labourer, Displaced</t>
         </is>
       </c>
       <c r="F336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the set whose steps it starts from; its own step of the same id replaces the parent's (blank: none)</t>
+          <t xml:space="preserve">a traveller kind, or default: the steps of a kind with no set of its own</t>
         </is>
       </c>
     </row>
@@ -8013,44 +8013,54 @@
       </c>
       <c r="B337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dataOnly</t>
+          <t xml:space="preserve">inherit</t>
         </is>
       </c>
       <c r="C337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E337" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'pcStepSets'</t>
         </is>
       </c>
       <c r="F337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true while the kind is not in play yet: its forms and categories may name what a later phase adds</t>
+          <t xml:space="preserve">the set whose steps it starts from; its own step of the same id replaces the parent's (blank: none)</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSteps</t>
+          <t xml:space="preserve">pcStepSets</t>
+        </is>
+      </c>
+      <c r="B338" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dataOnly</t>
         </is>
       </c>
       <c r="C338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E338" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.steps.sets[].steps, in order; the first column names the parent row</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D338" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
       <c r="F338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a set's steps, in order</t>
+          <t xml:space="preserve">true while the kind is not in play yet: its forms and categories may name what a later phase adds</t>
         </is>
       </c>
     </row>
@@ -8060,24 +8070,19 @@
           <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
-      <c r="B339" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stepSet</t>
-        </is>
-      </c>
       <c r="C339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D339" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'pcStepSets' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.pc.steps.sets[].steps, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F339" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a set's steps, in order</t>
         </is>
       </c>
     </row>
@@ -8089,12 +8094,12 @@
       </c>
       <c r="B340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">stepSet</t>
         </is>
       </c>
       <c r="C340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D340" s="1" t="inlineStr">
@@ -8102,9 +8107,9 @@
           <t xml:space="preserve">(required)</t>
         </is>
       </c>
-      <c r="F340" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its label is the UI string steps.{id}</t>
+      <c r="E340" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'pcStepSets' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -8116,7 +8121,7 @@
       </c>
       <c r="B341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">when</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C341" s="1" t="inlineStr">
@@ -8129,14 +8134,9 @@
           <t xml:space="preserve">(required)</t>
         </is>
       </c>
-      <c r="E341" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one of: PapersReceived, PaperRead, Requested, RulesViewed, RecordViewed, Compared, Asked, LookedAt</t>
-        </is>
-      </c>
       <c r="F341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the check it waits for, never what the check found</t>
+          <t xml:space="preserve">its label is the UI string steps.{id}</t>
         </is>
       </c>
     </row>
@@ -8148,27 +8148,27 @@
       </c>
       <c r="B342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">categories</t>
+          <t xml:space="preserve">when</t>
         </is>
       </c>
       <c r="C342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">separate items with |</t>
+          <t xml:space="preserve">one of: PapersReceived, PaperRead, Requested, RulesViewed, RecordViewed, Compared, Asked, LookedAt</t>
         </is>
       </c>
       <c r="F342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the categories a Compared or Asked step counts (blank: derived from the case)</t>
+          <t xml:space="preserve">the check it waits for, never what the check found</t>
         </is>
       </c>
     </row>
@@ -8180,27 +8180,27 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">statement</t>
+          <t xml:space="preserve">categories</t>
         </is>
       </c>
       <c r="C343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
         </is>
       </c>
       <c r="E343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: Any, Field, Answer, Garment</t>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
       <c r="F343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Compared step's statement side (blank: any)</t>
+          <t xml:space="preserve">the categories a Compared or Asked step counts (blank: derived from the case)</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="B344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">truth</t>
+          <t xml:space="preserve">statement</t>
         </is>
       </c>
       <c r="C344" s="1" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="E344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: Any, Reference, Record, Paper</t>
+          <t xml:space="preserve">one of: Any, Field, Answer, Garment</t>
         </is>
       </c>
       <c r="F344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Compared step's truth side (blank: any)</t>
+          <t xml:space="preserve">a Compared step's statement side (blank: any)</t>
         </is>
       </c>
     </row>
@@ -8244,27 +8244,27 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">forms</t>
+          <t xml:space="preserve">truth</t>
         </is>
       </c>
       <c r="C345" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D345" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E345" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">separate items with |</t>
+          <t xml:space="preserve">one of: Any, Reference, Record, Paper</t>
         </is>
       </c>
       <c r="F345" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the form numbers a paper step counts (blank: every paper)</t>
+          <t xml:space="preserve">a Compared step's truth side (blank: any)</t>
         </is>
       </c>
     </row>
@@ -8276,27 +8276,27 @@
       </c>
       <c r="B346" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">jump.source</t>
+          <t xml:space="preserve">forms</t>
         </is>
       </c>
       <c r="C346" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D346" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
         </is>
       </c>
       <c r="E346" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: Documents, Records, Reference, Transcript, Report, Rules</t>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
       <c r="F346" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the tab a click on the step shows</t>
+          <t xml:space="preserve">the form numbers a paper step counts (blank: every paper)</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="B347" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">jump.link</t>
+          <t xml:space="preserve">jump.source</t>
         </is>
       </c>
       <c r="C347" s="1" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="E347" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: PrimaryName, FirstUncheckedField, CostumeClaimed</t>
+          <t xml:space="preserve">one of: Documents, Records, Reference, Transcript, Report, Rules</t>
         </is>
       </c>
       <c r="F347" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">where a click goes instead of a tab</t>
+          <t xml:space="preserve">the tab a click on the step shows</t>
         </is>
       </c>
     </row>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="B348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hint</t>
+          <t xml:space="preserve">jump.link</t>
         </is>
       </c>
       <c r="C348" s="1" t="inlineStr">
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'uiStrings'</t>
+          <t xml:space="preserve">one of: PrimaryName, FirstUncheckedField, CostumeClaimed</t>
         </is>
       </c>
       <c r="F348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the UI string of the toast a click shows instead of a jump</t>
+          <t xml:space="preserve">where a click goes instead of a tab</t>
         </is>
       </c>
     </row>
@@ -8372,44 +8372,54 @@
       </c>
       <c r="B349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">hint</t>
         </is>
       </c>
       <c r="C349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (left out of the JSON)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E349" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'uiStrings'</t>
         </is>
       </c>
       <c r="F349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">its first day (blank: day 1)</t>
+          <t xml:space="preserve">the UI string of the toast a click shows instead of a jump</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSites</t>
+          <t xml:space="preserve">pcSteps</t>
+        </is>
+      </c>
+      <c r="B350" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E350" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.sites, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D350" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 (left out of the JSON)</t>
         </is>
       </c>
       <c r="F350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Internet's sites</t>
+          <t xml:space="preserve">its first day (blank: day 1)</t>
         </is>
       </c>
     </row>
@@ -8419,24 +8429,19 @@
           <t xml:space="preserve">pcSites</t>
         </is>
       </c>
-      <c r="B351" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C351" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D351" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E351" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.pc.sites, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F351" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the Internet's sites</t>
         </is>
       </c>
     </row>
@@ -8448,7 +8453,7 @@
       </c>
       <c r="B352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C352" s="1" t="inlineStr">
@@ -8458,17 +8463,12 @@
       </c>
       <c r="D352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: News, History, Ancestry, Static</t>
-        </is>
-      </c>
-      <c r="F352" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the page builder that serves it</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="B353" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C353" s="1" t="inlineStr">
@@ -8491,6 +8491,16 @@
       <c r="D353" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E353" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: News, History, Ancestry, Static</t>
+        </is>
+      </c>
+      <c r="F353" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the page builder that serves it</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8512,7 @@
       </c>
       <c r="B354" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">domain</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C354" s="1" t="inlineStr">
@@ -8513,11 +8523,6 @@
       <c r="D354" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F354" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chronet://{domain}: lower-case letters, digits, dots and dashes</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8534,7 @@
       </c>
       <c r="B355" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">glyph</t>
+          <t xml:space="preserve">domain</t>
         </is>
       </c>
       <c r="C355" s="1" t="inlineStr">
@@ -8544,7 +8549,7 @@
       </c>
       <c r="F355" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the start-page tile's art key</t>
+          <t xml:space="preserve">chronet://{domain}: lower-case letters, digits, dots and dashes</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8561,7 @@
       </c>
       <c r="B356" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb</t>
+          <t xml:space="preserve">glyph</t>
         </is>
       </c>
       <c r="C356" s="1" t="inlineStr">
@@ -8567,6 +8572,11 @@
       <c r="D356" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F356" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the start-page tile's art key</t>
         </is>
       </c>
     </row>
@@ -8578,44 +8588,44 @@
       </c>
       <c r="B357" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">blurb</t>
         </is>
       </c>
       <c r="C357" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D357" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F357" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the first day it is listed</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPages</t>
+          <t xml:space="preserve">pcSites</t>
+        </is>
+      </c>
+      <c r="B358" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C358" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E358" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.pages, in order; a row's name is {site}/{path}, unique</t>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D358" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F358" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Static site's authored pages</t>
+          <t xml:space="preserve">the first day it is listed</t>
         </is>
       </c>
     </row>
@@ -8625,24 +8635,19 @@
           <t xml:space="preserve">pcPages</t>
         </is>
       </c>
-      <c r="B359" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">site</t>
-        </is>
-      </c>
       <c r="C359" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D359" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E359" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name; names a row of 'pcSites'</t>
+          <t xml:space="preserve">one row per item of the list $.pc.pages, in order; a row's name is {site}/{path}, unique</t>
+        </is>
+      </c>
+      <c r="F359" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a Static site's authored pages</t>
         </is>
       </c>
     </row>
@@ -8654,7 +8659,7 @@
       </c>
       <c r="B360" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">path</t>
+          <t xml:space="preserve">site</t>
         </is>
       </c>
       <c r="C360" s="1" t="inlineStr">
@@ -8664,17 +8669,12 @@
       </c>
       <c r="D360" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E360" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
-        </is>
-      </c>
-      <c r="F360" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank: the site's front page</t>
+          <t xml:space="preserve">part of the row's name; names a row of 'pcSites'</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">title</t>
+          <t xml:space="preserve">path</t>
         </is>
       </c>
       <c r="C361" s="1" t="inlineStr">
@@ -8697,23 +8697,38 @@
       <c r="D361" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E361" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
+        </is>
+      </c>
+      <c r="F361" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank: the site's front page</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPageBlocks</t>
+          <t xml:space="preserve">pcPages</t>
+        </is>
+      </c>
+      <c r="B362" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">title</t>
         </is>
       </c>
       <c r="C362" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E362" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.pages[].blocks, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D362" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -8723,24 +8738,14 @@
           <t xml:space="preserve">pcPageBlocks</t>
         </is>
       </c>
-      <c r="B363" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">page</t>
-        </is>
-      </c>
       <c r="C363" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D363" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E363" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'pcPages' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.pc.pages[].blocks, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -8752,22 +8757,22 @@
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">page</t>
         </is>
       </c>
       <c r="C364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: Headline, Heading, Paragraph, Note, Link, Box</t>
+          <t xml:space="preserve">names the row of 'pcPages' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8784,7 @@
       </c>
       <c r="B365" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C365" s="1" t="inlineStr">
@@ -8790,6 +8795,11 @@
       <c r="D365" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E365" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: Headline, Heading, Paragraph, Note, Link, Box</t>
         </is>
       </c>
     </row>
@@ -8801,7 +8811,7 @@
       </c>
       <c r="B366" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">address</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C366" s="1" t="inlineStr">
@@ -8811,12 +8821,7 @@
       </c>
       <c r="D366" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="F366" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a Link's site name, domain or chronet:// address</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -8828,49 +8833,54 @@
       </c>
       <c r="B367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines</t>
+          <t xml:space="preserve">address</t>
         </is>
       </c>
       <c r="C367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E367" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="F367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Box's lines</t>
+          <t xml:space="preserve">a Link's site name, domain or chronet:// address</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPeople</t>
+          <t xml:space="preserve">pcPageBlocks</t>
+        </is>
+      </c>
+      <c r="B368" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lines</t>
         </is>
       </c>
       <c r="C368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text list</t>
+        </is>
+      </c>
+      <c r="D368" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
         </is>
       </c>
       <c r="E368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.ancestry.people, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
       <c r="F368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Lineage Archive's people of the past (no traveller's name)</t>
+          <t xml:space="preserve">a Box's lines</t>
         </is>
       </c>
     </row>
@@ -8880,24 +8890,19 @@
           <t xml:space="preserve">pcPeople</t>
         </is>
       </c>
-      <c r="B369" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C369" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D369" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E369" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.pc.ancestry.people, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F369" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the Lineage Archive's people of the past (no traveller's name)</t>
         </is>
       </c>
     </row>
@@ -8909,7 +8914,7 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C370" s="1" t="inlineStr">
@@ -8919,7 +8924,12 @@
       </c>
       <c r="D370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E370" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8941,7 @@
       </c>
       <c r="B371" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">born</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C371" s="1" t="inlineStr">
@@ -8953,7 +8963,7 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">died</t>
+          <t xml:space="preserve">born</t>
         </is>
       </c>
       <c r="C372" s="1" t="inlineStr">
@@ -8975,7 +8985,7 @@
       </c>
       <c r="B373" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">died</t>
         </is>
       </c>
       <c r="C373" s="1" t="inlineStr">
@@ -8986,11 +8996,6 @@
       <c r="D373" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E373" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9007,7 @@
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">note</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C374" s="1" t="inlineStr">
@@ -9013,28 +9018,33 @@
       <c r="D374" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E374" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcRelations</t>
+          <t xml:space="preserve">pcPeople</t>
+        </is>
+      </c>
+      <c r="B375" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">note</t>
         </is>
       </c>
       <c r="C375" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E375" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.ancestry.relations, in order</t>
-        </is>
-      </c>
-      <c r="F375" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one direction per row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D375" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9044,24 +9054,19 @@
           <t xml:space="preserve">pcRelations</t>
         </is>
       </c>
-      <c r="B376" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">person</t>
-        </is>
-      </c>
       <c r="C376" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D376" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E376" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.ancestry.relations, in order</t>
         </is>
       </c>
       <c r="F376" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a person's or a premade's id: the card it shows on</t>
+          <t xml:space="preserve">one direction per row</t>
         </is>
       </c>
     </row>
@@ -9073,7 +9078,7 @@
       </c>
       <c r="B377" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">person</t>
         </is>
       </c>
       <c r="C377" s="1" t="inlineStr">
@@ -9083,7 +9088,12 @@
       </c>
       <c r="D377" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="F377" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a person's or a premade's id: the card it shows on</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9105,7 @@
       </c>
       <c r="B378" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">other</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C378" s="1" t="inlineStr">
@@ -9105,34 +9115,34 @@
       </c>
       <c r="D378" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="F378" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the other card's id</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMail</t>
+          <t xml:space="preserve">pcRelations</t>
+        </is>
+      </c>
+      <c r="B379" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">other</t>
         </is>
       </c>
       <c r="C379" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E379" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.mail, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D379" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="F379" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mail's authored messages</t>
+          <t xml:space="preserve">the other card's id</t>
         </is>
       </c>
     </row>
@@ -9142,24 +9152,19 @@
           <t xml:space="preserve">pcMail</t>
         </is>
       </c>
-      <c r="B380" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C380" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D380" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E380" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.pc.mail, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F380" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mail's authored messages</t>
         </is>
       </c>
     </row>
@@ -9171,22 +9176,22 @@
       </c>
       <c r="B381" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C381" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D381" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F381" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the day it arrives (its date)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E381" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -9198,7 +9203,7 @@
       </c>
       <c r="B382" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">untilDay</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C382" s="1" t="inlineStr">
@@ -9213,7 +9218,7 @@
       </c>
       <c r="F382" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the last day it is in the inbox; 0 keeps it for the run</t>
+          <t xml:space="preserve">the day it arrives (its date)</t>
         </is>
       </c>
     </row>
@@ -9225,22 +9230,22 @@
       </c>
       <c r="B383" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flag</t>
+          <t xml:space="preserve">untilDay</t>
         </is>
       </c>
       <c r="C383" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D383" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F383" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a story flag it waits for (blank: none)</t>
+          <t xml:space="preserve">the last day it is in the inbox; 0 keeps it for the run</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9257,7 @@
       </c>
       <c r="B384" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">from</t>
+          <t xml:space="preserve">flag</t>
         </is>
       </c>
       <c r="C384" s="1" t="inlineStr">
@@ -9263,6 +9268,11 @@
       <c r="D384" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F384" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a story flag it waits for (blank: none)</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9284,7 @@
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">subject</t>
+          <t xml:space="preserve">from</t>
         </is>
       </c>
       <c r="C385" s="1" t="inlineStr">
@@ -9291,22 +9301,22 @@
     <row r="386">
       <c r="A386" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMailBody</t>
+          <t xml:space="preserve">pcMail</t>
+        </is>
+      </c>
+      <c r="B386" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subject</t>
         </is>
       </c>
       <c r="C386" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Values</t>
-        </is>
-      </c>
-      <c r="E386" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.mail[].body, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F386" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its paragraphs</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D386" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9316,24 +9326,19 @@
           <t xml:space="preserve">pcMailBody</t>
         </is>
       </c>
-      <c r="B387" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mail</t>
-        </is>
-      </c>
       <c r="C387" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D387" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Values</t>
         </is>
       </c>
       <c r="E387" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'pcMail' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.pc.mail[].body, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F387" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its paragraphs</t>
         </is>
       </c>
     </row>
@@ -9345,34 +9350,44 @@
       </c>
       <c r="B388" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">mail</t>
         </is>
       </c>
       <c r="C388" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D388" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E388" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'pcMail' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">pcMailBody</t>
+        </is>
+      </c>
+      <c r="B389" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C389" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E389" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.ui</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D389" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -9382,19 +9397,14 @@
           <t xml:space="preserve">ui</t>
         </is>
       </c>
-      <c r="B390" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">readingLanguage</t>
-        </is>
-      </c>
       <c r="C390" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D390" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E390" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.ui</t>
         </is>
       </c>
     </row>
@@ -9406,17 +9416,17 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">glossPercent</t>
+          <t xml:space="preserve">readingLanguage</t>
         </is>
       </c>
       <c r="C391" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D391" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9428,12 +9438,12 @@
       </c>
       <c r="B392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">labelMinScale</t>
+          <t xml:space="preserve">glossPercent</t>
         </is>
       </c>
       <c r="C392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D392" s="1" t="inlineStr">
@@ -9450,7 +9460,7 @@
       </c>
       <c r="B393" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.text</t>
+          <t xml:space="preserve">labelMinScale</t>
         </is>
       </c>
       <c r="C393" s="1" t="inlineStr">
@@ -9472,7 +9482,7 @@
       </c>
       <c r="B394" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.largeText</t>
+          <t xml:space="preserve">contrast.text</t>
         </is>
       </c>
       <c r="C394" s="1" t="inlineStr">
@@ -9494,7 +9504,7 @@
       </c>
       <c r="B395" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.glyph</t>
+          <t xml:space="preserve">contrast.largeText</t>
         </is>
       </c>
       <c r="C395" s="1" t="inlineStr">
@@ -9516,7 +9526,7 @@
       </c>
       <c r="B396" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.hint</t>
+          <t xml:space="preserve">contrast.glyph</t>
         </is>
       </c>
       <c r="C396" s="1" t="inlineStr">
@@ -9538,7 +9548,7 @@
       </c>
       <c r="B397" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.outline</t>
+          <t xml:space="preserve">contrast.hint</t>
         </is>
       </c>
       <c r="C397" s="1" t="inlineStr">
@@ -9560,7 +9570,7 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.minTextFillAlpha</t>
+          <t xml:space="preserve">contrast.outline</t>
         </is>
       </c>
       <c r="C398" s="1" t="inlineStr">
@@ -9582,34 +9592,39 @@
       </c>
       <c r="B399" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">latinFallbackFont</t>
+          <t xml:space="preserve">contrast.minTextFillAlpha</t>
         </is>
       </c>
       <c r="C399" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D399" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="B400" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">latinFallbackFont</t>
         </is>
       </c>
       <c r="C400" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E400" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.paletteMap, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D400" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9619,19 +9634,14 @@
           <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
-      <c r="B401" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">role</t>
-        </is>
-      </c>
       <c r="C401" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D401" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E401" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.paletteMap, in order</t>
         </is>
       </c>
     </row>
@@ -9643,7 +9653,7 @@
       </c>
       <c r="B402" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fill</t>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C402" s="1" t="inlineStr">
@@ -9665,17 +9675,17 @@
       </c>
       <c r="B403" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">alpha</t>
+          <t xml:space="preserve">fill</t>
         </is>
       </c>
       <c r="C403" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D403" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9687,17 +9697,17 @@
       </c>
       <c r="B404" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ink</t>
+          <t xml:space="preserve">alpha</t>
         </is>
       </c>
       <c r="C404" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D404" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9719,7 @@
       </c>
       <c r="B405" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">textClass</t>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C405" s="1" t="inlineStr">
@@ -9726,17 +9736,22 @@
     <row r="406">
       <c r="A406" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">uiPalette</t>
+        </is>
+      </c>
+      <c r="B406" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">textClass</t>
         </is>
       </c>
       <c r="C406" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E406" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.ui.neutral</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D406" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9746,19 +9761,14 @@
           <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
-      <c r="B407" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C407" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D407" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E407" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.ui.neutral</t>
         </is>
       </c>
     </row>
@@ -9770,7 +9780,7 @@
       </c>
       <c r="B408" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C408" s="1" t="inlineStr">
@@ -9792,7 +9802,7 @@
       </c>
       <c r="B409" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C409" s="1" t="inlineStr">
@@ -9814,17 +9824,17 @@
       </c>
       <c r="B410" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">runtimeFont</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C410" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D410" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9836,17 +9846,17 @@
       </c>
       <c r="B411" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">headingAdd</t>
+          <t xml:space="preserve">runtimeFont</t>
         </is>
       </c>
       <c r="C411" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D411" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9868,7 @@
       </c>
       <c r="B412" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">buttonAdd</t>
+          <t xml:space="preserve">headingAdd</t>
         </is>
       </c>
       <c r="C412" s="1" t="inlineStr">
@@ -9880,17 +9890,17 @@
       </c>
       <c r="B413" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">stripItalic</t>
+          <t xml:space="preserve">buttonAdd</t>
         </is>
       </c>
       <c r="C413" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D413" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9902,39 +9912,39 @@
       </c>
       <c r="B414" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wallpaper</t>
+          <t xml:space="preserve">stripItalic</t>
         </is>
       </c>
       <c r="C414" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D414" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiNeutral</t>
+        </is>
+      </c>
+      <c r="B415" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wallpaper</t>
         </is>
       </c>
       <c r="C415" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E415" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.fonts, in order</t>
-        </is>
-      </c>
-      <c r="F415" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D415" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9944,19 +9954,19 @@
           <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
-      <c r="B416" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">file</t>
-        </is>
-      </c>
       <c r="C416" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D416" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E416" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.fonts, in order</t>
+        </is>
+      </c>
+      <c r="F416" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
         </is>
       </c>
     </row>
@@ -9968,17 +9978,17 @@
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">face</t>
+          <t xml:space="preserve">file</t>
         </is>
       </c>
       <c r="C417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9990,17 +10000,17 @@
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">family</t>
+          <t xml:space="preserve">face</t>
         </is>
       </c>
       <c r="C418" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D418" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10022,7 @@
       </c>
       <c r="B419" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">style</t>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C419" s="1" t="inlineStr">
@@ -10029,17 +10039,22 @@
     <row r="420">
       <c r="A420" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
+          <t xml:space="preserve">neutralFonts</t>
+        </is>
+      </c>
+      <c r="B420" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">style</t>
         </is>
       </c>
       <c r="C420" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E420" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.seeds, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D420" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10049,19 +10064,14 @@
           <t xml:space="preserve">neutralSeeds</t>
         </is>
       </c>
-      <c r="B421" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
       <c r="C421" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D421" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E421" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.seeds, in order</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10083,7 @@
       </c>
       <c r="B422" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hex</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C422" s="1" t="inlineStr">
@@ -10090,17 +10100,22 @@
     <row r="423">
       <c r="A423" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">neutralSeeds</t>
+        </is>
+      </c>
+      <c r="B423" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C423" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E423" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.overrides, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D423" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10110,19 +10125,14 @@
           <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
-      <c r="B424" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">role</t>
-        </is>
-      </c>
       <c r="C424" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D424" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E424" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.overrides, in order</t>
         </is>
       </c>
     </row>
@@ -10134,7 +10144,7 @@
       </c>
       <c r="B425" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fill</t>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C425" s="1" t="inlineStr">
@@ -10156,7 +10166,7 @@
       </c>
       <c r="B426" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ink</t>
+          <t xml:space="preserve">fill</t>
         </is>
       </c>
       <c r="C426" s="1" t="inlineStr">
@@ -10173,17 +10183,22 @@
     <row r="427">
       <c r="A427" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
+          <t xml:space="preserve">neutralOverrides</t>
+        </is>
+      </c>
+      <c r="B427" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C427" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E427" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.art, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D427" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10193,19 +10208,14 @@
           <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
-      <c r="B428" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
       <c r="C428" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D428" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E428" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.art, in order</t>
         </is>
       </c>
     </row>
@@ -10217,7 +10227,7 @@
       </c>
       <c r="B429" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hex</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C429" s="1" t="inlineStr">
@@ -10234,17 +10244,22 @@
     <row r="430">
       <c r="A430" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">neutralArt</t>
+        </is>
+      </c>
+      <c r="B430" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C430" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E430" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.strings, in order; a row's name is key, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D430" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10254,24 +10269,14 @@
           <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
-      <c r="B431" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">key</t>
-        </is>
-      </c>
       <c r="C431" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D431" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E431" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.ui.strings, in order; a row's name is key, unique</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10288,7 @@
       </c>
       <c r="B432" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C432" s="1" t="inlineStr">
@@ -10293,7 +10298,12 @@
       </c>
       <c r="D432" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E432" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -10305,7 +10315,7 @@
       </c>
       <c r="B433" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gloss</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C433" s="1" t="inlineStr">
@@ -10327,7 +10337,7 @@
       </c>
       <c r="B434" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tier</t>
+          <t xml:space="preserve">gloss</t>
         </is>
       </c>
       <c r="C434" s="1" t="inlineStr">
@@ -10344,17 +10354,22 @@
     <row r="435">
       <c r="A435" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
+          <t xml:space="preserve">uiStrings</t>
+        </is>
+      </c>
+      <c r="B435" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tier</t>
         </is>
       </c>
       <c r="C435" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E435" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.languages, in order; a row's name is language, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D435" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10364,24 +10379,14 @@
           <t xml:space="preserve">uiLanguages</t>
         </is>
       </c>
-      <c r="B436" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">language</t>
-        </is>
-      </c>
       <c r="C436" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D436" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E436" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.ui.languages, in order; a row's name is language, unique</t>
         </is>
       </c>
     </row>
@@ -10393,34 +10398,44 @@
       </c>
       <c r="B437" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rtl</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C437" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D437" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E437" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
+          <t xml:space="preserve">uiLanguages</t>
+        </is>
+      </c>
+      <c r="B438" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rtl</t>
         </is>
       </c>
       <c r="C438" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E438" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.languages[].entries, in order; the first column names the parent row</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D438" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -10430,24 +10445,14 @@
           <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
-      <c r="B439" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">language</t>
-        </is>
-      </c>
       <c r="C439" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D439" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E439" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'uiLanguages' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.ui.languages[].entries, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -10459,22 +10464,22 @@
       </c>
       <c r="B440" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C440" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D440" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E440" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'uiStrings'</t>
+          <t xml:space="preserve">names the row of 'uiLanguages' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10491,7 @@
       </c>
       <c r="B441" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C441" s="1" t="inlineStr">
@@ -10497,23 +10502,33 @@
       <c r="D441" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E441" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'uiStrings'</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
+        </is>
+      </c>
+      <c r="B442" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C442" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E442" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.translation</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D442" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10523,19 +10538,14 @@
           <t xml:space="preserve">translation</t>
         </is>
       </c>
-      <c r="B443" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fromDay</t>
-        </is>
-      </c>
       <c r="C443" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D443" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E443" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.translation</t>
         </is>
       </c>
     </row>
@@ -10547,17 +10557,17 @@
       </c>
       <c r="B444" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">announce</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C444" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D444" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -10569,17 +10579,17 @@
       </c>
       <c r="B445" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.startDelay</t>
+          <t xml:space="preserve">announce</t>
         </is>
       </c>
       <c r="C445" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D445" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10601,7 @@
       </c>
       <c r="B446" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.letterInterval</t>
+          <t xml:space="preserve">flip.startDelay</t>
         </is>
       </c>
       <c r="C446" s="1" t="inlineStr">
@@ -10613,7 +10623,7 @@
       </c>
       <c r="B447" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.letterSeconds</t>
+          <t xml:space="preserve">flip.letterInterval</t>
         </is>
       </c>
       <c r="C447" s="1" t="inlineStr">
@@ -10635,12 +10645,12 @@
       </c>
       <c r="B448" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.scrambleSteps</t>
+          <t xml:space="preserve">flip.letterSeconds</t>
         </is>
       </c>
       <c r="C448" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D448" s="1" t="inlineStr">
@@ -10657,27 +10667,17 @@
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.slots</t>
+          <t xml:space="preserve">flip.scrambleSteps</t>
         </is>
       </c>
       <c r="C449" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D449" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E449" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F449" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">slots whose value stays English in untranslated speech</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="B450" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.words</t>
+          <t xml:space="preserve">keyWords.slots</t>
         </is>
       </c>
       <c r="C450" s="1" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="F450" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">words that stay English in untranslated speech</t>
+          <t xml:space="preserve">slots whose value stays English in untranslated speech</t>
         </is>
       </c>
     </row>
@@ -10721,17 +10721,27 @@
       </c>
       <c r="B451" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.digits</t>
+          <t xml:space="preserve">keyWords.words</t>
         </is>
       </c>
       <c r="C451" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D451" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E451" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F451" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">words that stay English in untranslated speech</t>
         </is>
       </c>
     </row>
@@ -10743,34 +10753,39 @@
       </c>
       <c r="B452" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fallbackGlyphs</t>
+          <t xml:space="preserve">keyWords.digits</t>
         </is>
       </c>
       <c r="C452" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D452" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
+          <t xml:space="preserve">translation</t>
+        </is>
+      </c>
+      <c r="B453" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fallbackGlyphs</t>
         </is>
       </c>
       <c r="C453" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E453" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.scripts, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D453" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10780,24 +10795,14 @@
           <t xml:space="preserve">scripts</t>
         </is>
       </c>
-      <c r="B454" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C454" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D454" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E454" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.translation.scripts, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -10809,39 +10814,44 @@
       </c>
       <c r="B455" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rightToLeft</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C455" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D455" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E455" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">scripts</t>
+        </is>
+      </c>
+      <c r="B456" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rightToLeft</t>
         </is>
       </c>
       <c r="C456" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E456" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.scripts[].fonts, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F456" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D456" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -10851,24 +10861,19 @@
           <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
-      <c r="B457" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">script</t>
-        </is>
-      </c>
       <c r="C457" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D457" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E457" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'scripts' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.translation.scripts[].fonts, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F457" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
         </is>
       </c>
     </row>
@@ -10880,17 +10885,22 @@
       </c>
       <c r="B458" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">file</t>
+          <t xml:space="preserve">script</t>
         </is>
       </c>
       <c r="C458" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D458" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E458" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'scripts' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -10902,17 +10912,17 @@
       </c>
       <c r="B459" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">face</t>
+          <t xml:space="preserve">file</t>
         </is>
       </c>
       <c r="C459" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D459" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10924,17 +10934,17 @@
       </c>
       <c r="B460" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">family</t>
+          <t xml:space="preserve">face</t>
         </is>
       </c>
       <c r="C460" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D460" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -10946,7 +10956,7 @@
       </c>
       <c r="B461" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">style</t>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C461" s="1" t="inlineStr">
@@ -10963,17 +10973,22 @@
     <row r="462">
       <c r="A462" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">scriptFonts</t>
+        </is>
+      </c>
+      <c r="B462" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">style</t>
         </is>
       </c>
       <c r="C462" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E462" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.packs, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D462" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10983,24 +10998,14 @@
           <t xml:space="preserve">packs</t>
         </is>
       </c>
-      <c r="B463" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C463" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D463" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E463" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.translation.packs, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -11012,7 +11017,7 @@
       </c>
       <c r="B464" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C464" s="1" t="inlineStr">
@@ -11022,7 +11027,12 @@
       </c>
       <c r="D464" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E464" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -11034,34 +11044,39 @@
       </c>
       <c r="B465" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">spokenCost</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C465" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D465" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">packs</t>
+        </is>
+      </c>
+      <c r="B466" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spokenCost</t>
         </is>
       </c>
       <c r="C466" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E466" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D466" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -11071,24 +11086,14 @@
           <t xml:space="preserve">tongues</t>
         </is>
       </c>
-      <c r="B467" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C467" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D467" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E467" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -11100,7 +11105,7 @@
       </c>
       <c r="B468" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C468" s="1" t="inlineStr">
@@ -11110,7 +11115,12 @@
       </c>
       <c r="D468" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E468" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11132,7 @@
       </c>
       <c r="B469" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">script</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C469" s="1" t="inlineStr">
@@ -11133,11 +11143,6 @@
       <c r="D469" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E469" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'scripts'</t>
         </is>
       </c>
     </row>
@@ -11149,7 +11154,7 @@
       </c>
       <c r="B470" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pack</t>
+          <t xml:space="preserve">script</t>
         </is>
       </c>
       <c r="C470" s="1" t="inlineStr">
@@ -11164,7 +11169,7 @@
       </c>
       <c r="E470" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'packs'</t>
+          <t xml:space="preserve">names a row of 'scripts'</t>
         </is>
       </c>
     </row>
@@ -11176,15 +11181,42 @@
       </c>
       <c r="B471" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">pack</t>
+        </is>
+      </c>
+      <c r="C471" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D471" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E471" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'packs'</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B472" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">glyphs</t>
         </is>
       </c>
-      <c r="C471" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D471" s="1" t="inlineStr">
+      <c r="C472" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D472" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
         </is>
@@ -14679,11 +14711,12 @@
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="39" style="1" customWidth="1"/>
-    <col min="7" max="7" width="46" style="1" customWidth="1"/>
-    <col min="8" max="8" width="32" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="6" max="6" width="47" style="1" customWidth="1"/>
+    <col min="7" max="7" width="39" style="1" customWidth="1"/>
+    <col min="8" max="8" width="46" style="1" customWidth="1"/>
+    <col min="9" max="9" width="32" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14714,25 +14747,30 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">lies</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">countries</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">rules</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">premades</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">premadeChance</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">costumeErrorChance</t>
         </is>
@@ -14760,13 +14798,23 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">PoorPosingAsRich|DoctoredIdentity|FalseOrigin</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">egypt|iraq|greece|italy</t>
         </is>
       </c>
-      <c r="I2">
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rule_LeisureDepartures</t>
+        </is>
+      </c>
+      <c r="J2">
         <v>0.05</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.0</v>
       </c>
     </row>
@@ -14792,23 +14840,28 @@
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">FalseOrigin</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">egypt|iraq|greece|italy|china|britain</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Rule_NoAncientEgypt|Rule_DressForDestination</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">aspasia|banzhao|arib|khwarizmi</t>
         </is>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.05</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.1</v>
       </c>
     </row>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -4498,7 +4498,7 @@
       </c>
       <c r="F187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the lies enabled this day (FalseOrigin, PoorPosingAsRich, DoctoredIdentity); a traveller draws among those that fit their kind</t>
+          <t xml:space="preserve">the lies enabled this day (FalseOrigin, PoorPosingAsRich, DoctoredIdentity, FakeDisplaced); a traveller draws among those that fit their kind</t>
         </is>
       </c>
     </row>
@@ -14711,10 +14711,10 @@
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="47" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35" style="1" customWidth="1"/>
     <col min="7" max="7" width="39" style="1" customWidth="1"/>
     <col min="8" max="8" width="46" style="1" customWidth="1"/>
-    <col min="9" max="9" width="32" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10" style="1" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
   </cols>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PoorPosingAsRich|DoctoredIdentity|FalseOrigin</t>
+          <t xml:space="preserve">PoorPosingAsRich|DoctoredIdentity</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
@@ -14812,7 +14812,7 @@
         </is>
       </c>
       <c r="J2">
-        <v>0.05</v>
+        <v>0.0</v>
       </c>
       <c r="K2">
         <v>0.0</v>
@@ -14840,7 +14840,7 @@
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">FalseOrigin</t>
+          <t xml:space="preserve">PoorPosingAsRich|DoctoredIdentity</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
@@ -14853,13 +14853,8 @@
           <t xml:space="preserve">Rule_NoAncientEgypt|Rule_DressForDestination</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aspasia|banzhao|arib|khwarizmi</t>
-        </is>
-      </c>
       <c r="J3">
-        <v>0.05</v>
+        <v>0.0</v>
       </c>
       <c r="K3">
         <v>0.1</v>
@@ -14913,31 +14908,16 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Displaced</t>
+          <t xml:space="preserve">RichTourist</t>
         </is>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Displaced</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -15025,7 +15005,7 @@
   <cols>
     <col min="1" max="1" width="8" style="1" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="10" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15048,36 +15028,6 @@
       <c r="D1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">blueprint</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">senenmut</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">socrates</t>
         </is>
       </c>
     </row>
@@ -19737,11 +19687,11 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Budget cuts close the interpreter pool. From today, foreign speech reaches the desk untranslated but for its key words; translators are sold at Home. Papers are still filled in English.</t>
+          <t xml:space="preserve">Budget cuts close the interpreter pool. From tomorrow, the displaced reach the desk speaking their own tongues, untranslated but for their key words; Speech translators are sold at Home tonight. Papers are still filled in English.</t>
         </is>
       </c>
       <c r="C2">

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -4498,7 +4498,7 @@
       </c>
       <c r="F187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the lies enabled this day (FalseOrigin, PoorPosingAsRich, DoctoredIdentity); a traveller draws among those that fit their kind</t>
+          <t xml:space="preserve">the lies enabled this day (FalseOrigin, PoorPosingAsRich, DoctoredIdentity, Smuggling); a traveller draws among those that fit their kind</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">guarantee</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -4574,17 +4574,17 @@
       </c>
       <c r="D190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
         </is>
       </c>
       <c r="E190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">each item names a row of 'premades'; separate items with |</t>
+          <t xml:space="preserve">each item names a row of 'rules'; separate items with |</t>
         </is>
       </c>
       <c r="F190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades that may roll this day</t>
+          <t xml:space="preserve">the standing procedures guaranteed one faulty traveller today, their first day (NoPresentGoods: a smuggler; PaperDates: a falsified date); each among the day's rules</t>
         </is>
       </c>
     </row>
@@ -4596,17 +4596,27 @@
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeChance</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D191" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E191" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">each item names a row of 'premades'; separate items with |</t>
+        </is>
+      </c>
+      <c r="F191" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">premades that may roll this day</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4628,7 @@
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">costumeErrorChance</t>
+          <t xml:space="preserve">premadeChance</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
@@ -4629,33 +4639,33 @@
       <c r="D192" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F192" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chance per 2150 citizen of a costume error (0 before the dress rule's first day)</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayKinds</t>
+          <t xml:space="preserve">days</t>
+        </is>
+      </c>
+      <c r="B193" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">costumeErrorChance</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E193" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.days[].kinds, in order; the first column names the parent row</t>
+          <t xml:space="preserve">decimal</t>
+        </is>
+      </c>
+      <c r="D193" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the day's traveller mix: each kind's weight</t>
+          <t xml:space="preserve">chance per 2150 citizen of a costume error (0 before the dress rule's first day)</t>
         </is>
       </c>
     </row>
@@ -4665,24 +4675,19 @@
           <t xml:space="preserve">dayKinds</t>
         </is>
       </c>
-      <c r="B194" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">day</t>
-        </is>
-      </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D194" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.days[].kinds, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F194" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the day's traveller mix: each kind's weight</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4699,12 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">day</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D195" s="1" t="inlineStr">
@@ -4709,7 +4714,7 @@
       </c>
       <c r="E195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
+          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -4721,34 +4726,44 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E196" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayEras</t>
+          <t xml:space="preserve">dayKinds</t>
+        </is>
+      </c>
+      <c r="B197" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weight</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E197" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.days[].eras, in order; the first column names the parent row</t>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D197" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -4758,24 +4773,14 @@
           <t xml:space="preserve">dayEras</t>
         </is>
       </c>
-      <c r="B198" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">day</t>
-        </is>
-      </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D198" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E198" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.days[].eras, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -4787,22 +4792,22 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">day</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'eras'</t>
+          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -4814,34 +4819,44 @@
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E200" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'eras'</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dayForced</t>
+          <t xml:space="preserve">dayEras</t>
+        </is>
+      </c>
+      <c r="B201" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weight</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E201" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.days[].forced, in order; the first column names the parent row</t>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D201" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -4851,24 +4866,14 @@
           <t xml:space="preserve">dayForced</t>
         </is>
       </c>
-      <c r="B202" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">day</t>
-        </is>
-      </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D202" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.days[].forced, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -4880,17 +4885,22 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">slot</t>
+          <t xml:space="preserve">day</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E203" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'days' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -4902,22 +4912,17 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premade</t>
+          <t xml:space="preserve">slot</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D204" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E204" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'premades'</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4934,7 @@
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">blueprint</t>
+          <t xml:space="preserve">premade</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
@@ -4940,28 +4945,33 @@
       <c r="D205" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E205" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'premades'</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interview</t>
+          <t xml:space="preserve">dayForced</t>
+        </is>
+      </c>
+      <c r="B206" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blueprint</t>
         </is>
       </c>
       <c r="C206" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E206" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.interview</t>
-        </is>
-      </c>
-      <c r="F206" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the interview's wording</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D206" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -4971,19 +4981,19 @@
           <t xml:space="preserve">interview</t>
         </is>
       </c>
-      <c r="B207" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deskName</t>
-        </is>
-      </c>
       <c r="C207" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D207" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E207" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.interview</t>
+        </is>
+      </c>
+      <c r="F207" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the interview's wording</t>
         </is>
       </c>
     </row>
@@ -4995,7 +5005,7 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">opener</t>
+          <t xml:space="preserve">deskName</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
@@ -5017,7 +5027,7 @@
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">openerLegendary</t>
+          <t xml:space="preserve">opener</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr">
@@ -5039,7 +5049,7 @@
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificMale</t>
+          <t xml:space="preserve">openerLegendary</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
@@ -5061,7 +5071,7 @@
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificFemale</t>
+          <t xml:space="preserve">honorificMale</t>
         </is>
       </c>
       <c r="C211" s="1" t="inlineStr">
@@ -5083,7 +5093,7 @@
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">honorificUnknown</t>
+          <t xml:space="preserve">honorificFemale</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
@@ -5105,7 +5115,7 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">requestLabel</t>
+          <t xml:space="preserve">honorificUnknown</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
@@ -5127,7 +5137,7 @@
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">papersLabel</t>
+          <t xml:space="preserve">requestLabel</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
@@ -5138,11 +5148,6 @@
       <c r="D214" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F214" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the hub entry that opens the papers menu</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5159,7 @@
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">requestPrompt</t>
+          <t xml:space="preserve">papersLabel</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
@@ -5165,6 +5170,11 @@
       <c r="D215" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F215" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the hub entry that opens the papers menu</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5186,7 @@
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">requestReply</t>
+          <t xml:space="preserve">requestPrompt</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
@@ -5198,7 +5208,7 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">askLabel</t>
+          <t xml:space="preserve">requestReply</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
@@ -5220,7 +5230,7 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">backLabel</t>
+          <t xml:space="preserve">askLabel</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
@@ -5231,6 +5241,11 @@
       <c r="D218" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F218" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the ask entry for the displaced</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5257,7 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">smallTalkLabel</t>
+          <t xml:space="preserve">tripAskLabel</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr">
@@ -5253,6 +5268,11 @@
       <c r="D219" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F219" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the ask entry for a 2150 citizen, who is asked about the trip</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5284,7 @@
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">smallTalkPrompt</t>
+          <t xml:space="preserve">backLabel</t>
         </is>
       </c>
       <c r="C220" s="1" t="inlineStr">
@@ -5286,17 +5306,17 @@
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">menuCapacity</t>
+          <t xml:space="preserve">smallTalkLabel</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5308,17 +5328,17 @@
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">maxLineChars</t>
+          <t xml:space="preserve">smallTalkPrompt</t>
         </is>
       </c>
       <c r="C222" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D222" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5330,51 +5350,51 @@
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lookLabel</t>
+          <t xml:space="preserve">menuCapacity</t>
         </is>
       </c>
       <c r="C223" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D223" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">claims</t>
+          <t xml:space="preserve">interview</t>
+        </is>
+      </c>
+      <c r="B224" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maxLineChars</t>
         </is>
       </c>
       <c r="C224" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E224" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.interview.claims, in order</t>
-        </is>
-      </c>
-      <c r="F224" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the claim per traveller kind ({place}): one row per kind a blueprint makes</t>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D224" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">claims</t>
+          <t xml:space="preserve">interview</t>
         </is>
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">lookLabel</t>
         </is>
       </c>
       <c r="C225" s="1" t="inlineStr">
@@ -5384,12 +5404,7 @@
       </c>
       <c r="D225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E225" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5399,53 +5414,58 @@
           <t xml:space="preserve">claims</t>
         </is>
       </c>
-      <c r="B226" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
       <c r="C226" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D226" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E226" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.interview.claims, in order</t>
+        </is>
+      </c>
+      <c r="F226" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the claim per traveller kind ({place}): one row per kind a blueprint makes</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interviewRequests</t>
+          <t xml:space="preserve">claims</t>
+        </is>
+      </c>
+      <c r="B227" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C227" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D227" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E227" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.interview.requests, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F227" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spoken requests: the wheel entry, the desk's prompt and the traveller's reply</t>
+          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interviewRequests</t>
+          <t xml:space="preserve">claims</t>
         </is>
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C228" s="1" t="inlineStr">
@@ -5455,12 +5475,7 @@
       </c>
       <c r="D228" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E228" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5470,19 +5485,19 @@
           <t xml:space="preserve">interviewRequests</t>
         </is>
       </c>
-      <c r="B229" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">label</t>
-        </is>
-      </c>
       <c r="C229" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D229" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E229" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.interview.requests, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F229" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spoken requests: the wheel entry, the desk's prompt and the traveller's reply</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5509,7 @@
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C230" s="1" t="inlineStr">
@@ -5504,7 +5519,12 @@
       </c>
       <c r="D230" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E230" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5536,7 @@
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">reply</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C231" s="1" t="inlineStr">
@@ -5533,29 +5553,34 @@
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
+          <t xml:space="preserve">interviewRequests</t>
+        </is>
+      </c>
+      <c r="B232" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C232" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E232" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.questions, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D232" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
+          <t xml:space="preserve">interviewRequests</t>
         </is>
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">reply</t>
         </is>
       </c>
       <c r="C233" s="1" t="inlineStr">
@@ -5565,12 +5590,7 @@
       </c>
       <c r="D233" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E233" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5580,19 +5600,14 @@
           <t xml:space="preserve">questions</t>
         </is>
       </c>
-      <c r="B234" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">category</t>
-        </is>
-      </c>
       <c r="C234" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D234" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E234" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.questions, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5619,7 @@
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C235" s="1" t="inlineStr">
@@ -5614,7 +5629,12 @@
       </c>
       <c r="D235" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E235" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5646,7 @@
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C236" s="1" t="inlineStr">
@@ -5648,17 +5668,27 @@
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">kinds</t>
         </is>
       </c>
       <c r="C237" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D237" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E237" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F237" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the traveller kinds the desk asks it of (RichTourist, PoorTourist, Labourer, Displaced); blank: every kind; one question per category per kind</t>
         </is>
       </c>
     </row>
@@ -5670,17 +5700,17 @@
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5722,7 @@
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">announce</t>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C239" s="1" t="inlineStr">
@@ -5709,61 +5739,56 @@
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questions</t>
+        </is>
+      </c>
+      <c r="B240" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">answer</t>
         </is>
       </c>
       <c r="C240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E240" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.questions[].conditions, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F240" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all must pass</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D240" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questions</t>
         </is>
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">question</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C241" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D241" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E241" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questions</t>
         </is>
       </c>
       <c r="B242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">announce</t>
         </is>
       </c>
       <c r="C242" s="1" t="inlineStr">
@@ -5773,7 +5798,7 @@
       </c>
       <c r="D242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5783,19 +5808,19 @@
           <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
-      <c r="B243" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">key</t>
-        </is>
-      </c>
       <c r="C243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D243" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E243" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.questions[].conditions, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F243" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all must pass</t>
         </is>
       </c>
     </row>
@@ -5807,17 +5832,22 @@
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">question</t>
         </is>
       </c>
       <c r="C244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E244" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5859,7 @@
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C245" s="1" t="inlineStr">
@@ -5839,12 +5869,7 @@
       </c>
       <c r="D245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E245" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5881,7 @@
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C246" s="1" t="inlineStr">
@@ -5866,12 +5891,7 @@
       </c>
       <c r="D246" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E246" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5883,83 +5903,83 @@
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E247" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
+          <t xml:space="preserve">questionConditions</t>
+        </is>
+      </c>
+      <c r="B248" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D248" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.questions[].overrides, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F248" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the wording in one era</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
+          <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">question</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
+          <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
       <c r="B250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C250" s="1" t="inlineStr">
@@ -5969,12 +5989,12 @@
       </c>
       <c r="D250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'eras'</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
@@ -5984,19 +6004,19 @@
           <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
-      <c r="B251" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prompt</t>
-        </is>
-      </c>
       <c r="C251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D251" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E251" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.questions[].overrides, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F251" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the wording in one era</t>
         </is>
       </c>
     </row>
@@ -6008,51 +6028,61 @@
       </c>
       <c r="B252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">question</t>
         </is>
       </c>
       <c r="C252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E252" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
+          <t xml:space="preserve">questionOverrides</t>
+        </is>
+      </c>
+      <c r="B253" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D253" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F253" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">narrative dialogs: nodes, their lines and the player's choices</t>
+          <t xml:space="preserve">names a row of 'eras'</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
+          <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C254" s="1" t="inlineStr">
@@ -6062,24 +6092,19 @@
       </c>
       <c r="D254" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E254" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
+          <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">answer</t>
         </is>
       </c>
       <c r="C255" s="1" t="inlineStr">
@@ -6090,11 +6115,6 @@
       <c r="D255" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F255" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the wheel entry</t>
         </is>
       </c>
     </row>
@@ -6104,90 +6124,95 @@
           <t xml:space="preserve">dialogs</t>
         </is>
       </c>
-      <c r="B256" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">repeatable</t>
-        </is>
-      </c>
       <c r="C256" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
-        </is>
-      </c>
-      <c r="D256" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E256" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F256" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrative dialogs: nodes, their lines and the player's choices</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
+          <t xml:space="preserve">dialogs</t>
+        </is>
+      </c>
+      <c r="B257" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D257" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].conditions, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F257" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all must pass</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
+          <t xml:space="preserve">dialogs</t>
         </is>
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E258" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F258" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the wheel entry</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
+          <t xml:space="preserve">dialogs</t>
         </is>
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">repeatable</t>
         </is>
       </c>
       <c r="C259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -6197,19 +6222,19 @@
           <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
-      <c r="B260" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">key</t>
-        </is>
-      </c>
       <c r="C260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D260" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E260" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].conditions, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F260" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all must pass</t>
         </is>
       </c>
     </row>
@@ -6221,17 +6246,22 @@
       </c>
       <c r="B261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E261" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6273,7 @@
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C262" s="1" t="inlineStr">
@@ -6253,12 +6283,7 @@
       </c>
       <c r="D262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E262" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6295,7 @@
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C263" s="1" t="inlineStr">
@@ -6280,12 +6305,7 @@
       </c>
       <c r="D263" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E263" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6297,78 +6317,83 @@
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E264" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogNodes</t>
+          <t xml:space="preserve">dialogConditions</t>
+        </is>
+      </c>
+      <c r="B265" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D265" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes, in order; a row's name is id, unique per parent row; the first column names the parent row</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogNodes</t>
+          <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogNodes</t>
+          <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C267" s="1" t="inlineStr">
@@ -6378,19 +6403,19 @@
       </c>
       <c r="D267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
+          <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
       <c r="C268" s="1" t="inlineStr">
@@ -6400,14 +6425,14 @@
       </c>
       <c r="E268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].lines, in order; the first columns name the parent row</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes, in order; a row's name is id, unique per parent row; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
+          <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
       <c r="B269" s="1" t="inlineStr">
@@ -6434,17 +6459,17 @@
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
+          <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D270" s="1" t="inlineStr">
@@ -6454,7 +6479,7 @@
       </c>
       <c r="E270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -6464,19 +6489,14 @@
           <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
-      <c r="B271" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C271" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D271" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E271" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].lines, in order; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -6488,17 +6508,22 @@
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">speaker</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E272" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6510,17 +6535,22 @@
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">expression</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E273" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6562,7 @@
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
@@ -6549,71 +6579,66 @@
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">dialogLines</t>
+        </is>
+      </c>
+      <c r="B275" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">speaker</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E275" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices, in order; a row's name is id, unique per parent row; the first columns name the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D275" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">expression</t>
         </is>
       </c>
       <c r="C276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E276" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E277" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6623,24 +6648,14 @@
           <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
-      <c r="B278" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D278" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices, in order; a row's name is id, unique per parent row; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -6652,17 +6667,22 @@
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D279" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E279" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6674,22 +6694,22 @@
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">next</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F280" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the node it leads to (blank: the dialog ends)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E280" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6721,7 @@
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">effect</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C281" s="1" t="inlineStr">
@@ -6711,78 +6731,83 @@
       </c>
       <c r="D281" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E281" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">dialogChoices</t>
+        </is>
+      </c>
+      <c r="B282" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E282" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices[].lines, in order; the first columns name the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D282" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">next</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E283" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F283" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the node it leads to (blank: the dialog ends)</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">effect</t>
         </is>
       </c>
       <c r="C284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E284" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6792,24 +6817,14 @@
           <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
-      <c r="B285" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">choice</t>
-        </is>
-      </c>
       <c r="C285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D285" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogChoices' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices[].lines, in order; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -6821,17 +6836,22 @@
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C286" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D286" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E286" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6843,17 +6863,22 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">speaker</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E287" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6865,17 +6890,22 @@
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">expression</t>
+          <t xml:space="preserve">choice</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D288" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E288" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogChoices' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6917,7 @@
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C289" s="1" t="inlineStr">
@@ -6904,34 +6934,34 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">choiceLines</t>
+        </is>
+      </c>
+      <c r="B290" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">speaker</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E290" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.premades, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F290" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">premade characters: real people and written stories</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D290" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">expression</t>
         </is>
       </c>
       <c r="C291" s="1" t="inlineStr">
@@ -6941,24 +6971,19 @@
       </c>
       <c r="D291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E291" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
@@ -6978,19 +7003,19 @@
           <t xml:space="preserve">premades</t>
         </is>
       </c>
-      <c r="B293" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gender</t>
-        </is>
-      </c>
       <c r="C293" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D293" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E293" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.premades, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F293" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">premade characters: real people and written stories</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7027,7 @@
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C294" s="1" t="inlineStr">
@@ -7012,12 +7037,12 @@
       </c>
       <c r="D294" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E294" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7054,7 @@
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">truePlace</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
@@ -7040,16 +7065,6 @@
       <c r="D295" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E295" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
-        </is>
-      </c>
-      <c r="F295" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">where they really come from (blank: honest)</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7076,7 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">birthDate</t>
+          <t xml:space="preserve">gender</t>
         </is>
       </c>
       <c r="C296" s="1" t="inlineStr">
@@ -7083,7 +7098,7 @@
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">archetype</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C297" s="1" t="inlineStr">
@@ -7094,6 +7109,11 @@
       <c r="D297" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E297" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -7105,7 +7125,7 @@
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">intro</t>
+          <t xml:space="preserve">truePlace</t>
         </is>
       </c>
       <c r="C298" s="1" t="inlineStr">
@@ -7116,6 +7136,16 @@
       <c r="D298" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E298" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
+        </is>
+      </c>
+      <c r="F298" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">where they really come from (blank: honest)</t>
         </is>
       </c>
     </row>
@@ -7127,7 +7157,7 @@
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">recordNote</t>
+          <t xml:space="preserve">birthDate</t>
         </is>
       </c>
       <c r="C299" s="1" t="inlineStr">
@@ -7149,7 +7179,7 @@
       </c>
       <c r="B300" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">archetype</t>
         </is>
       </c>
       <c r="C300" s="1" t="inlineStr">
@@ -7160,11 +7190,6 @@
       <c r="D300" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E300" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'dialogs'</t>
         </is>
       </c>
     </row>
@@ -7176,88 +7201,88 @@
       </c>
       <c r="B301" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">repeatable</t>
+          <t xml:space="preserve">intro</t>
         </is>
       </c>
       <c r="C301" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D301" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">premades</t>
+        </is>
+      </c>
+      <c r="B302" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">recordNote</t>
         </is>
       </c>
       <c r="C302" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E302" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.premades[].impacts, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D302" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premade</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'premades' this row belongs to</t>
+          <t xml:space="preserve">names a row of 'dialogs'</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">repeatable</t>
         </is>
       </c>
       <c r="C304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E304" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -7267,19 +7292,14 @@
           <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
-      <c r="B305" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">onCorrect</t>
-        </is>
-      </c>
       <c r="C305" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
-        </is>
-      </c>
-      <c r="D305" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E305" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.premades[].impacts, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -7291,17 +7311,22 @@
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">onWrong</t>
+          <t xml:space="preserve">premade</t>
         </is>
       </c>
       <c r="C306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E306" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'premades' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7313,78 +7338,88 @@
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">skipNationScore</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E307" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">premadeImpacts</t>
+        </is>
+      </c>
+      <c r="B308" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">onCorrect</t>
         </is>
       </c>
       <c r="C308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E308" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.history</t>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D308" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.leaderGained</t>
+          <t xml:space="preserve">onWrong</t>
         </is>
       </c>
       <c r="C309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
       <c r="B310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.leaderLost</t>
+          <t xml:space="preserve">skipNationScore</t>
         </is>
       </c>
       <c r="C310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -7394,19 +7429,14 @@
           <t xml:space="preserve">history</t>
         </is>
       </c>
-      <c r="B311" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lines.carry</t>
-        </is>
-      </c>
       <c r="C311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D311" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E311" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.history</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7448,7 @@
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.dominant</t>
+          <t xml:space="preserve">lines.leaderGained</t>
         </is>
       </c>
       <c r="C312" s="1" t="inlineStr">
@@ -7429,11 +7459,6 @@
       <c r="D312" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F312" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">an attribute becomes dominant in a place: {attribute} and {place}</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7470,7 @@
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.panic</t>
+          <t xml:space="preserve">lines.leaderLost</t>
         </is>
       </c>
       <c r="C313" s="1" t="inlineStr">
@@ -7456,45 +7481,40 @@
       <c r="D313" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F313" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">an accepted costume error caused a panic: {place} and {value} (the wrong item)</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyRules</t>
+          <t xml:space="preserve">history</t>
+        </is>
+      </c>
+      <c r="B314" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lines.carry</t>
         </is>
       </c>
       <c r="C314" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E314" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F314" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">history rules: when their conditions pass at night they rewrite a place's fact</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D314" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyRules</t>
+          <t xml:space="preserve">history</t>
         </is>
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">lines.dominant</t>
         </is>
       </c>
       <c r="C315" s="1" t="inlineStr">
@@ -7504,24 +7524,24 @@
       </c>
       <c r="D315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E315" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F315" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">an attribute becomes dominant in a place: {attribute} and {place}</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyRules</t>
+          <t xml:space="preserve">history</t>
         </is>
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">lines.panic</t>
         </is>
       </c>
       <c r="C316" s="1" t="inlineStr">
@@ -7532,6 +7552,11 @@
       <c r="D316" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F316" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">an accepted costume error caused a panic: {place} and {value} (the wrong item)</t>
         </is>
       </c>
     </row>
@@ -7541,75 +7566,80 @@
           <t xml:space="preserve">historyRules</t>
         </is>
       </c>
-      <c r="B317" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">news</t>
-        </is>
-      </c>
       <c r="C317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D317" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E317" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.history.rules, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F317" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">history rules: when their conditions pass at night they rewrite a place's fact</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
+          <t xml:space="preserve">historyRules</t>
+        </is>
+      </c>
+      <c r="B318" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C318" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D318" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E318" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules[].conditions, in order; the first column names the parent row</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
+          <t xml:space="preserve">historyRules</t>
         </is>
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rule</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E319" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
+          <t xml:space="preserve">historyRules</t>
         </is>
       </c>
       <c r="B320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">news</t>
         </is>
       </c>
       <c r="C320" s="1" t="inlineStr">
@@ -7619,7 +7649,7 @@
       </c>
       <c r="D320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7629,19 +7659,14 @@
           <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
-      <c r="B321" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">key</t>
-        </is>
-      </c>
       <c r="C321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D321" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E321" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.history.rules[].conditions, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -7653,22 +7678,22 @@
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">rule</t>
         </is>
       </c>
       <c r="C322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7680,7 +7705,7 @@
       </c>
       <c r="B323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C323" s="1" t="inlineStr">
@@ -7690,12 +7715,7 @@
       </c>
       <c r="D323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E323" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7727,7 @@
       </c>
       <c r="B324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C324" s="1" t="inlineStr">
@@ -7718,11 +7738,6 @@
       <c r="D324" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E324" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
@@ -7734,88 +7749,98 @@
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (left out of the JSON)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E325" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
+          <t xml:space="preserve">historyConditions</t>
+        </is>
+      </c>
+      <c r="B326" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C326" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D326" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E326" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules[].edits, in order; the first column names the parent row</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
+          <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rule</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
+          <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E328" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">0 (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -7825,19 +7850,14 @@
           <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
-      <c r="B329" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">category</t>
-        </is>
-      </c>
       <c r="C329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D329" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E329" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.history.rules[].edits, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -7849,51 +7869,61 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">rule</t>
         </is>
       </c>
       <c r="C330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E330" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">newsDebt</t>
+          <t xml:space="preserve">historyEdits</t>
+        </is>
+      </c>
+      <c r="B331" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Values</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D331" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.news.debt, in order</t>
-        </is>
-      </c>
-      <c r="F331" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the morning paper's debt lines: one a day, in a shuffled order per run</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">newsDebt</t>
+          <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
       <c r="B332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C332" s="1" t="inlineStr">
@@ -7903,137 +7933,117 @@
       </c>
       <c r="D332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pc</t>
+          <t xml:space="preserve">historyEdits</t>
+        </is>
+      </c>
+      <c r="B333" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">value</t>
         </is>
       </c>
       <c r="C333" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E333" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.pc</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D333" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pc</t>
-        </is>
-      </c>
-      <c r="B334" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ancestry.includePremades</t>
+          <t xml:space="preserve">newsDebt</t>
         </is>
       </c>
       <c r="C334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
-        </is>
-      </c>
-      <c r="D334" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">Values</t>
+        </is>
+      </c>
+      <c r="E334" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.news.debt, in order</t>
         </is>
       </c>
       <c r="F334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the premades who are who they claim get cards</t>
+          <t xml:space="preserve">the morning paper's debt lines: one a day, in a shuffled order per run</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcStepSets</t>
+          <t xml:space="preserve">newsDebt</t>
+        </is>
+      </c>
+      <c r="B335" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E335" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.steps.sets, in order; a row's name is type, unique</t>
-        </is>
-      </c>
-      <c r="F335" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the optional steps checklist, one set per traveller kind</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D335" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcStepSets</t>
-        </is>
-      </c>
-      <c r="B336" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">pc</t>
         </is>
       </c>
       <c r="C336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D336" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Single</t>
         </is>
       </c>
       <c r="E336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name; one of: default, RichTourist, PoorTourist, Labourer, Displaced</t>
-        </is>
-      </c>
-      <c r="F336" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a traveller kind, or default: the steps of a kind with no set of its own</t>
+          <t xml:space="preserve">one row: the object $.pc</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcStepSets</t>
+          <t xml:space="preserve">pc</t>
         </is>
       </c>
       <c r="B337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">inherit</t>
+          <t xml:space="preserve">ancestry.includePremades</t>
         </is>
       </c>
       <c r="C337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E337" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'pcStepSets'</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="F337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the set whose steps it starts from; its own step of the same id replaces the parent's (blank: none)</t>
+          <t xml:space="preserve">the premades who are who they claim get cards</t>
         </is>
       </c>
     </row>
@@ -8043,100 +8053,110 @@
           <t xml:space="preserve">pcStepSets</t>
         </is>
       </c>
-      <c r="B338" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dataOnly</t>
-        </is>
-      </c>
       <c r="C338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
-        </is>
-      </c>
-      <c r="D338" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E338" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.steps.sets, in order; a row's name is type, unique</t>
         </is>
       </c>
       <c r="F338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true while the kind is not in play yet: its forms and categories may name what a later phase adds</t>
+          <t xml:space="preserve">the optional steps checklist, one set per traveller kind</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSteps</t>
+          <t xml:space="preserve">pcStepSets</t>
+        </is>
+      </c>
+      <c r="B339" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D339" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.steps.sets[].steps, in order; the first column names the parent row</t>
+          <t xml:space="preserve">part of the row's name; one of: default, RichTourist, PoorTourist, Labourer, Displaced</t>
         </is>
       </c>
       <c r="F339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a set's steps, in order</t>
+          <t xml:space="preserve">a traveller kind, or default: the steps of a kind with no set of its own</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSteps</t>
+          <t xml:space="preserve">pcStepSets</t>
         </is>
       </c>
       <c r="B340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">stepSet</t>
+          <t xml:space="preserve">inherit</t>
         </is>
       </c>
       <c r="C340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'pcStepSets' this row belongs to</t>
+          <t xml:space="preserve">names a row of 'pcStepSets'</t>
+        </is>
+      </c>
+      <c r="F340" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the set whose steps it starts from; its own step of the same id replaces the parent's (blank: none)</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSteps</t>
+          <t xml:space="preserve">pcStepSets</t>
         </is>
       </c>
       <c r="B341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">dataOnly</t>
         </is>
       </c>
       <c r="C341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
       <c r="F341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">its label is the UI string steps.{id}</t>
+          <t xml:space="preserve">true while the kind is not in play yet: its forms and categories may name what a later phase adds</t>
         </is>
       </c>
     </row>
@@ -8146,29 +8166,19 @@
           <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
-      <c r="B342" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">when</t>
-        </is>
-      </c>
       <c r="C342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D342" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: PapersReceived, PaperRead, Requested, RulesViewed, RecordViewed, Compared, Asked, LookedAt</t>
+          <t xml:space="preserve">one row per item of the list $.pc.steps.sets[].steps, in order; the first column names the parent row</t>
         </is>
       </c>
       <c r="F342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the check it waits for, never what the check found</t>
+          <t xml:space="preserve">a set's steps, in order</t>
         </is>
       </c>
     </row>
@@ -8180,27 +8190,22 @@
       </c>
       <c r="B343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">categories</t>
+          <t xml:space="preserve">stepSet</t>
         </is>
       </c>
       <c r="C343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F343" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the categories a Compared or Asked step counts (blank: derived from the case)</t>
+          <t xml:space="preserve">names the row of 'pcStepSets' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8217,7 @@
       </c>
       <c r="B344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">statement</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C344" s="1" t="inlineStr">
@@ -8222,17 +8227,12 @@
       </c>
       <c r="D344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E344" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one of: Any, Field, Answer, Garment</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="F344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Compared step's statement side (blank: any)</t>
+          <t xml:space="preserve">its label is the UI string steps.{id}</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">truth</t>
+          <t xml:space="preserve">when</t>
         </is>
       </c>
       <c r="C345" s="1" t="inlineStr">
@@ -8254,17 +8254,17 @@
       </c>
       <c r="D345" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E345" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: Any, Reference, Record, Paper</t>
+          <t xml:space="preserve">one of: PapersReceived, PaperRead, Requested, RulesViewed, RecordViewed, Compared, Asked, LookedAt</t>
         </is>
       </c>
       <c r="F345" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Compared step's truth side (blank: any)</t>
+          <t xml:space="preserve">the check it waits for, never what the check found</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="B346" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">forms</t>
+          <t xml:space="preserve">categories</t>
         </is>
       </c>
       <c r="C346" s="1" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="F346" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the form numbers a paper step counts (blank: every paper)</t>
+          <t xml:space="preserve">the categories a Compared or Asked step counts (blank: derived from the case)</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="B347" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">jump.source</t>
+          <t xml:space="preserve">statement</t>
         </is>
       </c>
       <c r="C347" s="1" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="E347" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: Documents, Records, Reference, Transcript, Report, Rules</t>
+          <t xml:space="preserve">one of: Any, Field, Answer, Garment</t>
         </is>
       </c>
       <c r="F347" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the tab a click on the step shows</t>
+          <t xml:space="preserve">a Compared step's statement side (blank: any)</t>
         </is>
       </c>
     </row>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="B348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">jump.link</t>
+          <t xml:space="preserve">truth</t>
         </is>
       </c>
       <c r="C348" s="1" t="inlineStr">
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: PrimaryName, FirstUncheckedField, CostumeClaimed</t>
+          <t xml:space="preserve">one of: Any, Reference, Record, Paper</t>
         </is>
       </c>
       <c r="F348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">where a click goes instead of a tab</t>
+          <t xml:space="preserve">a Compared step's truth side (blank: any)</t>
         </is>
       </c>
     </row>
@@ -8372,27 +8372,27 @@
       </c>
       <c r="B349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hint</t>
+          <t xml:space="preserve">forms</t>
         </is>
       </c>
       <c r="C349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
         </is>
       </c>
       <c r="E349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'uiStrings'</t>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
       <c r="F349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the UI string of the toast a click shows instead of a jump</t>
+          <t xml:space="preserve">the form numbers a paper step counts (blank: every paper)</t>
         </is>
       </c>
     </row>
@@ -8404,56 +8404,71 @@
       </c>
       <c r="B350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">jump.source</t>
         </is>
       </c>
       <c r="C350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (left out of the JSON)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E350" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: Documents, Records, Reference, Transcript, Report, Rules</t>
         </is>
       </c>
       <c r="F350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">its first day (blank: day 1)</t>
+          <t xml:space="preserve">the tab a click on the step shows</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSites</t>
+          <t xml:space="preserve">pcSteps</t>
+        </is>
+      </c>
+      <c r="B351" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jump.link</t>
         </is>
       </c>
       <c r="C351" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D351" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E351" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.sites, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">one of: PrimaryName, FirstUncheckedField, CostumeClaimed</t>
         </is>
       </c>
       <c r="F351" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Internet's sites</t>
+          <t xml:space="preserve">where a click goes instead of a tab</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSites</t>
+          <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
       <c r="B352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">hint</t>
         </is>
       </c>
       <c r="C352" s="1" t="inlineStr">
@@ -8463,44 +8478,44 @@
       </c>
       <c r="D352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">names a row of 'uiStrings'</t>
+        </is>
+      </c>
+      <c r="F352" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the UI string of the toast a click shows instead of a jump</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSites</t>
+          <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
       <c r="B353" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C353" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D353" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E353" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one of: News, History, Ancestry, Static</t>
+          <t xml:space="preserve">0 (left out of the JSON)</t>
         </is>
       </c>
       <c r="F353" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the page builder that serves it</t>
+          <t xml:space="preserve">its first day (blank: day 1)</t>
         </is>
       </c>
     </row>
@@ -8510,19 +8525,19 @@
           <t xml:space="preserve">pcSites</t>
         </is>
       </c>
-      <c r="B354" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
       <c r="C354" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D354" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E354" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.sites, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F354" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the Internet's sites</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8549,7 @@
       </c>
       <c r="B355" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">domain</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C355" s="1" t="inlineStr">
@@ -8544,12 +8559,12 @@
       </c>
       <c r="D355" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F355" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chronet://{domain}: lower-case letters, digits, dots and dashes</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E355" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8576,7 @@
       </c>
       <c r="B356" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">glyph</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C356" s="1" t="inlineStr">
@@ -8574,9 +8589,14 @@
           <t xml:space="preserve">empty text</t>
         </is>
       </c>
+      <c r="E356" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: News, History, Ancestry, Static</t>
+        </is>
+      </c>
       <c r="F356" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the start-page tile's art key</t>
+          <t xml:space="preserve">the page builder that serves it</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8608,7 @@
       </c>
       <c r="B357" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C357" s="1" t="inlineStr">
@@ -8610,56 +8630,61 @@
       </c>
       <c r="B358" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">domain</t>
         </is>
       </c>
       <c r="C358" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D358" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F358" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the first day it is listed</t>
+          <t xml:space="preserve">chronet://{domain}: lower-case letters, digits, dots and dashes</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPages</t>
+          <t xml:space="preserve">pcSites</t>
+        </is>
+      </c>
+      <c r="B359" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">glyph</t>
         </is>
       </c>
       <c r="C359" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E359" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.pages, in order; a row's name is {site}/{path}, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D359" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F359" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Static site's authored pages</t>
+          <t xml:space="preserve">the start-page tile's art key</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPages</t>
+          <t xml:space="preserve">pcSites</t>
         </is>
       </c>
       <c r="B360" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">site</t>
+          <t xml:space="preserve">blurb</t>
         </is>
       </c>
       <c r="C360" s="1" t="inlineStr">
@@ -8669,44 +8694,34 @@
       </c>
       <c r="D360" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E360" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name; names a row of 'pcSites'</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPages</t>
+          <t xml:space="preserve">pcSites</t>
         </is>
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">path</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C361" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D361" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E361" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F361" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank: the site's front page</t>
+          <t xml:space="preserve">the first day it is listed</t>
         </is>
       </c>
     </row>
@@ -8716,75 +8731,90 @@
           <t xml:space="preserve">pcPages</t>
         </is>
       </c>
-      <c r="B362" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">title</t>
-        </is>
-      </c>
       <c r="C362" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D362" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E362" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.pages, in order; a row's name is {site}/{path}, unique</t>
+        </is>
+      </c>
+      <c r="F362" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a Static site's authored pages</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPageBlocks</t>
+          <t xml:space="preserve">pcPages</t>
+        </is>
+      </c>
+      <c r="B363" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">site</t>
         </is>
       </c>
       <c r="C363" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D363" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E363" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.pages[].blocks, in order; the first column names the parent row</t>
+          <t xml:space="preserve">part of the row's name; names a row of 'pcSites'</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPageBlocks</t>
+          <t xml:space="preserve">pcPages</t>
         </is>
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">page</t>
+          <t xml:space="preserve">path</t>
         </is>
       </c>
       <c r="C364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'pcPages' this row belongs to</t>
+          <t xml:space="preserve">part of the row's name</t>
+        </is>
+      </c>
+      <c r="F364" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank: the site's front page</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPageBlocks</t>
+          <t xml:space="preserve">pcPages</t>
         </is>
       </c>
       <c r="B365" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">title</t>
         </is>
       </c>
       <c r="C365" s="1" t="inlineStr">
@@ -8795,11 +8825,6 @@
       <c r="D365" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E365" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one of: Headline, Heading, Paragraph, Note, Link, Box</t>
         </is>
       </c>
     </row>
@@ -8809,19 +8834,14 @@
           <t xml:space="preserve">pcPageBlocks</t>
         </is>
       </c>
-      <c r="B366" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
       <c r="C366" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D366" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E366" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.pages[].blocks, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -8833,22 +8853,22 @@
       </c>
       <c r="B367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">address</t>
+          <t xml:space="preserve">page</t>
         </is>
       </c>
       <c r="C367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="F367" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a Link's site name, domain or chronet:// address</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E367" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'pcPages' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -8860,61 +8880,56 @@
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F368" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a Box's lines</t>
+          <t xml:space="preserve">one of: Headline, Heading, Paragraph, Note, Link, Box</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPeople</t>
+          <t xml:space="preserve">pcPageBlocks</t>
+        </is>
+      </c>
+      <c r="B369" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C369" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E369" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.ancestry.people, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F369" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the Lineage Archive's people of the past (no traveller's name)</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D369" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPeople</t>
+          <t xml:space="preserve">pcPageBlocks</t>
         </is>
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">address</t>
         </is>
       </c>
       <c r="C370" s="1" t="inlineStr">
@@ -8924,34 +8939,44 @@
       </c>
       <c r="D370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E370" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="F370" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a Link's site name, domain or chronet:// address</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPeople</t>
+          <t xml:space="preserve">pcPageBlocks</t>
         </is>
       </c>
       <c r="B371" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">lines</t>
         </is>
       </c>
       <c r="C371" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D371" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E371" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F371" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a Box's lines</t>
         </is>
       </c>
     </row>
@@ -8961,19 +8986,19 @@
           <t xml:space="preserve">pcPeople</t>
         </is>
       </c>
-      <c r="B372" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">born</t>
-        </is>
-      </c>
       <c r="C372" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D372" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E372" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.ancestry.people, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F372" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the Lineage Archive's people of the past (no traveller's name)</t>
         </is>
       </c>
     </row>
@@ -8985,7 +9010,7 @@
       </c>
       <c r="B373" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">died</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C373" s="1" t="inlineStr">
@@ -8995,7 +9020,12 @@
       </c>
       <c r="D373" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E373" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9037,7 @@
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C374" s="1" t="inlineStr">
@@ -9018,11 +9048,6 @@
       <c r="D374" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E374" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -9034,7 +9059,7 @@
       </c>
       <c r="B375" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">note</t>
+          <t xml:space="preserve">born</t>
         </is>
       </c>
       <c r="C375" s="1" t="inlineStr">
@@ -9051,34 +9076,34 @@
     <row r="376">
       <c r="A376" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcRelations</t>
+          <t xml:space="preserve">pcPeople</t>
+        </is>
+      </c>
+      <c r="B376" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">died</t>
         </is>
       </c>
       <c r="C376" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E376" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.ancestry.relations, in order</t>
-        </is>
-      </c>
-      <c r="F376" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one direction per row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D376" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcRelations</t>
+          <t xml:space="preserve">pcPeople</t>
         </is>
       </c>
       <c r="B377" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">person</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C377" s="1" t="inlineStr">
@@ -9088,24 +9113,24 @@
       </c>
       <c r="D377" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="F377" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a person's or a premade's id: the card it shows on</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E377" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcRelations</t>
+          <t xml:space="preserve">pcPeople</t>
         </is>
       </c>
       <c r="B378" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">note</t>
         </is>
       </c>
       <c r="C378" s="1" t="inlineStr">
@@ -9125,58 +9150,58 @@
           <t xml:space="preserve">pcRelations</t>
         </is>
       </c>
-      <c r="B379" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">other</t>
-        </is>
-      </c>
       <c r="C379" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D379" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E379" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.ancestry.relations, in order</t>
         </is>
       </c>
       <c r="F379" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the other card's id</t>
+          <t xml:space="preserve">one direction per row</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMail</t>
+          <t xml:space="preserve">pcRelations</t>
+        </is>
+      </c>
+      <c r="B380" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">person</t>
         </is>
       </c>
       <c r="C380" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E380" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.mail, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D380" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="F380" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mail's authored messages</t>
+          <t xml:space="preserve">a person's or a premade's id: the card it shows on</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMail</t>
+          <t xml:space="preserve">pcRelations</t>
         </is>
       </c>
       <c r="B381" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C381" s="1" t="inlineStr">
@@ -9186,39 +9211,34 @@
       </c>
       <c r="D381" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E381" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMail</t>
+          <t xml:space="preserve">pcRelations</t>
         </is>
       </c>
       <c r="B382" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">other</t>
         </is>
       </c>
       <c r="C382" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D382" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="F382" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the day it arrives (its date)</t>
+          <t xml:space="preserve">the other card's id</t>
         </is>
       </c>
     </row>
@@ -9228,24 +9248,19 @@
           <t xml:space="preserve">pcMail</t>
         </is>
       </c>
-      <c r="B383" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">untilDay</t>
-        </is>
-      </c>
       <c r="C383" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D383" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E383" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.mail, in order; a row's name is id, unique</t>
         </is>
       </c>
       <c r="F383" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the last day it is in the inbox; 0 keeps it for the run</t>
+          <t xml:space="preserve">Mail's authored messages</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9272,7 @@
       </c>
       <c r="B384" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flag</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C384" s="1" t="inlineStr">
@@ -9267,12 +9282,12 @@
       </c>
       <c r="D384" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F384" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a story flag it waits for (blank: none)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E384" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -9284,17 +9299,22 @@
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">from</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C385" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D385" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F385" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the day it arrives (its date)</t>
         </is>
       </c>
     </row>
@@ -9306,78 +9326,83 @@
       </c>
       <c r="B386" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">subject</t>
+          <t xml:space="preserve">untilDay</t>
         </is>
       </c>
       <c r="C386" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D386" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F386" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the last day it is in the inbox; 0 keeps it for the run</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMailBody</t>
+          <t xml:space="preserve">pcMail</t>
+        </is>
+      </c>
+      <c r="B387" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flag</t>
         </is>
       </c>
       <c r="C387" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Values</t>
-        </is>
-      </c>
-      <c r="E387" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.mail[].body, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D387" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F387" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">its paragraphs</t>
+          <t xml:space="preserve">a story flag it waits for (blank: none)</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMailBody</t>
+          <t xml:space="preserve">pcMail</t>
         </is>
       </c>
       <c r="B388" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">mail</t>
+          <t xml:space="preserve">from</t>
         </is>
       </c>
       <c r="C388" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D388" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E388" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'pcMail' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMailBody</t>
+          <t xml:space="preserve">pcMail</t>
         </is>
       </c>
       <c r="B389" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">subject</t>
         </is>
       </c>
       <c r="C389" s="1" t="inlineStr">
@@ -9387,68 +9412,78 @@
       </c>
       <c r="D389" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">pcMailBody</t>
         </is>
       </c>
       <c r="C390" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
+          <t xml:space="preserve">Values</t>
         </is>
       </c>
       <c r="E390" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row: the object $.ui</t>
+          <t xml:space="preserve">one row per item of the list $.pc.mail[].body, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F390" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its paragraphs</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">pcMailBody</t>
         </is>
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">readingLanguage</t>
+          <t xml:space="preserve">mail</t>
         </is>
       </c>
       <c r="C391" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D391" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E391" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'pcMail' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">pcMailBody</t>
         </is>
       </c>
       <c r="B392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">glossPercent</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -9458,19 +9493,14 @@
           <t xml:space="preserve">ui</t>
         </is>
       </c>
-      <c r="B393" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">labelMinScale</t>
-        </is>
-      </c>
       <c r="C393" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
-        </is>
-      </c>
-      <c r="D393" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E393" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.ui</t>
         </is>
       </c>
     </row>
@@ -9482,17 +9512,17 @@
       </c>
       <c r="B394" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.text</t>
+          <t xml:space="preserve">readingLanguage</t>
         </is>
       </c>
       <c r="C394" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D394" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9504,12 +9534,12 @@
       </c>
       <c r="B395" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.largeText</t>
+          <t xml:space="preserve">glossPercent</t>
         </is>
       </c>
       <c r="C395" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D395" s="1" t="inlineStr">
@@ -9526,7 +9556,7 @@
       </c>
       <c r="B396" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.glyph</t>
+          <t xml:space="preserve">labelMinScale</t>
         </is>
       </c>
       <c r="C396" s="1" t="inlineStr">
@@ -9548,7 +9578,7 @@
       </c>
       <c r="B397" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.hint</t>
+          <t xml:space="preserve">contrast.text</t>
         </is>
       </c>
       <c r="C397" s="1" t="inlineStr">
@@ -9570,7 +9600,7 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.outline</t>
+          <t xml:space="preserve">contrast.largeText</t>
         </is>
       </c>
       <c r="C398" s="1" t="inlineStr">
@@ -9592,7 +9622,7 @@
       </c>
       <c r="B399" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.minTextFillAlpha</t>
+          <t xml:space="preserve">contrast.glyph</t>
         </is>
       </c>
       <c r="C399" s="1" t="inlineStr">
@@ -9614,68 +9644,73 @@
       </c>
       <c r="B400" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">latinFallbackFont</t>
+          <t xml:space="preserve">contrast.hint</t>
         </is>
       </c>
       <c r="C400" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D400" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="B401" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">contrast.outline</t>
         </is>
       </c>
       <c r="C401" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E401" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.paletteMap, in order</t>
+          <t xml:space="preserve">decimal</t>
+        </is>
+      </c>
+      <c r="D401" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B402" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">role</t>
+          <t xml:space="preserve">contrast.minTextFillAlpha</t>
         </is>
       </c>
       <c r="C402" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D402" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B403" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fill</t>
+          <t xml:space="preserve">latinFallbackFont</t>
         </is>
       </c>
       <c r="C403" s="1" t="inlineStr">
@@ -9695,19 +9730,14 @@
           <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
-      <c r="B404" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">alpha</t>
-        </is>
-      </c>
       <c r="C404" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
-        </is>
-      </c>
-      <c r="D404" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E404" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.paletteMap, in order</t>
         </is>
       </c>
     </row>
@@ -9719,7 +9749,7 @@
       </c>
       <c r="B405" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ink</t>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C405" s="1" t="inlineStr">
@@ -9741,7 +9771,7 @@
       </c>
       <c r="B406" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">textClass</t>
+          <t xml:space="preserve">fill</t>
         </is>
       </c>
       <c r="C406" s="1" t="inlineStr">
@@ -9758,29 +9788,34 @@
     <row r="407">
       <c r="A407" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">uiPalette</t>
+        </is>
+      </c>
+      <c r="B407" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alpha</t>
         </is>
       </c>
       <c r="C407" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E407" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.ui.neutral</t>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D407" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="B408" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C408" s="1" t="inlineStr">
@@ -9797,12 +9832,12 @@
     <row r="409">
       <c r="A409" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="B409" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">textClass</t>
         </is>
       </c>
       <c r="C409" s="1" t="inlineStr">
@@ -9822,19 +9857,14 @@
           <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
-      <c r="B410" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">language</t>
-        </is>
-      </c>
       <c r="C410" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D410" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E410" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.ui.neutral</t>
         </is>
       </c>
     </row>
@@ -9846,17 +9876,17 @@
       </c>
       <c r="B411" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">runtimeFont</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C411" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D411" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9898,7 @@
       </c>
       <c r="B412" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">headingAdd</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C412" s="1" t="inlineStr">
@@ -9890,7 +9920,7 @@
       </c>
       <c r="B413" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">buttonAdd</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C413" s="1" t="inlineStr">
@@ -9912,7 +9942,7 @@
       </c>
       <c r="B414" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">stripItalic</t>
+          <t xml:space="preserve">runtimeFont</t>
         </is>
       </c>
       <c r="C414" s="1" t="inlineStr">
@@ -9934,7 +9964,7 @@
       </c>
       <c r="B415" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wallpaper</t>
+          <t xml:space="preserve">headingAdd</t>
         </is>
       </c>
       <c r="C415" s="1" t="inlineStr">
@@ -9951,66 +9981,66 @@
     <row r="416">
       <c r="A416" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiNeutral</t>
+        </is>
+      </c>
+      <c r="B416" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">buttonAdd</t>
         </is>
       </c>
       <c r="C416" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E416" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.fonts, in order</t>
-        </is>
-      </c>
-      <c r="F416" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D416" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">file</t>
+          <t xml:space="preserve">stripItalic</t>
         </is>
       </c>
       <c r="C417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">face</t>
+          <t xml:space="preserve">wallpaper</t>
         </is>
       </c>
       <c r="C418" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D418" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10020,19 +10050,19 @@
           <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
-      <c r="B419" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">family</t>
-        </is>
-      </c>
       <c r="C419" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D419" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E419" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.fonts, in order</t>
+        </is>
+      </c>
+      <c r="F419" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
         </is>
       </c>
     </row>
@@ -10044,7 +10074,7 @@
       </c>
       <c r="B420" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">style</t>
+          <t xml:space="preserve">file</t>
         </is>
       </c>
       <c r="C420" s="1" t="inlineStr">
@@ -10061,29 +10091,34 @@
     <row r="421">
       <c r="A421" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
+          <t xml:space="preserve">neutralFonts</t>
+        </is>
+      </c>
+      <c r="B421" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">face</t>
         </is>
       </c>
       <c r="C421" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E421" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.seeds, in order</t>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D421" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
+          <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
       <c r="B422" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C422" s="1" t="inlineStr">
@@ -10100,12 +10135,12 @@
     <row r="423">
       <c r="A423" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
+          <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
       <c r="B423" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hex</t>
+          <t xml:space="preserve">style</t>
         </is>
       </c>
       <c r="C423" s="1" t="inlineStr">
@@ -10122,7 +10157,7 @@
     <row r="424">
       <c r="A424" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">neutralSeeds</t>
         </is>
       </c>
       <c r="C424" s="1" t="inlineStr">
@@ -10132,19 +10167,19 @@
       </c>
       <c r="E424" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.overrides, in order</t>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.seeds, in order</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">neutralSeeds</t>
         </is>
       </c>
       <c r="B425" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">role</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C425" s="1" t="inlineStr">
@@ -10161,12 +10196,12 @@
     <row r="426">
       <c r="A426" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">neutralSeeds</t>
         </is>
       </c>
       <c r="B426" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fill</t>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C426" s="1" t="inlineStr">
@@ -10186,48 +10221,48 @@
           <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
-      <c r="B427" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ink</t>
-        </is>
-      </c>
       <c r="C427" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D427" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E427" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.overrides, in order</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
+          <t xml:space="preserve">neutralOverrides</t>
+        </is>
+      </c>
+      <c r="B428" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C428" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E428" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.art, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D428" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
+          <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
       <c r="B429" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">fill</t>
         </is>
       </c>
       <c r="C429" s="1" t="inlineStr">
@@ -10244,12 +10279,12 @@
     <row r="430">
       <c r="A430" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
+          <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
       <c r="B430" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hex</t>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C430" s="1" t="inlineStr">
@@ -10266,7 +10301,7 @@
     <row r="431">
       <c r="A431" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
       <c r="C431" s="1" t="inlineStr">
@@ -10276,19 +10311,19 @@
       </c>
       <c r="E431" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.ui.strings, in order; a row's name is key, unique</t>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.art, in order</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
       <c r="B432" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C432" s="1" t="inlineStr">
@@ -10298,24 +10333,19 @@
       </c>
       <c r="D432" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E432" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
       <c r="B433" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C433" s="1" t="inlineStr">
@@ -10335,19 +10365,14 @@
           <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
-      <c r="B434" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gloss</t>
-        </is>
-      </c>
       <c r="C434" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D434" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E434" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.strings, in order; a row's name is key, unique</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10384,7 @@
       </c>
       <c r="B435" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tier</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C435" s="1" t="inlineStr">
@@ -10369,36 +10394,46 @@
       </c>
       <c r="D435" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E435" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
+          <t xml:space="preserve">uiStrings</t>
+        </is>
+      </c>
+      <c r="B436" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C436" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E436" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.languages, in order; a row's name is language, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D436" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
+          <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
       <c r="B437" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">gloss</t>
         </is>
       </c>
       <c r="C437" s="1" t="inlineStr">
@@ -10408,41 +10443,36 @@
       </c>
       <c r="D437" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E437" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
+          <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
       <c r="B438" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rtl</t>
+          <t xml:space="preserve">tier</t>
         </is>
       </c>
       <c r="C438" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D438" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
+          <t xml:space="preserve">uiLanguages</t>
         </is>
       </c>
       <c r="C439" s="1" t="inlineStr">
@@ -10452,14 +10482,14 @@
       </c>
       <c r="E439" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.ui.languages[].entries, in order; the first column names the parent row</t>
+          <t xml:space="preserve">one row per item of the list $.ui.languages, in order; a row's name is language, unique</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
+          <t xml:space="preserve">uiLanguages</t>
         </is>
       </c>
       <c r="B440" s="1" t="inlineStr">
@@ -10469,7 +10499,7 @@
       </c>
       <c r="C440" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D440" s="1" t="inlineStr">
@@ -10479,34 +10509,29 @@
       </c>
       <c r="E440" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'uiLanguages' this row belongs to</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
+          <t xml:space="preserve">uiLanguages</t>
         </is>
       </c>
       <c r="B441" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">rtl</t>
         </is>
       </c>
       <c r="C441" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D441" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E441" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'uiStrings'</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -10516,70 +10541,80 @@
           <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
-      <c r="B442" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
       <c r="C442" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D442" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E442" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.languages[].entries, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
+        </is>
+      </c>
+      <c r="B443" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C443" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D443" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E443" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row: the object $.translation</t>
+          <t xml:space="preserve">names the row of 'uiLanguages' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
       <c r="B444" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C444" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D444" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E444" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'uiStrings'</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
       <c r="B445" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">announce</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C445" s="1" t="inlineStr">
@@ -10599,19 +10634,14 @@
           <t xml:space="preserve">translation</t>
         </is>
       </c>
-      <c r="B446" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">flip.startDelay</t>
-        </is>
-      </c>
       <c r="C446" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
-        </is>
-      </c>
-      <c r="D446" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E446" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.translation</t>
         </is>
       </c>
     </row>
@@ -10623,12 +10653,12 @@
       </c>
       <c r="B447" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.letterInterval</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C447" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D447" s="1" t="inlineStr">
@@ -10645,17 +10675,17 @@
       </c>
       <c r="B448" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.letterSeconds</t>
+          <t xml:space="preserve">announce</t>
         </is>
       </c>
       <c r="C448" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D448" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10667,12 +10697,12 @@
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.scrambleSteps</t>
+          <t xml:space="preserve">flip.startDelay</t>
         </is>
       </c>
       <c r="C449" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D449" s="1" t="inlineStr">
@@ -10689,27 +10719,17 @@
       </c>
       <c r="B450" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.slots</t>
+          <t xml:space="preserve">flip.letterInterval</t>
         </is>
       </c>
       <c r="C450" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D450" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E450" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F450" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">slots whose value stays English in untranslated speech</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -10721,27 +10741,17 @@
       </c>
       <c r="B451" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.words</t>
+          <t xml:space="preserve">flip.letterSeconds</t>
         </is>
       </c>
       <c r="C451" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D451" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E451" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F451" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">words that stay English in untranslated speech</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -10753,17 +10763,17 @@
       </c>
       <c r="B452" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.digits</t>
+          <t xml:space="preserve">flip.scrambleSteps</t>
         </is>
       </c>
       <c r="C452" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D452" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -10775,90 +10785,110 @@
       </c>
       <c r="B453" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fallbackGlyphs</t>
+          <t xml:space="preserve">keyWords.slots</t>
         </is>
       </c>
       <c r="C453" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D453" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E453" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F453" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slots whose value stays English in untranslated speech</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
+          <t xml:space="preserve">translation</t>
+        </is>
+      </c>
+      <c r="B454" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">keyWords.words</t>
         </is>
       </c>
       <c r="C454" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text list</t>
+        </is>
+      </c>
+      <c r="D454" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no items</t>
         </is>
       </c>
       <c r="E454" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.translation.scripts, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F454" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">words that stay English in untranslated speech</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B455" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">keyWords.digits</t>
         </is>
       </c>
       <c r="C455" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D455" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E455" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B456" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rightToLeft</t>
+          <t xml:space="preserve">fallbackGlyphs</t>
         </is>
       </c>
       <c r="C456" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D456" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">scripts</t>
         </is>
       </c>
       <c r="C457" s="1" t="inlineStr">
@@ -10868,29 +10898,24 @@
       </c>
       <c r="E457" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.translation.scripts[].fonts, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F457" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">one row per item of the list $.translation.scripts, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">scripts</t>
         </is>
       </c>
       <c r="B458" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">script</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C458" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D458" s="1" t="inlineStr">
@@ -10900,29 +10925,29 @@
       </c>
       <c r="E458" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'scripts' this row belongs to</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">scripts</t>
         </is>
       </c>
       <c r="B459" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">file</t>
+          <t xml:space="preserve">rightToLeft</t>
         </is>
       </c>
       <c r="C459" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D459" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -10932,19 +10957,19 @@
           <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
-      <c r="B460" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">face</t>
-        </is>
-      </c>
       <c r="C460" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D460" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E460" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.translation.scripts[].fonts, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F460" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
         </is>
       </c>
     </row>
@@ -10956,17 +10981,22 @@
       </c>
       <c r="B461" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">family</t>
+          <t xml:space="preserve">script</t>
         </is>
       </c>
       <c r="C461" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D461" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E461" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'scripts' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -10978,7 +11008,7 @@
       </c>
       <c r="B462" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">style</t>
+          <t xml:space="preserve">file</t>
         </is>
       </c>
       <c r="C462" s="1" t="inlineStr">
@@ -10995,29 +11025,34 @@
     <row r="463">
       <c r="A463" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">scriptFonts</t>
+        </is>
+      </c>
+      <c r="B463" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">face</t>
         </is>
       </c>
       <c r="C463" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E463" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.packs, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D463" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
       <c r="B464" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C464" s="1" t="inlineStr">
@@ -11027,24 +11062,19 @@
       </c>
       <c r="D464" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E464" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
       <c r="B465" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">style</t>
         </is>
       </c>
       <c r="C465" s="1" t="inlineStr">
@@ -11064,48 +11094,53 @@
           <t xml:space="preserve">packs</t>
         </is>
       </c>
-      <c r="B466" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spokenCost</t>
-        </is>
-      </c>
       <c r="C466" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D466" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E466" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.translation.packs, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">packs</t>
+        </is>
+      </c>
+      <c r="B467" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C467" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D467" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E467" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">packs</t>
         </is>
       </c>
       <c r="B468" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C468" s="1" t="inlineStr">
@@ -11115,34 +11150,29 @@
       </c>
       <c r="D468" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E468" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">packs</t>
         </is>
       </c>
       <c r="B469" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">spokenCost</t>
         </is>
       </c>
       <c r="C469" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D469" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -11152,24 +11182,14 @@
           <t xml:space="preserve">tongues</t>
         </is>
       </c>
-      <c r="B470" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">script</t>
-        </is>
-      </c>
       <c r="C470" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D470" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E470" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'scripts'</t>
+          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -11181,7 +11201,7 @@
       </c>
       <c r="B471" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pack</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C471" s="1" t="inlineStr">
@@ -11191,12 +11211,12 @@
       </c>
       <c r="D471" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E471" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'packs'</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -11208,15 +11228,91 @@
       </c>
       <c r="B472" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">displayName</t>
+        </is>
+      </c>
+      <c r="C472" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D472" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B473" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">script</t>
+        </is>
+      </c>
+      <c r="C473" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D473" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E473" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'scripts'</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B474" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pack</t>
+        </is>
+      </c>
+      <c r="C474" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D474" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E474" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'packs'</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B475" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">glyphs</t>
         </is>
       </c>
-      <c r="C472" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D472" s="1" t="inlineStr">
+      <c r="C475" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D475" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
         </is>
@@ -14714,9 +14810,10 @@
     <col min="6" max="6" width="47" style="1" customWidth="1"/>
     <col min="7" max="7" width="39" style="1" customWidth="1"/>
     <col min="8" max="8" width="46" style="1" customWidth="1"/>
-    <col min="9" max="9" width="32" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="9" max="9" width="11" style="1" customWidth="1"/>
+    <col min="10" max="10" width="32" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14762,15 +14859,20 @@
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">guarantee</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">premades</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">premadeChance</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">costumeErrorChance</t>
         </is>
@@ -14811,10 +14913,10 @@
           <t xml:space="preserve">Rule_LeisureDepartures</t>
         </is>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.05</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.0</v>
       </c>
     </row>
@@ -14853,15 +14955,15 @@
           <t xml:space="preserve">Rule_NoAncientEgypt|Rule_DressForDestination</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">aspasia|banzhao|arib|khwarizmi</t>
         </is>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.05</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.1</v>
       </c>
     </row>
@@ -15144,12 +15246,13 @@
     <col min="9" max="9" width="26" style="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="1" customWidth="1"/>
     <col min="11" max="11" width="18" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" customWidth="1"/>
-    <col min="14" max="14" width="24" style="1" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="12" max="12" width="22" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11" style="1" customWidth="1"/>
+    <col min="14" max="14" width="16" style="1" customWidth="1"/>
+    <col min="15" max="15" width="24" style="1" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="11" style="1" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15210,30 +15313,35 @@
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">tripAskLabel</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">backLabel</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">smallTalkLabel</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">smallTalkPrompt</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">menuCapacity</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">maxLineChars</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">lookLabel</t>
         </is>
@@ -15297,26 +15405,31 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ask about the trip &gt;</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">&lt; Back</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Small talk</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">How is life back home?</t>
         </is>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>8</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>100</v>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Look &gt;</t>
         </is>
@@ -15460,11 +15573,12 @@
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10" style="1" customWidth="1"/>
-    <col min="4" max="4" width="37" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="10" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37" style="1" customWidth="1"/>
+    <col min="6" max="6" width="27" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15480,25 +15594,30 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">kinds</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">label</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">prompt</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">answer</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">fromDay</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">announce</t>
         </is>
@@ -15517,20 +15636,25 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Currency</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">What money do you pay with at home?</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">We pay in {value}.</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>1</v>
       </c>
     </row>
@@ -15547,20 +15671,25 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Language</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">What language do you speak at home?</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">At home we speak {value}.</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>1</v>
       </c>
     </row>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -4553,7 +4553,7 @@
       </c>
       <c r="F189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the lies enabled this day (FalseOrigin, PoorPosingAsRich, DoctoredIdentity, FakeDisplaced); a traveller draws among those that fit their kind</t>
+          <t xml:space="preserve">the lies enabled this day (FalseOrigin, PoorPosingAsRich, DoctoredIdentity, FakeDisplaced, Smuggling); a traveller draws among those that fit their kind</t>
         </is>
       </c>
     </row>
@@ -5266,6 +5266,11 @@
           <t xml:space="preserve">empty text</t>
         </is>
       </c>
+      <c r="F219" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the ask entry for the displaced</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
@@ -5275,7 +5280,7 @@
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">backLabel</t>
+          <t xml:space="preserve">tripAskLabel</t>
         </is>
       </c>
       <c r="C220" s="1" t="inlineStr">
@@ -5286,6 +5291,11 @@
       <c r="D220" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F220" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the ask entry for a 2150 citizen, who is asked about the trip</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5307,7 @@
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">smallTalkLabel</t>
+          <t xml:space="preserve">backLabel</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr">
@@ -5319,7 +5329,7 @@
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">smallTalkPrompt</t>
+          <t xml:space="preserve">smallTalkLabel</t>
         </is>
       </c>
       <c r="C222" s="1" t="inlineStr">
@@ -5341,17 +5351,17 @@
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">menuCapacity</t>
+          <t xml:space="preserve">smallTalkPrompt</t>
         </is>
       </c>
       <c r="C223" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D223" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5373,7 @@
       </c>
       <c r="B224" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">maxLineChars</t>
+          <t xml:space="preserve">menuCapacity</t>
         </is>
       </c>
       <c r="C224" s="1" t="inlineStr">
@@ -5385,39 +5395,39 @@
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lookLabel</t>
+          <t xml:space="preserve">maxLineChars</t>
         </is>
       </c>
       <c r="C225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">claims</t>
+          <t xml:space="preserve">interview</t>
+        </is>
+      </c>
+      <c r="B226" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lookLabel</t>
         </is>
       </c>
       <c r="C226" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E226" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.interview.claims, in order</t>
-        </is>
-      </c>
-      <c r="F226" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the claim per traveller kind ({place}): one row per kind a blueprint makes</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D226" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5427,24 +5437,19 @@
           <t xml:space="preserve">claims</t>
         </is>
       </c>
-      <c r="B227" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kind</t>
-        </is>
-      </c>
       <c r="C227" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D227" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E227" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
+          <t xml:space="preserve">one row per item of the list $.interview.claims, in order</t>
+        </is>
+      </c>
+      <c r="F227" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the claim per traveller kind ({place}): one row per kind a blueprint makes</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5461,7 @@
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C228" s="1" t="inlineStr">
@@ -5466,29 +5471,34 @@
       </c>
       <c r="D228" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E228" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interviewRequests</t>
+          <t xml:space="preserve">claims</t>
+        </is>
+      </c>
+      <c r="B229" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C229" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E229" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.interview.requests, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F229" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spoken requests: the wheel entry, the desk's prompt and the traveller's reply</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D229" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5498,24 +5508,19 @@
           <t xml:space="preserve">interviewRequests</t>
         </is>
       </c>
-      <c r="B230" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C230" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D230" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E230" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.interview.requests, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F230" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spoken requests: the wheel entry, the desk's prompt and the traveller's reply</t>
         </is>
       </c>
     </row>
@@ -5527,7 +5532,7 @@
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C231" s="1" t="inlineStr">
@@ -5537,7 +5542,12 @@
       </c>
       <c r="D231" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E231" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5559,7 @@
       </c>
       <c r="B232" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C232" s="1" t="inlineStr">
@@ -5571,7 +5581,7 @@
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">reply</t>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C233" s="1" t="inlineStr">
@@ -5588,17 +5598,22 @@
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
+          <t xml:space="preserve">interviewRequests</t>
+        </is>
+      </c>
+      <c r="B234" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reply</t>
         </is>
       </c>
       <c r="C234" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E234" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.questions, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D234" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5608,24 +5623,14 @@
           <t xml:space="preserve">questions</t>
         </is>
       </c>
-      <c r="B235" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C235" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D235" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E235" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.questions, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5642,7 @@
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C236" s="1" t="inlineStr">
@@ -5647,7 +5652,12 @@
       </c>
       <c r="D236" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E236" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5669,7 @@
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C237" s="1" t="inlineStr">
@@ -5681,17 +5691,27 @@
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">kinds</t>
         </is>
       </c>
       <c r="C238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E238" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F238" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the traveller kinds the desk asks it of (RichTourist, PoorTourist, Labourer, Displaced); blank: every kind; one question per category per kind</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5723,7 @@
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C239" s="1" t="inlineStr">
@@ -5725,17 +5745,17 @@
       </c>
       <c r="B240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5767,7 @@
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">announce</t>
+          <t xml:space="preserve">answer</t>
         </is>
       </c>
       <c r="C241" s="1" t="inlineStr">
@@ -5764,49 +5784,44 @@
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questions</t>
+        </is>
+      </c>
+      <c r="B242" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E242" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.questions[].conditions, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F242" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all must pass</t>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D242" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questions</t>
         </is>
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">question</t>
+          <t xml:space="preserve">announce</t>
         </is>
       </c>
       <c r="C243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E243" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5816,19 +5831,19 @@
           <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
-      <c r="B244" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">type</t>
-        </is>
-      </c>
       <c r="C244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D244" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E244" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.questions[].conditions, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F244" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all must pass</t>
         </is>
       </c>
     </row>
@@ -5840,17 +5855,22 @@
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">question</t>
         </is>
       </c>
       <c r="C245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E245" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -5862,17 +5882,17 @@
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C246" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D246" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5904,7 @@
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C247" s="1" t="inlineStr">
@@ -5894,12 +5914,7 @@
       </c>
       <c r="D247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E247" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -5911,22 +5926,17 @@
       </c>
       <c r="B248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E248" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5948,7 @@
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C249" s="1" t="inlineStr">
@@ -5953,56 +5963,61 @@
       </c>
       <c r="E249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
+          <t xml:space="preserve">questionConditions</t>
+        </is>
+      </c>
+      <c r="B250" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D250" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.questions[].overrides, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F250" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the wording in one era</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
+          <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">question</t>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
@@ -6012,24 +6027,19 @@
           <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
-      <c r="B252" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">era</t>
-        </is>
-      </c>
       <c r="C252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D252" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'eras'</t>
+          <t xml:space="preserve">one row per item of the list $.questions[].overrides, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F252" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the wording in one era</t>
         </is>
       </c>
     </row>
@@ -6041,17 +6051,22 @@
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">question</t>
         </is>
       </c>
       <c r="C253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E253" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6078,7 @@
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C254" s="1" t="inlineStr">
@@ -6074,40 +6089,45 @@
       <c r="D254" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E254" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'eras'</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
+          <t xml:space="preserve">questionOverrides</t>
+        </is>
+      </c>
+      <c r="B255" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E255" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F255" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">narrative dialogs: nodes, their lines and the player's choices</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D255" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
+          <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">answer</t>
         </is>
       </c>
       <c r="C256" s="1" t="inlineStr">
@@ -6117,12 +6137,7 @@
       </c>
       <c r="D256" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E256" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6132,24 +6147,19 @@
           <t xml:space="preserve">dialogs</t>
         </is>
       </c>
-      <c r="B257" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">label</t>
-        </is>
-      </c>
       <c r="C257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D257" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E257" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs, in order; a row's name is id, unique</t>
         </is>
       </c>
       <c r="F257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the wheel entry</t>
+          <t xml:space="preserve">narrative dialogs: nodes, their lines and the player's choices</t>
         </is>
       </c>
     </row>
@@ -6161,66 +6171,71 @@
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">repeatable</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E258" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
+          <t xml:space="preserve">dialogs</t>
+        </is>
+      </c>
+      <c r="B259" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E259" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].conditions, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D259" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">all must pass</t>
+          <t xml:space="preserve">the wheel entry</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
+          <t xml:space="preserve">dialogs</t>
         </is>
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">repeatable</t>
         </is>
       </c>
       <c r="C260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E260" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -6230,19 +6245,19 @@
           <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
-      <c r="B261" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">type</t>
-        </is>
-      </c>
       <c r="C261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D261" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E261" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].conditions, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F261" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all must pass</t>
         </is>
       </c>
     </row>
@@ -6254,17 +6269,22 @@
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E262" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6276,17 +6296,17 @@
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C263" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D263" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6318,7 @@
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C264" s="1" t="inlineStr">
@@ -6308,12 +6328,7 @@
       </c>
       <c r="D264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E264" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6325,22 +6340,17 @@
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E265" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6362,7 @@
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C266" s="1" t="inlineStr">
@@ -6367,51 +6377,61 @@
       </c>
       <c r="E266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogNodes</t>
+          <t xml:space="preserve">dialogConditions</t>
+        </is>
+      </c>
+      <c r="B267" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D267" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes, in order; a row's name is id, unique per parent row; the first column names the parent row</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogNodes</t>
+          <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
@@ -6421,58 +6441,58 @@
           <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
-      <c r="B269" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D269" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes, in order; a row's name is id, unique per parent row; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
+          <t xml:space="preserve">dialogNodes</t>
+        </is>
+      </c>
+      <c r="B270" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D270" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].lines, in order; the first columns name the parent row</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
+          <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D271" s="1" t="inlineStr">
@@ -6482,7 +6502,7 @@
       </c>
       <c r="E271" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -6492,24 +6512,14 @@
           <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
-      <c r="B272" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">node</t>
-        </is>
-      </c>
       <c r="C272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D272" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].lines, in order; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -6521,17 +6531,22 @@
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E273" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6543,17 +6558,22 @@
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">speaker</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E274" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6585,7 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">expression</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr">
@@ -6575,7 +6595,7 @@
       </c>
       <c r="D275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6607,7 @@
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">speaker</t>
         </is>
       </c>
       <c r="C276" s="1" t="inlineStr">
@@ -6604,44 +6624,44 @@
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">dialogLines</t>
+        </is>
+      </c>
+      <c r="B277" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">expression</t>
         </is>
       </c>
       <c r="C277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E277" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices, in order; a row's name is id, unique per parent row; the first columns name the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D277" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E278" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6651,24 +6671,14 @@
           <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
-      <c r="B279" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">node</t>
-        </is>
-      </c>
       <c r="C279" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D279" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E279" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices, in order; a row's name is id, unique per parent row; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -6680,12 +6690,12 @@
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D280" s="1" t="inlineStr">
@@ -6695,7 +6705,7 @@
       </c>
       <c r="E280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6707,17 +6717,22 @@
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C281" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D281" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E281" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6744,7 @@
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">next</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
@@ -6739,12 +6754,12 @@
       </c>
       <c r="D282" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F282" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the node it leads to (blank: the dialog ends)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E282" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6771,7 @@
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">effect</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
@@ -6773,44 +6788,49 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">dialogChoices</t>
+        </is>
+      </c>
+      <c r="B284" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">next</t>
         </is>
       </c>
       <c r="C284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E284" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices[].lines, in order; the first columns name the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D284" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F284" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the node it leads to (blank: the dialog ends)</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">effect</t>
         </is>
       </c>
       <c r="C285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E285" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6820,24 +6840,14 @@
           <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
-      <c r="B286" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">node</t>
-        </is>
-      </c>
       <c r="C286" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D286" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E286" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices[].lines, in order; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6859,7 @@
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choice</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
@@ -6864,7 +6874,7 @@
       </c>
       <c r="E287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogChoices' this row belongs to</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6876,17 +6886,22 @@
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D288" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E288" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6898,17 +6913,22 @@
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">speaker</t>
+          <t xml:space="preserve">choice</t>
         </is>
       </c>
       <c r="C289" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D289" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E289" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogChoices' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6940,7 @@
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">expression</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
@@ -6930,7 +6950,7 @@
       </c>
       <c r="D290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6942,7 +6962,7 @@
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">speaker</t>
         </is>
       </c>
       <c r="C291" s="1" t="inlineStr">
@@ -6959,34 +6979,34 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">choiceLines</t>
+        </is>
+      </c>
+      <c r="B292" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">expression</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E292" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.premades, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F292" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">premade characters: real people and written stories</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D292" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C293" s="1" t="inlineStr">
@@ -6996,12 +7016,7 @@
       </c>
       <c r="D293" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E293" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7011,19 +7026,19 @@
           <t xml:space="preserve">premades</t>
         </is>
       </c>
-      <c r="B294" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
       <c r="C294" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D294" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E294" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.premades, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F294" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">premade characters: real people and written stories</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7050,7 @@
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gender</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
@@ -7045,7 +7060,12 @@
       </c>
       <c r="D295" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E295" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -7057,7 +7077,7 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C296" s="1" t="inlineStr">
@@ -7068,11 +7088,6 @@
       <c r="D296" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E296" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7099,7 @@
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">truePlace</t>
+          <t xml:space="preserve">gender</t>
         </is>
       </c>
       <c r="C297" s="1" t="inlineStr">
@@ -7095,16 +7110,6 @@
       <c r="D297" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E297" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
-        </is>
-      </c>
-      <c r="F297" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">where they really come from (blank: honest)</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7121,7 @@
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">birthDate</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C298" s="1" t="inlineStr">
@@ -7127,6 +7132,11 @@
       <c r="D298" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E298" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -7138,7 +7148,7 @@
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">archetype</t>
+          <t xml:space="preserve">truePlace</t>
         </is>
       </c>
       <c r="C299" s="1" t="inlineStr">
@@ -7149,6 +7159,16 @@
       <c r="D299" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E299" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
+        </is>
+      </c>
+      <c r="F299" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">where they really come from (blank: honest)</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7180,7 @@
       </c>
       <c r="B300" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">intro</t>
+          <t xml:space="preserve">birthDate</t>
         </is>
       </c>
       <c r="C300" s="1" t="inlineStr">
@@ -7182,7 +7202,7 @@
       </c>
       <c r="B301" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">recordNote</t>
+          <t xml:space="preserve">archetype</t>
         </is>
       </c>
       <c r="C301" s="1" t="inlineStr">
@@ -7204,7 +7224,7 @@
       </c>
       <c r="B302" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">intro</t>
         </is>
       </c>
       <c r="C302" s="1" t="inlineStr">
@@ -7215,11 +7235,6 @@
       <c r="D302" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E302" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'dialogs'</t>
         </is>
       </c>
     </row>
@@ -7231,61 +7246,66 @@
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">repeatable</t>
+          <t xml:space="preserve">recordNote</t>
         </is>
       </c>
       <c r="C303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">premades</t>
+        </is>
+      </c>
+      <c r="B304" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D304" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.premades[].impacts, in order; the first column names the parent row</t>
+          <t xml:space="preserve">names a row of 'dialogs'</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="B305" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premade</t>
+          <t xml:space="preserve">repeatable</t>
         </is>
       </c>
       <c r="C305" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D305" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E305" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'premades' this row belongs to</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -7295,24 +7315,14 @@
           <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
-      <c r="B306" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attribute</t>
-        </is>
-      </c>
       <c r="C306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D306" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">one row per item of the list $.premades[].impacts, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -7324,17 +7334,22 @@
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">onCorrect</t>
+          <t xml:space="preserve">premade</t>
         </is>
       </c>
       <c r="C307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E307" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'premades' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7346,17 +7361,22 @@
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">onWrong</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E308" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
@@ -7368,56 +7388,61 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">skipNationScore</t>
+          <t xml:space="preserve">onCorrect</t>
         </is>
       </c>
       <c r="C309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">premadeImpacts</t>
+        </is>
+      </c>
+      <c r="B310" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">onWrong</t>
         </is>
       </c>
       <c r="C310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E310" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.history</t>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D310" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
       <c r="B311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.leaderGained</t>
+          <t xml:space="preserve">skipNationScore</t>
         </is>
       </c>
       <c r="C311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -7427,19 +7452,14 @@
           <t xml:space="preserve">history</t>
         </is>
       </c>
-      <c r="B312" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lines.leaderLost</t>
-        </is>
-      </c>
       <c r="C312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D312" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E312" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.history</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7471,7 @@
       </c>
       <c r="B313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.carry</t>
+          <t xml:space="preserve">lines.leaderGained</t>
         </is>
       </c>
       <c r="C313" s="1" t="inlineStr">
@@ -7473,7 +7493,7 @@
       </c>
       <c r="B314" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.dominant</t>
+          <t xml:space="preserve">lines.leaderLost</t>
         </is>
       </c>
       <c r="C314" s="1" t="inlineStr">
@@ -7484,11 +7504,6 @@
       <c r="D314" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F314" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">an attribute becomes dominant in a place: {attribute} and {place}</t>
         </is>
       </c>
     </row>
@@ -7500,7 +7515,7 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.panic</t>
+          <t xml:space="preserve">lines.carry</t>
         </is>
       </c>
       <c r="C315" s="1" t="inlineStr">
@@ -7511,45 +7526,45 @@
       <c r="D315" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F315" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">an accepted costume error caused a panic: {place} and {value} (the wrong item)</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyRules</t>
+          <t xml:space="preserve">history</t>
+        </is>
+      </c>
+      <c r="B316" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lines.dominant</t>
         </is>
       </c>
       <c r="C316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E316" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D316" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history rules: when their conditions pass at night they rewrite a place's fact</t>
+          <t xml:space="preserve">an attribute becomes dominant in a place: {attribute} and {place}</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyRules</t>
+          <t xml:space="preserve">history</t>
         </is>
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">lines.panic</t>
         </is>
       </c>
       <c r="C317" s="1" t="inlineStr">
@@ -7559,12 +7574,12 @@
       </c>
       <c r="D317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E317" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F317" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">an accepted costume error caused a panic: {place} and {value} (the wrong item)</t>
         </is>
       </c>
     </row>
@@ -7574,19 +7589,19 @@
           <t xml:space="preserve">historyRules</t>
         </is>
       </c>
-      <c r="B318" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
       <c r="C318" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D318" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E318" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.history.rules, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F318" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">history rules: when their conditions pass at night they rewrite a place's fact</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7613,7 @@
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">news</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C319" s="1" t="inlineStr">
@@ -7608,51 +7623,56 @@
       </c>
       <c r="D319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E319" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
+          <t xml:space="preserve">historyRules</t>
+        </is>
+      </c>
+      <c r="B320" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E320" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules[].conditions, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D320" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
+          <t xml:space="preserve">historyRules</t>
         </is>
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rule</t>
+          <t xml:space="preserve">news</t>
         </is>
       </c>
       <c r="C321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E321" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7662,19 +7682,14 @@
           <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
-      <c r="B322" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">type</t>
-        </is>
-      </c>
       <c r="C322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D322" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E322" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.history.rules[].conditions, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -7686,17 +7701,22 @@
       </c>
       <c r="B323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">rule</t>
         </is>
       </c>
       <c r="C323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E323" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7708,7 +7728,7 @@
       </c>
       <c r="B324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C324" s="1" t="inlineStr">
@@ -7718,12 +7738,7 @@
       </c>
       <c r="D324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E324" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -7735,7 +7750,7 @@
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C325" s="1" t="inlineStr">
@@ -7746,11 +7761,6 @@
       <c r="D325" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E325" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7772,7 @@
       </c>
       <c r="B326" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C326" s="1" t="inlineStr">
@@ -7777,7 +7787,7 @@
       </c>
       <c r="E326" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
@@ -7789,61 +7799,71 @@
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (left out of the JSON)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E327" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
+          <t xml:space="preserve">historyConditions</t>
+        </is>
+      </c>
+      <c r="B328" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D328" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules[].edits, in order; the first column names the parent row</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
+          <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rule</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E329" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
+          <t xml:space="preserve">0 (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -7853,24 +7873,14 @@
           <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
-      <c r="B330" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">place</t>
-        </is>
-      </c>
       <c r="C330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D330" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">one row per item of the list $.history.rules[].edits, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -7882,17 +7892,22 @@
       </c>
       <c r="B331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">rule</t>
         </is>
       </c>
       <c r="C331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E331" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7919,7 @@
       </c>
       <c r="B332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C332" s="1" t="inlineStr">
@@ -7915,40 +7930,45 @@
       <c r="D332" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E332" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">news</t>
+          <t xml:space="preserve">historyEdits</t>
+        </is>
+      </c>
+      <c r="B333" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C333" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E333" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.news</t>
-        </is>
-      </c>
-      <c r="F333" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the morning paper's debt-theme lines</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D333" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">news</t>
+          <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">stranded</t>
+          <t xml:space="preserve">value</t>
         </is>
       </c>
       <c r="C334" s="1" t="inlineStr">
@@ -7959,45 +7979,40 @@
       <c r="D334" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F334" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the morning paper's line per traveller stranded the day before: {name} and {place}</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">newsDebt</t>
+          <t xml:space="preserve">news</t>
         </is>
       </c>
       <c r="C335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Values</t>
+          <t xml:space="preserve">Single</t>
         </is>
       </c>
       <c r="E335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.news.debt, in order</t>
+          <t xml:space="preserve">one row: the object $.news</t>
         </is>
       </c>
       <c r="F335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the morning paper's debt lines: one a day, in a shuffled order per run</t>
+          <t xml:space="preserve">the morning paper's debt-theme lines</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">newsDebt</t>
+          <t xml:space="preserve">news</t>
         </is>
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">stranded</t>
         </is>
       </c>
       <c r="C336" s="1" t="inlineStr">
@@ -8007,105 +8022,100 @@
       </c>
       <c r="D336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F336" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the morning paper's line per traveller stranded the day before: {name} and {place}</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pc</t>
+          <t xml:space="preserve">newsDebt</t>
         </is>
       </c>
       <c r="C337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
+          <t xml:space="preserve">Values</t>
         </is>
       </c>
       <c r="E337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row: the object $.pc</t>
+          <t xml:space="preserve">one row per item of the list $.news.debt, in order</t>
+        </is>
+      </c>
+      <c r="F337" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the morning paper's debt lines: one a day, in a shuffled order per run</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pc</t>
+          <t xml:space="preserve">newsDebt</t>
         </is>
       </c>
       <c r="B338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ancestry.includePremades</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
-        </is>
-      </c>
-      <c r="F338" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the premades who are who they claim get cards</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcStepSets</t>
+          <t xml:space="preserve">pc</t>
         </is>
       </c>
       <c r="C339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">Single</t>
         </is>
       </c>
       <c r="E339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.steps.sets, in order; a row's name is type, unique</t>
-        </is>
-      </c>
-      <c r="F339" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the optional steps checklist, one set per traveller kind</t>
+          <t xml:space="preserve">one row: the object $.pc</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcStepSets</t>
+          <t xml:space="preserve">pc</t>
         </is>
       </c>
       <c r="B340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">ancestry.includePremades</t>
         </is>
       </c>
       <c r="C340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E340" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name; one of: default, RichTourist, PoorTourist, Labourer, Displaced</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="F340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a traveller kind, or default: the steps of a kind with no set of its own</t>
+          <t xml:space="preserve">the premades who are who they claim get cards</t>
         </is>
       </c>
     </row>
@@ -8115,29 +8125,19 @@
           <t xml:space="preserve">pcStepSets</t>
         </is>
       </c>
-      <c r="B341" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inherit</t>
-        </is>
-      </c>
       <c r="C341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D341" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'pcStepSets'</t>
+          <t xml:space="preserve">one row per item of the list $.pc.steps.sets, in order; a row's name is type, unique</t>
         </is>
       </c>
       <c r="F341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the set whose steps it starts from; its own step of the same id replaces the parent's (blank: none)</t>
+          <t xml:space="preserve">the optional steps checklist, one set per traveller kind</t>
         </is>
       </c>
     </row>
@@ -8149,71 +8149,86 @@
       </c>
       <c r="B342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dataOnly</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E342" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name; one of: default, RichTourist, PoorTourist, Labourer, Displaced</t>
         </is>
       </c>
       <c r="F342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true while the kind is not in play yet: its forms and categories may name what a later phase adds</t>
+          <t xml:space="preserve">a traveller kind, or default: the steps of a kind with no set of its own</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSteps</t>
+          <t xml:space="preserve">pcStepSets</t>
+        </is>
+      </c>
+      <c r="B343" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inherit</t>
         </is>
       </c>
       <c r="C343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D343" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.steps.sets[].steps, in order; the first column names the parent row</t>
+          <t xml:space="preserve">names a row of 'pcStepSets'</t>
         </is>
       </c>
       <c r="F343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a set's steps, in order</t>
+          <t xml:space="preserve">the set whose steps it starts from; its own step of the same id replaces the parent's (blank: none)</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSteps</t>
+          <t xml:space="preserve">pcStepSets</t>
         </is>
       </c>
       <c r="B344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">stepSet</t>
+          <t xml:space="preserve">dataOnly</t>
         </is>
       </c>
       <c r="C344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E344" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'pcStepSets' this row belongs to</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="F344" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">true while the kind is not in play yet: its forms and categories may name what a later phase adds</t>
         </is>
       </c>
     </row>
@@ -8223,24 +8238,19 @@
           <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
-      <c r="B345" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C345" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D345" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E345" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.steps.sets[].steps, in order; the first column names the parent row</t>
         </is>
       </c>
       <c r="F345" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">its label is the UI string steps.{id}</t>
+          <t xml:space="preserve">a set's steps, in order</t>
         </is>
       </c>
     </row>
@@ -8252,12 +8262,12 @@
       </c>
       <c r="B346" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">when</t>
+          <t xml:space="preserve">stepSet</t>
         </is>
       </c>
       <c r="C346" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D346" s="1" t="inlineStr">
@@ -8267,12 +8277,7 @@
       </c>
       <c r="E346" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: PapersReceived, PaperRead, Requested, RulesViewed, RecordViewed, Compared, Asked, LookedAt</t>
-        </is>
-      </c>
-      <c r="F346" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the check it waits for, never what the check found</t>
+          <t xml:space="preserve">names the row of 'pcStepSets' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -8284,27 +8289,22 @@
       </c>
       <c r="B347" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">categories</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C347" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D347" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E347" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="F347" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the categories a Compared or Asked step counts (blank: derived from the case)</t>
+          <t xml:space="preserve">its label is the UI string steps.{id}</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="B348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">statement</t>
+          <t xml:space="preserve">when</t>
         </is>
       </c>
       <c r="C348" s="1" t="inlineStr">
@@ -8326,17 +8326,17 @@
       </c>
       <c r="D348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: Any, Field, Answer, Garment</t>
+          <t xml:space="preserve">one of: PapersReceived, PaperRead, Requested, RulesViewed, RecordViewed, Compared, Asked, LookedAt</t>
         </is>
       </c>
       <c r="F348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Compared step's statement side (blank: any)</t>
+          <t xml:space="preserve">the check it waits for, never what the check found</t>
         </is>
       </c>
     </row>
@@ -8348,27 +8348,27 @@
       </c>
       <c r="B349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">truth</t>
+          <t xml:space="preserve">categories</t>
         </is>
       </c>
       <c r="C349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
         </is>
       </c>
       <c r="E349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: Any, Reference, Record, Paper</t>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
       <c r="F349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Compared step's truth side (blank: any)</t>
+          <t xml:space="preserve">the categories a Compared or Asked step counts (blank: derived from the case)</t>
         </is>
       </c>
     </row>
@@ -8380,27 +8380,27 @@
       </c>
       <c r="B350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">forms</t>
+          <t xml:space="preserve">statement</t>
         </is>
       </c>
       <c r="C350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">separate items with |</t>
+          <t xml:space="preserve">one of: Any, Field, Answer, Garment</t>
         </is>
       </c>
       <c r="F350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the form numbers a paper step counts (blank: every paper)</t>
+          <t xml:space="preserve">a Compared step's statement side (blank: any)</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="B351" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">jump.source</t>
+          <t xml:space="preserve">truth</t>
         </is>
       </c>
       <c r="C351" s="1" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E351" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: Documents, Records, Reference, Transcript, Report, Rules</t>
+          <t xml:space="preserve">one of: Any, Reference, Record, Paper</t>
         </is>
       </c>
       <c r="F351" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the tab a click on the step shows</t>
+          <t xml:space="preserve">a Compared step's truth side (blank: any)</t>
         </is>
       </c>
     </row>
@@ -8444,27 +8444,27 @@
       </c>
       <c r="B352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">jump.link</t>
+          <t xml:space="preserve">forms</t>
         </is>
       </c>
       <c r="C352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
         </is>
       </c>
       <c r="E352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: PrimaryName, FirstUncheckedField, CostumeClaimed</t>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
       <c r="F352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">where a click goes instead of a tab</t>
+          <t xml:space="preserve">the form numbers a paper step counts (blank: every paper)</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="B353" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hint</t>
+          <t xml:space="preserve">jump.source</t>
         </is>
       </c>
       <c r="C353" s="1" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E353" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'uiStrings'</t>
+          <t xml:space="preserve">one of: Documents, Records, Reference, Transcript, Report, Rules</t>
         </is>
       </c>
       <c r="F353" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the UI string of the toast a click shows instead of a jump</t>
+          <t xml:space="preserve">the tab a click on the step shows</t>
         </is>
       </c>
     </row>
@@ -8508,71 +8508,86 @@
       </c>
       <c r="B354" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">jump.link</t>
         </is>
       </c>
       <c r="C354" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D354" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (left out of the JSON)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E354" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: PrimaryName, FirstUncheckedField, CostumeClaimed</t>
         </is>
       </c>
       <c r="F354" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">its first day (blank: day 1)</t>
+          <t xml:space="preserve">where a click goes instead of a tab</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSites</t>
+          <t xml:space="preserve">pcSteps</t>
+        </is>
+      </c>
+      <c r="B355" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hint</t>
         </is>
       </c>
       <c r="C355" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D355" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E355" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.sites, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">names a row of 'uiStrings'</t>
         </is>
       </c>
       <c r="F355" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Internet's sites</t>
+          <t xml:space="preserve">the UI string of the toast a click shows instead of a jump</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSites</t>
+          <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
       <c r="B356" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C356" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D356" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E356" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">0 (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="F356" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its first day (blank: day 1)</t>
         </is>
       </c>
     </row>
@@ -8582,29 +8597,19 @@
           <t xml:space="preserve">pcSites</t>
         </is>
       </c>
-      <c r="B357" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kind</t>
-        </is>
-      </c>
       <c r="C357" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D357" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E357" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: News, History, Ancestry, Static</t>
+          <t xml:space="preserve">one row per item of the list $.pc.sites, in order; a row's name is id, unique</t>
         </is>
       </c>
       <c r="F357" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the page builder that serves it</t>
+          <t xml:space="preserve">the Internet's sites</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8621,7 @@
       </c>
       <c r="B358" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C358" s="1" t="inlineStr">
@@ -8626,7 +8631,12 @@
       </c>
       <c r="D358" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E358" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8648,7 @@
       </c>
       <c r="B359" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">domain</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C359" s="1" t="inlineStr">
@@ -8651,9 +8661,14 @@
           <t xml:space="preserve">empty text</t>
         </is>
       </c>
+      <c r="E359" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: News, History, Ancestry, Static</t>
+        </is>
+      </c>
       <c r="F359" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">chronet://{domain}: lower-case letters, digits, dots and dashes</t>
+          <t xml:space="preserve">the page builder that serves it</t>
         </is>
       </c>
     </row>
@@ -8665,7 +8680,7 @@
       </c>
       <c r="B360" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">glyph</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C360" s="1" t="inlineStr">
@@ -8676,11 +8691,6 @@
       <c r="D360" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F360" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the start-page tile's art key</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8702,7 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">blurb</t>
+          <t xml:space="preserve">domain</t>
         </is>
       </c>
       <c r="C361" s="1" t="inlineStr">
@@ -8703,6 +8713,11 @@
       <c r="D361" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F361" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chronet://{domain}: lower-case letters, digits, dots and dashes</t>
         </is>
       </c>
     </row>
@@ -8714,71 +8729,71 @@
       </c>
       <c r="B362" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">glyph</t>
         </is>
       </c>
       <c r="C362" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D362" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F362" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the first day it is listed</t>
+          <t xml:space="preserve">the start-page tile's art key</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPages</t>
+          <t xml:space="preserve">pcSites</t>
+        </is>
+      </c>
+      <c r="B363" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blurb</t>
         </is>
       </c>
       <c r="C363" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E363" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.pages, in order; a row's name is {site}/{path}, unique</t>
-        </is>
-      </c>
-      <c r="F363" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a Static site's authored pages</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D363" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPages</t>
+          <t xml:space="preserve">pcSites</t>
         </is>
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">site</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E364" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name; names a row of 'pcSites'</t>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F364" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the first day it is listed</t>
         </is>
       </c>
     </row>
@@ -8788,29 +8803,19 @@
           <t xml:space="preserve">pcPages</t>
         </is>
       </c>
-      <c r="B365" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">path</t>
-        </is>
-      </c>
       <c r="C365" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D365" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E365" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.pc.pages, in order; a row's name is {site}/{path}, unique</t>
         </is>
       </c>
       <c r="F365" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">blank: the site's front page</t>
+          <t xml:space="preserve">a Static site's authored pages</t>
         </is>
       </c>
     </row>
@@ -8822,7 +8827,7 @@
       </c>
       <c r="B366" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">title</t>
+          <t xml:space="preserve">site</t>
         </is>
       </c>
       <c r="C366" s="1" t="inlineStr">
@@ -8832,51 +8837,66 @@
       </c>
       <c r="D366" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E366" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name; names a row of 'pcSites'</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPageBlocks</t>
+          <t xml:space="preserve">pcPages</t>
+        </is>
+      </c>
+      <c r="B367" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">path</t>
         </is>
       </c>
       <c r="C367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D367" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.pages[].blocks, in order; the first column names the parent row</t>
+          <t xml:space="preserve">part of the row's name</t>
+        </is>
+      </c>
+      <c r="F367" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blank: the site's front page</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPageBlocks</t>
+          <t xml:space="preserve">pcPages</t>
         </is>
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">page</t>
+          <t xml:space="preserve">title</t>
         </is>
       </c>
       <c r="C368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E368" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'pcPages' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -8886,24 +8906,14 @@
           <t xml:space="preserve">pcPageBlocks</t>
         </is>
       </c>
-      <c r="B369" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kind</t>
-        </is>
-      </c>
       <c r="C369" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D369" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E369" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: Headline, Heading, Paragraph, Note, Link, Box</t>
+          <t xml:space="preserve">one row per item of the list $.pc.pages[].blocks, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -8915,17 +8925,22 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">page</t>
         </is>
       </c>
       <c r="C370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E370" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'pcPages' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -8937,7 +8952,7 @@
       </c>
       <c r="B371" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">address</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C371" s="1" t="inlineStr">
@@ -8947,12 +8962,12 @@
       </c>
       <c r="D371" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="F371" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a Link's site name, domain or chronet:// address</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E371" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: Headline, Heading, Paragraph, Note, Link, Box</t>
         </is>
       </c>
     </row>
@@ -8964,76 +8979,76 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C372" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D372" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E372" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F372" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a Box's lines</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPeople</t>
+          <t xml:space="preserve">pcPageBlocks</t>
+        </is>
+      </c>
+      <c r="B373" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">address</t>
         </is>
       </c>
       <c r="C373" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E373" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.ancestry.people, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D373" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="F373" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Lineage Archive's people of the past (no traveller's name)</t>
+          <t xml:space="preserve">a Link's site name, domain or chronet:// address</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPeople</t>
+          <t xml:space="preserve">pcPageBlocks</t>
         </is>
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">lines</t>
         </is>
       </c>
       <c r="C374" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D374" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
         </is>
       </c>
       <c r="E374" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F374" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a Box's lines</t>
         </is>
       </c>
     </row>
@@ -9043,19 +9058,19 @@
           <t xml:space="preserve">pcPeople</t>
         </is>
       </c>
-      <c r="B375" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
-        </is>
-      </c>
       <c r="C375" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D375" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E375" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.ancestry.people, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F375" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the Lineage Archive's people of the past (no traveller's name)</t>
         </is>
       </c>
     </row>
@@ -9067,7 +9082,7 @@
       </c>
       <c r="B376" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">born</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C376" s="1" t="inlineStr">
@@ -9077,7 +9092,12 @@
       </c>
       <c r="D376" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E376" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9109,7 @@
       </c>
       <c r="B377" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">died</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C377" s="1" t="inlineStr">
@@ -9111,7 +9131,7 @@
       </c>
       <c r="B378" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">born</t>
         </is>
       </c>
       <c r="C378" s="1" t="inlineStr">
@@ -9122,11 +9142,6 @@
       <c r="D378" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E378" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9153,7 @@
       </c>
       <c r="B379" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">note</t>
+          <t xml:space="preserve">died</t>
         </is>
       </c>
       <c r="C379" s="1" t="inlineStr">
@@ -9155,34 +9170,39 @@
     <row r="380">
       <c r="A380" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcRelations</t>
+          <t xml:space="preserve">pcPeople</t>
+        </is>
+      </c>
+      <c r="B380" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C380" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D380" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E380" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.ancestry.relations, in order</t>
-        </is>
-      </c>
-      <c r="F380" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one direction per row</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcRelations</t>
+          <t xml:space="preserve">pcPeople</t>
         </is>
       </c>
       <c r="B381" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">person</t>
+          <t xml:space="preserve">note</t>
         </is>
       </c>
       <c r="C381" s="1" t="inlineStr">
@@ -9192,12 +9212,7 @@
       </c>
       <c r="D381" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="F381" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a person's or a premade's id: the card it shows on</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9207,19 +9222,19 @@
           <t xml:space="preserve">pcRelations</t>
         </is>
       </c>
-      <c r="B382" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kind</t>
-        </is>
-      </c>
       <c r="C382" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D382" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E382" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.ancestry.relations, in order</t>
+        </is>
+      </c>
+      <c r="F382" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one direction per row</t>
         </is>
       </c>
     </row>
@@ -9231,7 +9246,7 @@
       </c>
       <c r="B383" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">other</t>
+          <t xml:space="preserve">person</t>
         </is>
       </c>
       <c r="C383" s="1" t="inlineStr">
@@ -9246,41 +9261,41 @@
       </c>
       <c r="F383" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the other card's id</t>
+          <t xml:space="preserve">a person's or a premade's id: the card it shows on</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMail</t>
+          <t xml:space="preserve">pcRelations</t>
+        </is>
+      </c>
+      <c r="B384" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C384" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E384" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.mail, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F384" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mail's authored messages</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D384" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMail</t>
+          <t xml:space="preserve">pcRelations</t>
         </is>
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">other</t>
         </is>
       </c>
       <c r="C385" s="1" t="inlineStr">
@@ -9293,9 +9308,9 @@
           <t xml:space="preserve">(required)</t>
         </is>
       </c>
-      <c r="E385" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+      <c r="F385" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the other card's id</t>
         </is>
       </c>
     </row>
@@ -9305,24 +9320,19 @@
           <t xml:space="preserve">pcMail</t>
         </is>
       </c>
-      <c r="B386" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fromDay</t>
-        </is>
-      </c>
       <c r="C386" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D386" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E386" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.mail, in order; a row's name is id, unique</t>
         </is>
       </c>
       <c r="F386" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the day it arrives (its date)</t>
+          <t xml:space="preserve">Mail's authored messages</t>
         </is>
       </c>
     </row>
@@ -9334,22 +9344,22 @@
       </c>
       <c r="B387" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">untilDay</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C387" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D387" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F387" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the last day it is in the inbox; 0 keeps it for the run</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E387" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -9361,22 +9371,22 @@
       </c>
       <c r="B388" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flag</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C388" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D388" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F388" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a story flag it waits for (blank: none)</t>
+          <t xml:space="preserve">the day it arrives (its date)</t>
         </is>
       </c>
     </row>
@@ -9388,17 +9398,22 @@
       </c>
       <c r="B389" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">from</t>
+          <t xml:space="preserve">untilDay</t>
         </is>
       </c>
       <c r="C389" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D389" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F389" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the last day it is in the inbox; 0 keeps it for the run</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9425,7 @@
       </c>
       <c r="B390" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">subject</t>
+          <t xml:space="preserve">flag</t>
         </is>
       </c>
       <c r="C390" s="1" t="inlineStr">
@@ -9421,55 +9436,55 @@
       <c r="D390" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F390" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a story flag it waits for (blank: none)</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMailBody</t>
+          <t xml:space="preserve">pcMail</t>
+        </is>
+      </c>
+      <c r="B391" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">from</t>
         </is>
       </c>
       <c r="C391" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Values</t>
-        </is>
-      </c>
-      <c r="E391" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.mail[].body, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F391" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its paragraphs</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D391" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMailBody</t>
+          <t xml:space="preserve">pcMail</t>
         </is>
       </c>
       <c r="B392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">mail</t>
+          <t xml:space="preserve">subject</t>
         </is>
       </c>
       <c r="C392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E392" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'pcMail' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9479,48 +9494,58 @@
           <t xml:space="preserve">pcMailBody</t>
         </is>
       </c>
-      <c r="B393" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
       <c r="C393" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D393" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Values</t>
+        </is>
+      </c>
+      <c r="E393" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.mail[].body, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F393" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its paragraphs</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">pcMailBody</t>
+        </is>
+      </c>
+      <c r="B394" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mail</t>
         </is>
       </c>
       <c r="C394" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D394" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E394" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row: the object $.ui</t>
+          <t xml:space="preserve">names the row of 'pcMail' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">pcMailBody</t>
         </is>
       </c>
       <c r="B395" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">readingLanguage</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C395" s="1" t="inlineStr">
@@ -9530,7 +9555,7 @@
       </c>
       <c r="D395" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -9540,19 +9565,14 @@
           <t xml:space="preserve">ui</t>
         </is>
       </c>
-      <c r="B396" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">glossPercent</t>
-        </is>
-      </c>
       <c r="C396" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D396" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E396" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.ui</t>
         </is>
       </c>
     </row>
@@ -9564,17 +9584,17 @@
       </c>
       <c r="B397" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">labelMinScale</t>
+          <t xml:space="preserve">readingLanguage</t>
         </is>
       </c>
       <c r="C397" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D397" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9586,12 +9606,12 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.text</t>
+          <t xml:space="preserve">glossPercent</t>
         </is>
       </c>
       <c r="C398" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D398" s="1" t="inlineStr">
@@ -9608,7 +9628,7 @@
       </c>
       <c r="B399" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.largeText</t>
+          <t xml:space="preserve">labelMinScale</t>
         </is>
       </c>
       <c r="C399" s="1" t="inlineStr">
@@ -9630,7 +9650,7 @@
       </c>
       <c r="B400" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.glyph</t>
+          <t xml:space="preserve">contrast.text</t>
         </is>
       </c>
       <c r="C400" s="1" t="inlineStr">
@@ -9652,7 +9672,7 @@
       </c>
       <c r="B401" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.hint</t>
+          <t xml:space="preserve">contrast.largeText</t>
         </is>
       </c>
       <c r="C401" s="1" t="inlineStr">
@@ -9674,7 +9694,7 @@
       </c>
       <c r="B402" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.outline</t>
+          <t xml:space="preserve">contrast.glyph</t>
         </is>
       </c>
       <c r="C402" s="1" t="inlineStr">
@@ -9696,7 +9716,7 @@
       </c>
       <c r="B403" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.minTextFillAlpha</t>
+          <t xml:space="preserve">contrast.hint</t>
         </is>
       </c>
       <c r="C403" s="1" t="inlineStr">
@@ -9718,46 +9738,51 @@
       </c>
       <c r="B404" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">latinFallbackFont</t>
+          <t xml:space="preserve">contrast.outline</t>
         </is>
       </c>
       <c r="C404" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D404" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">ui</t>
+        </is>
+      </c>
+      <c r="B405" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">contrast.minTextFillAlpha</t>
         </is>
       </c>
       <c r="C405" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E405" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.paletteMap, in order</t>
+          <t xml:space="preserve">decimal</t>
+        </is>
+      </c>
+      <c r="D405" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B406" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">role</t>
+          <t xml:space="preserve">latinFallbackFont</t>
         </is>
       </c>
       <c r="C406" s="1" t="inlineStr">
@@ -9777,19 +9802,14 @@
           <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
-      <c r="B407" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fill</t>
-        </is>
-      </c>
       <c r="C407" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D407" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E407" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.paletteMap, in order</t>
         </is>
       </c>
     </row>
@@ -9801,17 +9821,17 @@
       </c>
       <c r="B408" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">alpha</t>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C408" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D408" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9823,7 +9843,7 @@
       </c>
       <c r="B409" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ink</t>
+          <t xml:space="preserve">fill</t>
         </is>
       </c>
       <c r="C409" s="1" t="inlineStr">
@@ -9845,46 +9865,51 @@
       </c>
       <c r="B410" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">textClass</t>
+          <t xml:space="preserve">alpha</t>
         </is>
       </c>
       <c r="C410" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D410" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">uiPalette</t>
+        </is>
+      </c>
+      <c r="B411" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C411" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E411" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.ui.neutral</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D411" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="B412" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">textClass</t>
         </is>
       </c>
       <c r="C412" s="1" t="inlineStr">
@@ -9904,19 +9929,14 @@
           <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
-      <c r="B413" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">displayName</t>
-        </is>
-      </c>
       <c r="C413" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D413" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E413" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.ui.neutral</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9948,7 @@
       </c>
       <c r="B414" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C414" s="1" t="inlineStr">
@@ -9950,17 +9970,17 @@
       </c>
       <c r="B415" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">runtimeFont</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C415" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D415" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9972,7 +9992,7 @@
       </c>
       <c r="B416" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">headingAdd</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C416" s="1" t="inlineStr">
@@ -9994,17 +10014,17 @@
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">buttonAdd</t>
+          <t xml:space="preserve">runtimeFont</t>
         </is>
       </c>
       <c r="C417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -10016,17 +10036,17 @@
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">stripItalic</t>
+          <t xml:space="preserve">headingAdd</t>
         </is>
       </c>
       <c r="C418" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D418" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10058,7 @@
       </c>
       <c r="B419" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wallpaper</t>
+          <t xml:space="preserve">buttonAdd</t>
         </is>
       </c>
       <c r="C419" s="1" t="inlineStr">
@@ -10055,34 +10075,34 @@
     <row r="420">
       <c r="A420" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiNeutral</t>
+        </is>
+      </c>
+      <c r="B420" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stripItalic</t>
         </is>
       </c>
       <c r="C420" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E420" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.fonts, in order</t>
-        </is>
-      </c>
-      <c r="F420" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D420" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="B421" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">file</t>
+          <t xml:space="preserve">wallpaper</t>
         </is>
       </c>
       <c r="C421" s="1" t="inlineStr">
@@ -10102,19 +10122,19 @@
           <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
-      <c r="B422" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">face</t>
-        </is>
-      </c>
       <c r="C422" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D422" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E422" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.fonts, in order</t>
+        </is>
+      </c>
+      <c r="F422" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10146,7 @@
       </c>
       <c r="B423" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">family</t>
+          <t xml:space="preserve">file</t>
         </is>
       </c>
       <c r="C423" s="1" t="inlineStr">
@@ -10148,46 +10168,51 @@
       </c>
       <c r="B424" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">style</t>
+          <t xml:space="preserve">face</t>
         </is>
       </c>
       <c r="C424" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D424" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
+          <t xml:space="preserve">neutralFonts</t>
+        </is>
+      </c>
+      <c r="B425" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C425" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E425" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.seeds, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D425" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
+          <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
       <c r="B426" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">style</t>
         </is>
       </c>
       <c r="C426" s="1" t="inlineStr">
@@ -10207,48 +10232,48 @@
           <t xml:space="preserve">neutralSeeds</t>
         </is>
       </c>
-      <c r="B427" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hex</t>
-        </is>
-      </c>
       <c r="C427" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D427" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E427" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.seeds, in order</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">neutralSeeds</t>
+        </is>
+      </c>
+      <c r="B428" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C428" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E428" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.overrides, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D428" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">neutralSeeds</t>
         </is>
       </c>
       <c r="B429" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">role</t>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C429" s="1" t="inlineStr">
@@ -10268,19 +10293,14 @@
           <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
-      <c r="B430" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fill</t>
-        </is>
-      </c>
       <c r="C430" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D430" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E430" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.overrides, in order</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10312,7 @@
       </c>
       <c r="B431" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ink</t>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C431" s="1" t="inlineStr">
@@ -10309,29 +10329,34 @@
     <row r="432">
       <c r="A432" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
+          <t xml:space="preserve">neutralOverrides</t>
+        </is>
+      </c>
+      <c r="B432" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fill</t>
         </is>
       </c>
       <c r="C432" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E432" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.art, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D432" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
+          <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
       <c r="B433" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C433" s="1" t="inlineStr">
@@ -10351,48 +10376,48 @@
           <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
-      <c r="B434" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hex</t>
-        </is>
-      </c>
       <c r="C434" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D434" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E434" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.art, in order</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">neutralArt</t>
+        </is>
+      </c>
+      <c r="B435" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C435" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E435" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.strings, in order; a row's name is key, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D435" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
       <c r="B436" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">hex</t>
         </is>
       </c>
       <c r="C436" s="1" t="inlineStr">
@@ -10402,12 +10427,7 @@
       </c>
       <c r="D436" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E436" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10417,19 +10437,14 @@
           <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
-      <c r="B437" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
       <c r="C437" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D437" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E437" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.strings, in order; a row's name is key, unique</t>
         </is>
       </c>
     </row>
@@ -10441,7 +10456,7 @@
       </c>
       <c r="B438" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gloss</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C438" s="1" t="inlineStr">
@@ -10451,7 +10466,12 @@
       </c>
       <c r="D438" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E438" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -10463,7 +10483,7 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tier</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C439" s="1" t="inlineStr">
@@ -10480,29 +10500,34 @@
     <row r="440">
       <c r="A440" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
+          <t xml:space="preserve">uiStrings</t>
+        </is>
+      </c>
+      <c r="B440" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gloss</t>
         </is>
       </c>
       <c r="C440" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E440" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.languages, in order; a row's name is language, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D440" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
+          <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
       <c r="B441" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">tier</t>
         </is>
       </c>
       <c r="C441" s="1" t="inlineStr">
@@ -10512,12 +10537,7 @@
       </c>
       <c r="D441" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E441" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10527,63 +10547,63 @@
           <t xml:space="preserve">uiLanguages</t>
         </is>
       </c>
-      <c r="B442" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rtl</t>
-        </is>
-      </c>
       <c r="C442" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
-        </is>
-      </c>
-      <c r="D442" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E442" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.languages, in order; a row's name is language, unique</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
+          <t xml:space="preserve">uiLanguages</t>
+        </is>
+      </c>
+      <c r="B443" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C443" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D443" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E443" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.ui.languages[].entries, in order; the first column names the parent row</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
+          <t xml:space="preserve">uiLanguages</t>
         </is>
       </c>
       <c r="B444" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">rtl</t>
         </is>
       </c>
       <c r="C444" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D444" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E444" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'uiLanguages' this row belongs to</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -10593,24 +10613,14 @@
           <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
-      <c r="B445" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">key</t>
-        </is>
-      </c>
       <c r="C445" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D445" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E445" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'uiStrings'</t>
+          <t xml:space="preserve">one row per item of the list $.ui.languages[].entries, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -10622,56 +10632,71 @@
       </c>
       <c r="B446" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C446" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D446" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E446" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'uiLanguages' this row belongs to</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
+        </is>
+      </c>
+      <c r="B447" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C447" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D447" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E447" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row: the object $.translation</t>
+          <t xml:space="preserve">names a row of 'uiStrings'</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
       <c r="B448" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C448" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D448" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10681,19 +10706,14 @@
           <t xml:space="preserve">translation</t>
         </is>
       </c>
-      <c r="B449" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">announce</t>
-        </is>
-      </c>
       <c r="C449" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D449" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E449" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.translation</t>
         </is>
       </c>
     </row>
@@ -10705,12 +10725,12 @@
       </c>
       <c r="B450" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.startDelay</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C450" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D450" s="1" t="inlineStr">
@@ -10727,17 +10747,17 @@
       </c>
       <c r="B451" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.letterInterval</t>
+          <t xml:space="preserve">announce</t>
         </is>
       </c>
       <c r="C451" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D451" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10769,7 @@
       </c>
       <c r="B452" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.letterSeconds</t>
+          <t xml:space="preserve">flip.startDelay</t>
         </is>
       </c>
       <c r="C452" s="1" t="inlineStr">
@@ -10771,12 +10791,12 @@
       </c>
       <c r="B453" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.scrambleSteps</t>
+          <t xml:space="preserve">flip.letterInterval</t>
         </is>
       </c>
       <c r="C453" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D453" s="1" t="inlineStr">
@@ -10793,27 +10813,17 @@
       </c>
       <c r="B454" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.slots</t>
+          <t xml:space="preserve">flip.letterSeconds</t>
         </is>
       </c>
       <c r="C454" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D454" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E454" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F454" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">slots whose value stays English in untranslated speech</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -10825,27 +10835,17 @@
       </c>
       <c r="B455" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.words</t>
+          <t xml:space="preserve">flip.scrambleSteps</t>
         </is>
       </c>
       <c r="C455" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D455" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E455" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F455" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">words that stay English in untranslated speech</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -10857,17 +10857,27 @@
       </c>
       <c r="B456" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.digits</t>
+          <t xml:space="preserve">keyWords.slots</t>
         </is>
       </c>
       <c r="C456" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D456" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E456" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F456" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slots whose value stays English in untranslated speech</t>
         </is>
       </c>
     </row>
@@ -10879,46 +10889,61 @@
       </c>
       <c r="B457" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fallbackGlyphs</t>
+          <t xml:space="preserve">keyWords.words</t>
         </is>
       </c>
       <c r="C457" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D457" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E457" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F457" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">words that stay English in untranslated speech</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
+          <t xml:space="preserve">translation</t>
+        </is>
+      </c>
+      <c r="B458" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">keyWords.digits</t>
         </is>
       </c>
       <c r="C458" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E458" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.scripts, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D458" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B459" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">fallbackGlyphs</t>
         </is>
       </c>
       <c r="C459" s="1" t="inlineStr">
@@ -10928,12 +10953,7 @@
       </c>
       <c r="D459" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E459" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10943,68 +10963,63 @@
           <t xml:space="preserve">scripts</t>
         </is>
       </c>
-      <c r="B460" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rightToLeft</t>
-        </is>
-      </c>
       <c r="C460" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
-        </is>
-      </c>
-      <c r="D460" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E460" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.translation.scripts, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">scripts</t>
+        </is>
+      </c>
+      <c r="B461" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C461" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D461" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E461" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.translation.scripts[].fonts, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F461" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">scripts</t>
         </is>
       </c>
       <c r="B462" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">script</t>
+          <t xml:space="preserve">rightToLeft</t>
         </is>
       </c>
       <c r="C462" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D462" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E462" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'scripts' this row belongs to</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -11014,19 +11029,19 @@
           <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
-      <c r="B463" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">file</t>
-        </is>
-      </c>
       <c r="C463" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D463" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E463" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.translation.scripts[].fonts, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F463" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
         </is>
       </c>
     </row>
@@ -11038,17 +11053,22 @@
       </c>
       <c r="B464" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">face</t>
+          <t xml:space="preserve">script</t>
         </is>
       </c>
       <c r="C464" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D464" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E464" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'scripts' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -11060,7 +11080,7 @@
       </c>
       <c r="B465" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">family</t>
+          <t xml:space="preserve">file</t>
         </is>
       </c>
       <c r="C465" s="1" t="inlineStr">
@@ -11082,46 +11102,51 @@
       </c>
       <c r="B466" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">style</t>
+          <t xml:space="preserve">face</t>
         </is>
       </c>
       <c r="C466" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D466" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">scriptFonts</t>
+        </is>
+      </c>
+      <c r="B467" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C467" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E467" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.packs, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D467" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
       <c r="B468" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">style</t>
         </is>
       </c>
       <c r="C468" s="1" t="inlineStr">
@@ -11131,12 +11156,7 @@
       </c>
       <c r="D468" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E468" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -11146,19 +11166,14 @@
           <t xml:space="preserve">packs</t>
         </is>
       </c>
-      <c r="B469" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">displayName</t>
-        </is>
-      </c>
       <c r="C469" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D469" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E469" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.translation.packs, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -11170,61 +11185,66 @@
       </c>
       <c r="B470" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">spokenCost</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C470" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D470" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E470" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">packs</t>
+        </is>
+      </c>
+      <c r="B471" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C471" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E471" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D471" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">packs</t>
         </is>
       </c>
       <c r="B472" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">spokenCost</t>
         </is>
       </c>
       <c r="C472" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D472" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E472" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -11234,19 +11254,14 @@
           <t xml:space="preserve">tongues</t>
         </is>
       </c>
-      <c r="B473" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">displayName</t>
-        </is>
-      </c>
       <c r="C473" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D473" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E473" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11273,7 @@
       </c>
       <c r="B474" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">script</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C474" s="1" t="inlineStr">
@@ -11268,12 +11283,12 @@
       </c>
       <c r="D474" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E474" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'scripts'</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -11285,7 +11300,7 @@
       </c>
       <c r="B475" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pack</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C475" s="1" t="inlineStr">
@@ -11296,11 +11311,6 @@
       <c r="D475" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E475" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'packs'</t>
         </is>
       </c>
     </row>
@@ -11312,15 +11322,69 @@
       </c>
       <c r="B476" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">script</t>
+        </is>
+      </c>
+      <c r="C476" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D476" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E476" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'scripts'</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B477" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pack</t>
+        </is>
+      </c>
+      <c r="C477" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D477" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E477" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'packs'</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B478" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">glyphs</t>
         </is>
       </c>
-      <c r="C476" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D476" s="1" t="inlineStr">
+      <c r="C478" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D478" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
         </is>
@@ -15216,12 +15280,13 @@
     <col min="9" max="9" width="26" style="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="1" customWidth="1"/>
     <col min="11" max="11" width="18" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" customWidth="1"/>
-    <col min="14" max="14" width="24" style="1" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="12" max="12" width="22" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11" style="1" customWidth="1"/>
+    <col min="14" max="14" width="16" style="1" customWidth="1"/>
+    <col min="15" max="15" width="24" style="1" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="11" style="1" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15282,30 +15347,35 @@
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">tripAskLabel</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">backLabel</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">smallTalkLabel</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">smallTalkPrompt</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">menuCapacity</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">maxLineChars</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">lookLabel</t>
         </is>
@@ -15369,26 +15439,31 @@
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ask about the trip &gt;</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">&lt; Back</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Small talk</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">How is life back home?</t>
         </is>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>8</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>100</v>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Look &gt;</t>
         </is>
@@ -15532,11 +15607,12 @@
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10" style="1" customWidth="1"/>
-    <col min="4" max="4" width="37" style="1" customWidth="1"/>
-    <col min="5" max="5" width="27" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="10" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37" style="1" customWidth="1"/>
+    <col min="6" max="6" width="27" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15552,25 +15628,30 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">kinds</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">label</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">prompt</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">answer</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">fromDay</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">announce</t>
         </is>
@@ -15589,20 +15670,25 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Currency</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">What money do you pay with at home?</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">We pay in {value}.</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>1</v>
       </c>
     </row>
@@ -15619,20 +15705,25 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Language</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">What language do you speak at home?</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">At home we speak {value}.</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>1</v>
       </c>
     </row>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -20013,7 +20013,7 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">الاستقرار: {0:0}%</t>
+          <t xml:space="preserve">الاستقرار: {0}</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Σταθερότητα: {0:0}%</t>
+          <t xml:space="preserve">Σταθερότητα: {0}</t>
         </is>
       </c>
     </row>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -18157,7 +18157,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="60" style="1" customWidth="1"/>
-    <col min="2" max="2" width="49" style="1" customWidth="1"/>
+    <col min="2" max="2" width="54" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">{count} citizens left on Debt Relief yesterday.</t>
+          <t xml:space="preserve">Citizens who left on Debt Relief yesterday: {count}.</t>
         </is>
       </c>
     </row>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -16014,10 +16014,10 @@
         <v>0.0</v>
       </c>
       <c r="K3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="L3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -5785,7 +5785,7 @@
       </c>
       <c r="F238" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the ask entry for the displaced</t>
+          <t xml:space="preserve">the ask entry, the same for every traveller</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tripAskLabel</t>
+          <t xml:space="preserve">backLabel</t>
         </is>
       </c>
       <c r="C239" s="1" t="inlineStr">
@@ -5808,11 +5808,6 @@
       <c r="D239" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F239" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the ask entry for a 2150 citizen, who is asked about the trip</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5819,7 @@
       </c>
       <c r="B240" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">backLabel</t>
+          <t xml:space="preserve">smallTalkLabel</t>
         </is>
       </c>
       <c r="C240" s="1" t="inlineStr">
@@ -5846,7 +5841,7 @@
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">smallTalkLabel</t>
+          <t xml:space="preserve">smallTalkPrompt</t>
         </is>
       </c>
       <c r="C241" s="1" t="inlineStr">
@@ -5868,17 +5863,17 @@
       </c>
       <c r="B242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">smallTalkPrompt</t>
+          <t xml:space="preserve">menuCapacity</t>
         </is>
       </c>
       <c r="C242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D242" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5885,7 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">menuCapacity</t>
+          <t xml:space="preserve">maxLineChars</t>
         </is>
       </c>
       <c r="C243" s="1" t="inlineStr">
@@ -5912,39 +5907,39 @@
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">maxLineChars</t>
+          <t xml:space="preserve">lookLabel</t>
         </is>
       </c>
       <c r="C244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interview</t>
-        </is>
-      </c>
-      <c r="B245" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lookLabel</t>
+          <t xml:space="preserve">claims</t>
         </is>
       </c>
       <c r="C245" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D245" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E245" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.interview.claims, in order</t>
+        </is>
+      </c>
+      <c r="F245" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the claim per traveller kind ({place}): one row per kind a blueprint makes</t>
         </is>
       </c>
     </row>
@@ -5954,19 +5949,24 @@
           <t xml:space="preserve">claims</t>
         </is>
       </c>
+      <c r="B246" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kind</t>
+        </is>
+      </c>
       <c r="C246" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D246" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E246" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.interview.claims, in order</t>
-        </is>
-      </c>
-      <c r="F246" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the claim per traveller kind ({place}): one row per kind a blueprint makes</t>
+          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C247" s="1" t="inlineStr">
@@ -5988,34 +5988,29 @@
       </c>
       <c r="D247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E247" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">claims</t>
-        </is>
-      </c>
-      <c r="B248" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">askGroups</t>
         </is>
       </c>
       <c r="C248" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D248" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E248" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.interview.askGroups, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F248" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">request groups: several forms as one request</t>
         </is>
       </c>
     </row>
@@ -6025,19 +6020,29 @@
           <t xml:space="preserve">askGroups</t>
         </is>
       </c>
+      <c r="B249" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
       <c r="C249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D249" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.interview.askGroups, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
       <c r="F249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">request groups: several forms as one request</t>
+          <t xml:space="preserve">the request group (DocumentTemplateSO.askGroup; proof: the proofs of means)</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6054,7 @@
       </c>
       <c r="B250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C250" s="1" t="inlineStr">
@@ -6059,44 +6064,34 @@
       </c>
       <c r="D250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E250" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the request group (DocumentTemplateSO.askGroup; proof: the proofs of means)</t>
+          <t xml:space="preserve">the papers menu's one entry for the group</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">askGroups</t>
-        </is>
-      </c>
-      <c r="B251" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">interviewRequests</t>
         </is>
       </c>
       <c r="C251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D251" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E251" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.interview.requests, in order; a row's name is id, unique</t>
         </is>
       </c>
       <c r="F251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the papers menu's one entry for the group</t>
+          <t xml:space="preserve">spoken requests: the wheel entry, the desk's prompt and the traveller's reply</t>
         </is>
       </c>
     </row>
@@ -6106,19 +6101,24 @@
           <t xml:space="preserve">interviewRequests</t>
         </is>
       </c>
+      <c r="B252" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
       <c r="C252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D252" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.interview.requests, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F252" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spoken requests: the wheel entry, the desk's prompt and the traveller's reply</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C253" s="1" t="inlineStr">
@@ -6140,12 +6140,7 @@
       </c>
       <c r="D253" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E253" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6157,7 +6152,7 @@
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C254" s="1" t="inlineStr">
@@ -6179,7 +6174,7 @@
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">reply</t>
         </is>
       </c>
       <c r="C255" s="1" t="inlineStr">
@@ -6196,22 +6191,22 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">interviewRequests</t>
-        </is>
-      </c>
-      <c r="B256" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">reply</t>
+          <t xml:space="preserve">missingFormReplies</t>
         </is>
       </c>
       <c r="C256" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D256" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E256" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.interview.missingFormReplies, in order</t>
+        </is>
+      </c>
+      <c r="F256" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">what a kind says when asked for a request they carry no form of</t>
         </is>
       </c>
     </row>
@@ -6221,19 +6216,24 @@
           <t xml:space="preserve">missingFormReplies</t>
         </is>
       </c>
+      <c r="B257" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kind</t>
+        </is>
+      </c>
       <c r="C257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D257" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.interview.missingFormReplies, in order</t>
-        </is>
-      </c>
-      <c r="F257" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">what a kind says when asked for a request they carry no form of</t>
+          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">request</t>
         </is>
       </c>
       <c r="C258" s="1" t="inlineStr">
@@ -6258,9 +6258,9 @@
           <t xml:space="preserve">(required)</t>
         </is>
       </c>
-      <c r="E258" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one of: RichTourist, PoorTourist, Labourer, Displaced</t>
+      <c r="F258" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a form number (TC-310) or a request group's id (proof)</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">request</t>
+          <t xml:space="preserve">variant</t>
         </is>
       </c>
       <c r="C259" s="1" t="inlineStr">
@@ -6282,12 +6282,17 @@
       </c>
       <c r="D259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E259" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: Honest, Missing</t>
         </is>
       </c>
       <c r="F259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a form number (TC-310) or a request group's id (proof)</t>
+          <t xml:space="preserve">Honest: the kind never needs it; Missing: they should have it (a paper-set fault)</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6304,7 @@
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">variant</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C260" s="1" t="inlineStr">
@@ -6310,38 +6315,28 @@
       <c r="D260" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E260" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one of: Honest, Missing</t>
-        </is>
-      </c>
-      <c r="F260" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Honest: the kind never needs it; Missing: they should have it (a paper-set fault)</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">missingFormReplies</t>
-        </is>
-      </c>
-      <c r="B261" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">questions</t>
         </is>
       </c>
       <c r="C261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D261" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E261" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.questions, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F261" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one question per category, asked of every traveller in the same words</t>
         </is>
       </c>
     </row>
@@ -6351,14 +6346,24 @@
           <t xml:space="preserve">questions</t>
         </is>
       </c>
+      <c r="B262" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
       <c r="C262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D262" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.questions, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6375,7 @@
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C263" s="1" t="inlineStr">
@@ -6380,12 +6385,7 @@
       </c>
       <c r="D263" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E263" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C264" s="1" t="inlineStr">
@@ -6419,27 +6419,17 @@
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kinds</t>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D265" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E265" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F265" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the traveller kinds the desk asks it of (RichTourist, PoorTourist, Labourer, Displaced); blank: every kind; one question per category per kind</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6451,7 +6441,7 @@
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">answer</t>
         </is>
       </c>
       <c r="C266" s="1" t="inlineStr">
@@ -6473,17 +6463,17 @@
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6485,7 @@
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">announce</t>
         </is>
       </c>
       <c r="C268" s="1" t="inlineStr">
@@ -6512,44 +6502,49 @@
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
-        </is>
-      </c>
-      <c r="B269" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
       <c r="C269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
-        </is>
-      </c>
-      <c r="D269" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E269" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.questions[].conditions, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F269" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all must pass</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
+          <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">announce</t>
+          <t xml:space="preserve">question</t>
         </is>
       </c>
       <c r="C270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D270" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E270" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6559,19 +6554,19 @@
           <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
+      <c r="B271" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
       <c r="C271" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E271" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.questions[].conditions, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F271" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all must pass</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D271" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -6583,22 +6578,17 @@
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">question</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E272" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -6610,17 +6600,17 @@
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -6632,7 +6622,7 @@
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
@@ -6642,7 +6632,12 @@
       </c>
       <c r="D274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E274" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -6654,17 +6649,22 @@
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E275" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C276" s="1" t="inlineStr">
@@ -6691,61 +6691,56 @@
       </c>
       <c r="E276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
-        </is>
-      </c>
-      <c r="B277" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
       <c r="C277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D277" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">one row per item of the list $.questions[].overrides, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F277" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the answer for some kinds, an era or both (the most specific wins: kinds 2, era 1); every traveller is asked the question's own prompt</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
+          <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">question</t>
         </is>
       </c>
       <c r="C278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6755,19 +6750,29 @@
           <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
+      <c r="B279" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">era</t>
+        </is>
+      </c>
       <c r="C279" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D279" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E279" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.questions[].overrides, in order; the first column names the parent row</t>
+          <t xml:space="preserve">names a row of 'eras'</t>
         </is>
       </c>
       <c r="F279" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the wording in one era</t>
+          <t xml:space="preserve">the claimed era (blank: any)</t>
         </is>
       </c>
     </row>
@@ -6779,22 +6784,27 @@
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">question</t>
+          <t xml:space="preserve">kinds</t>
         </is>
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
         </is>
       </c>
       <c r="E280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F280" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the traveller kinds (RichTourist, PoorTourist, Labourer, Displaced); blank: any</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6816,7 @@
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">answer</t>
         </is>
       </c>
       <c r="C281" s="1" t="inlineStr">
@@ -6817,45 +6827,40 @@
       <c r="D281" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E281" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'eras'</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
-        </is>
-      </c>
-      <c r="B282" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">dialogs</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D282" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E282" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F282" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrative dialogs: nodes, their lines and the player's choices</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
+          <t xml:space="preserve">dialogs</t>
         </is>
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
@@ -6865,7 +6870,12 @@
       </c>
       <c r="D283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E283" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -6875,19 +6885,24 @@
           <t xml:space="preserve">dialogs</t>
         </is>
       </c>
+      <c r="B284" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">label</t>
+        </is>
+      </c>
       <c r="C284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E284" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D284" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">narrative dialogs: nodes, their lines and the player's choices</t>
+          <t xml:space="preserve">the wheel entry</t>
         </is>
       </c>
     </row>
@@ -6899,71 +6914,66 @@
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">repeatable</t>
         </is>
       </c>
       <c r="C285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E285" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
-        </is>
-      </c>
-      <c r="B286" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
       <c r="C286" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D286" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E286" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].conditions, in order; the first column names the parent row</t>
         </is>
       </c>
       <c r="F286" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the wheel entry</t>
+          <t xml:space="preserve">all must pass</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
+          <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">repeatable</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E287" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -6973,19 +6983,19 @@
           <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
+      <c r="B288" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
       <c r="C288" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E288" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].conditions, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F288" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all must pass</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D288" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -6997,22 +7007,17 @@
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C289" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D289" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E289" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7024,17 +7029,17 @@
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7051,7 @@
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C291" s="1" t="inlineStr">
@@ -7056,7 +7061,12 @@
       </c>
       <c r="D291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E291" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -7068,17 +7078,22 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D292" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E292" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7105,7 @@
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C293" s="1" t="inlineStr">
@@ -7105,61 +7120,51 @@
       </c>
       <c r="E293" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
-        </is>
-      </c>
-      <c r="B294" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
       <c r="C294" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D294" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E294" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes, in order; a row's name is id, unique per parent row; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
+          <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D295" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E295" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7169,58 +7174,58 @@
           <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
+      <c r="B296" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
       <c r="C296" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D296" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E296" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes, in order; a row's name is id, unique per parent row; the first column names the parent row</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogNodes</t>
-        </is>
-      </c>
-      <c r="B297" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
       <c r="C297" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D297" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E297" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].lines, in order; the first columns name the parent row</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogNodes</t>
+          <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C298" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D298" s="1" t="inlineStr">
@@ -7230,7 +7235,7 @@
       </c>
       <c r="E298" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7240,14 +7245,24 @@
           <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
+      <c r="B299" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">node</t>
+        </is>
+      </c>
       <c r="C299" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D299" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E299" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].lines, in order; the first columns name the parent row</t>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7259,22 +7274,17 @@
       </c>
       <c r="B300" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C300" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D300" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E300" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7286,22 +7296,17 @@
       </c>
       <c r="B301" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">speaker</t>
         </is>
       </c>
       <c r="C301" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D301" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E301" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7318,7 @@
       </c>
       <c r="B302" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">expression</t>
         </is>
       </c>
       <c r="C302" s="1" t="inlineStr">
@@ -7323,7 +7328,7 @@
       </c>
       <c r="D302" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7340,7 @@
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">speaker</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C303" s="1" t="inlineStr">
@@ -7352,44 +7357,44 @@
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
-        </is>
-      </c>
-      <c r="B304" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">expression</t>
+          <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
       <c r="C304" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D304" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E304" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices, in order; a row's name is id, unique per parent row; the first columns name the parent row</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
+          <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
       <c r="B305" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C305" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D305" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E305" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7399,14 +7404,24 @@
           <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
+      <c r="B306" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">node</t>
+        </is>
+      </c>
       <c r="C306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D306" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices, in order; a row's name is id, unique per parent row; the first columns name the parent row</t>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7418,12 +7433,12 @@
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D307" s="1" t="inlineStr">
@@ -7433,7 +7448,7 @@
       </c>
       <c r="E307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -7445,22 +7460,17 @@
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D308" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E308" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7482,7 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">next</t>
         </is>
       </c>
       <c r="C309" s="1" t="inlineStr">
@@ -7482,12 +7492,12 @@
       </c>
       <c r="D309" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E309" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F309" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the node it leads to (blank: the dialog ends)</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7509,7 @@
       </c>
       <c r="B310" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">effect</t>
         </is>
       </c>
       <c r="C310" s="1" t="inlineStr">
@@ -7516,49 +7526,44 @@
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
-        </is>
-      </c>
-      <c r="B311" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">next</t>
+          <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
       <c r="C311" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D311" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F311" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the node it leads to (blank: the dialog ends)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E311" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices[].lines, in order; the first columns name the parent row</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
+          <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
       <c r="B312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">effect</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D312" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E312" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7568,14 +7573,24 @@
           <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
+      <c r="B313" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">node</t>
+        </is>
+      </c>
       <c r="C313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D313" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E313" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices[].lines, in order; the first columns name the parent row</t>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7587,7 +7602,7 @@
       </c>
       <c r="B314" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">choice</t>
         </is>
       </c>
       <c r="C314" s="1" t="inlineStr">
@@ -7602,7 +7617,7 @@
       </c>
       <c r="E314" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">names the row of 'dialogChoices' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -7614,22 +7629,17 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D315" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E315" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7641,22 +7651,17 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choice</t>
+          <t xml:space="preserve">speaker</t>
         </is>
       </c>
       <c r="C316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D316" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E316" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogChoices' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7668,7 +7673,7 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">expression</t>
         </is>
       </c>
       <c r="C317" s="1" t="inlineStr">
@@ -7678,7 +7683,7 @@
       </c>
       <c r="D317" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7695,7 @@
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">speaker</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C318" s="1" t="inlineStr">
@@ -7707,34 +7712,34 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
-        </is>
-      </c>
-      <c r="B319" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">expression</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="C319" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D319" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E319" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.premades, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F319" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">premade characters: real people and written stories</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="B320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C320" s="1" t="inlineStr">
@@ -7744,7 +7749,12 @@
       </c>
       <c r="D320" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E320" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -7754,19 +7764,19 @@
           <t xml:space="preserve">premades</t>
         </is>
       </c>
+      <c r="B321" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
       <c r="C321" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E321" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.premades, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F321" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">premade characters: real people and written stories</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D321" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7788,7 @@
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">gender</t>
         </is>
       </c>
       <c r="C322" s="1" t="inlineStr">
@@ -7788,12 +7798,7 @@
       </c>
       <c r="D322" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E322" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7810,7 @@
       </c>
       <c r="B323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C323" s="1" t="inlineStr">
@@ -7816,6 +7821,11 @@
       <c r="D323" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E323" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -7827,7 +7837,7 @@
       </c>
       <c r="B324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gender</t>
+          <t xml:space="preserve">truePlace</t>
         </is>
       </c>
       <c r="C324" s="1" t="inlineStr">
@@ -7838,6 +7848,16 @@
       <c r="D324" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E324" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
+        </is>
+      </c>
+      <c r="F324" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">where they really come from (blank: honest)</t>
         </is>
       </c>
     </row>
@@ -7849,7 +7869,7 @@
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">birthDate</t>
         </is>
       </c>
       <c r="C325" s="1" t="inlineStr">
@@ -7860,11 +7880,6 @@
       <c r="D325" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E325" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7891,7 @@
       </c>
       <c r="B326" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">truePlace</t>
+          <t xml:space="preserve">archetype</t>
         </is>
       </c>
       <c r="C326" s="1" t="inlineStr">
@@ -7887,16 +7902,6 @@
       <c r="D326" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E326" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
-        </is>
-      </c>
-      <c r="F326" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">where they really come from (blank: honest)</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7913,7 @@
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">birthDate</t>
+          <t xml:space="preserve">intro</t>
         </is>
       </c>
       <c r="C327" s="1" t="inlineStr">
@@ -7930,7 +7935,7 @@
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">archetype</t>
+          <t xml:space="preserve">recordNote</t>
         </is>
       </c>
       <c r="C328" s="1" t="inlineStr">
@@ -7952,7 +7957,7 @@
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">intro</t>
+          <t xml:space="preserve">dialog</t>
         </is>
       </c>
       <c r="C329" s="1" t="inlineStr">
@@ -7963,6 +7968,11 @@
       <c r="D329" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E329" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'dialogs'</t>
         </is>
       </c>
     </row>
@@ -7974,66 +7984,61 @@
       </c>
       <c r="B330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">recordNote</t>
+          <t xml:space="preserve">repeatable</t>
         </is>
       </c>
       <c r="C330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D330" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
-        </is>
-      </c>
-      <c r="B331" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
       <c r="C331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D331" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E331" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'dialogs'</t>
+          <t xml:space="preserve">one row per item of the list $.premades[].impacts, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premades</t>
+          <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
       <c r="B332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">repeatable</t>
+          <t xml:space="preserve">premade</t>
         </is>
       </c>
       <c r="C332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D332" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E332" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'premades' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -8043,14 +8048,24 @@
           <t xml:space="preserve">premadeImpacts</t>
         </is>
       </c>
+      <c r="B333" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attribute</t>
+        </is>
+      </c>
       <c r="C333" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D333" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E333" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.premades[].impacts, in order; the first column names the parent row</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
@@ -8062,22 +8077,17 @@
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premade</t>
+          <t xml:space="preserve">onCorrect</t>
         </is>
       </c>
       <c r="C334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D334" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E334" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'premades' this row belongs to</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -8089,22 +8099,17 @@
       </c>
       <c r="B335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">onWrong</t>
         </is>
       </c>
       <c r="C335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D335" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E335" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -8116,61 +8121,56 @@
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">onCorrect</t>
+          <t xml:space="preserve">skipNationScore</t>
         </is>
       </c>
       <c r="C336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D336" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
-        </is>
-      </c>
-      <c r="B337" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">onWrong</t>
+          <t xml:space="preserve">history</t>
         </is>
       </c>
       <c r="C337" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
-        </is>
-      </c>
-      <c r="D337" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E337" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.history</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">premadeImpacts</t>
+          <t xml:space="preserve">history</t>
         </is>
       </c>
       <c r="B338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">skipNationScore</t>
+          <t xml:space="preserve">lines.leaderGained</t>
         </is>
       </c>
       <c r="C338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D338" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -8180,14 +8180,19 @@
           <t xml:space="preserve">history</t>
         </is>
       </c>
+      <c r="B339" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lines.leaderLost</t>
+        </is>
+      </c>
       <c r="C339" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E339" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.history</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D339" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -8199,7 +8204,7 @@
       </c>
       <c r="B340" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.leaderGained</t>
+          <t xml:space="preserve">lines.carry</t>
         </is>
       </c>
       <c r="C340" s="1" t="inlineStr">
@@ -8221,7 +8226,7 @@
       </c>
       <c r="B341" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.leaderLost</t>
+          <t xml:space="preserve">lines.dominant</t>
         </is>
       </c>
       <c r="C341" s="1" t="inlineStr">
@@ -8232,6 +8237,11 @@
       <c r="D341" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F341" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">an attribute becomes dominant in a place: {attribute} and {place}</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8253,7 @@
       </c>
       <c r="B342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.carry</t>
+          <t xml:space="preserve">lines.panic</t>
         </is>
       </c>
       <c r="C342" s="1" t="inlineStr">
@@ -8254,45 +8264,45 @@
       <c r="D342" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F342" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">an accepted costume error caused a panic: {place} and {value} (the wrong item)</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
-        </is>
-      </c>
-      <c r="B343" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lines.dominant</t>
+          <t xml:space="preserve">historyRules</t>
         </is>
       </c>
       <c r="C343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D343" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E343" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.history.rules, in order; a row's name is id, unique</t>
         </is>
       </c>
       <c r="F343" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">an attribute becomes dominant in a place: {attribute} and {place}</t>
+          <t xml:space="preserve">history rules: when their conditions pass at night they rewrite a place's fact</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">history</t>
+          <t xml:space="preserve">historyRules</t>
         </is>
       </c>
       <c r="B344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines.panic</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C344" s="1" t="inlineStr">
@@ -8302,12 +8312,12 @@
       </c>
       <c r="D344" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F344" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">an accepted costume error caused a panic: {place} and {value} (the wrong item)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E344" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -8317,19 +8327,19 @@
           <t xml:space="preserve">historyRules</t>
         </is>
       </c>
+      <c r="B345" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
       <c r="C345" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E345" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F345" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">history rules: when their conditions pass at night they rewrite a place's fact</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D345" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8351,7 @@
       </c>
       <c r="B346" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">news</t>
         </is>
       </c>
       <c r="C346" s="1" t="inlineStr">
@@ -8351,56 +8361,51 @@
       </c>
       <c r="D346" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E346" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyRules</t>
-        </is>
-      </c>
-      <c r="B347" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
       <c r="C347" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D347" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E347" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.history.rules[].conditions, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyRules</t>
+          <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
       <c r="B348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">news</t>
+          <t xml:space="preserve">rule</t>
         </is>
       </c>
       <c r="C348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D348" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E348" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -8410,14 +8415,19 @@
           <t xml:space="preserve">historyConditions</t>
         </is>
       </c>
+      <c r="B349" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
       <c r="C349" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E349" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules[].conditions, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D349" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
@@ -8429,22 +8439,17 @@
       </c>
       <c r="B350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rule</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D350" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E350" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -8456,7 +8461,7 @@
       </c>
       <c r="B351" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C351" s="1" t="inlineStr">
@@ -8466,7 +8471,12 @@
       </c>
       <c r="D351" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E351" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8488,7 @@
       </c>
       <c r="B352" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C352" s="1" t="inlineStr">
@@ -8489,6 +8499,11 @@
       <c r="D352" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E352" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8515,7 @@
       </c>
       <c r="B353" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C353" s="1" t="inlineStr">
@@ -8515,7 +8530,7 @@
       </c>
       <c r="E353" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
@@ -8527,71 +8542,61 @@
       </c>
       <c r="B354" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C354" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D354" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E354" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">0 (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
-        </is>
-      </c>
-      <c r="B355" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
       <c r="C355" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D355" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E355" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">one row per item of the list $.history.rules[].edits, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyConditions</t>
+          <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
       <c r="B356" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">rule</t>
         </is>
       </c>
       <c r="C356" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D356" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E356" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -8601,14 +8606,24 @@
           <t xml:space="preserve">historyEdits</t>
         </is>
       </c>
+      <c r="B357" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">place</t>
+        </is>
+      </c>
       <c r="C357" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D357" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E357" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.history.rules[].edits, in order; the first column names the parent row</t>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -8620,22 +8635,17 @@
       </c>
       <c r="B358" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rule</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C358" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D358" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E358" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'historyRules' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -8647,7 +8657,7 @@
       </c>
       <c r="B359" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">value</t>
         </is>
       </c>
       <c r="C359" s="1" t="inlineStr">
@@ -8658,45 +8668,40 @@
       <c r="D359" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E359" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
-        </is>
-      </c>
-      <c r="B360" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">news</t>
         </is>
       </c>
       <c r="C360" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D360" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E360" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.news</t>
+        </is>
+      </c>
+      <c r="F360" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the morning paper's debt-theme lines</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">historyEdits</t>
+          <t xml:space="preserve">news</t>
         </is>
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t xml:space="preserve">stranded</t>
         </is>
       </c>
       <c r="C361" s="1" t="inlineStr">
@@ -8707,6 +8712,11 @@
       <c r="D361" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F361" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the morning paper's line per traveller stranded the day before: {name} and {place}</t>
         </is>
       </c>
     </row>
@@ -8716,58 +8726,58 @@
           <t xml:space="preserve">news</t>
         </is>
       </c>
+      <c r="B362" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debtReliefCount</t>
+        </is>
+      </c>
       <c r="C362" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E362" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.news</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D362" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F362" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the morning paper's debt-theme lines</t>
+          <t xml:space="preserve">the morning paper's count of the Debt Relief departures the last shift approved: {count}</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">news</t>
-        </is>
-      </c>
-      <c r="B363" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stranded</t>
+          <t xml:space="preserve">newsDebt</t>
         </is>
       </c>
       <c r="C363" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D363" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Values</t>
+        </is>
+      </c>
+      <c r="E363" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.news.debt, in order</t>
         </is>
       </c>
       <c r="F363" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the morning paper's line per traveller stranded the day before: {name} and {place}</t>
+          <t xml:space="preserve">the morning paper's debt lines: one a day, in a shuffled order per run</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">news</t>
+          <t xml:space="preserve">newsDebt</t>
         </is>
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">debtReliefCount</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C364" s="1" t="inlineStr">
@@ -8777,100 +8787,105 @@
       </c>
       <c r="D364" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F364" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the morning paper's count of the Debt Relief departures the last shift approved: {count}</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">newsDebt</t>
+          <t xml:space="preserve">pc</t>
         </is>
       </c>
       <c r="C365" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Values</t>
+          <t xml:space="preserve">Single</t>
         </is>
       </c>
       <c r="E365" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.news.debt, in order</t>
-        </is>
-      </c>
-      <c r="F365" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the morning paper's debt lines: one a day, in a shuffled order per run</t>
+          <t xml:space="preserve">one row: the object $.pc</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">newsDebt</t>
+          <t xml:space="preserve">pc</t>
         </is>
       </c>
       <c r="B366" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">ancestry.includePremades</t>
         </is>
       </c>
       <c r="C366" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D366" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="F366" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the premades who are who they claim get cards</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pc</t>
+          <t xml:space="preserve">pcStepSets</t>
         </is>
       </c>
       <c r="C367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E367" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row: the object $.pc</t>
+          <t xml:space="preserve">one row per item of the list $.pc.steps.sets, in order; a row's name is type, unique</t>
+        </is>
+      </c>
+      <c r="F367" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the optional steps checklist, one set per traveller kind</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pc</t>
+          <t xml:space="preserve">pcStepSets</t>
         </is>
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ancestry.includePremades</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E368" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name; one of: default, RichTourist, PoorTourist, Labourer, Displaced</t>
         </is>
       </c>
       <c r="F368" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the premades who are who they claim get cards</t>
+          <t xml:space="preserve">a traveller kind, or default: the steps of a kind with no set of its own</t>
         </is>
       </c>
     </row>
@@ -8880,19 +8895,29 @@
           <t xml:space="preserve">pcStepSets</t>
         </is>
       </c>
+      <c r="B369" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inherit</t>
+        </is>
+      </c>
       <c r="C369" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D369" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E369" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.steps.sets, in order; a row's name is type, unique</t>
+          <t xml:space="preserve">names a row of 'pcStepSets'</t>
         </is>
       </c>
       <c r="F369" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the optional steps checklist, one set per traveller kind</t>
+          <t xml:space="preserve">the set whose steps it starts from; its own step of the same id replaces the parent's (blank: none)</t>
         </is>
       </c>
     </row>
@@ -8904,86 +8929,71 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">dataOnly</t>
         </is>
       </c>
       <c r="C370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E370" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name; one of: default, RichTourist, PoorTourist, Labourer, Displaced</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
       <c r="F370" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a traveller kind, or default: the steps of a kind with no set of its own</t>
+          <t xml:space="preserve">true while the kind is not in play yet: its forms and categories may name what a later phase adds</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcStepSets</t>
-        </is>
-      </c>
-      <c r="B371" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inherit</t>
+          <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
       <c r="C371" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D371" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E371" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'pcStepSets'</t>
+          <t xml:space="preserve">one row per item of the list $.pc.steps.sets[].steps, in order; the first column names the parent row</t>
         </is>
       </c>
       <c r="F371" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the set whose steps it starts from; its own step of the same id replaces the parent's (blank: none)</t>
+          <t xml:space="preserve">a set's steps, in order</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcStepSets</t>
+          <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dataOnly</t>
+          <t xml:space="preserve">stepSet</t>
         </is>
       </c>
       <c r="C372" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D372" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="F372" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">true while the kind is not in play yet: its forms and categories may name what a later phase adds</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E372" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'pcStepSets' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -8993,19 +9003,24 @@
           <t xml:space="preserve">pcSteps</t>
         </is>
       </c>
+      <c r="B373" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
       <c r="C373" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E373" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.steps.sets[].steps, in order; the first column names the parent row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D373" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="F373" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a set's steps, in order</t>
+          <t xml:space="preserve">its label is the UI string steps.{id}</t>
         </is>
       </c>
     </row>
@@ -9017,12 +9032,12 @@
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">stepSet</t>
+          <t xml:space="preserve">when</t>
         </is>
       </c>
       <c r="C374" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D374" s="1" t="inlineStr">
@@ -9032,7 +9047,12 @@
       </c>
       <c r="E374" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'pcStepSets' this row belongs to</t>
+          <t xml:space="preserve">one of: PapersReceived, PaperRead, Requested, RulesViewed, RecordViewed, Compared, Asked, LookedAt</t>
+        </is>
+      </c>
+      <c r="F374" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the check it waits for, never what the check found</t>
         </is>
       </c>
     </row>
@@ -9044,22 +9064,27 @@
       </c>
       <c r="B375" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">categories</t>
         </is>
       </c>
       <c r="C375" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D375" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E375" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
       <c r="F375" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">its label is the UI string steps.{id}</t>
+          <t xml:space="preserve">the categories a Compared or Asked step counts (blank: derived from the case)</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9096,7 @@
       </c>
       <c r="B376" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">when</t>
+          <t xml:space="preserve">statement</t>
         </is>
       </c>
       <c r="C376" s="1" t="inlineStr">
@@ -9081,17 +9106,17 @@
       </c>
       <c r="D376" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E376" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: PapersReceived, PaperRead, Requested, RulesViewed, RecordViewed, Compared, Asked, LookedAt</t>
+          <t xml:space="preserve">one of: Any, Field, Answer, Garment</t>
         </is>
       </c>
       <c r="F376" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the check it waits for, never what the check found</t>
+          <t xml:space="preserve">a Compared step's statement side (blank: any)</t>
         </is>
       </c>
     </row>
@@ -9103,27 +9128,27 @@
       </c>
       <c r="B377" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">categories</t>
+          <t xml:space="preserve">truth</t>
         </is>
       </c>
       <c r="C377" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D377" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E377" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">separate items with |</t>
+          <t xml:space="preserve">one of: Any, Reference, Record, Paper</t>
         </is>
       </c>
       <c r="F377" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the categories a Compared or Asked step counts (blank: derived from the case)</t>
+          <t xml:space="preserve">a Compared step's truth side (blank: any)</t>
         </is>
       </c>
     </row>
@@ -9135,27 +9160,27 @@
       </c>
       <c r="B378" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">statement</t>
+          <t xml:space="preserve">forms</t>
         </is>
       </c>
       <c r="C378" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D378" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
         </is>
       </c>
       <c r="E378" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: Any, Field, Answer, Garment</t>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
       <c r="F378" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Compared step's statement side (blank: any)</t>
+          <t xml:space="preserve">the form numbers a paper step counts (blank: every paper)</t>
         </is>
       </c>
     </row>
@@ -9167,7 +9192,7 @@
       </c>
       <c r="B379" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">truth</t>
+          <t xml:space="preserve">jump.source</t>
         </is>
       </c>
       <c r="C379" s="1" t="inlineStr">
@@ -9182,12 +9207,12 @@
       </c>
       <c r="E379" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: Any, Reference, Record, Paper</t>
+          <t xml:space="preserve">one of: Documents, Records, Reference, Transcript, Report, Rules</t>
         </is>
       </c>
       <c r="F379" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Compared step's truth side (blank: any)</t>
+          <t xml:space="preserve">the tab a click on the step shows</t>
         </is>
       </c>
     </row>
@@ -9199,27 +9224,27 @@
       </c>
       <c r="B380" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">forms</t>
+          <t xml:space="preserve">jump.link</t>
         </is>
       </c>
       <c r="C380" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D380" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E380" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">separate items with |</t>
+          <t xml:space="preserve">one of: PrimaryName, FirstUncheckedField, CostumeClaimed</t>
         </is>
       </c>
       <c r="F380" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the form numbers a paper step counts (blank: every paper)</t>
+          <t xml:space="preserve">where a click goes instead of a tab</t>
         </is>
       </c>
     </row>
@@ -9231,7 +9256,7 @@
       </c>
       <c r="B381" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">jump.source</t>
+          <t xml:space="preserve">hint</t>
         </is>
       </c>
       <c r="C381" s="1" t="inlineStr">
@@ -9246,12 +9271,12 @@
       </c>
       <c r="E381" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: Documents, Records, Reference, Transcript, Report, Rules</t>
+          <t xml:space="preserve">names a row of 'uiStrings'</t>
         </is>
       </c>
       <c r="F381" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the tab a click on the step shows</t>
+          <t xml:space="preserve">the UI string of the toast a click shows instead of a jump</t>
         </is>
       </c>
     </row>
@@ -9263,86 +9288,71 @@
       </c>
       <c r="B382" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">jump.link</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C382" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D382" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E382" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one of: PrimaryName, FirstUncheckedField, CostumeClaimed</t>
+          <t xml:space="preserve">0 (left out of the JSON)</t>
         </is>
       </c>
       <c r="F382" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">where a click goes instead of a tab</t>
+          <t xml:space="preserve">its first day (blank: day 1)</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSteps</t>
-        </is>
-      </c>
-      <c r="B383" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hint</t>
+          <t xml:space="preserve">pcSites</t>
         </is>
       </c>
       <c r="C383" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D383" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E383" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'uiStrings'</t>
+          <t xml:space="preserve">one row per item of the list $.pc.sites, in order; a row's name is id, unique</t>
         </is>
       </c>
       <c r="F383" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the UI string of the toast a click shows instead of a jump</t>
+          <t xml:space="preserve">the Internet's sites</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSteps</t>
+          <t xml:space="preserve">pcSites</t>
         </is>
       </c>
       <c r="B384" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C384" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D384" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="F384" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its first day (blank: day 1)</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E384" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -9352,19 +9362,29 @@
           <t xml:space="preserve">pcSites</t>
         </is>
       </c>
+      <c r="B385" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kind</t>
+        </is>
+      </c>
       <c r="C385" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D385" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E385" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.sites, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">one of: News, History, Ancestry, Static</t>
         </is>
       </c>
       <c r="F385" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the Internet's sites</t>
+          <t xml:space="preserve">the page builder that serves it</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9396,7 @@
       </c>
       <c r="B386" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C386" s="1" t="inlineStr">
@@ -9386,12 +9406,7 @@
       </c>
       <c r="D386" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E386" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9418,7 @@
       </c>
       <c r="B387" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">domain</t>
         </is>
       </c>
       <c r="C387" s="1" t="inlineStr">
@@ -9416,14 +9431,9 @@
           <t xml:space="preserve">empty text</t>
         </is>
       </c>
-      <c r="E387" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one of: News, History, Ancestry, Static</t>
-        </is>
-      </c>
       <c r="F387" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the page builder that serves it</t>
+          <t xml:space="preserve">chronet://{domain}: lower-case letters, digits, dots and dashes</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9445,7 @@
       </c>
       <c r="B388" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">glyph</t>
         </is>
       </c>
       <c r="C388" s="1" t="inlineStr">
@@ -9446,6 +9456,11 @@
       <c r="D388" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F388" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the start-page tile's art key</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9472,7 @@
       </c>
       <c r="B389" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">domain</t>
+          <t xml:space="preserve">blurb</t>
         </is>
       </c>
       <c r="C389" s="1" t="inlineStr">
@@ -9468,11 +9483,6 @@
       <c r="D389" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F389" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chronet://{domain}: lower-case letters, digits, dots and dashes</t>
         </is>
       </c>
     </row>
@@ -9484,71 +9494,71 @@
       </c>
       <c r="B390" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">glyph</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C390" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D390" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F390" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the start-page tile's art key</t>
+          <t xml:space="preserve">the first day it is listed</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSites</t>
-        </is>
-      </c>
-      <c r="B391" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blurb</t>
+          <t xml:space="preserve">pcPages</t>
         </is>
       </c>
       <c r="C391" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D391" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E391" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.pages, in order; a row's name is {site}/{path}, unique</t>
+        </is>
+      </c>
+      <c r="F391" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a Static site's authored pages</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcSites</t>
+          <t xml:space="preserve">pcPages</t>
         </is>
       </c>
       <c r="B392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">site</t>
         </is>
       </c>
       <c r="C392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D392" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F392" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the first day it is listed</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E392" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name; names a row of 'pcSites'</t>
         </is>
       </c>
     </row>
@@ -9558,19 +9568,29 @@
           <t xml:space="preserve">pcPages</t>
         </is>
       </c>
+      <c r="B393" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">path</t>
+        </is>
+      </c>
       <c r="C393" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D393" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E393" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.pages, in order; a row's name is {site}/{path}, unique</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
       <c r="F393" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Static site's authored pages</t>
+          <t xml:space="preserve">blank: the site's front page</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9602,7 @@
       </c>
       <c r="B394" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">site</t>
+          <t xml:space="preserve">title</t>
         </is>
       </c>
       <c r="C394" s="1" t="inlineStr">
@@ -9592,66 +9612,51 @@
       </c>
       <c r="D394" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E394" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name; names a row of 'pcSites'</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPages</t>
-        </is>
-      </c>
-      <c r="B395" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">path</t>
+          <t xml:space="preserve">pcPageBlocks</t>
         </is>
       </c>
       <c r="C395" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D395" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E395" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
-        </is>
-      </c>
-      <c r="F395" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">blank: the site's front page</t>
+          <t xml:space="preserve">one row per item of the list $.pc.pages[].blocks, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPages</t>
+          <t xml:space="preserve">pcPageBlocks</t>
         </is>
       </c>
       <c r="B396" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">title</t>
+          <t xml:space="preserve">page</t>
         </is>
       </c>
       <c r="C396" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D396" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E396" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'pcPages' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -9661,14 +9666,24 @@
           <t xml:space="preserve">pcPageBlocks</t>
         </is>
       </c>
+      <c r="B397" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kind</t>
+        </is>
+      </c>
       <c r="C397" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D397" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E397" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.pc.pages[].blocks, in order; the first column names the parent row</t>
+          <t xml:space="preserve">one of: Headline, Heading, Paragraph, Note, Link, Box</t>
         </is>
       </c>
     </row>
@@ -9680,22 +9695,17 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">page</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C398" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D398" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E398" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'pcPages' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9707,7 +9717,7 @@
       </c>
       <c r="B399" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">address</t>
         </is>
       </c>
       <c r="C399" s="1" t="inlineStr">
@@ -9717,12 +9727,12 @@
       </c>
       <c r="D399" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E399" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one of: Headline, Heading, Paragraph, Note, Link, Box</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="F399" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a Link's site name, domain or chronet:// address</t>
         </is>
       </c>
     </row>
@@ -9734,76 +9744,76 @@
       </c>
       <c r="B400" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">lines</t>
         </is>
       </c>
       <c r="C400" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D400" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E400" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F400" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a Box's lines</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPageBlocks</t>
-        </is>
-      </c>
-      <c r="B401" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">address</t>
+          <t xml:space="preserve">pcPeople</t>
         </is>
       </c>
       <c r="C401" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D401" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E401" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.ancestry.people, in order; a row's name is id, unique</t>
         </is>
       </c>
       <c r="F401" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Link's site name, domain or chronet:// address</t>
+          <t xml:space="preserve">the Lineage Archive's people of the past (no traveller's name)</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPageBlocks</t>
+          <t xml:space="preserve">pcPeople</t>
         </is>
       </c>
       <c r="B402" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lines</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C402" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D402" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E402" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F402" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a Box's lines</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -9813,19 +9823,19 @@
           <t xml:space="preserve">pcPeople</t>
         </is>
       </c>
+      <c r="B403" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
       <c r="C403" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E403" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.ancestry.people, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F403" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the Lineage Archive's people of the past (no traveller's name)</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D403" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9837,7 +9847,7 @@
       </c>
       <c r="B404" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">born</t>
         </is>
       </c>
       <c r="C404" s="1" t="inlineStr">
@@ -9847,12 +9857,7 @@
       </c>
       <c r="D404" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E404" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -9864,7 +9869,7 @@
       </c>
       <c r="B405" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">died</t>
         </is>
       </c>
       <c r="C405" s="1" t="inlineStr">
@@ -9886,7 +9891,7 @@
       </c>
       <c r="B406" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">born</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C406" s="1" t="inlineStr">
@@ -9897,6 +9902,11 @@
       <c r="D406" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E406" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -9908,7 +9918,7 @@
       </c>
       <c r="B407" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">died</t>
+          <t xml:space="preserve">note</t>
         </is>
       </c>
       <c r="C407" s="1" t="inlineStr">
@@ -9925,39 +9935,34 @@
     <row r="408">
       <c r="A408" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPeople</t>
-        </is>
-      </c>
-      <c r="B408" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">pcRelations</t>
         </is>
       </c>
       <c r="C408" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D408" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E408" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">one row per item of the list $.pc.ancestry.relations, in order</t>
+        </is>
+      </c>
+      <c r="F408" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one direction per row</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcPeople</t>
+          <t xml:space="preserve">pcRelations</t>
         </is>
       </c>
       <c r="B409" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">note</t>
+          <t xml:space="preserve">person</t>
         </is>
       </c>
       <c r="C409" s="1" t="inlineStr">
@@ -9967,7 +9972,12 @@
       </c>
       <c r="D409" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="F409" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a person's or a premade's id: the card it shows on</t>
         </is>
       </c>
     </row>
@@ -9977,19 +9987,19 @@
           <t xml:space="preserve">pcRelations</t>
         </is>
       </c>
+      <c r="B410" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kind</t>
+        </is>
+      </c>
       <c r="C410" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E410" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.ancestry.relations, in order</t>
-        </is>
-      </c>
-      <c r="F410" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one direction per row</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D410" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10011,7 @@
       </c>
       <c r="B411" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">person</t>
+          <t xml:space="preserve">other</t>
         </is>
       </c>
       <c r="C411" s="1" t="inlineStr">
@@ -10016,41 +10026,41 @@
       </c>
       <c r="F411" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a person's or a premade's id: the card it shows on</t>
+          <t xml:space="preserve">the other card's id</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcRelations</t>
-        </is>
-      </c>
-      <c r="B412" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kind</t>
+          <t xml:space="preserve">pcMail</t>
         </is>
       </c>
       <c r="C412" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D412" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E412" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.mail, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F412" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mail's authored messages</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcRelations</t>
+          <t xml:space="preserve">pcMail</t>
         </is>
       </c>
       <c r="B413" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">other</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C413" s="1" t="inlineStr">
@@ -10063,9 +10073,9 @@
           <t xml:space="preserve">(required)</t>
         </is>
       </c>
-      <c r="F413" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the other card's id</t>
+      <c r="E413" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -10075,19 +10085,24 @@
           <t xml:space="preserve">pcMail</t>
         </is>
       </c>
+      <c r="B414" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fromDay</t>
+        </is>
+      </c>
       <c r="C414" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E414" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.mail, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D414" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F414" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mail's authored messages</t>
+          <t xml:space="preserve">the day it arrives (its date)</t>
         </is>
       </c>
     </row>
@@ -10099,22 +10114,22 @@
       </c>
       <c r="B415" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">untilDay</t>
         </is>
       </c>
       <c r="C415" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D415" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E415" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F415" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the last day it is in the inbox; 0 keeps it for the run</t>
         </is>
       </c>
     </row>
@@ -10126,22 +10141,22 @@
       </c>
       <c r="B416" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">flag</t>
         </is>
       </c>
       <c r="C416" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D416" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F416" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the day it arrives (its date)</t>
+          <t xml:space="preserve">a story flag it waits for (blank: none)</t>
         </is>
       </c>
     </row>
@@ -10153,22 +10168,17 @@
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">untilDay</t>
+          <t xml:space="preserve">from</t>
         </is>
       </c>
       <c r="C417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D417" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F417" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the last day it is in the inbox; 0 keeps it for the run</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10190,7 @@
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flag</t>
+          <t xml:space="preserve">subject</t>
         </is>
       </c>
       <c r="C418" s="1" t="inlineStr">
@@ -10191,55 +10201,55 @@
       <c r="D418" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F418" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a story flag it waits for (blank: none)</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMail</t>
-        </is>
-      </c>
-      <c r="B419" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">from</t>
+          <t xml:space="preserve">pcMailBody</t>
         </is>
       </c>
       <c r="C419" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D419" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Values</t>
+        </is>
+      </c>
+      <c r="E419" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.pc.mail[].body, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F419" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its paragraphs</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMail</t>
+          <t xml:space="preserve">pcMailBody</t>
         </is>
       </c>
       <c r="B420" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">subject</t>
+          <t xml:space="preserve">mail</t>
         </is>
       </c>
       <c r="C420" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D420" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E420" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'pcMail' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -10249,58 +10259,48 @@
           <t xml:space="preserve">pcMailBody</t>
         </is>
       </c>
+      <c r="B421" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
       <c r="C421" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Values</t>
-        </is>
-      </c>
-      <c r="E421" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.pc.mail[].body, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F421" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">its paragraphs</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D421" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMailBody</t>
-        </is>
-      </c>
-      <c r="B422" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mail</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="C422" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
-        </is>
-      </c>
-      <c r="D422" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Single</t>
         </is>
       </c>
       <c r="E422" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'pcMail' this row belongs to</t>
+          <t xml:space="preserve">one row: the object $.ui</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pcMailBody</t>
+          <t xml:space="preserve">ui</t>
         </is>
       </c>
       <c r="B423" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">readingLanguage</t>
         </is>
       </c>
       <c r="C423" s="1" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="D423" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10320,14 +10320,19 @@
           <t xml:space="preserve">ui</t>
         </is>
       </c>
+      <c r="B424" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">glossPercent</t>
+        </is>
+      </c>
       <c r="C424" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E424" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.ui</t>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D424" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -10339,17 +10344,17 @@
       </c>
       <c r="B425" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">readingLanguage</t>
+          <t xml:space="preserve">labelMinScale</t>
         </is>
       </c>
       <c r="C425" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D425" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -10361,12 +10366,12 @@
       </c>
       <c r="B426" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">glossPercent</t>
+          <t xml:space="preserve">contrast.text</t>
         </is>
       </c>
       <c r="C426" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D426" s="1" t="inlineStr">
@@ -10383,7 +10388,7 @@
       </c>
       <c r="B427" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">labelMinScale</t>
+          <t xml:space="preserve">contrast.largeText</t>
         </is>
       </c>
       <c r="C427" s="1" t="inlineStr">
@@ -10405,7 +10410,7 @@
       </c>
       <c r="B428" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.text</t>
+          <t xml:space="preserve">contrast.glyph</t>
         </is>
       </c>
       <c r="C428" s="1" t="inlineStr">
@@ -10427,7 +10432,7 @@
       </c>
       <c r="B429" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.largeText</t>
+          <t xml:space="preserve">contrast.hint</t>
         </is>
       </c>
       <c r="C429" s="1" t="inlineStr">
@@ -10449,7 +10454,7 @@
       </c>
       <c r="B430" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.glyph</t>
+          <t xml:space="preserve">contrast.outline</t>
         </is>
       </c>
       <c r="C430" s="1" t="inlineStr">
@@ -10471,7 +10476,7 @@
       </c>
       <c r="B431" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.hint</t>
+          <t xml:space="preserve">contrast.minTextFillAlpha</t>
         </is>
       </c>
       <c r="C431" s="1" t="inlineStr">
@@ -10493,51 +10498,46 @@
       </c>
       <c r="B432" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">contrast.outline</t>
+          <t xml:space="preserve">latinFallbackFont</t>
         </is>
       </c>
       <c r="C432" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D432" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
-        </is>
-      </c>
-      <c r="B433" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">contrast.minTextFillAlpha</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="C433" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
-        </is>
-      </c>
-      <c r="D433" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E433" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.paletteMap, in order</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ui</t>
+          <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
       <c r="B434" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">latinFallbackFont</t>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C434" s="1" t="inlineStr">
@@ -10557,14 +10557,19 @@
           <t xml:space="preserve">uiPalette</t>
         </is>
       </c>
+      <c r="B435" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fill</t>
+        </is>
+      </c>
       <c r="C435" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E435" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.paletteMap, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D435" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10576,17 +10581,17 @@
       </c>
       <c r="B436" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">role</t>
+          <t xml:space="preserve">alpha</t>
         </is>
       </c>
       <c r="C436" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D436" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -10598,7 +10603,7 @@
       </c>
       <c r="B437" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fill</t>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C437" s="1" t="inlineStr">
@@ -10620,51 +10625,46 @@
       </c>
       <c r="B438" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">alpha</t>
+          <t xml:space="preserve">textClass</t>
         </is>
       </c>
       <c r="C438" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D438" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
-        </is>
-      </c>
-      <c r="B439" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ink</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="C439" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D439" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E439" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.ui.neutral</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiPalette</t>
+          <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
       <c r="B440" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">textClass</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C440" s="1" t="inlineStr">
@@ -10684,14 +10684,19 @@
           <t xml:space="preserve">uiNeutral</t>
         </is>
       </c>
+      <c r="B441" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">displayName</t>
+        </is>
+      </c>
       <c r="C441" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E441" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.ui.neutral</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D441" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10703,7 +10708,7 @@
       </c>
       <c r="B442" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C442" s="1" t="inlineStr">
@@ -10725,17 +10730,17 @@
       </c>
       <c r="B443" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">runtimeFont</t>
         </is>
       </c>
       <c r="C443" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D443" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10752,7 @@
       </c>
       <c r="B444" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">headingAdd</t>
         </is>
       </c>
       <c r="C444" s="1" t="inlineStr">
@@ -10769,17 +10774,17 @@
       </c>
       <c r="B445" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">runtimeFont</t>
+          <t xml:space="preserve">buttonAdd</t>
         </is>
       </c>
       <c r="C445" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D445" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -10791,17 +10796,17 @@
       </c>
       <c r="B446" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">headingAdd</t>
+          <t xml:space="preserve">stripItalic</t>
         </is>
       </c>
       <c r="C446" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D446" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -10813,7 +10818,7 @@
       </c>
       <c r="B447" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">buttonAdd</t>
+          <t xml:space="preserve">wallpaper</t>
         </is>
       </c>
       <c r="C447" s="1" t="inlineStr">
@@ -10830,34 +10835,34 @@
     <row r="448">
       <c r="A448" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
-        </is>
-      </c>
-      <c r="B448" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stripItalic</t>
+          <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
       <c r="C448" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
-        </is>
-      </c>
-      <c r="D448" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E448" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.fonts, in order</t>
+        </is>
+      </c>
+      <c r="F448" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiNeutral</t>
+          <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wallpaper</t>
+          <t xml:space="preserve">file</t>
         </is>
       </c>
       <c r="C449" s="1" t="inlineStr">
@@ -10877,19 +10882,19 @@
           <t xml:space="preserve">neutralFonts</t>
         </is>
       </c>
+      <c r="B450" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">face</t>
+        </is>
+      </c>
       <c r="C450" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E450" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.fonts, in order</t>
-        </is>
-      </c>
-      <c r="F450" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D450" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -10901,7 +10906,7 @@
       </c>
       <c r="B451" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">file</t>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C451" s="1" t="inlineStr">
@@ -10923,51 +10928,46 @@
       </c>
       <c r="B452" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">face</t>
+          <t xml:space="preserve">style</t>
         </is>
       </c>
       <c r="C452" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D452" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
-        </is>
-      </c>
-      <c r="B453" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">family</t>
+          <t xml:space="preserve">neutralSeeds</t>
         </is>
       </c>
       <c r="C453" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D453" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E453" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.seeds, in order</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralFonts</t>
+          <t xml:space="preserve">neutralSeeds</t>
         </is>
       </c>
       <c r="B454" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">style</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C454" s="1" t="inlineStr">
@@ -10987,48 +10987,48 @@
           <t xml:space="preserve">neutralSeeds</t>
         </is>
       </c>
+      <c r="B455" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hex</t>
+        </is>
+      </c>
       <c r="C455" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E455" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.seeds, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D455" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
-        </is>
-      </c>
-      <c r="B456" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
       <c r="C456" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D456" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E456" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.overrides, in order</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralSeeds</t>
+          <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
       <c r="B457" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hex</t>
+          <t xml:space="preserve">role</t>
         </is>
       </c>
       <c r="C457" s="1" t="inlineStr">
@@ -11048,14 +11048,19 @@
           <t xml:space="preserve">neutralOverrides</t>
         </is>
       </c>
+      <c r="B458" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fill</t>
+        </is>
+      </c>
       <c r="C458" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E458" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.overrides, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D458" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11072,7 @@
       </c>
       <c r="B459" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">role</t>
+          <t xml:space="preserve">ink</t>
         </is>
       </c>
       <c r="C459" s="1" t="inlineStr">
@@ -11084,34 +11089,29 @@
     <row r="460">
       <c r="A460" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
-        </is>
-      </c>
-      <c r="B460" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fill</t>
+          <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
       <c r="C460" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D460" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E460" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.neutral.art, in order</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralOverrides</t>
+          <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
       <c r="B461" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ink</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C461" s="1" t="inlineStr">
@@ -11131,48 +11131,48 @@
           <t xml:space="preserve">neutralArt</t>
         </is>
       </c>
+      <c r="B462" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hex</t>
+        </is>
+      </c>
       <c r="C462" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E462" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.neutral.art, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D462" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
-        </is>
-      </c>
-      <c r="B463" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
       <c r="C463" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D463" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E463" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.strings, in order; a row's name is key, unique</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">neutralArt</t>
+          <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
       <c r="B464" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hex</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C464" s="1" t="inlineStr">
@@ -11182,7 +11182,12 @@
       </c>
       <c r="D464" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E464" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -11192,14 +11197,19 @@
           <t xml:space="preserve">uiStrings</t>
         </is>
       </c>
+      <c r="B465" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
       <c r="C465" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E465" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.strings, in order; a row's name is key, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D465" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -11211,7 +11221,7 @@
       </c>
       <c r="B466" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">gloss</t>
         </is>
       </c>
       <c r="C466" s="1" t="inlineStr">
@@ -11221,12 +11231,7 @@
       </c>
       <c r="D466" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E466" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11243,7 @@
       </c>
       <c r="B467" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">tier</t>
         </is>
       </c>
       <c r="C467" s="1" t="inlineStr">
@@ -11255,34 +11260,29 @@
     <row r="468">
       <c r="A468" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
-        </is>
-      </c>
-      <c r="B468" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gloss</t>
+          <t xml:space="preserve">uiLanguages</t>
         </is>
       </c>
       <c r="C468" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D468" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E468" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.ui.languages, in order; a row's name is language, unique</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiStrings</t>
+          <t xml:space="preserve">uiLanguages</t>
         </is>
       </c>
       <c r="B469" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tier</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C469" s="1" t="inlineStr">
@@ -11292,7 +11292,12 @@
       </c>
       <c r="D469" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E469" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -11302,63 +11307,63 @@
           <t xml:space="preserve">uiLanguages</t>
         </is>
       </c>
+      <c r="B470" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rtl</t>
+        </is>
+      </c>
       <c r="C470" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E470" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.ui.languages, in order; a row's name is language, unique</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D470" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
-        </is>
-      </c>
-      <c r="B471" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
       <c r="C471" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D471" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E471" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.ui.languages[].entries, in order; the first column names the parent row</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguages</t>
+          <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
       <c r="B472" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rtl</t>
+          <t xml:space="preserve">language</t>
         </is>
       </c>
       <c r="C472" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D472" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E472" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'uiLanguages' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -11368,14 +11373,24 @@
           <t xml:space="preserve">uiLanguageEntries</t>
         </is>
       </c>
+      <c r="B473" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">key</t>
+        </is>
+      </c>
       <c r="C473" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D473" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E473" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.ui.languages[].entries, in order; the first column names the parent row</t>
+          <t xml:space="preserve">names a row of 'uiStrings'</t>
         </is>
       </c>
     </row>
@@ -11387,71 +11402,56 @@
       </c>
       <c r="B474" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">language</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C474" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D474" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E474" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'uiLanguages' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
-        </is>
-      </c>
-      <c r="B475" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="C475" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D475" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Single</t>
         </is>
       </c>
       <c r="E475" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'uiStrings'</t>
+          <t xml:space="preserve">one row: the object $.translation</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">uiLanguageEntries</t>
+          <t xml:space="preserve">translation</t>
         </is>
       </c>
       <c r="B476" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C476" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D476" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -11461,14 +11461,19 @@
           <t xml:space="preserve">translation</t>
         </is>
       </c>
+      <c r="B477" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">announce</t>
+        </is>
+      </c>
       <c r="C477" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Single</t>
-        </is>
-      </c>
-      <c r="E477" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row: the object $.translation</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D477" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -11480,12 +11485,12 @@
       </c>
       <c r="B478" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">flip.startDelay</t>
         </is>
       </c>
       <c r="C478" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D478" s="1" t="inlineStr">
@@ -11502,17 +11507,17 @@
       </c>
       <c r="B479" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">announce</t>
+          <t xml:space="preserve">flip.letterInterval</t>
         </is>
       </c>
       <c r="C479" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">decimal</t>
         </is>
       </c>
       <c r="D479" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11529,7 @@
       </c>
       <c r="B480" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.startDelay</t>
+          <t xml:space="preserve">flip.letterSeconds</t>
         </is>
       </c>
       <c r="C480" s="1" t="inlineStr">
@@ -11546,12 +11551,12 @@
       </c>
       <c r="B481" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.letterInterval</t>
+          <t xml:space="preserve">flip.scrambleSteps</t>
         </is>
       </c>
       <c r="C481" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D481" s="1" t="inlineStr">
@@ -11568,17 +11573,27 @@
       </c>
       <c r="B482" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.letterSeconds</t>
+          <t xml:space="preserve">keyWords.slots</t>
         </is>
       </c>
       <c r="C482" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">decimal</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D482" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E482" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F482" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">slots whose value stays English in untranslated speech</t>
         </is>
       </c>
     </row>
@@ -11590,17 +11605,27 @@
       </c>
       <c r="B483" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">flip.scrambleSteps</t>
+          <t xml:space="preserve">keyWords.words</t>
         </is>
       </c>
       <c r="C483" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D483" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E483" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F483" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">words that stay English in untranslated speech</t>
         </is>
       </c>
     </row>
@@ -11612,27 +11637,17 @@
       </c>
       <c r="B484" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.slots</t>
+          <t xml:space="preserve">keyWords.digits</t>
         </is>
       </c>
       <c r="C484" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D484" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E484" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F484" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">slots whose value stays English in untranslated speech</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
@@ -11644,61 +11659,46 @@
       </c>
       <c r="B485" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">keyWords.words</t>
+          <t xml:space="preserve">fallbackGlyphs</t>
         </is>
       </c>
       <c r="C485" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D485" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items</t>
-        </is>
-      </c>
-      <c r="E485" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F485" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">words that stay English in untranslated speech</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
-        </is>
-      </c>
-      <c r="B486" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">keyWords.digits</t>
+          <t xml:space="preserve">scripts</t>
         </is>
       </c>
       <c r="C486" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
-        </is>
-      </c>
-      <c r="D486" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E486" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.translation.scripts, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">translation</t>
+          <t xml:space="preserve">scripts</t>
         </is>
       </c>
       <c r="B487" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fallbackGlyphs</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C487" s="1" t="inlineStr">
@@ -11708,7 +11708,12 @@
       </c>
       <c r="D487" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E487" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -11718,63 +11723,68 @@
           <t xml:space="preserve">scripts</t>
         </is>
       </c>
+      <c r="B488" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rightToLeft</t>
+        </is>
+      </c>
       <c r="C488" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E488" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.scripts, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">true/false</t>
+        </is>
+      </c>
+      <c r="D488" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
-        </is>
-      </c>
-      <c r="B489" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
       <c r="C489" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D489" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E489" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.translation.scripts[].fonts, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F489" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">font candidates, tried in order</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scripts</t>
+          <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
       <c r="B490" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">rightToLeft</t>
+          <t xml:space="preserve">script</t>
         </is>
       </c>
       <c r="C490" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
+          <t xml:space="preserve">row name</t>
         </is>
       </c>
       <c r="D490" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E490" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'scripts' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -11784,19 +11794,19 @@
           <t xml:space="preserve">scriptFonts</t>
         </is>
       </c>
+      <c r="B491" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">file</t>
+        </is>
+      </c>
       <c r="C491" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E491" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.scripts[].fonts, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F491" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">font candidates, tried in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D491" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -11808,22 +11818,17 @@
       </c>
       <c r="B492" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">script</t>
+          <t xml:space="preserve">face</t>
         </is>
       </c>
       <c r="C492" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D492" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E492" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'scripts' this row belongs to</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -11835,7 +11840,7 @@
       </c>
       <c r="B493" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">file</t>
+          <t xml:space="preserve">family</t>
         </is>
       </c>
       <c r="C493" s="1" t="inlineStr">
@@ -11857,51 +11862,46 @@
       </c>
       <c r="B494" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">face</t>
+          <t xml:space="preserve">style</t>
         </is>
       </c>
       <c r="C494" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D494" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
-        </is>
-      </c>
-      <c r="B495" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">family</t>
+          <t xml:space="preserve">packs</t>
         </is>
       </c>
       <c r="C495" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D495" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E495" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.translation.packs, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scriptFonts</t>
+          <t xml:space="preserve">packs</t>
         </is>
       </c>
       <c r="B496" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">style</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C496" s="1" t="inlineStr">
@@ -11911,7 +11911,12 @@
       </c>
       <c r="D496" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E496" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -11921,14 +11926,19 @@
           <t xml:space="preserve">packs</t>
         </is>
       </c>
+      <c r="B497" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">displayName</t>
+        </is>
+      </c>
       <c r="C497" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E497" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.packs, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D497" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -11940,66 +11950,61 @@
       </c>
       <c r="B498" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">spokenCost</t>
         </is>
       </c>
       <c r="C498" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D498" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E498" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
-        </is>
-      </c>
-      <c r="B499" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">tongues</t>
         </is>
       </c>
       <c r="C499" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D499" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E499" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">packs</t>
+          <t xml:space="preserve">tongues</t>
         </is>
       </c>
       <c r="B500" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">spokenCost</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C500" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D500" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E500" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -12009,14 +12014,19 @@
           <t xml:space="preserve">tongues</t>
         </is>
       </c>
+      <c r="B501" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">displayName</t>
+        </is>
+      </c>
       <c r="C501" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E501" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D501" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12038,7 @@
       </c>
       <c r="B502" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">script</t>
         </is>
       </c>
       <c r="C502" s="1" t="inlineStr">
@@ -12038,12 +12048,12 @@
       </c>
       <c r="D502" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="E502" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">names a row of 'scripts'</t>
         </is>
       </c>
     </row>
@@ -12055,7 +12065,7 @@
       </c>
       <c r="B503" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">pack</t>
         </is>
       </c>
       <c r="C503" s="1" t="inlineStr">
@@ -12066,6 +12076,11 @@
       <c r="D503" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E503" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'packs'</t>
         </is>
       </c>
     </row>
@@ -12077,7 +12092,7 @@
       </c>
       <c r="B504" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">script</t>
+          <t xml:space="preserve">glyphs</t>
         </is>
       </c>
       <c r="C504" s="1" t="inlineStr">
@@ -12086,60 +12101,6 @@
         </is>
       </c>
       <c r="D504" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E504" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'scripts'</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tongues</t>
-        </is>
-      </c>
-      <c r="B505" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pack</t>
-        </is>
-      </c>
-      <c r="C505" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D505" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E505" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'packs'</t>
-        </is>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tongues</t>
-        </is>
-      </c>
-      <c r="B506" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">glyphs</t>
-        </is>
-      </c>
-      <c r="C506" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D506" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
         </is>
@@ -16292,14 +16253,13 @@
     <col min="8" max="8" width="18" style="1" customWidth="1"/>
     <col min="9" max="9" width="26" style="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18" style="1" customWidth="1"/>
-    <col min="12" max="12" width="22" style="1" customWidth="1"/>
-    <col min="13" max="13" width="11" style="1" customWidth="1"/>
-    <col min="14" max="14" width="16" style="1" customWidth="1"/>
-    <col min="15" max="15" width="24" style="1" customWidth="1"/>
+    <col min="11" max="11" width="22" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11" style="1" customWidth="1"/>
+    <col min="13" max="13" width="16" style="1" customWidth="1"/>
+    <col min="14" max="14" width="24" style="1" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="14" customWidth="1"/>
-    <col min="18" max="18" width="11" style="1" customWidth="1"/>
+    <col min="17" max="17" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16360,35 +16320,30 @@
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">tripAskLabel</t>
+          <t xml:space="preserve">backLabel</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">backLabel</t>
+          <t xml:space="preserve">smallTalkLabel</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">smallTalkLabel</t>
+          <t xml:space="preserve">smallTalkPrompt</t>
         </is>
       </c>
       <c r="O1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">smallTalkPrompt</t>
+          <t xml:space="preserve">menuCapacity</t>
         </is>
       </c>
       <c r="P1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">menuCapacity</t>
+          <t xml:space="preserve">maxLineChars</t>
         </is>
       </c>
       <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">maxLineChars</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">lookLabel</t>
         </is>
@@ -16447,36 +16402,31 @@
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ask about home &gt;</t>
+          <t xml:space="preserve">Ask about the trip &gt;</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ask about the trip &gt;</t>
+          <t xml:space="preserve">&lt; Back</t>
         </is>
       </c>
       <c r="M2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt; Back</t>
+          <t xml:space="preserve">Small talk</t>
         </is>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Small talk</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
           <t xml:space="preserve">How is life back home?</t>
         </is>
       </c>
+      <c r="O2">
+        <v>8</v>
+      </c>
       <c r="P2">
-        <v>8</v>
-      </c>
-      <c r="Q2">
         <v>100</v>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Look &gt;</t>
         </is>
@@ -16736,12 +16686,11 @@
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10" style="1" customWidth="1"/>
+    <col min="4" max="4" width="42" style="1" customWidth="1"/>
     <col min="5" max="5" width="37" style="1" customWidth="1"/>
-    <col min="6" max="6" width="27" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="8" max="8" width="10" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="60" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16757,30 +16706,25 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kinds</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">answer</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fromDay</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">announce</t>
         </is>
@@ -16799,26 +16743,26 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Displaced</t>
+          <t xml:space="preserve">Currency</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Currency</t>
+          <t xml:space="preserve">What will you pay with in {place}?</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">What money do you pay with at home?</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">We pay in {value}.</t>
-        </is>
-      </c>
-      <c r="G2">
-        <v>1</v>
+          <t xml:space="preserve">I've changed my money into {value}.</t>
+        </is>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUREAU NOTICE: from today, desk officers ask every traveller what they will pay with. Check answers against the Currency Ledger: nothing from 2150 leaves 2150.</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -16834,26 +16778,26 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Displaced</t>
+          <t xml:space="preserve">Language</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Language</t>
+          <t xml:space="preserve">What language will you speak in {place}?</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">What language do you speak at home?</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">At home we speak {value}.</t>
-        </is>
-      </c>
-      <c r="G3">
-        <v>1</v>
+          <t xml:space="preserve">I've been practising my {value}.</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BUREAU NOTICE: desk officers may now ask every traveller what language they will speak. Check answers against Tongues &amp; Scripts.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -16920,8 +16864,8 @@
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" customWidth="1"/>
-    <col min="3" max="3" width="33" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16937,7 +16881,7 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">kinds</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -16952,19 +16896,53 @@
           <t xml:space="preserve">q_currency</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">We pay in {value}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q_currency</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">ancient</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">What do you trade with at home?</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">We trade with {value}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">q_language</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displaced</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">At home we speak {value}.</t>
         </is>
       </c>
     </row>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -18473,6 +18473,9 @@
           <t xml:space="preserve">FirstUncheckedField</t>
         </is>
       </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -18558,6 +18561,9 @@
         <is>
           <t xml:space="preserve">CostumeClaimed</t>
         </is>
+      </c>
+      <c r="K9">
+        <v>2</v>
       </c>
     </row>
     <row r="10">

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -15975,10 +15975,10 @@
         <v>0.0</v>
       </c>
       <c r="K3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="L3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -14101,17 +14101,32 @@
     <row r="574">
       <c r="A574" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tongues</t>
+          <t xml:space="preserve">packs</t>
+        </is>
+      </c>
+      <c r="B574" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requires</t>
         </is>
       </c>
       <c r="C574" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text list</t>
+        </is>
+      </c>
+      <c r="D574" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
         </is>
       </c>
       <c r="E574" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F574" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the upgrade ids the translator's Orders node needs owned first (interview_protocols); blank: none</t>
         </is>
       </c>
     </row>
@@ -14121,24 +14136,14 @@
           <t xml:space="preserve">tongues</t>
         </is>
       </c>
-      <c r="B575" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
-        </is>
-      </c>
       <c r="C575" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D575" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E575" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.translation.tongues, in order; a row's name is id, unique</t>
         </is>
       </c>
     </row>
@@ -14150,7 +14155,7 @@
       </c>
       <c r="B576" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">displayName</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C576" s="1" t="inlineStr">
@@ -14160,7 +14165,12 @@
       </c>
       <c r="D576" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E576" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -14172,7 +14182,7 @@
       </c>
       <c r="B577" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">script</t>
+          <t xml:space="preserve">displayName</t>
         </is>
       </c>
       <c r="C577" s="1" t="inlineStr">
@@ -14183,11 +14193,6 @@
       <c r="D577" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E577" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'scripts'</t>
         </is>
       </c>
     </row>
@@ -14199,7 +14204,7 @@
       </c>
       <c r="B578" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pack</t>
+          <t xml:space="preserve">script</t>
         </is>
       </c>
       <c r="C578" s="1" t="inlineStr">
@@ -14214,7 +14219,7 @@
       </c>
       <c r="E578" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'packs'</t>
+          <t xml:space="preserve">names a row of 'scripts'</t>
         </is>
       </c>
     </row>
@@ -14226,15 +14231,42 @@
       </c>
       <c r="B579" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">pack</t>
+        </is>
+      </c>
+      <c r="C579" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D579" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E579" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'packs'</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tongues</t>
+        </is>
+      </c>
+      <c r="B580" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">glyphs</t>
         </is>
       </c>
-      <c r="C579" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D579" s="1" t="inlineStr">
+      <c r="C580" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D580" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
         </is>
@@ -23347,12 +23379,12 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.investigation</t>
+          <t xml:space="preserve">icon.orders</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">التحقيق</t>
+          <t xml:space="preserve">الطلبات</t>
         </is>
       </c>
     </row>
@@ -23364,12 +23396,12 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.mail</t>
+          <t xml:space="preserve">icon.investigation</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">البريد</t>
+          <t xml:space="preserve">التحقيق</t>
         </is>
       </c>
     </row>
@@ -23381,12 +23413,12 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.account</t>
+          <t xml:space="preserve">icon.mail</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">حساب المواطن</t>
+          <t xml:space="preserve">البريد</t>
         </is>
       </c>
     </row>
@@ -23398,12 +23430,12 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.settings</t>
+          <t xml:space="preserve">icon.account</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">الإعدادات</t>
+          <t xml:space="preserve">حساب المواطن</t>
         </is>
       </c>
     </row>
@@ -23415,12 +23447,12 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tray.day</t>
+          <t xml:space="preserve">icon.settings</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">اليوم {0}</t>
+          <t xml:space="preserve">الإعدادات</t>
         </is>
       </c>
     </row>
@@ -23432,12 +23464,12 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tray.stability</t>
+          <t xml:space="preserve">tray.day</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">الاستقرار: {0}</t>
+          <t xml:space="preserve">اليوم {0}</t>
         </is>
       </c>
     </row>
@@ -23449,12 +23481,12 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">taskbar.desk</t>
+          <t xml:space="preserve">tray.stability</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">العودة إلى المكتب</t>
+          <t xml:space="preserve">الاستقرار: {0}</t>
         </is>
       </c>
     </row>
@@ -23466,12 +23498,12 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">briefing.title</t>
+          <t xml:space="preserve">taskbar.desk</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">اليوم {0} — الإحاطة الصباحية</t>
+          <t xml:space="preserve">العودة إلى المكتب</t>
         </is>
       </c>
     </row>
@@ -23483,12 +23515,12 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">results.title</t>
+          <t xml:space="preserve">briefing.title</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">اليوم {0} — تقرير المناوبة</t>
+          <t xml:space="preserve">اليوم {0} — الإحاطة الصباحية</t>
         </is>
       </c>
     </row>
@@ -23500,29 +23532,29 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">briefing.newsHeader</t>
+          <t xml:space="preserve">results.title</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">— أخبار الخط الزمني —</t>
+          <t xml:space="preserve">اليوم {0} — تقرير المناوبة</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">el</t>
+          <t xml:space="preserve">ar</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">accept</t>
+          <t xml:space="preserve">briefing.newsHeader</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΕΓΚΡΙΣΗ</t>
+          <t xml:space="preserve">— أخبار الخط الزمني —</t>
         </is>
       </c>
     </row>
@@ -23534,12 +23566,12 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">deny</t>
+          <t xml:space="preserve">accept</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΑΠΟΡΡΙΨΗ</t>
+          <t xml:space="preserve">ΕΓΚΡΙΣΗ</t>
         </is>
       </c>
     </row>
@@ -23551,12 +23583,12 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">taskbar.start</t>
+          <t xml:space="preserve">deny</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">έναρξη</t>
+          <t xml:space="preserve">ΑΠΟΡΡΙΨΗ</t>
         </is>
       </c>
     </row>
@@ -23568,12 +23600,12 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">startmenu.settings</t>
+          <t xml:space="preserve">taskbar.start</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ρυθμίσεις</t>
+          <t xml:space="preserve">έναρξη</t>
         </is>
       </c>
     </row>
@@ -23585,12 +23617,12 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">startmenu.screenOff</t>
+          <t xml:space="preserve">startmenu.settings</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Σβήσιμο οθόνης</t>
+          <t xml:space="preserve">Ρυθμίσεις</t>
         </is>
       </c>
     </row>
@@ -23602,12 +23634,12 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">startmenu.quit</t>
+          <t xml:space="preserve">startmenu.screenOff</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Έξοδος από το παιχνίδι</t>
+          <t xml:space="preserve">Σβήσιμο οθόνης</t>
         </is>
       </c>
     </row>
@@ -23619,12 +23651,12 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">briefing.masthead</t>
+          <t xml:space="preserve">startmenu.quit</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Η ΧΡΟΝΙΚΗ ΕΦΗΜΕΡΙΔΑ</t>
+          <t xml:space="preserve">Έξοδος από το παιχνίδι</t>
         </is>
       </c>
     </row>
@@ -23636,12 +23668,12 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">briefing.start</t>
+          <t xml:space="preserve">briefing.masthead</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΕΝΑΡΞΗ ΒΑΡΔΙΑΣ</t>
+          <t xml:space="preserve">Η ΧΡΟΝΙΚΗ ΕΦΗΜΕΡΙΔΑ</t>
         </is>
       </c>
     </row>
@@ -23653,12 +23685,12 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">results.masthead</t>
+          <t xml:space="preserve">briefing.start</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΗΜΕΡΟΛΟΓΙΟ ΒΑΡΔΙΑΣ — ΑΠΟΓΕΥΜΑΤΙΝΗ ΕΚΔΟΣΗ</t>
+          <t xml:space="preserve">ΕΝΑΡΞΗ ΒΑΡΔΙΑΣ</t>
         </is>
       </c>
     </row>
@@ -23670,12 +23702,12 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">results.goHome</t>
+          <t xml:space="preserve">results.masthead</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΣΠΙΤΙ</t>
+          <t xml:space="preserve">ΗΜΕΡΟΛΟΓΙΟ ΒΑΡΔΙΑΣ — ΑΠΟΓΕΥΜΑΤΙΝΗ ΕΚΔΟΣΗ</t>
         </is>
       </c>
     </row>
@@ -23687,12 +23719,12 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">records.search</t>
+          <t xml:space="preserve">results.goHome</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΑΝΑΖΗΤΗΣΗ</t>
+          <t xml:space="preserve">ΣΠΙΤΙ</t>
         </is>
       </c>
     </row>
@@ -23704,12 +23736,12 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">compare.match</t>
+          <t xml:space="preserve">records.search</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΤΑΙΡΙΑΖΕΙ</t>
+          <t xml:space="preserve">ΑΝΑΖΗΤΗΣΗ</t>
         </is>
       </c>
     </row>
@@ -23721,12 +23753,12 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">compare.mismatch</t>
+          <t xml:space="preserve">compare.match</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΔΕΝ ΤΑΙΡΙΑΖΕΙ</t>
+          <t xml:space="preserve">ΤΑΙΡΙΑΖΕΙ</t>
         </is>
       </c>
     </row>
@@ -23738,12 +23770,12 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">citation.title</t>
+          <t xml:space="preserve">compare.mismatch</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΕΙΔΟΠΟΙΗΣΗ ΧΡΟΝΙΚΗΣ ΑΠΟΚΛΙΣΗΣ</t>
+          <t xml:space="preserve">ΔΕΝ ΤΑΙΡΙΑΖΕΙ</t>
         </is>
       </c>
     </row>
@@ -23755,12 +23787,12 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">citation.acknowledge</t>
+          <t xml:space="preserve">citation.title</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ελήφθη</t>
+          <t xml:space="preserve">ΕΙΔΟΠΟΙΗΣΗ ΧΡΟΝΙΚΗΣ ΑΠΟΚΛΙΣΗΣ</t>
         </is>
       </c>
     </row>
@@ -23772,12 +23804,12 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">window.settings</t>
+          <t xml:space="preserve">citation.acknowledge</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ρυθμίσεις</t>
+          <t xml:space="preserve">Ελήφθη</t>
         </is>
       </c>
     </row>
@@ -23789,12 +23821,12 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.internet</t>
+          <t xml:space="preserve">window.settings</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Διαδίκτυο</t>
+          <t xml:space="preserve">Ρυθμίσεις</t>
         </is>
       </c>
     </row>
@@ -23806,12 +23838,12 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.notes</t>
+          <t xml:space="preserve">icon.internet</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Σημειώσεις</t>
+          <t xml:space="preserve">Διαδίκτυο</t>
         </is>
       </c>
     </row>
@@ -23823,12 +23855,12 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.investigation</t>
+          <t xml:space="preserve">icon.notes</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Έρευνα</t>
+          <t xml:space="preserve">Σημειώσεις</t>
         </is>
       </c>
     </row>
@@ -23840,12 +23872,12 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.mail</t>
+          <t xml:space="preserve">icon.orders</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Αλληλογραφία</t>
+          <t xml:space="preserve">Παραγγελίες</t>
         </is>
       </c>
     </row>
@@ -23857,12 +23889,12 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.account</t>
+          <t xml:space="preserve">icon.investigation</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Λογαριασμός πολίτη</t>
+          <t xml:space="preserve">Έρευνα</t>
         </is>
       </c>
     </row>
@@ -23874,12 +23906,12 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">icon.settings</t>
+          <t xml:space="preserve">icon.mail</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ρυθμίσεις</t>
+          <t xml:space="preserve">Αλληλογραφία</t>
         </is>
       </c>
     </row>
@@ -23891,12 +23923,12 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tray.day</t>
+          <t xml:space="preserve">icon.account</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ημέρα {0}</t>
+          <t xml:space="preserve">Λογαριασμός πολίτη</t>
         </is>
       </c>
     </row>
@@ -23908,12 +23940,12 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">tray.stability</t>
+          <t xml:space="preserve">icon.settings</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Σταθερότητα: {0}</t>
+          <t xml:space="preserve">Ρυθμίσεις</t>
         </is>
       </c>
     </row>
@@ -23925,12 +23957,12 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">taskbar.desk</t>
+          <t xml:space="preserve">tray.day</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt; Γραφείο</t>
+          <t xml:space="preserve">Ημέρα {0}</t>
         </is>
       </c>
     </row>
@@ -23942,12 +23974,12 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">briefing.title</t>
+          <t xml:space="preserve">tray.stability</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ημέρα {0} — Πρωινή ενημέρωση</t>
+          <t xml:space="preserve">Σταθερότητα: {0}</t>
         </is>
       </c>
     </row>
@@ -23959,12 +23991,12 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">results.title</t>
+          <t xml:space="preserve">taskbar.desk</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ημέρα {0} — Αναφορά βάρδιας</t>
+          <t xml:space="preserve">&lt; Γραφείο</t>
         </is>
       </c>
     </row>
@@ -23976,10 +24008,44 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">briefing.title</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ημέρα {0} — Πρωινή ενημέρωση</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">results.title</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ημέρα {0} — Αναφορά βάρδιας</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">el</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">briefing.newsHeader</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">— ΕΙΔΗΣΕΙΣ ΧΡΟΝΟΓΡΑΜΜΗΣ —</t>
         </is>
@@ -24063,7 +24129,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Budget cuts close the interpreter pool. From tomorrow, the displaced reach the desk speaking their own tongues, untranslated but for their key words; Speech translators are sold at Home tonight. Papers are still filled in English.</t>
+          <t xml:space="preserve">Budget cuts close the interpreter pool. From the day after tomorrow, the displaced reach the desk speaking their own tongues, untranslated but for their key words. Order Interview Protocols today and a Speech translator tomorrow in Orders: each arrives the morning after it is ordered. Papers are still filled in English.</t>
         </is>
       </c>
       <c r="C2">
@@ -24194,6 +24260,7 @@
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="21" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24212,6 +24279,11 @@
           <t xml:space="preserve">spokenCost</t>
         </is>
       </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requires</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -24227,6 +24299,11 @@
       <c r="C2">
         <v>80</v>
       </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">interview_protocols</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -24241,6 +24318,11 @@
       </c>
       <c r="C3">
         <v>80</v>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">interview_protocols</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -103,6 +103,9 @@
     <sheet name="scriptFonts" sheetId="99" r:id="rId99"/>
     <sheet name="packs" sheetId="100" r:id="rId100"/>
     <sheet name="tongues" sheetId="101" r:id="rId101"/>
+    <sheet name="home" sheetId="102" r:id="rId102"/>
+    <sheet name="homeRadio" sheetId="103" r:id="rId103"/>
+    <sheet name="homeUpgrades" sheetId="104" r:id="rId104"/>
   </sheets>
 </workbook>
 </file>
@@ -15138,6 +15141,509 @@
         </is>
       </c>
     </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">home</t>
+        </is>
+      </c>
+      <c r="C612" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E612" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.home</t>
+        </is>
+      </c>
+      <c r="F612" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Home's house upgrades and the radio</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">home</t>
+        </is>
+      </c>
+      <c r="B613" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">radioUpgrade</t>
+        </is>
+      </c>
+      <c r="C613" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D613" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F613" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the house upgrade whose ownership plays a radio line on the sleep panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeRadio</t>
+        </is>
+      </c>
+      <c r="C614" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Values</t>
+        </is>
+      </c>
+      <c r="E614" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.home.radio, in order</t>
+        </is>
+      </c>
+      <c r="F614" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the radio's lines: one a night, in order by the day</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeRadio</t>
+        </is>
+      </c>
+      <c r="B615" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="C615" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D615" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="C616" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E616" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.home.upgrades, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F616" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the House tree: every effect never takes a knob below 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B617" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C617" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D617" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E617" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
+        </is>
+      </c>
+      <c r="F617" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the upgrade's id (saved as owned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B618" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="C618" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D618" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B619" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">category</t>
+        </is>
+      </c>
+      <c r="C619" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D619" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E619" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: Food, Housing, Security, Health, Comfort</t>
+        </is>
+      </c>
+      <c r="F619" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its column in the House panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B620" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cost</t>
+        </is>
+      </c>
+      <c r="C620" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D620" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F620" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the one-off price in cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B621" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">upkeep</t>
+        </is>
+      </c>
+      <c r="C621" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D621" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F621" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cr a night the household pays once it is owned (0: none)</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B622" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requires</t>
+        </is>
+      </c>
+      <c r="C622" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text list</t>
+        </is>
+      </c>
+      <c r="D622" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E622" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F622" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the house upgrades it needs owned first (ids of this sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B623" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">householdExpense</t>
+        </is>
+      </c>
+      <c r="C623" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D623" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F623" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cr a night on rent and utilities (negative saves)</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B624" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sicknessChance</t>
+        </is>
+      </c>
+      <c r="C624" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D624" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F624" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added to each member's nightly chance to worsen (-0.05 = 5 points less)</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B625" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">careCost</t>
+        </is>
+      </c>
+      <c r="C625" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D625" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F625" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cr on each treatment (negative cheaper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B626" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">medicalDrain</t>
+        </is>
+      </c>
+      <c r="C626" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D626" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F626" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cr on each condition point's nightly drain (negative lowers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B627" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mood</t>
+        </is>
+      </c>
+      <c r="C627" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D627" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F627" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the household's mood points (a sick member's nightly recovery chance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B628" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">breakInChance</t>
+        </is>
+      </c>
+      <c r="C628" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D628" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F628" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added to the nightly break-in chance (-0.03 = 3 points less)</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B629" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">breakInShare</t>
+        </is>
+      </c>
+      <c r="C629" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D629" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F629" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added to the share of the wallet a break-in takes</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B630" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blurb</t>
+        </is>
+      </c>
+      <c r="C630" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D630" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F630" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the House panel's line under its name</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -15329,6 +15835,262 @@
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">𓄿𓃀𓍿𓂧𓇋𓆑𓎼𓉔𓇌𓆓𓎡𓃭𓅓𓈖𓂝𓊪𓈎𓂋𓋴𓏏𓅱𓎛𓏲𓐍𓏭𓊃</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet102.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">radioUpgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">house_radio</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet103.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="60" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tonight's weather: overcast, with a chance of interest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Directorate reminds listeners that sleep is a privilege of the solvent.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet104.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="17" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="8" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="60" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">category</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cost</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">upkeep</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requires</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">householdExpense</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sicknessChance</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">careCost</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">medicalDrain</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mood</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">breakInChance</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">breakInShare</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blurb</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">house_rations_b</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ration Card, Tier B</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Food</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>40</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>-0.02</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tier B paste comes in two colours. The kid prefers the green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">house_veg_box</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vegetable Box</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Food</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>90</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">house_rations_b</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>-0.04</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Real vegetables, by drone, once a week. The carrots are small, but they are carrots.</t>
         </is>
       </c>
     </row>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -15904,7 +15904,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="1" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
@@ -15999,7 +15999,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ration Card, Tier B</t>
+          <t xml:space="preserve">Tier B Rations</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -105,6 +105,9 @@
     <sheet name="scriptFonts" sheetId="101" r:id="rId101"/>
     <sheet name="packs" sheetId="102" r:id="rId102"/>
     <sheet name="tongues" sheetId="103" r:id="rId103"/>
+    <sheet name="home" sheetId="104" r:id="rId104"/>
+    <sheet name="homeRadio" sheetId="105" r:id="rId105"/>
+    <sheet name="homeUpgrades" sheetId="106" r:id="rId106"/>
   </sheets>
 </workbook>
 </file>
@@ -15437,6 +15440,509 @@
         </is>
       </c>
     </row>
+    <row r="623">
+      <c r="A623" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">home</t>
+        </is>
+      </c>
+      <c r="C623" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E623" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.home</t>
+        </is>
+      </c>
+      <c r="F623" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Home's house upgrades and the radio</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">home</t>
+        </is>
+      </c>
+      <c r="B624" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">radioUpgrade</t>
+        </is>
+      </c>
+      <c r="C624" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D624" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F624" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the house upgrade whose ownership plays a radio line on the sleep panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeRadio</t>
+        </is>
+      </c>
+      <c r="C625" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Values</t>
+        </is>
+      </c>
+      <c r="E625" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.home.radio, in order</t>
+        </is>
+      </c>
+      <c r="F625" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the radio's lines: one a night, in order by the day</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeRadio</t>
+        </is>
+      </c>
+      <c r="B626" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="C626" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D626" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="C627" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E627" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.home.upgrades, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F627" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the House tree: every effect never takes a knob below 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B628" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C628" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D628" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E628" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
+        </is>
+      </c>
+      <c r="F628" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the upgrade's id (saved as owned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B629" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="C629" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D629" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B630" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">category</t>
+        </is>
+      </c>
+      <c r="C630" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D630" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E630" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: Food, Housing, Security, Health, Comfort</t>
+        </is>
+      </c>
+      <c r="F630" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">its column in the House panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B631" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cost</t>
+        </is>
+      </c>
+      <c r="C631" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D631" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F631" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the one-off price in cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B632" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">upkeep</t>
+        </is>
+      </c>
+      <c r="C632" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D632" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F632" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cr a night the household pays once it is owned (0: none)</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B633" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requires</t>
+        </is>
+      </c>
+      <c r="C633" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text list</t>
+        </is>
+      </c>
+      <c r="D633" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">no items</t>
+        </is>
+      </c>
+      <c r="E633" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
+        </is>
+      </c>
+      <c r="F633" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the house upgrades it needs owned first (ids of this sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B634" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">householdExpense</t>
+        </is>
+      </c>
+      <c r="C634" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D634" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F634" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cr a night on rent and utilities (negative saves)</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B635" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sicknessChance</t>
+        </is>
+      </c>
+      <c r="C635" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D635" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F635" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added to each member's nightly chance to worsen (-0.05 = 5 points less)</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B636" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">careCost</t>
+        </is>
+      </c>
+      <c r="C636" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D636" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F636" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cr on each treatment (negative cheaper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B637" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">medicalDrain</t>
+        </is>
+      </c>
+      <c r="C637" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D637" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F637" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cr on each condition point's nightly drain (negative lowers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B638" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mood</t>
+        </is>
+      </c>
+      <c r="C638" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D638" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F638" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the household's mood points (a sick member's nightly recovery chance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B639" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">breakInChance</t>
+        </is>
+      </c>
+      <c r="C639" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D639" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F639" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added to the nightly break-in chance (-0.03 = 3 points less)</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B640" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">breakInShare</t>
+        </is>
+      </c>
+      <c r="C640" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D640" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F640" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added to the share of the wallet a break-in takes</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeUpgrades</t>
+        </is>
+      </c>
+      <c r="B641" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blurb</t>
+        </is>
+      </c>
+      <c r="C641" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D641" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F641" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the House panel's line under its name</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -15714,6 +16220,262 @@
       <c r="E3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">𓄿𓃀𓍿𓂧𓇋𓆑𓎼𓉔𓇌𓆓𓎡𓃭𓅓𓈖𓂝𓊪𓈎𓂋𓋴𓏏𓅱𓎛𓏲𓐍𓏭𓊃</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet104.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">radioUpgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">house_radio</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet105.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="60" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tonight's weather: overcast, with a chance of interest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Directorate reminds listeners that sleep is a privilege of the solvent.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet106.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="17" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="8" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="60" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">category</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cost</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">upkeep</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">requires</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">householdExpense</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sicknessChance</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">careCost</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">medicalDrain</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mood</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">breakInChance</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">breakInShare</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blurb</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">house_rations_b</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tier B Rations</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Food</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>40</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>-0.02</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tier B paste comes in two colours. The kid prefers the green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">house_veg_box</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vegetable Box</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Food</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>90</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">house_rations_b</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>-0.04</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Real vegetables, by drone, once a week. The carrots are small, but they are carrots.</t>
         </is>
       </c>
     </row>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -108,6 +108,7 @@
     <sheet name="home" sheetId="104" r:id="rId104"/>
     <sheet name="homeRadio" sheetId="105" r:id="rId105"/>
     <sheet name="homeUpgrades" sheetId="106" r:id="rId106"/>
+    <sheet name="worldFactors" sheetId="107" r:id="rId107"/>
   </sheets>
 </workbook>
 </file>
@@ -15943,6 +15944,146 @@
         </is>
       </c>
     </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldFactors</t>
+        </is>
+      </c>
+      <c r="C642" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E642" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.world.factors, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F642" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the world's outcomes listed under END OF DEMO, in this order</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldFactors</t>
+        </is>
+      </c>
+      <c r="B643" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C643" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D643" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E643" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
+        </is>
+      </c>
+      <c r="F643" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the factor's id (the endings spec's outcomes name their factor by it)</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldFactors</t>
+        </is>
+      </c>
+      <c r="B644" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question</t>
+        </is>
+      </c>
+      <c r="C644" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D644" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F644" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the question the end of the demo answers about 2150</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldFactors</t>
+        </is>
+      </c>
+      <c r="B645" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">answer</t>
+        </is>
+      </c>
+      <c r="C645" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D645" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E645" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: AsFound, Leader</t>
+        </is>
+      </c>
+      <c r="F645" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AsFound: the foundAs text; Leader: the leading nation's name (foundAs while none leads)</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldFactors</t>
+        </is>
+      </c>
+      <c r="B646" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">foundAs</t>
+        </is>
+      </c>
+      <c r="C646" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D646" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F646" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the answer as the run found 2150</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -16476,6 +16617,86 @@
       <c r="N3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Real vegetables, by drone, once a week. The carrots are small, but they are carrots.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet107.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">answer</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">foundAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">government</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Who runs 2150?</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AsFound</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Directorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What does 2150 run on?</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AsFound</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Credit Age</t>
         </is>
       </c>
     </row>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -18999,7 +18999,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -18999,7 +18999,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -19014,7 +19014,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">monarchy</t>
+          <t xml:space="preserve">theocracy</t>
         </is>
       </c>
     </row>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -17932,7 +17932,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">#2157DB</t>
+          <t xml:space="preserve">#33507A</t>
         </is>
       </c>
     </row>
@@ -18244,7 +18244,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ابدأ</t>
+          <t xml:space="preserve">القائمة</t>
         </is>
       </c>
     </row>
@@ -18754,7 +18754,7 @@
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">έναρξη</t>
+          <t xml:space="preserve">Μενού</t>
         </is>
       </c>
     </row>
@@ -18890,7 +18890,7 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ΑΝΑΖΗΤΗΣΗ</t>
+          <t xml:space="preserve">Αναζήτηση</t>
         </is>
       </c>
     </row>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt; Γραφείο</t>
+          <t xml:space="preserve">Πίσω στο γραφείο</t>
         </is>
       </c>
     </row>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -29616,7 +29616,7 @@
     <col min="5" max="5" width="60" style="1" customWidth="1"/>
     <col min="6" max="6" width="60" style="1" customWidth="1"/>
     <col min="7" max="7" width="60" style="1" customWidth="1"/>
-    <col min="8" max="8" width="55" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29689,17 +29689,17 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">HISTORY: {name}, stamped through Desk 3 on day {day}, brought {value} to {place}.</t>
+          <t xml:space="preserve">HISTORY: {name}, stamped day {day}, brought {value} to {place}.</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PANIC in {place}: {name}, sent through Desk 3 on day {day}, was seen in "{value}" and the street fled.</t>
+          <t xml:space="preserve">PANIC in {place}: {name}, stamped day {day}, wore "{value}". The street fled.</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">It began at Desk 3 with {name}, stamped on day {day}.</t>
+          <t xml:space="preserve">Traced to Desk 3: {name}, day {day}.</t>
         </is>
       </c>
     </row>
@@ -30104,12 +30104,12 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Second time lucky: {name}, turned away at Desk 3 on day {day}, came back on day {back} and was stamped through.</t>
+          <t xml:space="preserve">Second time lucky: {name}, turned away on day {day}, stamped through on day {back}.</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">{name} tried Desk 3 again on day {back}, after a refusal on day {day}. Turned away twice.</t>
+          <t xml:space="preserve">{name}, turned away on day {day}, tried again on day {back}. Turned away twice.</t>
         </is>
       </c>
     </row>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -14261,12 +14261,12 @@
       </c>
       <c r="E558" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: News, Desk, Return</t>
+          <t xml:space="preserve">one of: News, Desk, Return, Front</t>
         </is>
       </c>
       <c r="F558" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">where the line goes: the paper's news (blank), the paper's desk section, or nowhere until the character returns (its fired flag, trig:history_{id}:fired)</t>
+          <t xml:space="preserve">where the line goes: the paper's news (blank), the paper's desk section, nowhere until the character returns (its fired flag, trig:history_{id}:fired), or the front page, leading the news (a famous traveller's homecoming)</t>
         </is>
       </c>
     </row>
@@ -19261,10 +19261,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8" style="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="1" customWidth="1"/>
     <col min="6" max="6" width="60" style="1" customWidth="1"/>
   </cols>
@@ -19326,22 +19326,17 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hatshepsut</t>
+          <t xml:space="preserve">senenmut</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hatshepsut</t>
+          <t xml:space="preserve">Senenmut</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">c. 1507 BCE</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1458 BCE</t>
+          <t xml:space="preserve">c. 1505 BCE</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
@@ -19351,7 +19346,7 @@
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharaoh of Egypt. Senenmut stewarded her household and built her temple.</t>
+          <t xml:space="preserve">Steward of Hatshepsut's household and architect of her temple at Deir el-Bahari.</t>
         </is>
       </c>
     </row>
@@ -30350,16 +30345,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13" style="1" customWidth="1"/>
     <col min="3" max="3" width="8" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16" style="1" customWidth="1"/>
     <col min="7" max="7" width="11" style="1" customWidth="1"/>
     <col min="8" max="8" width="60" style="1" customWidth="1"/>
     <col min="9" max="9" width="60" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16" style="1" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="8" style="1" customWidth="1"/>
     <col min="13" max="13" width="8" style="1" customWidth="1"/>
@@ -30453,17 +30448,17 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">senenmut</t>
+          <t xml:space="preserve">hatshepsut</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Senenmut</t>
+          <t xml:space="preserve">Hatshepsut</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Male</t>
+          <t xml:space="preserve">Female</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -30473,22 +30468,27 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 Mar 1505 BCE</t>
+          <t xml:space="preserve">2 Feb 1507 BCE</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">artist</t>
+          <t xml:space="preserve">diplomat</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priority arrival: Hatshepsut, Pharaoh of Egypt. She has brought her own beard.</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steward of the Pharaoh's household and architect of her temple.</t>
+          <t xml:space="preserve">Pharaoh of Upper and Lower Egypt. Wears the royal beard on official business.</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dlg_senenmut</t>
+          <t xml:space="preserve">dlg_hatshepsut</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -30498,47 +30498,37 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">socrates</t>
+          <t xml:space="preserve">kulthum</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Socrates</t>
+          <t xml:space="preserve">Umm Kulthum</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Male</t>
+          <t xml:space="preserve">Female</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">greece_ancient</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">italy_ancient</t>
+          <t xml:space="preserve">egypt_modern</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 Jun 470 BCE</t>
+          <t xml:space="preserve">4 May 1904</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wanderer</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Priority arrival: Socrates of Athens. He asks more questions than you do.</t>
+          <t xml:space="preserve">artist</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosopher. Known to question officials at length.</t>
+          <t xml:space="preserve">Singer of Cairo. Her Thursday concerts empty the streets.</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -30595,9 +30585,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="1" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -30626,7 +30616,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">senenmut</t>
+          <t xml:space="preserve">hatshepsut</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -30640,26 +30630,66 @@
         </is>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">socrates</t>
+          <t xml:space="preserve">hatshepsut</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">future</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">naturalism</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kulthum</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">money</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commons</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kulthum</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">government</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">democracy</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D5">
         <v>6</v>
       </c>
     </row>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -123,9 +123,19 @@
     <sheet name="home" sheetId="119" r:id="rId119"/>
     <sheet name="homeRadio" sheetId="120" r:id="rId120"/>
     <sheet name="homeUpgrades" sheetId="121" r:id="rId121"/>
-    <sheet name="worldFactors" sheetId="122" r:id="rId122"/>
-    <sheet name="worldOutcomes" sheetId="123" r:id="rId123"/>
-    <sheet name="worldRoles" sheetId="124" r:id="rId124"/>
+    <sheet name="homeBills" sheetId="122" r:id="rId122"/>
+    <sheet name="homePet" sheetId="123" r:id="rId123"/>
+    <sheet name="homePetKinds" sheetId="124" r:id="rId124"/>
+    <sheet name="homePetReactions" sheetId="125" r:id="rId125"/>
+    <sheet name="homePetToyLines" sheetId="126" r:id="rId126"/>
+    <sheet name="homePetHunger" sheetId="127" r:id="rId127"/>
+    <sheet name="homePetCold" sheetId="128" r:id="rId128"/>
+    <sheet name="homePetBoredom" sheetId="129" r:id="rId129"/>
+    <sheet name="homePetSickness" sheetId="130" r:id="rId130"/>
+    <sheet name="homeToys" sheetId="131" r:id="rId131"/>
+    <sheet name="worldFactors" sheetId="132" r:id="rId132"/>
+    <sheet name="worldOutcomes" sheetId="133" r:id="rId133"/>
+    <sheet name="worldRoles" sheetId="134" r:id="rId134"/>
   </sheets>
 </workbook>
 </file>
@@ -18245,7 +18255,7 @@
       </c>
       <c r="F725" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home's house upgrades and the radio</t>
+          <t xml:space="preserve">Home's house upgrades, the radio, the night's bills, the pet and its toys</t>
         </is>
       </c>
     </row>
@@ -18733,7 +18743,7 @@
     <row r="744">
       <c r="A744" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">worldFactors</t>
+          <t xml:space="preserve">homeBills</t>
         </is>
       </c>
       <c r="C744" s="1" t="inlineStr">
@@ -18743,24 +18753,24 @@
       </c>
       <c r="E744" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.world.factors, in order; a row's name is id, unique</t>
+          <t xml:space="preserve">one row per item of the list $.home.bills, in order; a row's name is bill, unique</t>
         </is>
       </c>
       <c r="F744" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the world's outcomes listed under END OF DEMO, in this order</t>
+          <t xml:space="preserve">the night's optional bills: the Heating and the TV work only with the Electricity paid</t>
         </is>
       </c>
     </row>
     <row r="745">
       <c r="A745" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">worldFactors</t>
+          <t xml:space="preserve">homeBills</t>
         </is>
       </c>
       <c r="B745" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">bill</t>
         </is>
       </c>
       <c r="C745" s="1" t="inlineStr">
@@ -18775,24 +18785,24 @@
       </c>
       <c r="E745" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">part of the row's name; one of: Food, Heating, Electricity, Tv, Medicine</t>
         </is>
       </c>
       <c r="F745" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the factor's id (the outcomes, leanings and pulls name their factor by it)</t>
+          <t xml:space="preserve">which of the night's bills (one row each)</t>
         </is>
       </c>
     </row>
     <row r="746">
       <c r="A746" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">worldFactors</t>
+          <t xml:space="preserve">homeBills</t>
         </is>
       </c>
       <c r="B746" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">question</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C746" s="1" t="inlineStr">
@@ -18807,51 +18817,46 @@
       </c>
       <c r="F746" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the question the end of the demo answers about 2150</t>
+          <t xml:space="preserve">its name on the bills panel</t>
         </is>
       </c>
     </row>
     <row r="747">
       <c r="A747" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">worldFactors</t>
+          <t xml:space="preserve">homeBills</t>
         </is>
       </c>
       <c r="B747" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="C747" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D747" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="E747" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one of: AsFound, Leader, Pulls</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F747" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">AsFound: the foundAs text; Leader: the leading nation's name (foundAs while none leads); Pulls: the outcome the run's choices pull most (worldOutcomes)</t>
+          <t xml:space="preserve">cr a night (the Medicine's with the house's careCost)</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="A748" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">worldFactors</t>
+          <t xml:space="preserve">homeBills</t>
         </is>
       </c>
       <c r="B748" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">foundAs</t>
+          <t xml:space="preserve">line</t>
         </is>
       </c>
       <c r="C748" s="1" t="inlineStr">
@@ -18861,78 +18866,73 @@
       </c>
       <c r="D748" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F748" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the answer as the run found 2150 (a Pulls factor's is its statusQuo outcome: blank)</t>
+          <t xml:space="preserve">a short line beside it</t>
         </is>
       </c>
     </row>
     <row r="749">
       <c r="A749" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">worldFactors</t>
-        </is>
-      </c>
-      <c r="B749" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">statusQuo</t>
+          <t xml:space="preserve">homePet</t>
         </is>
       </c>
       <c r="C749" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D749" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Single</t>
+        </is>
+      </c>
+      <c r="E749" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row: the object $.home.pet</t>
         </is>
       </c>
       <c r="F749" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Pulls factor's "as you found it" outcome id: it starts ahead (GameConfigSO worldStatusQuoWeight) and a denial pulls it</t>
+          <t xml:space="preserve">the pet's words: never a number</t>
         </is>
       </c>
     </row>
     <row r="750">
       <c r="A750" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">worldFactors</t>
+          <t xml:space="preserve">homePet</t>
         </is>
       </c>
       <c r="B750" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">splitLine</t>
+          <t xml:space="preserve">nameMaxLength</t>
         </is>
       </c>
       <c r="C750" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D750" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="F750" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a Pulls factor's answer when split between two outcomes: {a} and {b} are their names</t>
+          <t xml:space="preserve">the adoption's name limit, in characters</t>
         </is>
       </c>
     </row>
     <row r="751">
       <c r="A751" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">worldFactors</t>
+          <t xml:space="preserve">homePet</t>
         </is>
       </c>
       <c r="B751" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">splitHeadline</t>
+          <t xml:space="preserve">worse</t>
         </is>
       </c>
       <c r="C751" s="1" t="inlineStr">
@@ -18942,46 +18942,51 @@
       </c>
       <c r="D751" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F751" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the morning paper's line when the factor splits: {a} and {b}</t>
+          <t xml:space="preserve">Home's line after a night it got sicker</t>
         </is>
       </c>
     </row>
     <row r="752">
       <c r="A752" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">worldOutcomes</t>
+          <t xml:space="preserve">homePet</t>
+        </is>
+      </c>
+      <c r="B752" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">better</t>
         </is>
       </c>
       <c r="C752" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E752" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.world.outcomes, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D752" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F752" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">every answer of every factor answered by pulls: add rows for more combinations</t>
+          <t xml:space="preserve">Home's line after a night it got better</t>
         </is>
       </c>
     </row>
     <row r="753">
       <c r="A753" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">worldOutcomes</t>
+          <t xml:space="preserve">homePet</t>
         </is>
       </c>
       <c r="B753" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">factor</t>
+          <t xml:space="preserve">welfareNotice</t>
         </is>
       </c>
       <c r="C753" s="1" t="inlineStr">
@@ -18991,29 +18996,24 @@
       </c>
       <c r="D753" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E753" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'worldFactors'</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F753" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the factor it answers (a Pulls factor)</t>
+          <t xml:space="preserve">Home's warning after a night left at the worst</t>
         </is>
       </c>
     </row>
     <row r="754">
       <c r="A754" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">worldOutcomes</t>
+          <t xml:space="preserve">homePet</t>
         </is>
       </c>
       <c r="B754" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">paperAdopted</t>
         </is>
       </c>
       <c r="C754" s="1" t="inlineStr">
@@ -19023,24 +19023,24 @@
       </c>
       <c r="D754" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F754" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the outcome's id within its factor (leanings and pulls name it)</t>
+          <t xml:space="preserve">the paper the morning after the adoption: {name}, {kind}</t>
         </is>
       </c>
     </row>
     <row r="755">
       <c r="A755" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">worldOutcomes</t>
+          <t xml:space="preserve">homePet</t>
         </is>
       </c>
       <c r="B755" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">paperWelfare</t>
         </is>
       </c>
       <c r="C755" s="1" t="inlineStr">
@@ -19055,46 +19055,36 @@
       </c>
       <c r="F755" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the answer as the player reads it</t>
+          <t xml:space="preserve">the paper after a night left at the worst</t>
         </is>
       </c>
     </row>
     <row r="756">
       <c r="A756" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">worldOutcomes</t>
-        </is>
-      </c>
-      <c r="B756" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">headline</t>
+          <t xml:space="preserve">homePetKinds</t>
         </is>
       </c>
       <c r="C756" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D756" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F756" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the morning paper's line the morning after it takes the lead</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E756" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.home.pet.kinds, in order; a row's name is kind, unique</t>
         </is>
       </c>
     </row>
     <row r="757">
       <c r="A757" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">worldOutcomes</t>
+          <t xml:space="preserve">homePetKinds</t>
         </is>
       </c>
       <c r="B757" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="C757" s="1" t="inlineStr">
@@ -19104,46 +19094,51 @@
       </c>
       <c r="D757" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F757" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2150 under this answer in a sentence or two, with a joke and an upside, never a verdict</t>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E757" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name; one of: Dog, Cat</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">worldRoles</t>
+          <t xml:space="preserve">homePetKinds</t>
+        </is>
+      </c>
+      <c r="B758" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">word</t>
         </is>
       </c>
       <c r="C758" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
-        </is>
-      </c>
-      <c r="E758" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one row per item of the list $.world.roles, in order</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D758" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F758" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">which factor each role pulls; a role not listed pulls nothing</t>
+          <t xml:space="preserve">the kind in a sentence: {kind}</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">worldRoles</t>
+          <t xml:space="preserve">homePetKinds</t>
         </is>
       </c>
       <c r="B759" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">archetype</t>
+          <t xml:space="preserve">suggestedName</t>
         </is>
       </c>
       <c r="C759" s="1" t="inlineStr">
@@ -19153,69 +19148,971 @@
       </c>
       <c r="D759" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F759" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">an archetype id (content.archetypes)</t>
+          <t xml:space="preserve">the adoption panel's suggestion (a valid name)</t>
         </is>
       </c>
     </row>
     <row r="760">
       <c r="A760" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">worldRoles</t>
-        </is>
-      </c>
-      <c r="B760" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">factor</t>
+          <t xml:space="preserve">homePetReactions</t>
         </is>
       </c>
       <c r="C760" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D760" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Values</t>
         </is>
       </c>
       <c r="E760" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'worldFactors'</t>
+          <t xml:space="preserve">one row per item of the list $.home.pet.kinds[].reactions, in order; the first column names the parent row</t>
         </is>
       </c>
       <c r="F760" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the factor its accepted travellers pull, toward their destination's leaning</t>
+          <t xml:space="preserve">a pat's lines, in turn: {name}</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">homePetReactions</t>
+        </is>
+      </c>
+      <c r="B761" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kind</t>
+        </is>
+      </c>
+      <c r="C761" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D761" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E761" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'homePetKinds' this row belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homePetReactions</t>
+        </is>
+      </c>
+      <c r="B762" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="C762" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D762" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homePetToyLines</t>
+        </is>
+      </c>
+      <c r="C763" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Values</t>
+        </is>
+      </c>
+      <c r="E763" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.home.pet.kinds[].toyLines, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F763" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a toy's lines, in turn by the day: {name}, {toy}</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homePetToyLines</t>
+        </is>
+      </c>
+      <c r="B764" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kind</t>
+        </is>
+      </c>
+      <c r="C764" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D764" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E764" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names the row of 'homePetKinds' this row belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homePetToyLines</t>
+        </is>
+      </c>
+      <c r="B765" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="C765" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D765" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homePetHunger</t>
+        </is>
+      </c>
+      <c r="C766" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Values</t>
+        </is>
+      </c>
+      <c r="E766" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.home.pet.hunger, in order</t>
+        </is>
+      </c>
+      <c r="F766" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hunger in words, best first: {name}</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homePetHunger</t>
+        </is>
+      </c>
+      <c r="B767" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="C767" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D767" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homePetCold</t>
+        </is>
+      </c>
+      <c r="C768" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Values</t>
+        </is>
+      </c>
+      <c r="E768" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.home.pet.cold, in order</t>
+        </is>
+      </c>
+      <c r="F768" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cold in words, best first</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homePetCold</t>
+        </is>
+      </c>
+      <c r="B769" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="C769" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D769" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homePetBoredom</t>
+        </is>
+      </c>
+      <c r="C770" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Values</t>
+        </is>
+      </c>
+      <c r="E770" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.home.pet.boredom, in order</t>
+        </is>
+      </c>
+      <c r="F770" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boredom in words, best first</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homePetBoredom</t>
+        </is>
+      </c>
+      <c r="B771" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="C771" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D771" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homePetSickness</t>
+        </is>
+      </c>
+      <c r="C772" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Values</t>
+        </is>
+      </c>
+      <c r="E772" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.home.pet.sickness, in order</t>
+        </is>
+      </c>
+      <c r="F772" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sickness in words, best first</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homePetSickness</t>
+        </is>
+      </c>
+      <c r="B773" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="C773" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D773" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeToys</t>
+        </is>
+      </c>
+      <c r="C774" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E774" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.home.toys, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeToys</t>
+        </is>
+      </c>
+      <c r="B775" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C775" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D775" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E775" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
+        </is>
+      </c>
+      <c r="F775" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the toy's id (an Orders upgrade, saved as owned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeToys</t>
+        </is>
+      </c>
+      <c r="B776" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="C776" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D776" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeToys</t>
+        </is>
+      </c>
+      <c r="B777" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cost</t>
+        </is>
+      </c>
+      <c r="C777" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whole number</t>
+        </is>
+      </c>
+      <c r="D777" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F777" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the price in cr at the Orders app</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeToys</t>
+        </is>
+      </c>
+      <c r="B778" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mood</t>
+        </is>
+      </c>
+      <c r="C778" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">number</t>
+        </is>
+      </c>
+      <c r="D778" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="F778" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mood points while owned (fewer sick nights, quicker recovery)</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">homeToys</t>
+        </is>
+      </c>
+      <c r="B779" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blurb</t>
+        </is>
+      </c>
+      <c r="C779" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D779" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F779" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the Orders app's line</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldFactors</t>
+        </is>
+      </c>
+      <c r="C780" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E780" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.world.factors, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F780" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the world's outcomes listed under END OF DEMO, in this order</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldFactors</t>
+        </is>
+      </c>
+      <c r="B781" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C781" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D781" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E781" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">part of the row's name</t>
+        </is>
+      </c>
+      <c r="F781" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the factor's id (the outcomes, leanings and pulls name their factor by it)</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldFactors</t>
+        </is>
+      </c>
+      <c r="B782" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question</t>
+        </is>
+      </c>
+      <c r="C782" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D782" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F782" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the question the end of the demo answers about 2150</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldFactors</t>
+        </is>
+      </c>
+      <c r="B783" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">answer</t>
+        </is>
+      </c>
+      <c r="C783" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D783" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E783" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one of: AsFound, Leader, Pulls</t>
+        </is>
+      </c>
+      <c r="F783" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AsFound: the foundAs text; Leader: the leading nation's name (foundAs while none leads); Pulls: the outcome the run's choices pull most (worldOutcomes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldFactors</t>
+        </is>
+      </c>
+      <c r="B784" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">foundAs</t>
+        </is>
+      </c>
+      <c r="C784" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D784" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="F784" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the answer as the run found 2150 (a Pulls factor's is its statusQuo outcome: blank)</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldFactors</t>
+        </is>
+      </c>
+      <c r="B785" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">statusQuo</t>
+        </is>
+      </c>
+      <c r="C785" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D785" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="F785" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a Pulls factor's "as you found it" outcome id: it starts ahead (GameConfigSO worldStatusQuoWeight) and a denial pulls it</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldFactors</t>
+        </is>
+      </c>
+      <c r="B786" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">splitLine</t>
+        </is>
+      </c>
+      <c r="C786" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D786" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="F786" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a Pulls factor's answer when split between two outcomes: {a} and {b} are their names</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldFactors</t>
+        </is>
+      </c>
+      <c r="B787" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">splitHeadline</t>
+        </is>
+      </c>
+      <c r="C787" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D787" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="F787" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the morning paper's line when the factor splits: {a} and {b}</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldOutcomes</t>
+        </is>
+      </c>
+      <c r="C788" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E788" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.world.outcomes, in order</t>
+        </is>
+      </c>
+      <c r="F788" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">every answer of every factor answered by pulls: add rows for more combinations</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldOutcomes</t>
+        </is>
+      </c>
+      <c r="B789" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">factor</t>
+        </is>
+      </c>
+      <c r="C789" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D789" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="E789" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'worldFactors'</t>
+        </is>
+      </c>
+      <c r="F789" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the factor it answers (a Pulls factor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldOutcomes</t>
+        </is>
+      </c>
+      <c r="B790" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C790" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D790" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="F790" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the outcome's id within its factor (leanings and pulls name it)</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldOutcomes</t>
+        </is>
+      </c>
+      <c r="B791" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="C791" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D791" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F791" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the answer as the player reads it</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldOutcomes</t>
+        </is>
+      </c>
+      <c r="B792" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">headline</t>
+        </is>
+      </c>
+      <c r="C792" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D792" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F792" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the morning paper's line the morning after it takes the lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldOutcomes</t>
+        </is>
+      </c>
+      <c r="B793" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+      <c r="C793" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D793" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F793" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2150 under this answer in a sentence or two, with a joke and an upside, never a verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">worldRoles</t>
         </is>
       </c>
-      <c r="B761" s="1" t="inlineStr">
+      <c r="C794" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E794" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.world.roles, in order</t>
+        </is>
+      </c>
+      <c r="F794" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">which factor each role pulls; a role not listed pulls nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldRoles</t>
+        </is>
+      </c>
+      <c r="B795" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">archetype</t>
+        </is>
+      </c>
+      <c r="C795" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D795" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
+        </is>
+      </c>
+      <c r="F795" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">an archetype id (content.archetypes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldRoles</t>
+        </is>
+      </c>
+      <c r="B796" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">factor</t>
+        </is>
+      </c>
+      <c r="C796" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D796" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="E796" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'worldFactors'</t>
+        </is>
+      </c>
+      <c r="F796" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the factor its accepted travellers pull, toward their destination's leaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">worldRoles</t>
+        </is>
+      </c>
+      <c r="B797" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">pull</t>
         </is>
       </c>
-      <c r="C761" s="1" t="inlineStr">
+      <c r="C797" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">number</t>
         </is>
       </c>
-      <c r="D761" s="1" t="inlineStr">
+      <c r="D797" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="F761" s="1" t="inlineStr">
+      <c r="F797" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">one accepted traveller's pull, before the kind's scale (GameConfigSO)</t>
         </is>
@@ -22051,7 +22948,7 @@
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tier B paste comes in two colours. The kid prefers the green.</t>
+          <t xml:space="preserve">Tier B paste comes in two colours. The pet prefers the green.</t>
         </is>
       </c>
     </row>
@@ -22117,113 +23014,71 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" customWidth="1"/>
-    <col min="6" max="6" width="44" style="1" customWidth="1"/>
-    <col min="7" max="7" width="60" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">bill</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">question</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">price</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">foundAs</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">statusQuo</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">splitLine</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">splitHeadline</t>
+          <t xml:space="preserve">line</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">government</t>
+          <t xml:space="preserve">Food</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Who runs 2150?</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pulls</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">directorate</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{a} and {b}, sharing the building</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TWO GOVERNMENTS: {a} and {b} both claim the Directorate building. Each has opened its own queue.</t>
+          <t xml:space="preserve">Food</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A night's bowl of Directorate-grade kibble.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
+          <t xml:space="preserve">Heating</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">What does 2150 run on?</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pulls</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">credit_age</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{a} and {b}, one on each bank of the river</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2150 IS SPLIT: {a} on one bank of the river, {b} on the other. The bridge is very busy.</t>
+          <t xml:space="preserve">Heating</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The radiator's meter takes credits only.</t>
         </is>
       </c>
     </row>
@@ -22235,91 +23090,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="49" style="1" customWidth="1"/>
+    <col min="3" max="3" width="37" style="1" customWidth="1"/>
     <col min="4" max="4" width="60" style="1" customWidth="1"/>
     <col min="5" max="5" width="60" style="1" customWidth="1"/>
+    <col min="6" max="6" width="60" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">factor</t>
+          <t xml:space="preserve">nameMaxLength</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">worse</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">better</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">headline</t>
+          <t xml:space="preserve">welfareNotice</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">report</t>
+          <t xml:space="preserve">paperAdopted</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paperWelfare</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">government</t>
-        </is>
+      <c r="A2">
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">directorate</t>
+          <t xml:space="preserve">{name} caught something while you were at work.</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Directorate</t>
+          <t xml:space="preserve">{name} seems brighter this evening.</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECTORATE: the Customs Directorate carries on running 2150. The queues reopen at nine, as always.</t>
+          <t xml:space="preserve">A notice from the Animal Welfare Office is taped to your door: an inspector will look in on {name} tomorrow night.</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Customs Directorate runs 2150 as it always has: by form, by queue and by stamp. Every citizen knows exactly which counter to stand at.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">government</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">democracy</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Democracy</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2150 VOTES: the Directorate hands the building to an elected assembly. Its first sitting ran eleven hours.</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">An elected assembly runs 2150 and votes on everything, including the colour of the ballot papers. Anyone may stand for office, and nearly everyone does.</t>
+          <t xml:space="preserve">SHELTER NEWS: {name} the {kind} has gone home with a clerk of Temporal Customs, Desk 3.</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANIMAL WELFARE: inspectors are asking after a {kind} called {name} in Block C.</t>
         </is>
       </c>
     </row>
@@ -22331,56 +23168,372 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="1" max="1" width="8" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">archetype</t>
+          <t xml:space="preserve">kind</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">factor</t>
+          <t xml:space="preserve">word</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pull</t>
+          <t xml:space="preserve">suggestedName</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">scientist</t>
+          <t xml:space="preserve">Dog</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">future</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>4</v>
+          <t xml:space="preserve">dog</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biscuit</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">diplomat</t>
+          <t xml:space="preserve">Cat</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">government</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>3</v>
+          <t xml:space="preserve">cat</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Miso</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet125.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8" style="1" customWidth="1"/>
+    <col min="2" max="2" width="60" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kind</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dog</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} leans into your hand and sighs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dog</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name}'s tail thumps the floor twice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dog</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} rolls over for a belly rub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dog</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} licks your wrist, then looks embarrassed about it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cat</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} allows it. Briefly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cat</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} purrs like a small engine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cat</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} headbutts your chin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cat</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} pretends not to notice, then follows you to the kitchen.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet126.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8" style="1" customWidth="1"/>
+    <col min="2" max="2" width="60" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kind</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dog</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} carries the {toy} round the flat like a trophy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dog</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} drops the {toy} at your feet. Again. And again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dog</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} guards the {toy} from an invisible rival.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cat</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} ambushes the {toy} from under the sofa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cat</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} bats the {toy} under the radiator and stares at you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cat</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} decides the {toy} is beneath them, then pounces anyway.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet127.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} is fed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} is hungry.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet128.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} is warm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} is chilly.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet129.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} is playful.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} is restless.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -22460,6 +23613,400 @@
         <v>0</v>
       </c>
       <c r="E3">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet130.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} is healthy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{name} is a little unwell.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet131.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="60" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cost</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mood</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">blurb</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toy_ball</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pre-owned Tennis Ball</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slightly bald. It bounces in 2150 the way it bounced in 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toy_rope</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rope of Regulation Length</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>25</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Certified tug-worthy by the Bureau of Standards. Chewing voids the warranty.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet132.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" customWidth="1"/>
+    <col min="6" max="6" width="44" style="1" customWidth="1"/>
+    <col min="7" max="7" width="60" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">answer</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">foundAs</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">statusQuo</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">splitLine</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">splitHeadline</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">government</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Who runs 2150?</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pulls</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directorate</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{a} and {b}, sharing the building</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TWO GOVERNMENTS: {a} and {b} both claim the Directorate building. Each has opened its own queue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What does 2150 run on?</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pulls</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">credit_age</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{a} and {b}, one on each bank of the river</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2150 IS SPLIT: {a} on one bank of the river, {b} on the other. The bridge is very busy.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet133.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17" style="1" customWidth="1"/>
+    <col min="4" max="4" width="60" style="1" customWidth="1"/>
+    <col min="5" max="5" width="60" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">factor</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">headline</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">report</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">government</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directorate</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Directorate</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIRECTORATE: the Customs Directorate carries on running 2150. The queues reopen at nine, as always.</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Customs Directorate runs 2150 as it always has: by form, by queue and by stamp. Every citizen knows exactly which counter to stand at.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">government</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">democracy</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Democracy</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2150 VOTES: the Directorate hands the building to an elected assembly. Its first sitting ran eleven hours.</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An elected assembly runs 2150 and votes on everything, including the colour of the ballot papers. Anyone may stand for office, and nearly everyone does.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet134.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">archetype</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">factor</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pull</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scientist</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">future</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diplomat</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">government</t>
+        </is>
+      </c>
+      <c r="C3">
         <v>3</v>
       </c>
     </row>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E558" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: News, Desk, Return</t>
+          <t xml:space="preserve">one of: News, Desk, Return, Front</t>
         </is>
       </c>
       <c r="F558" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">where the line goes: the paper's news (blank), the paper's desk section, or nowhere until the character returns (its fired flag, trig:history_{id}:fired)</t>
+          <t xml:space="preserve">where the line goes: the paper's news (blank), the paper's desk section, nowhere until the character returns (its fired flag, trig:history_{id}:fired), or the front page, leading the news (a famous traveller's homecoming)</t>
         </is>
       </c>
     </row>
@@ -20158,10 +20158,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12" style="1" customWidth="1"/>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8" style="1" customWidth="1"/>
     <col min="5" max="5" width="15" style="1" customWidth="1"/>
     <col min="6" max="6" width="60" style="1" customWidth="1"/>
   </cols>
@@ -20223,22 +20223,17 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">hatshepsut</t>
+          <t xml:space="preserve">senenmut</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hatshepsut</t>
+          <t xml:space="preserve">Senenmut</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">c. 1507 BCE</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1458 BCE</t>
+          <t xml:space="preserve">c. 1505 BCE</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
@@ -20248,7 +20243,7 @@
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharaoh of Egypt. Senenmut stewarded her household and built her temple.</t>
+          <t xml:space="preserve">Steward of Hatshepsut's household and architect of her temple at Deir el-Bahari.</t>
         </is>
       </c>
     </row>
@@ -31897,16 +31892,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13" style="1" customWidth="1"/>
     <col min="3" max="3" width="8" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16" style="1" customWidth="1"/>
     <col min="7" max="7" width="11" style="1" customWidth="1"/>
     <col min="8" max="8" width="60" style="1" customWidth="1"/>
     <col min="9" max="9" width="60" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16" style="1" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="8" style="1" customWidth="1"/>
     <col min="13" max="13" width="8" style="1" customWidth="1"/>
@@ -32000,17 +31995,17 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">senenmut</t>
+          <t xml:space="preserve">hatshepsut</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Senenmut</t>
+          <t xml:space="preserve">Hatshepsut</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Male</t>
+          <t xml:space="preserve">Female</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -32020,22 +32015,27 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 Mar 1505 BCE</t>
+          <t xml:space="preserve">2 Feb 1507 BCE</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">artist</t>
+          <t xml:space="preserve">diplomat</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priority arrival: Hatshepsut, Pharaoh of Egypt. She has brought her own beard.</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steward of the Pharaoh's household and architect of her temple.</t>
+          <t xml:space="preserve">Pharaoh of Upper and Lower Egypt. Wears the royal beard on official business.</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dlg_senenmut</t>
+          <t xml:space="preserve">dlg_hatshepsut</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -32045,47 +32045,37 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">socrates</t>
+          <t xml:space="preserve">kulthum</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Socrates</t>
+          <t xml:space="preserve">Umm Kulthum</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Male</t>
+          <t xml:space="preserve">Female</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">greece_ancient</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">italy_ancient</t>
+          <t xml:space="preserve">egypt_modern</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 Jun 470 BCE</t>
+          <t xml:space="preserve">4 May 1904</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">wanderer</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Priority arrival: Socrates of Athens. He asks more questions than you do.</t>
+          <t xml:space="preserve">artist</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philosopher. Known to question officials at length.</t>
+          <t xml:space="preserve">Singer of Cairo. Her Thursday concerts empty the streets.</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -32142,7 +32132,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="1" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
@@ -32173,7 +32163,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">senenmut</t>
+          <t xml:space="preserve">hatshepsut</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -32187,26 +32177,66 @@
         </is>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">socrates</t>
+          <t xml:space="preserve">hatshepsut</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">money</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jubilee</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kulthum</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">money</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commons</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kulthum</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">government</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">democracy</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D5">
         <v>6</v>
       </c>
     </row>

--- a/ContentSheets/TimeDesk_Content_Template.xlsx
+++ b/ContentSheets/TimeDesk_Content_Template.xlsx
@@ -11556,7 +11556,7 @@
       </c>
       <c r="B448" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">entryLabel</t>
         </is>
       </c>
       <c r="C448" s="1" t="inlineStr">
@@ -11571,34 +11571,29 @@
       </c>
       <c r="F448" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the hub entry that opens the questions about the differences the clerk logged (shown while one is still to be asked)</t>
+          <t xml:space="preserve">one difference's entry in the ask menu: {category} and {value}</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">confront</t>
-        </is>
-      </c>
-      <c r="B449" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">entryLabel</t>
+          <t xml:space="preserve">confrontPrompts</t>
         </is>
       </c>
       <c r="C449" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D449" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E449" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.interview.confront.prompts, in order</t>
         </is>
       </c>
       <c r="F449" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one difference's entry: {category} and {value}</t>
+          <t xml:space="preserve">the desk's questions: one base row (blank category) per proof and statement kind is required</t>
         </is>
       </c>
     </row>
@@ -11608,19 +11603,24 @@
           <t xml:space="preserve">confrontPrompts</t>
         </is>
       </c>
+      <c r="B450" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">proof</t>
+        </is>
+      </c>
       <c r="C450" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D450" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E450" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.interview.confront.prompts, in order</t>
-        </is>
-      </c>
-      <c r="F450" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the desk's questions: one base row (blank category) per proof and statement kind is required</t>
+          <t xml:space="preserve">one of: ClaimMismatch, ForeignOrigin, RecordMismatch, CrossMismatch, PersonMismatch</t>
         </is>
       </c>
     </row>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="B451" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">proof</t>
+          <t xml:space="preserve">source</t>
         </is>
       </c>
       <c r="C451" s="1" t="inlineStr">
@@ -11647,7 +11647,12 @@
       </c>
       <c r="E451" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one of: ClaimMismatch, ForeignOrigin, RecordMismatch, CrossMismatch, PersonMismatch</t>
+          <t xml:space="preserve">one of: DocumentField, Answer, Appearance</t>
+        </is>
+      </c>
+      <c r="F451" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">what the statement was: papers, said or worn (a cross proof is always DocumentField)</t>
         </is>
       </c>
     </row>
@@ -11659,7 +11664,7 @@
       </c>
       <c r="B452" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">source</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C452" s="1" t="inlineStr">
@@ -11669,17 +11674,12 @@
       </c>
       <c r="D452" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E452" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one of: DocumentField, Answer, Appearance</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="F452" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">what the statement was: papers, said or worn (a cross proof is always DocumentField)</t>
+          <t xml:space="preserve">the clue category it is for (blank: any)</t>
         </is>
       </c>
     </row>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B453" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C453" s="1" t="inlineStr">
@@ -11701,12 +11701,12 @@
       </c>
       <c r="D453" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F453" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the clue category it is for (blank: any)</t>
+          <t xml:space="preserve">the desk's question: {value} and {other} required (here or in then); {category}, {place}, {document} (papers) and {otherDocument} (a cross proof) allowed</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B454" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">then</t>
         </is>
       </c>
       <c r="C454" s="1" t="inlineStr">
@@ -11728,39 +11728,34 @@
       </c>
       <c r="D454" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="F454" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the desk's question: {value} and {other} required (here or in then); {category}, {place}, {document} (papers) and {otherDocument} (a cross proof) allowed</t>
+          <t xml:space="preserve">an optional second desk line (each line fits a transcript row)</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">confrontPrompts</t>
-        </is>
-      </c>
-      <c r="B455" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">then</t>
+          <t xml:space="preserve">confrontReplies</t>
         </is>
       </c>
       <c r="C455" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D455" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E455" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.interview.confront.replies, in order</t>
         </is>
       </c>
       <c r="F455" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">an optional second desk line (each line fits a transcript row)</t>
+          <t xml:space="preserve">the default answers: one base row per outcome is required</t>
         </is>
       </c>
     </row>
@@ -11770,19 +11765,24 @@
           <t xml:space="preserve">confrontReplies</t>
         </is>
       </c>
+      <c r="B456" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">outcome</t>
+        </is>
+      </c>
       <c r="C456" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D456" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E456" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.interview.confront.replies, in order</t>
-        </is>
-      </c>
-      <c r="F456" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the default answers: one base row per outcome is required</t>
+          <t xml:space="preserve">one of: Explain, Crack, DoubleDown</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="B457" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">outcome</t>
+          <t xml:space="preserve">reason</t>
         </is>
       </c>
       <c r="C457" s="1" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="D457" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E457" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one of: Explain, Crack, DoubleDown</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="F457" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fault reason (blank: any)</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11821,7 @@
       </c>
       <c r="B458" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">reason</t>
+          <t xml:space="preserve">lie</t>
         </is>
       </c>
       <c r="C458" s="1" t="inlineStr">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="F458" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a fault reason (blank: any)</t>
+          <t xml:space="preserve">a lie kind (blank: any)</t>
         </is>
       </c>
     </row>
@@ -11848,22 +11848,27 @@
       </c>
       <c r="B459" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">lie</t>
+          <t xml:space="preserve">kinds</t>
         </is>
       </c>
       <c r="C459" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D459" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E459" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
       <c r="F459" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">a lie kind (blank: any)</t>
+          <t xml:space="preserve">the kinds it is for (blank: any)</t>
         </is>
       </c>
     </row>
@@ -11875,27 +11880,27 @@
       </c>
       <c r="B460" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kinds</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C460" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D460" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E460" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">separate items with |</t>
+          <t xml:space="preserve">names a row of 'eras'</t>
         </is>
       </c>
       <c r="F460" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the kinds it is for (blank: any)</t>
+          <t xml:space="preserve">the claimed era (blank: any)</t>
         </is>
       </c>
     </row>
@@ -11907,7 +11912,7 @@
       </c>
       <c r="B461" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C461" s="1" t="inlineStr">
@@ -11917,44 +11922,34 @@
       </c>
       <c r="D461" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E461" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names a row of 'eras'</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
       <c r="F461" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the claimed era (blank: any)</t>
+          <t xml:space="preserve">{value}, {other} and {place} allowed</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">confrontReplies</t>
-        </is>
-      </c>
-      <c r="B462" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">questions</t>
         </is>
       </c>
       <c r="C462" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D462" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E462" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.questions, in order; a row's name is id, unique</t>
         </is>
       </c>
       <c r="F462" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">{value}, {other} and {place} allowed</t>
+          <t xml:space="preserve">one question per category, asked of every traveller in the same words</t>
         </is>
       </c>
     </row>
@@ -11964,19 +11959,24 @@
           <t xml:space="preserve">questions</t>
         </is>
       </c>
+      <c r="B463" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
       <c r="C463" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D463" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E463" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.questions, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F463" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">one question per category, asked of every traveller in the same words</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -11988,7 +11988,7 @@
       </c>
       <c r="B464" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">category</t>
         </is>
       </c>
       <c r="C464" s="1" t="inlineStr">
@@ -11998,12 +11998,7 @@
       </c>
       <c r="D464" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E464" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12010,7 @@
       </c>
       <c r="B465" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">category</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C465" s="1" t="inlineStr">
@@ -12037,7 +12032,7 @@
       </c>
       <c r="B466" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">prompt</t>
         </is>
       </c>
       <c r="C466" s="1" t="inlineStr">
@@ -12059,7 +12054,7 @@
       </c>
       <c r="B467" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt</t>
+          <t xml:space="preserve">answer</t>
         </is>
       </c>
       <c r="C467" s="1" t="inlineStr">
@@ -12081,17 +12076,17 @@
       </c>
       <c r="B468" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">fromDay</t>
         </is>
       </c>
       <c r="C468" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">whole number</t>
         </is>
       </c>
       <c r="D468" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -12103,39 +12098,39 @@
       </c>
       <c r="B469" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">fromDay</t>
+          <t xml:space="preserve">announce</t>
         </is>
       </c>
       <c r="C469" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">whole number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D469" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questions</t>
-        </is>
-      </c>
-      <c r="B470" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">announce</t>
+          <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
       <c r="C470" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D470" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E470" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.questions[].conditions, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F470" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all must pass</t>
         </is>
       </c>
     </row>
@@ -12145,19 +12140,24 @@
           <t xml:space="preserve">questionConditions</t>
         </is>
       </c>
+      <c r="B471" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question</t>
+        </is>
+      </c>
       <c r="C471" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D471" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E471" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.questions[].conditions, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F471" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all must pass</t>
+          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -12169,22 +12169,17 @@
       </c>
       <c r="B472" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">question</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C472" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D472" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E472" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -12196,7 +12191,7 @@
       </c>
       <c r="B473" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C473" s="1" t="inlineStr">
@@ -12206,7 +12201,7 @@
       </c>
       <c r="D473" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -12218,17 +12213,17 @@
       </c>
       <c r="B474" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C474" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D474" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -12240,17 +12235,22 @@
       </c>
       <c r="B475" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C475" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D475" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E475" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="B476" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C476" s="1" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="E476" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="B477" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C477" s="1" t="inlineStr">
@@ -12304,34 +12304,29 @@
       </c>
       <c r="E477" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionConditions</t>
-        </is>
-      </c>
-      <c r="B478" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
       <c r="C478" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D478" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E478" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">one row per item of the list $.questions[].overrides, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F478" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the answer for some kinds, an era or both (the most specific wins: kinds 2, era 1); every traveller is asked the question's own prompt</t>
         </is>
       </c>
     </row>
@@ -12341,19 +12336,24 @@
           <t xml:space="preserve">questionOverrides</t>
         </is>
       </c>
+      <c r="B479" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">question</t>
+        </is>
+      </c>
       <c r="C479" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D479" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E479" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.questions[].overrides, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F479" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the answer for some kinds, an era or both (the most specific wins: kinds 2, era 1); every traveller is asked the question's own prompt</t>
+          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -12365,22 +12365,27 @@
       </c>
       <c r="B480" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">question</t>
+          <t xml:space="preserve">era</t>
         </is>
       </c>
       <c r="C480" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D480" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
       <c r="E480" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'questions' this row belongs to</t>
+          <t xml:space="preserve">names a row of 'eras'</t>
+        </is>
+      </c>
+      <c r="F480" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the claimed era (blank: any)</t>
         </is>
       </c>
     </row>
@@ -12392,27 +12397,27 @@
       </c>
       <c r="B481" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">era</t>
+          <t xml:space="preserve">kinds</t>
         </is>
       </c>
       <c r="C481" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">text list</t>
         </is>
       </c>
       <c r="D481" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">no items (left out of the JSON)</t>
         </is>
       </c>
       <c r="E481" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'eras'</t>
+          <t xml:space="preserve">separate items with |</t>
         </is>
       </c>
       <c r="F481" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">the claimed era (blank: any)</t>
+          <t xml:space="preserve">the traveller kinds (RichTourist, PoorTourist, Labourer, Displaced); blank: any</t>
         </is>
       </c>
     </row>
@@ -12424,49 +12429,39 @@
       </c>
       <c r="B482" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">kinds</t>
+          <t xml:space="preserve">answer</t>
         </is>
       </c>
       <c r="C482" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text list</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D482" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">no items (left out of the JSON)</t>
-        </is>
-      </c>
-      <c r="E482" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">separate items with |</t>
-        </is>
-      </c>
-      <c r="F482" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the traveller kinds (RichTourist, PoorTourist, Labourer, Displaced); blank: any</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">questionOverrides</t>
-        </is>
-      </c>
-      <c r="B483" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">answer</t>
+          <t xml:space="preserve">dialogs</t>
         </is>
       </c>
       <c r="C483" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D483" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E483" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F483" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">narrative dialogs: nodes, their lines and the player's choices</t>
         </is>
       </c>
     </row>
@@ -12476,19 +12471,24 @@
           <t xml:space="preserve">dialogs</t>
         </is>
       </c>
+      <c r="B484" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
       <c r="C484" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D484" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E484" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F484" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">narrative dialogs: nodes, their lines and the player's choices</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="B485" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C485" s="1" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="D485" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E485" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F485" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the wheel entry</t>
         </is>
       </c>
     </row>
@@ -12527,44 +12527,39 @@
       </c>
       <c r="B486" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">repeatable</t>
         </is>
       </c>
       <c r="C486" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">true/false</t>
         </is>
       </c>
       <c r="D486" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F486" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the wheel entry</t>
+          <t xml:space="preserve">false (left out of the JSON)</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogs</t>
-        </is>
-      </c>
-      <c r="B487" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">repeatable</t>
+          <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
       <c r="C487" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">true/false</t>
-        </is>
-      </c>
-      <c r="D487" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">false (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E487" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].conditions, in order; the first column names the parent row</t>
+        </is>
+      </c>
+      <c r="F487" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">all must pass</t>
         </is>
       </c>
     </row>
@@ -12574,19 +12569,24 @@
           <t xml:space="preserve">dialogConditions</t>
         </is>
       </c>
+      <c r="B488" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dialog</t>
+        </is>
+      </c>
       <c r="C488" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D488" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E488" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].conditions, in order; the first column names the parent row</t>
-        </is>
-      </c>
-      <c r="F488" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">all must pass</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -12598,22 +12598,17 @@
       </c>
       <c r="B489" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="C489" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D489" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E489" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -12625,7 +12620,7 @@
       </c>
       <c r="B490" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t xml:space="preserve">key</t>
         </is>
       </c>
       <c r="C490" s="1" t="inlineStr">
@@ -12635,7 +12630,7 @@
       </c>
       <c r="D490" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -12647,17 +12642,17 @@
       </c>
       <c r="B491" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">key</t>
+          <t xml:space="preserve">threshold</t>
         </is>
       </c>
       <c r="C491" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">number</t>
         </is>
       </c>
       <c r="D491" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -12669,17 +12664,22 @@
       </c>
       <c r="B492" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">threshold</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C492" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">number</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D492" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
+        </is>
+      </c>
+      <c r="E492" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">names a row of 'places'</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
       </c>
       <c r="B493" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">place</t>
+          <t xml:space="preserve">attribute</t>
         </is>
       </c>
       <c r="C493" s="1" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="E493" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'places'</t>
+          <t xml:space="preserve">names a row of 'contentAttributes'</t>
         </is>
       </c>
     </row>
@@ -12718,7 +12718,7 @@
       </c>
       <c r="B494" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">attribute</t>
+          <t xml:space="preserve">nation</t>
         </is>
       </c>
       <c r="C494" s="1" t="inlineStr">
@@ -12733,34 +12733,24 @@
       </c>
       <c r="E494" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'contentAttributes'</t>
+          <t xml:space="preserve">names a row of 'countries'</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogConditions</t>
-        </is>
-      </c>
-      <c r="B495" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nation</t>
+          <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
       <c r="C495" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D495" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E495" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names a row of 'countries'</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes, in order; a row's name is id, unique per parent row; the first column names the parent row</t>
         </is>
       </c>
     </row>
@@ -12770,14 +12760,24 @@
           <t xml:space="preserve">dialogNodes</t>
         </is>
       </c>
+      <c r="B496" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dialog</t>
+        </is>
+      </c>
       <c r="C496" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D496" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E496" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes, in order; a row's name is id, unique per parent row; the first column names the parent row</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -12789,12 +12789,12 @@
       </c>
       <c r="B497" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C497" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D497" s="1" t="inlineStr">
@@ -12804,34 +12804,24 @@
       </c>
       <c r="E497" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogNodes</t>
-        </is>
-      </c>
-      <c r="B498" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
       <c r="C498" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D498" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(required)</t>
+          <t xml:space="preserve">Rows</t>
         </is>
       </c>
       <c r="E498" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].lines, in order; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -12841,14 +12831,24 @@
           <t xml:space="preserve">dialogLines</t>
         </is>
       </c>
+      <c r="B499" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dialog</t>
+        </is>
+      </c>
       <c r="C499" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D499" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E499" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].lines, in order; the first columns name the parent row</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -12860,7 +12860,7 @@
       </c>
       <c r="B500" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C500" s="1" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="E500" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -12887,22 +12887,17 @@
       </c>
       <c r="B501" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C501" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D501" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E501" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12909,7 @@
       </c>
       <c r="B502" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">speaker</t>
         </is>
       </c>
       <c r="C502" s="1" t="inlineStr">
@@ -12936,7 +12931,7 @@
       </c>
       <c r="B503" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">speaker</t>
+          <t xml:space="preserve">expression</t>
         </is>
       </c>
       <c r="C503" s="1" t="inlineStr">
@@ -12946,7 +12941,7 @@
       </c>
       <c r="D503" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12953,7 @@
       </c>
       <c r="B504" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">expression</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C504" s="1" t="inlineStr">
@@ -12968,29 +12963,24 @@
       </c>
       <c r="D504" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogLines</t>
-        </is>
-      </c>
-      <c r="B505" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
       <c r="C505" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D505" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E505" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices, in order; a row's name is id, unique per parent row; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -13000,14 +12990,24 @@
           <t xml:space="preserve">dialogChoices</t>
         </is>
       </c>
+      <c r="B506" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dialog</t>
+        </is>
+      </c>
       <c r="C506" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D506" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E506" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices, in order; a row's name is id, unique per parent row; the first columns name the parent row</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="B507" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C507" s="1" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="E507" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -13046,12 +13046,12 @@
       </c>
       <c r="B508" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C508" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D508" s="1" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="E508" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -13073,7 +13073,7 @@
       </c>
       <c r="B509" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">label</t>
         </is>
       </c>
       <c r="C509" s="1" t="inlineStr">
@@ -13083,12 +13083,7 @@
       </c>
       <c r="D509" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E509" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -13100,7 +13095,7 @@
       </c>
       <c r="B510" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">label</t>
+          <t xml:space="preserve">next</t>
         </is>
       </c>
       <c r="C510" s="1" t="inlineStr">
@@ -13111,6 +13106,11 @@
       <c r="D510" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        </is>
+      </c>
+      <c r="F510" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the node it leads to (blank: the dialog ends)</t>
         </is>
       </c>
     </row>
@@ -13122,7 +13122,7 @@
       </c>
       <c r="B511" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">next</t>
+          <t xml:space="preserve">effect</t>
         </is>
       </c>
       <c r="C511" s="1" t="inlineStr">
@@ -13133,33 +13133,23 @@
       <c r="D511" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
-        </is>
-      </c>
-      <c r="F511" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the node it leads to (blank: the dialog ends)</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialogChoices</t>
-        </is>
-      </c>
-      <c r="B512" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">effect</t>
+          <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
       <c r="C512" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D512" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E512" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices[].lines, in order; the first columns name the parent row</t>
         </is>
       </c>
     </row>
@@ -13169,14 +13159,24 @@
           <t xml:space="preserve">choiceLines</t>
         </is>
       </c>
+      <c r="B513" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dialog</t>
+        </is>
+      </c>
       <c r="C513" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">row name</t>
+        </is>
+      </c>
+      <c r="D513" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E513" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.dialogs[].nodes[].choices[].lines, in order; the first columns name the parent row</t>
+          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="B514" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">dialog</t>
+          <t xml:space="preserve">node</t>
         </is>
       </c>
       <c r="C514" s="1" t="inlineStr">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="E514" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogs' this row belongs to</t>
+          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="B515" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">node</t>
+          <t xml:space="preserve">choice</t>
         </is>
       </c>
       <c r="C515" s="1" t="inlineStr">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="E515" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">names the row of 'dialogNodes' this row belongs to</t>
+          <t xml:space="preserve">names the row of 'dialogChoices' this row belongs to</t>
         </is>
       </c>
     </row>
@@ -13242,22 +13242,17 @@
       </c>
       <c r="B516" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choice</t>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="C516" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">row name</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="D516" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E516" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">names the row of 'dialogChoices' this row belongs to</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13264,7 @@
       </c>
       <c r="B517" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">speaker</t>
         </is>
       </c>
       <c r="C517" s="1" t="inlineStr">
@@ -13291,7 +13286,7 @@
       </c>
       <c r="B518" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">speaker</t>
+          <t xml:space="preserve">expression</t>
         </is>
       </c>
       <c r="C518" s="1" t="inlineStr">
@@ -13301,7 +13296,7 @@
       </c>
       <c r="D518" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">empty text (left out of the JSON)</t>
         </is>
       </c>
     </row>
@@ -13313,7 +13308,7 @@
       </c>
       <c r="B519" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">expression</t>
+          <t xml:space="preserve">text</t>
         </is>
       </c>
       <c r="C519" s="1" t="inlineStr">
@@ -13323,29 +13318,29 @@
       </c>
       <c r="D519" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">empty text (left out of the JSON)</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">choiceLines</t>
-        </is>
-      </c>
-      <c r="B520" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">text</t>
+          <t xml:space="preserve">premades</t>
         </is>
       </c>
       <c r="C520" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">text</t>
-        </is>
-      </c>
-      <c r="D520" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">empty text</t>
+          <t xml:space="preserve">Rows</t>
+        </is>
+      </c>
+      <c r="E520" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one row per item of the list $.premades, in order; a row's name is id, unique</t>
+        </is>
+      </c>
+      <c r="F520" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">premade characters: real people and written stories</t>
         </is>
       </c>
     </row>
@@ -13355,19 +13350,24 @@
           <t xml:space="preserve">premades</t>
         </is>
       </c>
+      <c r="B521" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">id</t>
+        </is>
+      </c>
       <c r="C521" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rows</t>
+          <t xml:space="preserve">text</t>
+        </is>
+      </c>
+      <c r="D521" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(required)</t>
         </is>
       </c>
       <c r="E521" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">one row per item of the list $.premades, in order; a row's name is id, unique</t>
-        </is>
-      </c>
-      <c r="F521" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">premade characters: real people and written stories</t>
+          <t xml:space="preserve">part of the row's name</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="B522" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">id</t>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C522" s="1" t="inlineStr">
@@ -13389,12 +13389,7 @@
       </c>
       <c r="D522" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">(required)</t>
-        </is>
-      </c>
-      <c r="E522" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">part of the row's name</t>
+          <t xml:space="preserve">empty text</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13401,7 @@
       </c>
       <c r="B523" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t xml:space="preserve">gender</t>
         </is>
       </c>
       <c r="C523" s="1" t="inlineStr">
@@ -13428,7 +13423,7 @@
       </c>
       <c r="B524" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gender</t>
+          <t xml:space="preserve">place</t>
         </is>
       </c>
       <c r="C524" s="1" t="inlineStr">
@@ -13439,6 +13434,11 @@
       <c r="D524" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">empty text</t>
+        